--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC19" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Turkey_Süp" displayName="AveragesTable_Turkey_Süp" ref="A1:EC19" headerRowCount="1">
   <autoFilter ref="A1:EC19"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>
@@ -1607,18 +1607,20 @@
         <v>3.53</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.44</v>
+        <v>3.61</v>
       </c>
       <c r="CA2" t="n">
         <v>3.79</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.44</v>
+        <v>3.83</v>
       </c>
       <c r="CC2" t="n">
         <v>4.24</v>
       </c>
-      <c r="CD2" t="inlineStr"/>
+      <c r="CD2" t="n">
+        <v>5.14</v>
+      </c>
       <c r="CE2" t="n">
         <v>1.35</v>
       </c>
@@ -1659,43 +1661,43 @@
         <v>3.07</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="CU2" t="n">
         <v>1.45</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.33</v>
+        <v>2.11</v>
       </c>
       <c r="CW2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DA2" t="n">
         <v>1.64</v>
       </c>
-      <c r="CX2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>1.71</v>
-      </c>
       <c r="DB2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="DD2" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
@@ -2008,19 +2010,19 @@
         <v>2.86</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.76</v>
+        <v>3.16</v>
       </c>
       <c r="CA3" t="n">
         <v>3.81</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="CC3" t="n">
         <v>5.78</v>
       </c>
       <c r="CD3" t="n">
-        <v>7.36</v>
+        <v>6.28</v>
       </c>
       <c r="CE3" t="n">
         <v>1.37</v>
@@ -2062,43 +2064,43 @@
         <v>3.2</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.89</v>
+        <v>2.97</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="CV3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CW3" t="n">
         <v>1.87</v>
       </c>
-      <c r="CW3" t="n">
-        <v>2</v>
-      </c>
       <c r="CX3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
@@ -2410,15 +2412,21 @@
       <c r="BY4" t="n">
         <v>1.73</v>
       </c>
-      <c r="BZ4" t="inlineStr"/>
+      <c r="BZ4" t="n">
+        <v>1.85</v>
+      </c>
       <c r="CA4" t="n">
         <v>4.17</v>
       </c>
-      <c r="CB4" t="inlineStr"/>
+      <c r="CB4" t="n">
+        <v>4.35</v>
+      </c>
       <c r="CC4" t="n">
         <v>2.49</v>
       </c>
-      <c r="CD4" t="inlineStr"/>
+      <c r="CD4" t="n">
+        <v>2.38</v>
+      </c>
       <c r="CE4" t="n">
         <v>1.27</v>
       </c>
@@ -2458,19 +2466,45 @@
       <c r="CQ4" t="n">
         <v>2.53</v>
       </c>
-      <c r="CR4" t="inlineStr"/>
-      <c r="CS4" t="inlineStr"/>
-      <c r="CT4" t="inlineStr"/>
-      <c r="CU4" t="inlineStr"/>
-      <c r="CV4" t="inlineStr"/>
-      <c r="CW4" t="inlineStr"/>
-      <c r="CX4" t="inlineStr"/>
-      <c r="CY4" t="inlineStr"/>
-      <c r="CZ4" t="inlineStr"/>
-      <c r="DA4" t="inlineStr"/>
-      <c r="DB4" t="inlineStr"/>
-      <c r="DC4" t="inlineStr"/>
-      <c r="DD4" t="inlineStr"/>
+      <c r="CR4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>2.62</v>
+      </c>
       <c r="DE4" t="n">
         <v>0.42</v>
       </c>
@@ -2782,18 +2816,20 @@
         <v>3.3</v>
       </c>
       <c r="BZ5" t="n">
-        <v>10.06</v>
+        <v>3.66</v>
       </c>
       <c r="CA5" t="n">
         <v>3.67</v>
       </c>
       <c r="CB5" t="n">
-        <v>5.52</v>
+        <v>3.83</v>
       </c>
       <c r="CC5" t="n">
         <v>4.2</v>
       </c>
-      <c r="CD5" t="inlineStr"/>
+      <c r="CD5" t="n">
+        <v>4.37</v>
+      </c>
       <c r="CE5" t="n">
         <v>1.36</v>
       </c>
@@ -2833,36 +2869,44 @@
       <c r="CQ5" t="n">
         <v>3.12</v>
       </c>
-      <c r="CR5" t="inlineStr"/>
+      <c r="CR5" t="n">
+        <v>1.4</v>
+      </c>
       <c r="CS5" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="CT5" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>3.03</v>
+      </c>
       <c r="CU5" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CX5" t="inlineStr"/>
+        <v>1.77</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>1.59</v>
+      </c>
       <c r="CY5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="CZ5" t="inlineStr"/>
+        <v>1.96</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>2.33</v>
+      </c>
       <c r="DA5" t="n">
-        <v>2.01</v>
+        <v>1.86</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.45</v>
+        <v>1.89</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.14</v>
+        <v>3.17</v>
       </c>
       <c r="DE5" t="n">
         <v>0.08</v>
@@ -3175,19 +3219,19 @@
         <v>3.19</v>
       </c>
       <c r="BZ6" t="n">
-        <v>4.26</v>
+        <v>3.33</v>
       </c>
       <c r="CA6" t="n">
         <v>4.12</v>
       </c>
       <c r="CB6" t="n">
-        <v>5.66</v>
+        <v>4.36</v>
       </c>
       <c r="CC6" t="n">
         <v>8.16</v>
       </c>
       <c r="CD6" t="n">
-        <v>19.2</v>
+        <v>8.9</v>
       </c>
       <c r="CE6" t="n">
         <v>1.34</v>
@@ -3229,43 +3273,43 @@
         <v>2.9</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.92</v>
+        <v>3.09</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="CW6" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
@@ -3578,19 +3622,19 @@
         <v>1.27</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="CA7" t="n">
         <v>5.11</v>
       </c>
       <c r="CB7" t="n">
-        <v>6.16</v>
+        <v>5.36</v>
       </c>
       <c r="CC7" t="n">
         <v>1.7</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.34</v>
+        <v>1.74</v>
       </c>
       <c r="CE7" t="n">
         <v>1.27</v>
@@ -3631,40 +3675,44 @@
       <c r="CQ7" t="n">
         <v>2.48</v>
       </c>
-      <c r="CR7" t="inlineStr"/>
+      <c r="CR7" t="n">
+        <v>1.37</v>
+      </c>
       <c r="CS7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="CT7" t="inlineStr"/>
+        <v>2.51</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>3.19</v>
+      </c>
       <c r="CU7" t="n">
         <v>1.58</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="DE7" t="n">
         <v>0.25</v>
@@ -3977,19 +4025,19 @@
         <v>1.3</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="CA8" t="n">
         <v>5.37</v>
       </c>
       <c r="CB8" t="n">
-        <v>6.79</v>
+        <v>5.78</v>
       </c>
       <c r="CC8" t="n">
         <v>1.43</v>
       </c>
       <c r="CD8" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="CE8" t="n">
         <v>1.22</v>
@@ -4039,27 +4087,31 @@
         <v>1.76</v>
       </c>
       <c r="CV8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="CX8" t="inlineStr"/>
+        <v>1.74</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>1.52</v>
+      </c>
       <c r="CY8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CZ8" t="inlineStr"/>
+        <v>1.79</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>2.45</v>
+      </c>
       <c r="DA8" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE8" t="n">
         <v>0.08</v>
@@ -4372,19 +4424,19 @@
         <v>3.21</v>
       </c>
       <c r="BZ9" t="n">
-        <v>7.14</v>
+        <v>3.37</v>
       </c>
       <c r="CA9" t="n">
         <v>3.63</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.27</v>
+        <v>3.69</v>
       </c>
       <c r="CC9" t="n">
         <v>3.65</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.27</v>
+        <v>3.85</v>
       </c>
       <c r="CE9" t="n">
         <v>1.34</v>
@@ -4426,43 +4478,43 @@
         <v>2.97</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="CT9" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DD9" t="n">
         <v>3.08</v>
-      </c>
-      <c r="CU9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="CV9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="CW9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CX9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CY9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="CZ9" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="DA9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="DB9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="DD9" t="n">
-        <v>2.76</v>
       </c>
       <c r="DE9" t="n">
         <v>0.17</v>
@@ -4775,18 +4827,20 @@
         <v>3.56</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.68</v>
+        <v>3.68</v>
       </c>
       <c r="CA10" t="n">
         <v>3.87</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.16</v>
+        <v>3.89</v>
       </c>
       <c r="CC10" t="n">
         <v>4.6</v>
       </c>
-      <c r="CD10" t="inlineStr"/>
+      <c r="CD10" t="n">
+        <v>6.25</v>
+      </c>
       <c r="CE10" t="n">
         <v>1.35</v>
       </c>
@@ -4827,43 +4881,43 @@
         <v>3.14</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.03</v>
+        <v>3.33</v>
       </c>
       <c r="DE10" t="n">
         <v>0.08</v>
@@ -5175,18 +5229,20 @@
       <c r="BY11" t="n">
         <v>2.24</v>
       </c>
-      <c r="BZ11" t="inlineStr"/>
+      <c r="BZ11" t="n">
+        <v>2.35</v>
+      </c>
       <c r="CA11" t="n">
         <v>3.55</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.47</v>
+        <v>3.68</v>
       </c>
       <c r="CC11" t="n">
         <v>3.04</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.62</v>
+        <v>3.32</v>
       </c>
       <c r="CE11" t="n">
         <v>1.37</v>
@@ -5231,40 +5287,40 @@
         <v>1.4</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CW11" t="n">
         <v>1.82</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.53</v>
+        <v>3.39</v>
       </c>
       <c r="DE11" t="n">
         <v>0.16</v>
@@ -5577,18 +5633,20 @@
         <v>3.67</v>
       </c>
       <c r="BZ12" t="n">
-        <v>6.34</v>
+        <v>4.27</v>
       </c>
       <c r="CA12" t="n">
         <v>3.58</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.38</v>
+        <v>3.64</v>
       </c>
       <c r="CC12" t="n">
         <v>2.97</v>
       </c>
-      <c r="CD12" t="inlineStr"/>
+      <c r="CD12" t="n">
+        <v>3.38</v>
+      </c>
       <c r="CE12" t="n">
         <v>1.35</v>
       </c>
@@ -5628,40 +5686,44 @@
       <c r="CQ12" t="n">
         <v>2.97</v>
       </c>
-      <c r="CR12" t="inlineStr"/>
+      <c r="CR12" t="n">
+        <v>1.41</v>
+      </c>
       <c r="CS12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="CT12" t="inlineStr"/>
+        <v>2.9</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>3.06</v>
+      </c>
       <c r="CU12" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.19</v>
+        <v>3.26</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
@@ -5973,15 +6035,21 @@
       <c r="BY13" t="n">
         <v>3.54</v>
       </c>
-      <c r="BZ13" t="inlineStr"/>
+      <c r="BZ13" t="n">
+        <v>3.9</v>
+      </c>
       <c r="CA13" t="n">
         <v>4</v>
       </c>
-      <c r="CB13" t="inlineStr"/>
+      <c r="CB13" t="n">
+        <v>4.24</v>
+      </c>
       <c r="CC13" t="n">
         <v>5.37</v>
       </c>
-      <c r="CD13" t="inlineStr"/>
+      <c r="CD13" t="n">
+        <v>5.9</v>
+      </c>
       <c r="CE13" t="n">
         <v>1.31</v>
       </c>
@@ -6021,19 +6089,45 @@
       <c r="CQ13" t="n">
         <v>2.73</v>
       </c>
-      <c r="CR13" t="inlineStr"/>
-      <c r="CS13" t="inlineStr"/>
-      <c r="CT13" t="inlineStr"/>
-      <c r="CU13" t="inlineStr"/>
-      <c r="CV13" t="inlineStr"/>
-      <c r="CW13" t="inlineStr"/>
-      <c r="CX13" t="inlineStr"/>
-      <c r="CY13" t="inlineStr"/>
-      <c r="CZ13" t="inlineStr"/>
-      <c r="DA13" t="inlineStr"/>
-      <c r="DB13" t="inlineStr"/>
-      <c r="DC13" t="inlineStr"/>
-      <c r="DD13" t="inlineStr"/>
+      <c r="CR13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>2.77</v>
+      </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
@@ -6344,18 +6438,20 @@
       <c r="BY14" t="n">
         <v>3.15</v>
       </c>
-      <c r="BZ14" t="inlineStr"/>
+      <c r="BZ14" t="n">
+        <v>3.23</v>
+      </c>
       <c r="CA14" t="n">
         <v>3.85</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.76</v>
+        <v>3.97</v>
       </c>
       <c r="CC14" t="n">
         <v>5.88</v>
       </c>
       <c r="CD14" t="n">
-        <v>5.09</v>
+        <v>6.1</v>
       </c>
       <c r="CE14" t="n">
         <v>1.35</v>
@@ -6397,43 +6493,43 @@
         <v>3.05</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="CU14" t="n">
         <v>1.46</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
@@ -6746,18 +6842,20 @@
         <v>2.26</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.92</v>
+        <v>2.29</v>
       </c>
       <c r="CA15" t="n">
         <v>3.7</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.57</v>
+        <v>3.71</v>
       </c>
       <c r="CC15" t="n">
         <v>4.27</v>
       </c>
-      <c r="CD15" t="inlineStr"/>
+      <c r="CD15" t="n">
+        <v>4.64</v>
+      </c>
       <c r="CE15" t="n">
         <v>1.36</v>
       </c>
@@ -6801,40 +6899,40 @@
         <v>1.4</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.17</v>
+        <v>3.27</v>
       </c>
       <c r="DE15" t="n">
         <v>0.08</v>
@@ -7147,19 +7245,19 @@
         <v>2.14</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="CA16" t="n">
         <v>3.78</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="CC16" t="n">
         <v>4.54</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.9</v>
+        <v>4.88</v>
       </c>
       <c r="CE16" t="n">
         <v>1.34</v>
@@ -7201,43 +7299,43 @@
         <v>2.92</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.99</v>
+        <v>2.79</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="DE16" t="n">
         <v>0.16</v>
@@ -7549,15 +7647,21 @@
       <c r="BY17" t="n">
         <v>2.19</v>
       </c>
-      <c r="BZ17" t="inlineStr"/>
+      <c r="BZ17" t="n">
+        <v>2.19</v>
+      </c>
       <c r="CA17" t="n">
         <v>3.62</v>
       </c>
-      <c r="CB17" t="inlineStr"/>
+      <c r="CB17" t="n">
+        <v>3.62</v>
+      </c>
       <c r="CC17" t="n">
         <v>3.01</v>
       </c>
-      <c r="CD17" t="inlineStr"/>
+      <c r="CD17" t="n">
+        <v>3.17</v>
+      </c>
       <c r="CE17" t="n">
         <v>1.37</v>
       </c>
@@ -7597,19 +7701,45 @@
       <c r="CQ17" t="n">
         <v>3.25</v>
       </c>
-      <c r="CR17" t="inlineStr"/>
-      <c r="CS17" t="inlineStr"/>
-      <c r="CT17" t="inlineStr"/>
-      <c r="CU17" t="inlineStr"/>
-      <c r="CV17" t="inlineStr"/>
-      <c r="CW17" t="inlineStr"/>
-      <c r="CX17" t="inlineStr"/>
-      <c r="CY17" t="inlineStr"/>
-      <c r="CZ17" t="inlineStr"/>
-      <c r="DA17" t="inlineStr"/>
-      <c r="DB17" t="inlineStr"/>
-      <c r="DC17" t="inlineStr"/>
-      <c r="DD17" t="inlineStr"/>
+      <c r="CR17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>3.38</v>
+      </c>
       <c r="DE17" t="n">
         <v>0.25</v>
       </c>
@@ -7921,18 +8051,20 @@
         <v>1.62</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="CA18" t="n">
         <v>4.01</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.3</v>
+        <v>4.11</v>
       </c>
       <c r="CC18" t="n">
         <v>3.99</v>
       </c>
-      <c r="CD18" t="inlineStr"/>
+      <c r="CD18" t="n">
+        <v>4.26</v>
+      </c>
       <c r="CE18" t="n">
         <v>1.33</v>
       </c>
@@ -7973,43 +8105,43 @@
         <v>2.78</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="DE18" t="n">
         <v>0.08</v>
@@ -8322,19 +8454,19 @@
         <v>2.45</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.09</v>
+        <v>2.53</v>
       </c>
       <c r="CA19" t="n">
         <v>3.54</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.41</v>
+        <v>3.61</v>
       </c>
       <c r="CC19" t="n">
         <v>2.98</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.03</v>
+        <v>3.12</v>
       </c>
       <c r="CE19" t="n">
         <v>1.35</v>
@@ -8376,43 +8508,43 @@
         <v>3.02</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.02</v>
+        <v>2.83</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.64</v>
+        <v>3.22</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -2588,61 +2588,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="G5" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="H5" t="n">
-        <v>76.17</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="J5" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>5.5</v>
+        <v>5.43</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M5" t="n">
-        <v>38.33</v>
+        <v>40.71</v>
       </c>
       <c r="N5" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O5" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="P5" t="n">
-        <v>9.5</v>
+        <v>10.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.17</v>
+        <v>13.86</v>
       </c>
       <c r="R5" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T5" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>52.67</v>
+        <v>53</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.5</v>
+        <v>11.57</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.33</v>
+        <v>7.43</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.83</v>
+        <v>18.57</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>2.67</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.42</v>
+        <v>10.46</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BN5" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="BQ5" t="n">
         <v>6</v>
       </c>
       <c r="BR5" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS5" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BT5" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BU5" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BV5" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="BZ5" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="CA5" t="n">
         <v>3.66</v>
       </c>
-      <c r="CA5" t="n">
-        <v>3.67</v>
-      </c>
       <c r="CB5" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="CC5" t="n">
         <v>4.2</v>
@@ -2837,7 +2837,7 @@
         <v>2.7</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CH5" t="n">
         <v>1.44</v>
@@ -2855,19 +2855,19 @@
         <v>2.04</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CR5" t="n">
         <v>1.4</v>
@@ -2882,19 +2882,19 @@
         <v>1.48</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY5" t="n">
         <v>1.96</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DA5" t="n">
         <v>1.86</v>
@@ -2912,43 +2912,43 @@
         <v>0.08</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="DH5" t="n">
-        <v>76.42</v>
+        <v>77.08</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.16</v>
+        <v>4.23</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DM5" t="n">
-        <v>37.16</v>
+        <v>38.54</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO5" t="n">
         <v>1.92</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.16</v>
+        <v>11.54</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.58</v>
+        <v>15.77</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.25</v>
+        <v>7.08</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51</v>
+        <v>51.31</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.34</v>
+        <v>11.39</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.75</v>
+        <v>7.77</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.08</v>
+        <v>18</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,46 +3084,46 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AI6" t="n">
-        <v>81.2</v>
+        <v>79</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.4</v>
+        <v>4.67</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>35.2</v>
+        <v>38</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13</v>
+        <v>13.83</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.2</v>
+        <v>13.67</v>
       </c>
       <c r="AS6" t="n">
-        <v>12</v>
+        <v>11.17</v>
       </c>
       <c r="AT6" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AU6" t="n">
         <v>1</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>41.8</v>
+        <v>42.33</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.8</v>
+        <v>12.17</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="BD6" t="n">
-        <v>20.2</v>
+        <v>21.67</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.67</v>
+        <v>9.77</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BM6" t="n">
         <v>0.92</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.17</v>
+        <v>5.23</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT6" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU6" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV6" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX6" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY6" t="n">
         <v>3.19</v>
@@ -3222,55 +3222,55 @@
         <v>3.33</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.36</v>
+        <v>4.3</v>
       </c>
       <c r="CC6" t="n">
-        <v>8.16</v>
+        <v>7.39</v>
       </c>
       <c r="CD6" t="n">
-        <v>8.9</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="CE6" t="n">
         <v>1.34</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="CH6" t="n">
         <v>1.47</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CK6" t="n">
         <v>1.58</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CN6" t="n">
         <v>1.78</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CR6" t="n">
         <v>1.4</v>
@@ -3285,28 +3285,28 @@
         <v>1.51</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DB6" t="n">
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DD6" t="n">
         <v>3.13</v>
@@ -3315,43 +3315,43 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="DH6" t="n">
-        <v>91</v>
+        <v>89.23</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DM6" t="n">
-        <v>36.08</v>
+        <v>37.31</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.42</v>
+        <v>14.69</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.66</v>
+        <v>14.77</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.84</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DS6" t="n">
         <v>0.08</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47.67</v>
+        <v>47.46</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.75</v>
+        <v>11.54</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.67</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.42</v>
+        <v>21.08</v>
       </c>
       <c r="EB6" t="n">
         <v>1.22</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="7">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F8" t="n">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="G8" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>102.67</v>
+        <v>99</v>
       </c>
       <c r="I8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M8" t="n">
+        <v>59.29</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P8" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>64.86</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="M8" t="n">
-        <v>57.83</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="P8" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>20.17</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>21.17</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.67</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,70 +3968,70 @@
         <v>2.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.17</v>
+        <v>8.92</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.92</v>
+        <v>4.69</v>
       </c>
       <c r="BR8" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS8" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT8" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU8" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.37</v>
+        <v>5.57</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.78</v>
+        <v>5.93</v>
       </c>
       <c r="CC8" t="n">
         <v>1.43</v>
@@ -4043,19 +4043,19 @@
         <v>1.22</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CK8" t="n">
         <v>1.47</v>
@@ -4073,33 +4073,33 @@
         <v>1.12</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY8" t="n">
         <v>1.79</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="DA8" t="n">
         <v>2.03</v>
@@ -4108,85 +4108,85 @@
         <v>1.15</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DE8" t="n">
         <v>0.08</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="DH8" t="n">
-        <v>96.84</v>
+        <v>95.31</v>
       </c>
       <c r="DI8" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="DM8" t="n">
-        <v>53.08</v>
+        <v>54.23</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.5</v>
+        <v>11.47</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.16</v>
+        <v>10.77</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.58</v>
+        <v>7.31</v>
       </c>
       <c r="DS8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>63.08</v>
+      </c>
+      <c r="DW8" t="n">
         <v>0.16</v>
       </c>
-      <c r="DT8" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV8" t="n">
-        <v>62.25</v>
-      </c>
-      <c r="DW8" t="n">
-        <v>0.08</v>
-      </c>
       <c r="DX8" t="n">
-        <v>17.58</v>
+        <v>18.39</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.34</v>
+        <v>11.92</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6.25</v>
+        <v>6.46</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.5</v>
+        <v>20.23</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="9">
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>0.29</v>
@@ -4289,136 +4289,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AI9" t="n">
-        <v>66</v>
+        <v>64.33</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AN9" t="n">
-        <v>30.4</v>
+        <v>30.83</v>
       </c>
       <c r="AO9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT9" t="n">
         <v>1</v>
       </c>
-      <c r="AP9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AU9" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>48.4</v>
+        <v>47.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.33</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="BD9" t="n">
-        <v>14.8</v>
+        <v>15.33</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BF9" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="BG9" t="n">
         <v>3.08</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.42</v>
+        <v>8.92</v>
       </c>
       <c r="BI9" t="n">
         <v>3.08</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK9" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.25</v>
+        <v>4.92</v>
       </c>
       <c r="BR9" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS9" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT9" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU9" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BV9" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY9" t="n">
         <v>3.21</v>
@@ -4427,169 +4427,169 @@
         <v>3.37</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CB9" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="CD9" t="n">
         <v>3.69</v>
       </c>
-      <c r="CC9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>3.85</v>
-      </c>
       <c r="CE9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CH9" t="n">
         <v>1.46</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CO9" t="n">
         <v>1.23</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="CT9" t="n">
         <v>3.21</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CX9" t="n">
         <v>1.58</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.31</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.67</v>
+        <v>78.77</v>
       </c>
       <c r="DI9" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.33</v>
+        <v>3.15</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.25</v>
+        <v>4.85</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM9" t="n">
-        <v>36.08</v>
+        <v>35.84</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.42</v>
+        <v>13.23</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.08</v>
+        <v>15.85</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.25</v>
+        <v>7.69</v>
       </c>
       <c r="DS9" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>54.07</v>
+      </c>
+      <c r="DW9" t="n">
         <v>0.16</v>
       </c>
-      <c r="DT9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV9" t="n">
-        <v>55</v>
-      </c>
-      <c r="DW9" t="n">
-        <v>0.17</v>
-      </c>
       <c r="DX9" t="n">
-        <v>14.92</v>
+        <v>14.23</v>
       </c>
       <c r="DY9" t="n">
-        <v>10</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.91</v>
+        <v>4.77</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.42</v>
+        <v>16.54</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="EC9" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="10">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4689,52 +4689,52 @@
         <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AI10" t="n">
-        <v>61.5</v>
+        <v>57.57</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN10" t="n">
-        <v>26.17</v>
+        <v>26.43</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14</v>
+        <v>12.86</v>
       </c>
       <c r="AR10" t="n">
-        <v>16</v>
+        <v>15.29</v>
       </c>
       <c r="AS10" t="n">
-        <v>11.33</v>
+        <v>11.43</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4746,82 +4746,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>38.83</v>
+        <v>37.14</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.33</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BB10" t="n">
         <v>6</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="BD10" t="n">
-        <v>17.5</v>
+        <v>18.14</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.75</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="BO10" t="n">
         <v>1.08</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.75</v>
+        <v>4.69</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.92</v>
+        <v>4.69</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT10" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU10" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY10" t="n">
         <v>3.56</v>
@@ -4830,166 +4830,166 @@
         <v>3.68</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.87</v>
+        <v>4.19</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.89</v>
+        <v>4.18</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.6</v>
+        <v>6.31</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.25</v>
+        <v>7.48</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.71</v>
+        <v>2.65</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CL10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="CR10" t="n">
         <v>1.4</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.96</v>
+        <v>2.89</v>
       </c>
       <c r="CT10" t="n">
         <v>3.04</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
       <c r="DE10" t="n">
         <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="DH10" t="n">
-        <v>66</v>
+        <v>63.54</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.25</v>
+        <v>4.08</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM10" t="n">
-        <v>28.33</v>
+        <v>28.31</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="DO10" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.34</v>
+        <v>12.77</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.5</v>
+        <v>14.23</v>
       </c>
       <c r="DR10" t="n">
-        <v>11.08</v>
+        <v>11.15</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>40.42</v>
+        <v>39.38</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.42</v>
+        <v>10.46</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.16</v>
+        <v>7.08</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.92</v>
+        <v>18.23</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="EC10" t="n">
         <v>2.08</v>
@@ -5808,10 +5808,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
@@ -5820,49 +5820,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="H13" t="n">
-        <v>85.67</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M13" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="O13" t="n">
         <v>3</v>
       </c>
-      <c r="K13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="M13" t="n">
-        <v>45</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.17</v>
-      </c>
       <c r="P13" t="n">
-        <v>12.5</v>
+        <v>12.71</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.5</v>
+        <v>13.14</v>
       </c>
       <c r="R13" t="n">
-        <v>9.33</v>
+        <v>8.43</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5874,28 +5874,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>51.17</v>
+        <v>52</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>11.67</v>
+        <v>12.14</v>
       </c>
       <c r="AA13" t="n">
-        <v>8</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.67</v>
+        <v>3.29</v>
       </c>
       <c r="AC13" t="n">
         <v>24</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5979,37 +5979,37 @@
         <v>2.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.17</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL13" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.83</v>
+        <v>4.62</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.42</v>
+        <v>5.08</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
@@ -6018,31 +6018,31 @@
         <v>100</v>
       </c>
       <c r="BT13" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU13" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BV13" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX13" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="CA13" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.24</v>
+        <v>4.19</v>
       </c>
       <c r="CC13" t="n">
         <v>5.37</v>
@@ -6060,19 +6060,19 @@
         <v>3.19</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CM13" t="n">
         <v>2.55</v>
@@ -6081,19 +6081,19 @@
         <v>1.95</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP13" t="n">
         <v>1.73</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CR13" t="n">
         <v>1.37</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CT13" t="n">
         <v>3.21</v>
@@ -6102,73 +6102,73 @@
         <v>1.55</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CX13" t="n">
         <v>1.52</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.44</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DB13" t="n">
         <v>1.22</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DD13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>85.31</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ13" t="n">
         <v>2.77</v>
       </c>
-      <c r="DE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="DG13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="DH13" t="n">
-        <v>85.92</v>
-      </c>
-      <c r="DI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ13" t="n">
-        <v>2.92</v>
-      </c>
       <c r="DK13" t="n">
-        <v>5.16</v>
+        <v>5</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="DM13" t="n">
-        <v>39.75</v>
+        <v>41.84</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.42</v>
+        <v>13.46</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.42</v>
+        <v>13.23</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.83</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6180,28 +6180,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.42</v>
+        <v>50</v>
       </c>
       <c r="DW13" t="n">
         <v>0.08</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.67</v>
+        <v>11.92</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.42</v>
+        <v>7.92</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.92</v>
+        <v>22.08</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="14">

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
@@ -1394,79 +1394,79 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6</v>
+        <v>3.67</v>
       </c>
       <c r="H2" t="n">
-        <v>84.2</v>
+        <v>94.5</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="M2" t="n">
-        <v>37</v>
+        <v>45.83</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="P2" t="n">
-        <v>11.6</v>
+        <v>11.17</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.6</v>
+        <v>14.83</v>
       </c>
       <c r="R2" t="n">
-        <v>6.6</v>
+        <v>6.33</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>48</v>
+        <v>51.33</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.6</v>
+        <v>13.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AB2" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>18</v>
+        <v>17.83</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,49 +1550,49 @@
         <v>2.43</v>
       </c>
       <c r="BG2" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BH2" t="n">
-        <v>7.92</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.75</v>
+        <v>5.15</v>
       </c>
       <c r="BR2" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT2" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BU2" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,19 +1601,19 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.53</v>
+        <v>3.27</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.61</v>
+        <v>3.33</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="CC2" t="n">
         <v>4.24</v>
@@ -1625,10 +1625,10 @@
         <v>1.35</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CH2" t="n">
         <v>1.46</v>
@@ -1637,16 +1637,16 @@
         <v>2.01</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK2" t="n">
         <v>1.74</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CN2" t="n">
         <v>1.6</v>
@@ -1655,10 +1655,10 @@
         <v>1.25</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CR2" t="n">
         <v>1.4</v>
@@ -1679,16 +1679,16 @@
         <v>1.79</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DB2" t="n">
         <v>1.28</v>
@@ -1697,82 +1697,82 @@
         <v>1.9</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.33</v>
+        <v>2.85</v>
       </c>
       <c r="DH2" t="n">
-        <v>76.91</v>
+        <v>82.23</v>
       </c>
       <c r="DI2" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.92</v>
+        <v>4.62</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DM2" t="n">
-        <v>35</v>
+        <v>39.23</v>
       </c>
       <c r="DN2" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="DQ2" t="n">
-        <v>15.25</v>
+        <v>15.3</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.59</v>
+        <v>7.39</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.75</v>
+        <v>47.46</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.08</v>
+        <v>12.46</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.42</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.67</v>
+        <v>3.85</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.25</v>
+        <v>19.07</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AI3" t="n">
-        <v>64.67</v>
+        <v>64.14</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AP3" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.67</v>
+        <v>11.14</v>
       </c>
       <c r="AR3" t="n">
-        <v>11</v>
+        <v>11.57</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.83</v>
+        <v>11.43</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>40.86</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BM3" t="n">
         <v>1</v>
       </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>40.83</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>18.83</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.08</v>
-      </c>
       <c r="BN3" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.42</v>
+        <v>4.77</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.83</v>
+        <v>4.69</v>
       </c>
       <c r="BR3" t="n">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="BS3" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BT3" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU3" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV3" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX3" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY3" t="n">
         <v>2.86</v>
@@ -2013,28 +2013,28 @@
         <v>3.16</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="CB3" t="n">
         <v>3.9</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.78</v>
+        <v>5.59</v>
       </c>
       <c r="CD3" t="n">
-        <v>6.28</v>
+        <v>6.09</v>
       </c>
       <c r="CE3" t="n">
         <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI3" t="n">
         <v>1.94</v>
@@ -2046,13 +2046,13 @@
         <v>1.58</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO3" t="n">
         <v>1.27</v>
@@ -2061,88 +2061,88 @@
         <v>1.9</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CV3" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CW3" t="n">
         <v>1.87</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY3" t="n">
         <v>2.01</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="DH3" t="n">
-        <v>71.58</v>
+        <v>70.77</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM3" t="n">
-        <v>29</v>
+        <v>28.38</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.84</v>
+        <v>11.54</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14</v>
+        <v>14.08</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.58</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>42.92</v>
+        <v>42.77</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.83</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.83</v>
+        <v>4.77</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4</v>
+        <v>3.69</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.25</v>
+        <v>18.92</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="H4" t="n">
-        <v>75.2</v>
+        <v>86.33</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>41.4</v>
+        <v>42.17</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>14.6</v>
+        <v>13.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.2</v>
+        <v>12.83</v>
       </c>
       <c r="R4" t="n">
-        <v>6.6</v>
+        <v>6.33</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.6</v>
+        <v>50.83</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.4</v>
+        <v>14.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AC4" t="n">
-        <v>14.8</v>
+        <v>15.83</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF4" t="n">
         <v>0.29</v>
@@ -2356,37 +2356,37 @@
         <v>2.57</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.58</v>
+        <v>10.31</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.33</v>
+        <v>5.23</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -2395,31 +2395,31 @@
         <v>100</v>
       </c>
       <c r="BT4" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU4" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV4" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="CC4" t="n">
         <v>2.49</v>
@@ -2428,34 +2428,34 @@
         <v>2.38</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI4" t="n">
         <v>2.18</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL4" t="n">
         <v>1.92</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CO4" t="n">
         <v>1.18</v>
@@ -2464,7 +2464,7 @@
         <v>1.63</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
@@ -2473,28 +2473,28 @@
         <v>2.53</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="CU4" t="n">
         <v>1.56</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX4" t="n">
         <v>1.54</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.41</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="DB4" t="n">
         <v>1.21</v>
@@ -2506,79 +2506,79 @@
         <v>2.62</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="DH4" t="n">
-        <v>81.25</v>
+        <v>85.92</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.92</v>
+        <v>4.85</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DM4" t="n">
-        <v>38.83</v>
+        <v>39.39</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.75</v>
+        <v>14.38</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.83</v>
+        <v>12.15</v>
       </c>
       <c r="DR4" t="n">
-        <v>8</v>
+        <v>7.77</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>51.67</v>
+        <v>52.46</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.83</v>
+        <v>13.85</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.58</v>
+        <v>8.85</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.17</v>
+        <v>18.38</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="5">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>0.17</v>
@@ -3484,52 +3484,52 @@
         <v>2.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>103</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP7" t="n">
         <v>3</v>
       </c>
-      <c r="AI7" t="n">
-        <v>101.33</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>42.17</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AQ7" t="n">
-        <v>15</v>
+        <v>13.71</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.67</v>
+        <v>13.14</v>
       </c>
       <c r="AS7" t="n">
-        <v>7</v>
+        <v>6.29</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>58.33</v>
+        <v>58.43</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA7" t="n">
-        <v>13.83</v>
+        <v>15.86</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.67</v>
+        <v>9.43</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.17</v>
+        <v>6.43</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.83</v>
+        <v>17.57</v>
       </c>
       <c r="BE7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO7" t="n">
         <v>1.54</v>
       </c>
-      <c r="BF7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BP7" t="n">
-        <v>4.75</v>
+        <v>5.15</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="BR7" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS7" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT7" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU7" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BV7" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BX7" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY7" t="n">
         <v>1.27</v>
@@ -3625,34 +3625,34 @@
         <v>1.27</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.11</v>
+        <v>5.04</v>
       </c>
       <c r="CB7" t="n">
-        <v>5.36</v>
+        <v>5.26</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI7" t="n">
         <v>1.95</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK7" t="n">
         <v>1.54</v>
@@ -3661,37 +3661,37 @@
         <v>1.94</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CN7" t="n">
         <v>1.82</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS7" t="n">
         <v>2.51</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="CU7" t="n">
         <v>1.58</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CX7" t="n">
         <v>1.55</v>
@@ -3700,10 +3700,10 @@
         <v>1.92</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB7" t="n">
         <v>1.22</v>
@@ -3715,79 +3715,79 @@
         <v>2.67</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF7" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="DH7" t="n">
-        <v>112.33</v>
+        <v>112.38</v>
       </c>
       <c r="DI7" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.16</v>
+        <v>6.39</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.75</v>
+        <v>52.92</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="DP7" t="n">
-        <v>13.84</v>
+        <v>13.23</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.08</v>
+        <v>13.31</v>
       </c>
       <c r="DR7" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>60.83</v>
+        <v>60.69</v>
       </c>
       <c r="DW7" t="n">
         <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>18.33</v>
+        <v>19.08</v>
       </c>
       <c r="DY7" t="n">
-        <v>11.5</v>
+        <v>11.69</v>
       </c>
       <c r="DZ7" t="n">
-        <v>6.84</v>
+        <v>7.39</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.16</v>
+        <v>18.92</v>
       </c>
       <c r="EB7" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="8">
@@ -5002,61 +5002,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
         <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>95.2</v>
+        <v>95</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M11" t="n">
-        <v>41</v>
+        <v>42.67</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>18.6</v>
+        <v>18.17</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="R11" t="n">
-        <v>8.4</v>
+        <v>8.17</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5068,28 +5068,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>36.6</v>
+        <v>37.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.4</v>
+        <v>12.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.4</v>
+        <v>9.17</v>
       </c>
       <c r="AB11" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>20</v>
+        <v>19.83</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AF11" t="n">
         <v>0.14</v>
@@ -5173,49 +5173,49 @@
         <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.75</v>
+        <v>9.77</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="BR11" t="n">
-        <v>83.33</v>
+        <v>76.92</v>
       </c>
       <c r="BS11" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BT11" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BU11" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5224,19 +5224,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
       <c r="CC11" t="n">
         <v>3.04</v>
@@ -5245,61 +5245,61 @@
         <v>3.32</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL11" t="n">
         <v>1.97</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="CX11" t="n">
         <v>1.53</v>
@@ -5314,55 +5314,55 @@
         <v>1.87</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.39</v>
+        <v>3.48</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DH11" t="n">
-        <v>92.75</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="DI11" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DM11" t="n">
-        <v>41.5</v>
+        <v>42.23</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="DP11" t="n">
-        <v>17.67</v>
+        <v>17.54</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.08</v>
+        <v>8.92</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.42</v>
+        <v>8.31</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,25 +5374,25 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>36.92</v>
+        <v>37.31</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.25</v>
+        <v>12.84</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.92</v>
+        <v>8.85</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.42</v>
+        <v>19.38</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="EC11" t="n">
         <v>2.08</v>
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5501,46 +5501,46 @@
         <v>2</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.83</v>
+        <v>3.43</v>
       </c>
       <c r="AI12" t="n">
-        <v>92.83</v>
+        <v>88</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AL12" t="n">
-        <v>5.17</v>
+        <v>4.57</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN12" t="n">
-        <v>42.67</v>
+        <v>39.43</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.67</v>
+        <v>15.71</v>
       </c>
       <c r="AR12" t="n">
-        <v>10.17</v>
+        <v>10</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.67</v>
+        <v>7.86</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AU12" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5552,82 +5552,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>45</v>
+        <v>43.14</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.5</v>
+        <v>10.14</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.83</v>
+        <v>7.29</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.17</v>
+        <v>20.29</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.25</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BP12" t="n">
         <v>4</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.25</v>
+        <v>5.62</v>
       </c>
       <c r="BR12" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT12" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BU12" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV12" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY12" t="n">
         <v>3.67</v>
@@ -5639,22 +5639,22 @@
         <v>3.58</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.97</v>
+        <v>3.12</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.38</v>
+        <v>3.52</v>
       </c>
       <c r="CE12" t="n">
         <v>1.35</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CH12" t="n">
         <v>1.44</v>
@@ -5666,25 +5666,25 @@
         <v>1.71</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CR12" t="n">
         <v>1.41</v>
@@ -5699,28 +5699,28 @@
         <v>1.44</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CW12" t="n">
         <v>1.76</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="DB12" t="n">
         <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DD12" t="n">
         <v>3.26</v>
@@ -5729,43 +5729,43 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="DH12" t="n">
-        <v>92.33</v>
+        <v>89.77</v>
       </c>
       <c r="DI12" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.25</v>
+        <v>4.92</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="DM12" t="n">
-        <v>44.84</v>
+        <v>42.92</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.92</v>
+        <v>15</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.58</v>
+        <v>12.31</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.5</v>
+        <v>7.62</v>
       </c>
       <c r="DS12" t="n">
         <v>0.08</v>
@@ -5777,28 +5777,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.75</v>
+        <v>45.61</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.84</v>
+        <v>11.54</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.08</v>
+        <v>8.69</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.25</v>
+        <v>19.85</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="13">
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6304,136 +6304,136 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>81</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>35</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG14" t="n">
         <v>2</v>
       </c>
-      <c r="AH14" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>33</v>
-      </c>
-      <c r="AO14" t="n">
+      <c r="BH14" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BL14" t="n">
         <v>1</v>
       </c>
-      <c r="AP14" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>17.17</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>8.83</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>47</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>8.58</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1.08</v>
-      </c>
       <c r="BM14" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.67</v>
+        <v>4.62</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="BR14" t="n">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="BS14" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BT14" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BU14" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV14" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY14" t="n">
         <v>3.15</v>
@@ -6442,37 +6442,37 @@
         <v>3.23</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.97</v>
+        <v>3.9</v>
       </c>
       <c r="CC14" t="n">
-        <v>5.88</v>
+        <v>5.65</v>
       </c>
       <c r="CD14" t="n">
-        <v>6.1</v>
+        <v>5.84</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL14" t="n">
         <v>2.13</v>
@@ -6484,31 +6484,31 @@
         <v>1.77</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CQ14" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="CT14" t="n">
         <v>3.05</v>
       </c>
-      <c r="CR14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CS14" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="CT14" t="n">
-        <v>3.1</v>
-      </c>
       <c r="CU14" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CX14" t="n">
         <v>1.6</v>
@@ -6523,88 +6523,88 @@
         <v>1.81</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.23</v>
+        <v>3.34</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DH14" t="n">
-        <v>84.34</v>
+        <v>83.39</v>
       </c>
       <c r="DI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.16</v>
+        <v>4.31</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="DM14" t="n">
-        <v>31.5</v>
+        <v>32.69</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.25</v>
+        <v>14.61</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.83</v>
+        <v>14</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.42</v>
+        <v>9.84</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>46.16</v>
+        <v>47.07</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX14" t="n">
-        <v>9.83</v>
+        <v>9.84</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.33</v>
+        <v>6.38</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.42</v>
+        <v>21.31</v>
       </c>
       <c r="EB14" t="n">
         <v>1.1</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="15">
@@ -6614,10 +6614,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -6626,82 +6626,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="G15" t="n">
-        <v>3.83</v>
+        <v>3.57</v>
       </c>
       <c r="H15" t="n">
-        <v>104.17</v>
+        <v>104.71</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="K15" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="M15" t="n">
-        <v>51.5</v>
+        <v>52.14</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="O15" t="n">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="P15" t="n">
-        <v>13.5</v>
+        <v>13.71</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.67</v>
+        <v>12</v>
       </c>
       <c r="R15" t="n">
-        <v>7.33</v>
+        <v>7.43</v>
       </c>
       <c r="S15" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="U15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>55.5</v>
+        <v>56</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.33</v>
+        <v>15.71</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.33</v>
+        <v>11.29</v>
       </c>
       <c r="AB15" t="n">
-        <v>5</v>
+        <v>4.43</v>
       </c>
       <c r="AC15" t="n">
-        <v>21.33</v>
+        <v>22.29</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="AF15" t="n">
         <v>0.17</v>
@@ -6785,70 +6785,70 @@
         <v>1.83</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.17</v>
+        <v>2.92</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.25</v>
+        <v>11.31</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.17</v>
+        <v>2.92</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.42</v>
+        <v>4.77</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.83</v>
+        <v>6.54</v>
       </c>
       <c r="BR15" t="n">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="BS15" t="n">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="BT15" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU15" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV15" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="CC15" t="n">
         <v>4.27</v>
@@ -6863,22 +6863,22 @@
         <v>2.71</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CH15" t="n">
         <v>1.45</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK15" t="n">
         <v>1.52</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CM15" t="n">
         <v>2.39</v>
@@ -6890,7 +6890,7 @@
         <v>1.27</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CQ15" t="n">
         <v>3.08</v>
@@ -6902,7 +6902,7 @@
         <v>2.86</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CU15" t="n">
         <v>1.47</v>
@@ -6929,85 +6929,85 @@
         <v>1.29</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="DE15" t="n">
         <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="DH15" t="n">
-        <v>97.92</v>
+        <v>98.69</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.08</v>
+        <v>6.39</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM15" t="n">
-        <v>45</v>
+        <v>45.84</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.92</v>
+        <v>12.15</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.5</v>
+        <v>13.08</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.25</v>
+        <v>8.23</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>53.25</v>
+        <v>53.69</v>
       </c>
       <c r="DW15" t="n">
         <v>0.08</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.33</v>
+        <v>14.15</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.58</v>
+        <v>9.69</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.75</v>
+        <v>4.46</v>
       </c>
       <c r="EA15" t="n">
-        <v>21</v>
+        <v>21.54</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="16">
@@ -7017,61 +7017,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="F16" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>87.83</v>
+        <v>84</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="L16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M16" t="n">
-        <v>41</v>
+        <v>40.14</v>
       </c>
       <c r="N16" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="P16" t="n">
-        <v>14.5</v>
+        <v>14.71</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.83</v>
+        <v>11.86</v>
       </c>
       <c r="R16" t="n">
-        <v>9</v>
+        <v>9.43</v>
       </c>
       <c r="S16" t="n">
-        <v>1.17</v>
+        <v>1.71</v>
       </c>
       <c r="T16" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -7083,28 +7083,28 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>55.17</v>
+        <v>53.14</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>15</v>
+        <v>13.71</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.83</v>
+        <v>10.71</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="AC16" t="n">
-        <v>21.17</v>
+        <v>20.14</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="AF16" t="n">
         <v>0.33</v>
@@ -7188,70 +7188,70 @@
         <v>3</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="BH16" t="n">
-        <v>7.92</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.75</v>
+        <v>1.08</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.67</v>
+        <v>4.15</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="BR16" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS16" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU16" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BV16" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BX16" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.14</v>
+        <v>2.55</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.19</v>
+        <v>2.74</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.78</v>
+        <v>3.81</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="CC16" t="n">
         <v>4.54</v>
@@ -7263,58 +7263,58 @@
         <v>1.34</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CH16" t="n">
         <v>1.49</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CP16" t="n">
         <v>1.84</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CV16" t="n">
         <v>2.17</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CX16" t="n">
         <v>1.59</v>
@@ -7332,85 +7332,85 @@
         <v>1.26</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="DD16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>33.84</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="DZ16" t="n">
         <v>3.08</v>
       </c>
-      <c r="DE16" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DF16" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="DH16" t="n">
-        <v>82.42</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ16" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="DK16" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="DL16" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DM16" t="n">
-        <v>33.75</v>
-      </c>
-      <c r="DN16" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="DO16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="DP16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="DQ16" t="n">
-        <v>12.83</v>
-      </c>
-      <c r="DR16" t="n">
-        <v>8.83</v>
-      </c>
-      <c r="DS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV16" t="n">
-        <v>49.92</v>
-      </c>
-      <c r="DW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX16" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="DY16" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="DZ16" t="n">
-        <v>3.17</v>
-      </c>
       <c r="EA16" t="n">
-        <v>18.08</v>
+        <v>17.77</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="17">
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>0.14</v>
@@ -7510,52 +7510,52 @@
         <v>1.71</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AI17" t="n">
-        <v>78.2</v>
+        <v>78.67</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="AL17" t="n">
-        <v>6.8</v>
+        <v>6.17</v>
       </c>
       <c r="AM17" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AN17" t="n">
-        <v>31.8</v>
+        <v>31.83</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14.8</v>
+        <v>15.17</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS17" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="AT17" t="n">
         <v>1</v>
       </c>
       <c r="AU17" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7567,82 +7567,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>44.4</v>
+        <v>43.33</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA17" t="n">
-        <v>12</v>
+        <v>12.33</v>
       </c>
       <c r="BB17" t="n">
         <v>8</v>
       </c>
       <c r="BC17" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="BD17" t="n">
-        <v>16.6</v>
+        <v>15.83</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BH17" t="n">
-        <v>11.42</v>
+        <v>11.08</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.92</v>
+        <v>4.85</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.58</v>
+        <v>6.31</v>
       </c>
       <c r="BR17" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS17" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU17" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV17" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY17" t="n">
         <v>2.19</v>
@@ -7651,136 +7651,136 @@
         <v>2.19</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="CB17" t="n">
         <v>3.62</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.01</v>
+        <v>3.14</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.17</v>
+        <v>3.3</v>
       </c>
       <c r="CE17" t="n">
         <v>1.37</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CH17" t="n">
         <v>1.41</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="CO17" t="n">
         <v>1.28</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CX17" t="n">
         <v>1.58</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.32</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.84</v>
+        <v>3.62</v>
       </c>
       <c r="DH17" t="n">
-        <v>97.25</v>
+        <v>96</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="DK17" t="n">
-        <v>6.67</v>
+        <v>6.39</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DM17" t="n">
-        <v>40</v>
+        <v>39.38</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="DP17" t="n">
-        <v>14.25</v>
+        <v>14.46</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.92</v>
+        <v>10.85</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.83</v>
+        <v>8.23</v>
       </c>
       <c r="DS17" t="n">
         <v>0.08</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>51.75</v>
+        <v>50.69</v>
       </c>
       <c r="DW17" t="n">
         <v>0.08</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.75</v>
+        <v>13.77</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.42</v>
+        <v>9.31</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.33</v>
+        <v>4.46</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.25</v>
+        <v>19.62</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="18">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7913,139 +7913,139 @@
         <v>1.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>73.8</v>
+        <v>75.83</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AL18" t="n">
-        <v>3</v>
+        <v>4.17</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN18" t="n">
-        <v>26</v>
+        <v>31.33</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="AR18" t="n">
-        <v>16.6</v>
+        <v>16.17</v>
       </c>
       <c r="AS18" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>45.2</v>
+        <v>48.33</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.2</v>
+        <v>12.17</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.2</v>
+        <v>6.83</v>
       </c>
       <c r="BC18" t="n">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.4</v>
+        <v>17.17</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.17</v>
+        <v>2.54</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.33</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.17</v>
+        <v>2.54</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="BN18" t="n">
-        <v>1</v>
+        <v>1.23</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.67</v>
+        <v>4.38</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.67</v>
+        <v>5.08</v>
       </c>
       <c r="BR18" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS18" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BT18" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BU18" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BV18" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BX18" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY18" t="n">
         <v>1.62</v>
@@ -8054,40 +8054,40 @@
         <v>1.62</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.01</v>
+        <v>3.97</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.11</v>
+        <v>4.06</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.99</v>
+        <v>3.84</v>
       </c>
       <c r="CD18" t="n">
-        <v>4.26</v>
+        <v>4.05</v>
       </c>
       <c r="CE18" t="n">
         <v>1.33</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK18" t="n">
         <v>1.53</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CM18" t="n">
         <v>2.37</v>
@@ -8099,49 +8099,49 @@
         <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CR18" t="n">
         <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CU18" t="n">
         <v>1.52</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CX18" t="n">
         <v>1.55</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.38</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB18" t="n">
         <v>1.24</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="DE18" t="n">
         <v>0.08</v>
@@ -8150,73 +8150,73 @@
         <v>1</v>
       </c>
       <c r="DG18" t="n">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="DH18" t="n">
-        <v>89.58</v>
+        <v>89.31</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.66</v>
+        <v>4.15</v>
       </c>
       <c r="DL18" t="n">
         <v>0.08</v>
       </c>
       <c r="DM18" t="n">
-        <v>34.67</v>
+        <v>36.46</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.25</v>
+        <v>12.16</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.75</v>
+        <v>14.69</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.08</v>
+        <v>8.85</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>50.25</v>
+        <v>51.31</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.17</v>
+        <v>14.77</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.41</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.75</v>
+        <v>5.31</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.83</v>
+        <v>19.54</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="19">
@@ -8226,10 +8226,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -8238,82 +8238,82 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="H19" t="n">
-        <v>77.40000000000001</v>
+        <v>76.67</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>42</v>
+        <v>40.83</v>
       </c>
       <c r="N19" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="P19" t="n">
-        <v>16.4</v>
+        <v>16.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="R19" t="n">
         <v>8</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>53</v>
+        <v>50.17</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.6</v>
+        <v>7.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8397,70 +8397,70 @@
         <v>2.14</v>
       </c>
       <c r="BG19" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.75</v>
+        <v>10.77</v>
       </c>
       <c r="BI19" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.92</v>
+        <v>4.62</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.75</v>
+        <v>6.08</v>
       </c>
       <c r="BR19" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS19" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT19" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BU19" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CC19" t="n">
         <v>2.98</v>
@@ -8472,7 +8472,7 @@
         <v>1.35</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CG19" t="n">
         <v>2.98</v>
@@ -8481,49 +8481,49 @@
         <v>1.44</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK19" t="n">
         <v>1.57</v>
       </c>
       <c r="CL19" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CM19" t="n">
         <v>2.28</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO19" t="n">
         <v>1.24</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CQ19" t="n">
         <v>3.02</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CU19" t="n">
         <v>1.46</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CX19" t="n">
         <v>1.56</v>
@@ -8541,85 +8541,85 @@
         <v>1.28</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="DG19" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.25</v>
+        <v>91.69</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="DK19" t="n">
-        <v>6</v>
+        <v>5.61</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DM19" t="n">
-        <v>46.5</v>
+        <v>45.61</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.08</v>
+        <v>13.23</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.5</v>
+        <v>14.15</v>
       </c>
       <c r="DR19" t="n">
         <v>7.92</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>58.08</v>
+        <v>56.38</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.75</v>
+        <v>12.46</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.83</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.75</v>
+        <v>17.61</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>50.83</v>
+        <v>50.67</v>
       </c>
       <c r="Y4" t="n">
         <v>0.33</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>52.46</v>
+        <v>52.39</v>
       </c>
       <c r="DW4" t="n">
         <v>0.15</v>
@@ -5068,7 +5068,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>37.5</v>
+        <v>37.33</v>
       </c>
       <c r="Y11" t="n">
         <v>0.33</v>
@@ -5374,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>37.31</v>
+        <v>37.23</v>
       </c>
       <c r="DW11" t="n">
         <v>0.23</v>
@@ -6358,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>48.57</v>
+        <v>48.71</v>
       </c>
       <c r="AZ14" t="n">
         <v>0.14</v>
@@ -6583,7 +6583,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47.07</v>
+        <v>47.15</v>
       </c>
       <c r="DW14" t="n">
         <v>0.15</v>
@@ -7567,7 +7567,7 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>43.33</v>
+        <v>43.5</v>
       </c>
       <c r="AZ17" t="n">
         <v>0.17</v>
@@ -7792,7 +7792,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.69</v>
+        <v>50.77</v>
       </c>
       <c r="DW17" t="n">
         <v>0.08</v>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4689,139 +4689,139 @@
         <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>57.57</v>
+        <v>60.62</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>26.43</v>
+        <v>26.12</v>
       </c>
       <c r="AO10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>38.38</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK10" t="n">
         <v>0.57</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="BL10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BN10" t="n">
         <v>1.43</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>12.86</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>15.29</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>37.14</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>18.14</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1.54</v>
-      </c>
       <c r="BO10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.69</v>
+        <v>4.71</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.69</v>
+        <v>4.5</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU10" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV10" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY10" t="n">
         <v>3.56</v>
@@ -4830,169 +4830,169 @@
         <v>3.68</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.19</v>
+        <v>4.13</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.18</v>
+        <v>4.14</v>
       </c>
       <c r="CC10" t="n">
-        <v>6.31</v>
+        <v>6.05</v>
       </c>
       <c r="CD10" t="n">
-        <v>7.48</v>
+        <v>7.24</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DB10" t="n">
         <v>1.29</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="DH10" t="n">
-        <v>63.54</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="DI10" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.61</v>
+        <v>2.43</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.08</v>
+        <v>3.86</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DM10" t="n">
-        <v>28.31</v>
+        <v>28</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.77</v>
+        <v>12.93</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.23</v>
+        <v>14.36</v>
       </c>
       <c r="DR10" t="n">
-        <v>11.15</v>
+        <v>10.86</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>39.38</v>
+        <v>39.93</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.46</v>
+        <v>10.07</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.08</v>
+        <v>6.93</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.23</v>
+        <v>18.36</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="11">
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
@@ -6223,82 +6223,82 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="G14" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="H14" t="n">
-        <v>86.17</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.17</v>
+        <v>-0.29</v>
       </c>
       <c r="J14" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>4.29</v>
       </c>
       <c r="L14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M14" t="n">
-        <v>30</v>
+        <v>33.14</v>
       </c>
       <c r="N14" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O14" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="P14" t="n">
-        <v>13.33</v>
+        <v>13.71</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.33</v>
+        <v>13.57</v>
       </c>
       <c r="R14" t="n">
-        <v>10</v>
+        <v>9.57</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V14" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>45.33</v>
+        <v>46.43</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.83</v>
+        <v>12.29</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.33</v>
+        <v>7.86</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="AC14" t="n">
-        <v>23.33</v>
+        <v>22.43</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6382,70 +6382,70 @@
         <v>3</v>
       </c>
       <c r="BG14" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.69</v>
+        <v>8.57</v>
       </c>
       <c r="BI14" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BL14" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.62</v>
+        <v>4.64</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="BR14" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS14" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BT14" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BU14" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV14" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.23</v>
+        <v>3.01</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="CC14" t="n">
         <v>5.65</v>
@@ -6457,154 +6457,154 @@
         <v>1.36</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="CH14" t="n">
         <v>1.43</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK14" t="n">
         <v>1.61</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="CR14" t="n">
         <v>1.41</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CY14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="DB14" t="n">
         <v>1.3</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="DG14" t="n">
         <v>2</v>
       </c>
       <c r="DH14" t="n">
-        <v>83.39</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.31</v>
+        <v>4.43</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DM14" t="n">
-        <v>32.69</v>
+        <v>34.07</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.61</v>
+        <v>14.71</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14</v>
+        <v>14.07</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.84</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47.15</v>
+        <v>47.57</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX14" t="n">
-        <v>9.84</v>
+        <v>10.22</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.38</v>
+        <v>6.72</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.31</v>
+        <v>21</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>0.14</v>
@@ -2678,139 +2678,139 @@
         <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>76</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>34.43</v>
+      </c>
+      <c r="AO5" t="n">
         <v>1</v>
       </c>
-      <c r="AI5" t="n">
-        <v>76.67</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0.83</v>
-      </c>
       <c r="AP5" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.83</v>
+        <v>13.57</v>
       </c>
       <c r="AR5" t="n">
-        <v>18</v>
+        <v>17.14</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.17</v>
+        <v>7.71</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>49.33</v>
+        <v>48.14</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.17</v>
+        <v>12</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.17</v>
+        <v>8.43</v>
       </c>
       <c r="BC5" t="n">
-        <v>3</v>
+        <v>3.57</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.33</v>
+        <v>17.29</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.46</v>
+        <v>11.07</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.38</v>
+        <v>4.57</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6</v>
+        <v>6.43</v>
       </c>
       <c r="BR5" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BT5" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BU5" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BV5" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BY5" t="n">
         <v>3.13</v>
@@ -2822,70 +2822,70 @@
         <v>3.66</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.37</v>
+        <v>4.32</v>
       </c>
       <c r="CE5" t="n">
         <v>1.36</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CH5" t="n">
         <v>1.44</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CK5" t="n">
         <v>1.56</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="CU5" t="n">
         <v>1.48</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX5" t="n">
         <v>1.58</v>
@@ -2900,88 +2900,88 @@
         <v>1.86</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="DH5" t="n">
-        <v>77.08</v>
+        <v>76.72</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.23</v>
+        <v>4.36</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM5" t="n">
-        <v>38.54</v>
+        <v>37.57</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.54</v>
+        <v>12</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.77</v>
+        <v>15.5</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.08</v>
+        <v>7.36</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.31</v>
+        <v>50.57</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.39</v>
+        <v>11.78</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.77</v>
+        <v>7.93</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.61</v>
+        <v>3.86</v>
       </c>
       <c r="EA5" t="n">
-        <v>18</v>
+        <v>17.93</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="6">
@@ -4196,94 +4196,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>4.29</v>
+        <v>4.62</v>
       </c>
       <c r="H9" t="n">
-        <v>91.14</v>
+        <v>92.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J9" t="n">
-        <v>3.57</v>
+        <v>3.25</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>6.88</v>
       </c>
       <c r="L9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M9" t="n">
-        <v>40.14</v>
+        <v>43</v>
       </c>
       <c r="N9" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="P9" t="n">
-        <v>12.43</v>
+        <v>12.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.86</v>
+        <v>17</v>
       </c>
       <c r="R9" t="n">
-        <v>6.57</v>
+        <v>6.75</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>59.71</v>
+        <v>59.62</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.29</v>
+        <v>10.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.71</v>
+        <v>5.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.57</v>
+        <v>19.12</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4367,64 +4367,64 @@
         <v>2.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.92</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BP9" t="n">
-        <v>4</v>
+        <v>4.21</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.92</v>
+        <v>5.43</v>
       </c>
       <c r="BR9" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS9" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT9" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV9" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.37</v>
+        <v>3.19</v>
       </c>
       <c r="CA9" t="n">
         <v>3.62</v>
@@ -4442,31 +4442,31 @@
         <v>1.33</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CH9" t="n">
         <v>1.46</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.7</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CO9" t="n">
         <v>1.23</v>
@@ -4475,7 +4475,7 @@
         <v>1.8</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
@@ -4517,79 +4517,79 @@
         <v>3.04</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.77</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.85</v>
+        <v>5.43</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.84</v>
+        <v>37.78</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.23</v>
+        <v>13.22</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.85</v>
+        <v>16</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.69</v>
+        <v>7.71</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>54.07</v>
+        <v>54.43</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.23</v>
+        <v>14.14</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.460000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.77</v>
+        <v>4.78</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.54</v>
+        <v>17.5</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="10">
@@ -5808,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5901,49 +5901,49 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AI13" t="n">
-        <v>86.17</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.83</v>
+        <v>4.86</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="AN13" t="n">
-        <v>34.5</v>
+        <v>35.29</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14.33</v>
+        <v>14.43</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.33</v>
+        <v>13.71</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.33</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5955,82 +5955,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>47.67</v>
+        <v>46.71</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.67</v>
+        <v>11.43</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.83</v>
+        <v>6.57</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.83</v>
+        <v>4.86</v>
       </c>
       <c r="BD13" t="n">
-        <v>19.83</v>
+        <v>18.71</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.38</v>
+        <v>3.21</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.38</v>
+        <v>3.21</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.62</v>
+        <v>4.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.08</v>
+        <v>5.21</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>100</v>
+        <v>92.86</v>
       </c>
       <c r="BT13" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU13" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BV13" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX13" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY13" t="n">
         <v>3.4</v>
@@ -6039,31 +6039,31 @@
         <v>3.7</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.19</v>
+        <v>4.15</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.37</v>
+        <v>5.18</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.9</v>
+        <v>5.66</v>
       </c>
       <c r="CE13" t="n">
         <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CH13" t="n">
         <v>1.52</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.69</v>
@@ -6072,22 +6072,22 @@
         <v>1.47</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CO13" t="n">
         <v>1.21</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CR13" t="n">
         <v>1.37</v>
@@ -6108,10 +6108,10 @@
         <v>1.69</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.44</v>
@@ -6126,49 +6126,49 @@
         <v>1.72</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DH13" t="n">
-        <v>85.31</v>
+        <v>85.14</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="DK13" t="n">
         <v>5</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.62</v>
+        <v>0.72</v>
       </c>
       <c r="DM13" t="n">
-        <v>41.84</v>
+        <v>41.72</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.46</v>
+        <v>13.57</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.23</v>
+        <v>13.42</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.380000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6180,28 +6180,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50</v>
+        <v>49.36</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.92</v>
+        <v>11.78</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.92</v>
+        <v>7.71</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.08</v>
+        <v>21.36</v>
       </c>
       <c r="EB13" t="n">
         <v>1.34</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="14">
@@ -7017,61 +7017,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="H16" t="n">
-        <v>84</v>
+        <v>90.5</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="K16" t="n">
-        <v>4.14</v>
+        <v>4.25</v>
       </c>
       <c r="L16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M16" t="n">
-        <v>40.14</v>
+        <v>43.88</v>
       </c>
       <c r="N16" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O16" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="P16" t="n">
-        <v>14.71</v>
+        <v>14.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.86</v>
+        <v>12.25</v>
       </c>
       <c r="R16" t="n">
-        <v>9.43</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="T16" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -7083,28 +7083,28 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>53.14</v>
+        <v>53.88</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.71</v>
+        <v>14</v>
       </c>
       <c r="AA16" t="n">
-        <v>10.71</v>
+        <v>11</v>
       </c>
       <c r="AB16" t="n">
         <v>3</v>
       </c>
       <c r="AC16" t="n">
-        <v>20.14</v>
+        <v>19.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AF16" t="n">
         <v>0.33</v>
@@ -7188,70 +7188,70 @@
         <v>3</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.380000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.15</v>
+        <v>4.07</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.15</v>
+        <v>4.36</v>
       </c>
       <c r="BR16" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT16" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV16" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW16" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX16" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="CA16" t="n">
         <v>3.81</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CC16" t="n">
         <v>4.54</v>
@@ -7263,40 +7263,40 @@
         <v>1.34</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CH16" t="n">
         <v>1.49</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CO16" t="n">
         <v>1.24</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="CR16" t="n">
         <v>1.38</v>
@@ -7311,73 +7311,73 @@
         <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB16" t="n">
         <v>1.26</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DF16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DG16" t="n">
         <v>2.08</v>
       </c>
-      <c r="DG16" t="n">
-        <v>1.85</v>
-      </c>
       <c r="DH16" t="n">
-        <v>80.77</v>
+        <v>84.70999999999999</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM16" t="n">
-        <v>33.84</v>
+        <v>36.43</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.61</v>
+        <v>14.72</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.31</v>
+        <v>12.5</v>
       </c>
       <c r="DR16" t="n">
-        <v>9.08</v>
+        <v>8.93</v>
       </c>
       <c r="DS16" t="n">
         <v>0</v>
@@ -7389,28 +7389,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>49.23</v>
+        <v>49.93</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.77</v>
+        <v>12.07</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.69</v>
+        <v>9</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.77</v>
+        <v>17.57</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="H3" t="n">
-        <v>78.5</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="J3" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>5.33</v>
+        <v>4.71</v>
       </c>
       <c r="L3" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="M3" t="n">
-        <v>33.5</v>
+        <v>33.29</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="O3" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="P3" t="n">
-        <v>12</v>
+        <v>11.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>17</v>
+        <v>17.43</v>
       </c>
       <c r="R3" t="n">
-        <v>7.33</v>
+        <v>7.43</v>
       </c>
       <c r="S3" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="T3" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>45</v>
+        <v>45.71</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.17</v>
+        <v>10.71</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.33</v>
+        <v>6.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.83</v>
+        <v>4.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.67</v>
+        <v>18.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>3</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.460000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BM3" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.77</v>
+        <v>4.71</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.69</v>
+        <v>4.43</v>
       </c>
       <c r="BR3" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS3" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU3" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV3" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX3" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.86</v>
+        <v>3.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.16</v>
+        <v>3.33</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="CC3" t="n">
         <v>5.59</v>
@@ -2025,28 +2025,28 @@
         <v>6.09</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="CH3" t="n">
         <v>1.41</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CK3" t="n">
         <v>1.58</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CM3" t="n">
         <v>2.27</v>
@@ -2055,34 +2055,34 @@
         <v>1.79</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CT3" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CY3" t="n">
         <v>2.01</v>
@@ -2094,55 +2094,55 @@
         <v>1.8</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.41</v>
+        <v>3.47</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DH3" t="n">
-        <v>70.77</v>
+        <v>71.36</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DM3" t="n">
-        <v>28.38</v>
+        <v>28.64</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.54</v>
+        <v>11.5</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.08</v>
+        <v>14.5</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.539999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>42.77</v>
+        <v>43.28</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.460000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.77</v>
+        <v>4.78</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.92</v>
+        <v>19.07</v>
       </c>
       <c r="EB3" t="n">
         <v>1</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0.5</v>
@@ -2275,115 +2275,115 @@
         <v>1.67</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AI4" t="n">
-        <v>85.56999999999999</v>
+        <v>86.88</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.29</v>
+        <v>4.88</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="AN4" t="n">
-        <v>37</v>
+        <v>39.88</v>
       </c>
       <c r="AO4" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>54.88</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BL4" t="n">
         <v>0.71</v>
       </c>
-      <c r="AP4" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>11.57</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>53.86</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>20.57</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.77</v>
-      </c>
       <c r="BM4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.23</v>
+        <v>5.29</v>
       </c>
       <c r="BQ4" t="n">
         <v>5</v>
@@ -2395,19 +2395,19 @@
         <v>100</v>
       </c>
       <c r="BT4" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU4" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV4" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY4" t="n">
         <v>1.77</v>
@@ -2416,16 +2416,16 @@
         <v>1.87</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="CB4" t="n">
         <v>4.29</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="CE4" t="n">
         <v>1.28</v>
@@ -2440,7 +2440,7 @@
         <v>1.53</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.64</v>
@@ -2449,7 +2449,7 @@
         <v>1.5</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CM4" t="n">
         <v>2.41</v>
@@ -2464,7 +2464,7 @@
         <v>1.63</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
@@ -2485,13 +2485,13 @@
         <v>1.66</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY4" t="n">
         <v>1.89</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DA4" t="n">
         <v>1.92</v>
@@ -2506,79 +2506,79 @@
         <v>2.62</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="DH4" t="n">
-        <v>85.92</v>
+        <v>86.64</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.85</v>
+        <v>5.15</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="DM4" t="n">
-        <v>39.39</v>
+        <v>40.86</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.38</v>
+        <v>14.14</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.15</v>
+        <v>12</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.77</v>
+        <v>8</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>52.39</v>
+        <v>53.08</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.85</v>
+        <v>14.78</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.85</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.38</v>
+        <v>18</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2828,7 +2828,7 @@
         <v>4.15</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.32</v>
+        <v>4.29</v>
       </c>
       <c r="CE5" t="n">
         <v>1.36</v>
@@ -2882,22 +2882,22 @@
         <v>1.48</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CW5" t="n">
         <v>1.75</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DB5" t="n">
         <v>1.27</v>
@@ -2906,7 +2906,7 @@
         <v>1.88</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="DE5" t="n">
         <v>0.14</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
@@ -3006,79 +3006,79 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="H6" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="L6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>36.71</v>
+        <v>36.25</v>
       </c>
       <c r="N6" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="P6" t="n">
-        <v>15.43</v>
+        <v>14.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.71</v>
+        <v>15.12</v>
       </c>
       <c r="R6" t="n">
-        <v>8.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="S6" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="U6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>51.86</v>
+        <v>50.12</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.57</v>
+        <v>20.38</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,67 +3162,67 @@
         <v>2.33</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.77</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.54</v>
+        <v>4.64</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.23</v>
+        <v>5.21</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU6" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV6" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX6" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.19</v>
+        <v>3.37</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="CB6" t="n">
         <v>4.3</v>
@@ -3237,40 +3237,40 @@
         <v>1.34</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CH6" t="n">
         <v>1.47</v>
       </c>
       <c r="CI6" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CL6" t="n">
         <v>2.11</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="CR6" t="n">
         <v>1.4</v>
@@ -3285,106 +3285,106 @@
         <v>1.51</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB6" t="n">
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="DH6" t="n">
-        <v>89.23</v>
+        <v>88.14</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="DK6" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DM6" t="n">
-        <v>37.31</v>
+        <v>37</v>
       </c>
       <c r="DN6" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.69</v>
+        <v>14.43</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.77</v>
+        <v>14.5</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.619999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47.46</v>
+        <v>46.78</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.54</v>
+        <v>11.22</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.539999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.08</v>
+        <v>20.93</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="7">
@@ -4424,7 +4424,7 @@
         <v>3.05</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CA9" t="n">
         <v>3.62</v>
@@ -4484,28 +4484,28 @@
         <v>2.73</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CU9" t="n">
         <v>1.49</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB9" t="n">
         <v>1.26</v>
@@ -4514,7 +4514,7 @@
         <v>1.84</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="DE9" t="n">
         <v>0.14</v>
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>0.17</v>
@@ -5092,52 +5092,52 @@
         <v>2.17</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AI11" t="n">
-        <v>91</v>
+        <v>94.62</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN11" t="n">
-        <v>41.86</v>
+        <v>43.88</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>17</v>
+        <v>17.38</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.57</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.43</v>
+        <v>7.88</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5149,73 +5149,73 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>37.14</v>
+        <v>38.75</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA11" t="n">
-        <v>13.14</v>
+        <v>13.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.57</v>
+        <v>8.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.57</v>
+        <v>5</v>
       </c>
       <c r="BD11" t="n">
-        <v>19</v>
+        <v>20.25</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="BF11" t="n">
         <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.77</v>
+        <v>9.43</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.38</v>
+        <v>4.36</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.38</v>
+        <v>5.07</v>
       </c>
       <c r="BR11" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BT11" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BU11" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BY11" t="n">
         <v>2.2</v>
@@ -5233,34 +5233,34 @@
         <v>2.31</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="CH11" t="n">
         <v>1.4</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CK11" t="n">
         <v>1.57</v>
@@ -5269,7 +5269,7 @@
         <v>1.97</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN11" t="n">
         <v>1.8</v>
@@ -5278,91 +5278,91 @@
         <v>1.28</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY11" t="n">
         <v>1.94</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DB11" t="n">
         <v>1.32</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="DH11" t="n">
-        <v>92.84999999999999</v>
+        <v>94.78</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.54</v>
+        <v>4.5</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DM11" t="n">
-        <v>42.23</v>
+        <v>43.36</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="DP11" t="n">
-        <v>17.54</v>
+        <v>17.72</v>
       </c>
       <c r="DQ11" t="n">
-        <v>8.92</v>
+        <v>9.07</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.31</v>
+        <v>8</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>37.23</v>
+        <v>38.14</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.84</v>
+        <v>13.07</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.85</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4</v>
+        <v>4.28</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.38</v>
+        <v>20.07</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="12">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
@@ -5417,82 +5417,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5</v>
+        <v>3.57</v>
       </c>
       <c r="H12" t="n">
-        <v>91.83</v>
+        <v>92.14</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="K12" t="n">
-        <v>5.33</v>
+        <v>6.29</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>47</v>
+        <v>48.29</v>
       </c>
       <c r="N12" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="P12" t="n">
-        <v>14.17</v>
+        <v>14</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>15.29</v>
       </c>
       <c r="R12" t="n">
-        <v>7.33</v>
+        <v>7.29</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="T12" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="U12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>48.5</v>
+        <v>48.71</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.17</v>
+        <v>13.57</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.33</v>
+        <v>10.43</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.33</v>
+        <v>19.86</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5576,70 +5576,70 @@
         <v>2.29</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.619999999999999</v>
+        <v>10</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BP12" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.62</v>
+        <v>6.07</v>
       </c>
       <c r="BR12" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BU12" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BV12" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.67</v>
+        <v>3.61</v>
       </c>
       <c r="BZ12" t="n">
-        <v>4.27</v>
+        <v>4.14</v>
       </c>
       <c r="CA12" t="n">
         <v>3.58</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CC12" t="n">
         <v>3.12</v>
@@ -5654,19 +5654,19 @@
         <v>2.62</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CH12" t="n">
         <v>1.44</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL12" t="n">
         <v>1.99</v>
@@ -5675,7 +5675,7 @@
         <v>2.38</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CO12" t="n">
         <v>1.25</v>
@@ -5687,31 +5687,31 @@
         <v>2.96</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX12" t="n">
         <v>1.54</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="DA12" t="n">
         <v>1.92</v>
@@ -5723,82 +5723,82 @@
         <v>1.94</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DG12" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="DH12" t="n">
-        <v>89.77</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.92</v>
+        <v>5.43</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DM12" t="n">
-        <v>42.92</v>
+        <v>43.86</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="DO12" t="n">
         <v>1.92</v>
       </c>
       <c r="DP12" t="n">
-        <v>15</v>
+        <v>14.86</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.31</v>
+        <v>12.64</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.62</v>
+        <v>7.58</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.61</v>
+        <v>45.92</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.54</v>
+        <v>11.86</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.69</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.85</v>
+        <v>20.07</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="13">
@@ -6042,13 +6042,13 @@
         <v>3.95</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="CC13" t="n">
         <v>5.18</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.66</v>
+        <v>5.65</v>
       </c>
       <c r="CE13" t="n">
         <v>1.31</v>
@@ -6096,16 +6096,16 @@
         <v>2.58</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="CU13" t="n">
         <v>1.55</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX13" t="n">
         <v>1.51</v>
@@ -6123,10 +6123,10 @@
         <v>1.22</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6704,139 +6704,139 @@
         <v>2.57</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="AI15" t="n">
-        <v>91.67</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.67</v>
+        <v>5.29</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.5</v>
+        <v>39.71</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.33</v>
+        <v>10.71</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.33</v>
+        <v>14.43</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.17</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>51</v>
+        <v>50.43</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>12.33</v>
+        <v>12.86</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.83</v>
+        <v>8.43</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="BD15" t="n">
-        <v>20.67</v>
+        <v>19.29</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.31</v>
+        <v>10.93</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.77</v>
+        <v>4.64</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.54</v>
+        <v>6.29</v>
       </c>
       <c r="BR15" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS15" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT15" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU15" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV15" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY15" t="n">
         <v>2.2</v>
@@ -6845,31 +6845,31 @@
         <v>2.21</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.27</v>
+        <v>4.59</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.64</v>
+        <v>4.91</v>
       </c>
       <c r="CE15" t="n">
         <v>1.36</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CH15" t="n">
         <v>1.45</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.73</v>
@@ -6878,136 +6878,136 @@
         <v>1.52</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="CN15" t="n">
         <v>1.85</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CU15" t="n">
         <v>1.47</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CW15" t="n">
         <v>1.76</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY15" t="n">
         <v>1.91</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="DA15" t="n">
         <v>1.9</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.46</v>
+        <v>3.36</v>
       </c>
       <c r="DH15" t="n">
-        <v>98.69</v>
+        <v>97.5</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.39</v>
+        <v>6.14</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DM15" t="n">
-        <v>45.84</v>
+        <v>45.92</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.15</v>
+        <v>12.21</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.08</v>
+        <v>13.22</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.23</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>53.69</v>
+        <v>53.22</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.15</v>
+        <v>14.28</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.69</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.54</v>
+        <v>20.79</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="16">
@@ -7251,7 +7251,7 @@
         <v>3.81</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="CC16" t="n">
         <v>4.54</v>
@@ -7302,16 +7302,16 @@
         <v>1.38</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CU16" t="n">
         <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CW16" t="n">
         <v>1.72</v>
@@ -7335,7 +7335,7 @@
         <v>1.83</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="DE16" t="n">
         <v>0.21</v>
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -7835,82 +7835,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="G18" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="H18" t="n">
-        <v>100.86</v>
+        <v>99.75</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="K18" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M18" t="n">
-        <v>40.86</v>
+        <v>41.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O18" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="P18" t="n">
-        <v>12.29</v>
+        <v>12.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.43</v>
+        <v>13.25</v>
       </c>
       <c r="R18" t="n">
-        <v>7.43</v>
+        <v>7.62</v>
       </c>
       <c r="S18" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="V18" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>53.86</v>
+        <v>53.75</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>17</v>
+        <v>17.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>11.71</v>
+        <v>11.62</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.29</v>
+        <v>5.62</v>
       </c>
       <c r="AC18" t="n">
-        <v>21.57</v>
+        <v>20.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AF18" t="n">
         <v>0.17</v>
@@ -7994,70 +7994,70 @@
         <v>1.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.460000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.38</v>
+        <v>4.29</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.08</v>
+        <v>4.93</v>
       </c>
       <c r="BR18" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS18" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT18" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BU18" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV18" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW18" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX18" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BZ18" t="n">
         <v>1.62</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="CC18" t="n">
         <v>3.84</v>
@@ -8069,19 +8069,19 @@
         <v>1.33</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CH18" t="n">
         <v>1.49</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK18" t="n">
         <v>1.53</v>
@@ -8090,34 +8090,34 @@
         <v>2.02</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CO18" t="n">
         <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CU18" t="n">
         <v>1.52</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CW18" t="n">
         <v>1.75</v>
@@ -8129,94 +8129,94 @@
         <v>1.92</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DB18" t="n">
         <v>1.24</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF18" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="DH18" t="n">
-        <v>89.31</v>
+        <v>89.5</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.15</v>
+        <v>4.07</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DM18" t="n">
-        <v>36.46</v>
+        <v>37.14</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.16</v>
+        <v>12.35</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.69</v>
+        <v>14.5</v>
       </c>
       <c r="DR18" t="n">
         <v>8.85</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>51.31</v>
+        <v>51.43</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.77</v>
+        <v>15.07</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.460000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.31</v>
+        <v>5.5</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.54</v>
+        <v>19.29</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="19">
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8319,49 +8319,49 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="AI19" t="n">
-        <v>104.57</v>
+        <v>103.12</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="AL19" t="n">
-        <v>6.71</v>
+        <v>6.25</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>49.71</v>
+        <v>46.88</v>
       </c>
       <c r="AO19" t="n">
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.71</v>
+        <v>11.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>15.57</v>
+        <v>15.25</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.86</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AT19" t="n">
         <v>1</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8373,82 +8373,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>61.71</v>
+        <v>60.25</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="BA19" t="n">
-        <v>13.71</v>
+        <v>13.38</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.710000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BC19" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="BD19" t="n">
-        <v>17.71</v>
+        <v>16.88</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.77</v>
+        <v>11.07</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BM19" t="n">
         <v>1</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.62</v>
+        <v>4.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.08</v>
+        <v>6.5</v>
       </c>
       <c r="BR19" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU19" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BV19" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX19" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY19" t="n">
         <v>2.44</v>
@@ -8457,16 +8457,16 @@
         <v>2.52</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.12</v>
+        <v>3.01</v>
       </c>
       <c r="CE19" t="n">
         <v>1.35</v>
@@ -8475,34 +8475,34 @@
         <v>2.69</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CH19" t="n">
         <v>1.44</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL19" t="n">
         <v>2.01</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CO19" t="n">
         <v>1.24</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CQ19" t="n">
         <v>3.02</v>
@@ -8514,28 +8514,28 @@
         <v>2.82</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CU19" t="n">
         <v>1.46</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB19" t="n">
         <v>1.28</v>
@@ -8544,82 +8544,82 @@
         <v>1.91</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="DG19" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="DH19" t="n">
-        <v>91.69</v>
+        <v>91.78</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.61</v>
+        <v>5.43</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="DM19" t="n">
-        <v>45.61</v>
+        <v>44.29</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.23</v>
+        <v>13.5</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.15</v>
+        <v>14.07</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.92</v>
+        <v>8.07</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>56.38</v>
+        <v>55.93</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.46</v>
+        <v>12.36</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.609999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.61</v>
+        <v>17.15</v>
       </c>
       <c r="EB19" t="n">
         <v>1.39</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1472,127 +1472,127 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>71.70999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN2" t="n">
-        <v>33.57</v>
+        <v>33.38</v>
       </c>
       <c r="AO2" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.71</v>
+        <v>12.62</v>
       </c>
       <c r="AR2" t="n">
-        <v>15.71</v>
+        <v>17.25</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.289999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>44.14</v>
+        <v>44.62</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.71</v>
+        <v>11.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.14</v>
+        <v>19.62</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.380000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.15</v>
+        <v>4.93</v>
       </c>
       <c r="BR2" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU2" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY2" t="n">
         <v>3.27</v>
@@ -1610,16 +1610,16 @@
         <v>3.33</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC2" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="CD2" t="n">
-        <v>5.14</v>
+        <v>5.1</v>
       </c>
       <c r="CE2" t="n">
         <v>1.35</v>
@@ -1628,37 +1628,37 @@
         <v>2.68</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI2" t="n">
         <v>2.01</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CO2" t="n">
         <v>1.25</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CR2" t="n">
         <v>1.4</v>
@@ -1673,19 +1673,19 @@
         <v>1.45</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CW2" t="n">
         <v>1.79</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DA2" t="n">
         <v>1.65</v>
@@ -1694,85 +1694,85 @@
         <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="DH2" t="n">
-        <v>82.23</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.62</v>
+        <v>4.35</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM2" t="n">
-        <v>39.23</v>
+        <v>38.72</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="DP2" t="n">
         <v>12</v>
       </c>
       <c r="DQ2" t="n">
-        <v>15.3</v>
+        <v>16.21</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.39</v>
+        <v>7.35</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47.46</v>
+        <v>47.5</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.46</v>
+        <v>12.28</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.619999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.07</v>
+        <v>18.85</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="3">
@@ -3394,31 +3394,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F7" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G7" t="n">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="H7" t="n">
-        <v>123.33</v>
+        <v>122.14</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="K7" t="n">
         <v>7</v>
@@ -3427,61 +3427,61 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>63.33</v>
+        <v>61.86</v>
       </c>
       <c r="N7" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="O7" t="n">
-        <v>4.17</v>
+        <v>3.86</v>
       </c>
       <c r="P7" t="n">
-        <v>12.67</v>
+        <v>12.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.5</v>
+        <v>14.71</v>
       </c>
       <c r="R7" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="U7" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V7" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>63.33</v>
+        <v>62.29</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>22.83</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>14.33</v>
+        <v>14.43</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.5</v>
+        <v>7.57</v>
       </c>
       <c r="AC7" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.49</v>
+        <v>2.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AF7" t="n">
         <v>0.29</v>
@@ -3565,70 +3565,70 @@
         <v>2.71</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.460000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.15</v>
+        <v>4.93</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.31</v>
+        <v>4.57</v>
       </c>
       <c r="BR7" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU7" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BV7" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW7" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX7" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.04</v>
+        <v>4.93</v>
       </c>
       <c r="CB7" t="n">
-        <v>5.26</v>
+        <v>5.13</v>
       </c>
       <c r="CC7" t="n">
         <v>1.68</v>
@@ -3643,19 +3643,19 @@
         <v>2.38</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL7" t="n">
         <v>1.94</v>
@@ -3670,7 +3670,7 @@
         <v>1.17</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CQ7" t="n">
         <v>2.51</v>
@@ -3688,10 +3688,10 @@
         <v>1.58</v>
       </c>
       <c r="CV7" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CX7" t="n">
         <v>1.55</v>
@@ -3700,7 +3700,7 @@
         <v>1.92</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DA7" t="n">
         <v>1.89</v>
@@ -3715,79 +3715,79 @@
         <v>2.67</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="DH7" t="n">
-        <v>112.38</v>
+        <v>112.57</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.39</v>
+        <v>6.43</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.92</v>
+        <v>52.93</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.54</v>
+        <v>3.43</v>
       </c>
       <c r="DP7" t="n">
-        <v>13.23</v>
+        <v>13.14</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.31</v>
+        <v>13.92</v>
       </c>
       <c r="DR7" t="n">
         <v>5</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>60.69</v>
+        <v>60.36</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX7" t="n">
-        <v>19.08</v>
+        <v>18.93</v>
       </c>
       <c r="DY7" t="n">
-        <v>11.69</v>
+        <v>11.93</v>
       </c>
       <c r="DZ7" t="n">
-        <v>7.39</v>
+        <v>7</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.92</v>
+        <v>18.78</v>
       </c>
       <c r="EB7" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>0.14</v>
@@ -3890,136 +3890,136 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AI8" t="n">
-        <v>91</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AL8" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN8" t="n">
-        <v>48.33</v>
+        <v>45.57</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.67</v>
+        <v>13.14</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.5</v>
+        <v>11.57</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AU8" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>61</v>
+        <v>58.57</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>15</v>
+        <v>13.71</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.5</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.83</v>
+        <v>17.86</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.92</v>
+        <v>9</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.23</v>
+        <v>4.07</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.69</v>
+        <v>4.93</v>
       </c>
       <c r="BR8" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS8" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU8" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV8" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>1.28</v>
@@ -4028,81 +4028,81 @@
         <v>1.32</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.57</v>
+        <v>5.42</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.93</v>
+        <v>5.75</v>
       </c>
       <c r="CC8" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="CD8" t="n">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="CE8" t="n">
         <v>1.22</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.85</v>
+        <v>3.79</v>
       </c>
       <c r="CH8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CJ8" t="n">
         <v>1.71</v>
       </c>
-      <c r="CI8" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="CJ8" t="n">
-        <v>1.72</v>
-      </c>
       <c r="CK8" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO8" t="n">
         <v>1.12</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CX8" t="n">
         <v>1.51</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DB8" t="n">
         <v>1.15</v>
@@ -4114,79 +4114,79 @@
         <v>2.22</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="DH8" t="n">
-        <v>95.31</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DM8" t="n">
-        <v>54.23</v>
+        <v>52.43</v>
       </c>
       <c r="DN8" t="n">
         <v>1.07</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.47</v>
+        <v>12.22</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.77</v>
+        <v>10.86</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.31</v>
+        <v>7.64</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>63.08</v>
+        <v>61.72</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX8" t="n">
-        <v>18.39</v>
+        <v>17.5</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.92</v>
+        <v>11.36</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6.46</v>
+        <v>6.14</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.23</v>
+        <v>20.08</v>
       </c>
       <c r="EB8" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="9">
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>48.71</v>
+        <v>48.86</v>
       </c>
       <c r="Y12" t="n">
         <v>0.14</v>
@@ -5777,7 +5777,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.92</v>
+        <v>46</v>
       </c>
       <c r="DW12" t="n">
         <v>0.14</v>
@@ -7420,94 +7420,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F17" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="G17" t="n">
-        <v>4.29</v>
+        <v>3.88</v>
       </c>
       <c r="H17" t="n">
-        <v>110.86</v>
+        <v>107.25</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="K17" t="n">
-        <v>6.57</v>
+        <v>6.12</v>
       </c>
       <c r="L17" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="M17" t="n">
-        <v>45.86</v>
+        <v>43.88</v>
       </c>
       <c r="N17" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="O17" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="P17" t="n">
-        <v>13.86</v>
+        <v>15.62</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.43</v>
+        <v>12.38</v>
       </c>
       <c r="R17" t="n">
-        <v>5.43</v>
+        <v>5.25</v>
       </c>
       <c r="S17" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="T17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="U17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>57</v>
+        <v>56.38</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="Z17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.43</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.57</v>
+        <v>4.12</v>
       </c>
       <c r="AC17" t="n">
-        <v>22.86</v>
+        <v>21.62</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AF17" t="n">
         <v>0.33</v>
@@ -7591,67 +7591,67 @@
         <v>3</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BH17" t="n">
-        <v>11.08</v>
+        <v>10.57</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.85</v>
+        <v>4.64</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.31</v>
+        <v>6</v>
       </c>
       <c r="BR17" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU17" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV17" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="CB17" t="n">
         <v>3.62</v>
@@ -7663,13 +7663,13 @@
         <v>3.3</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF17" t="n">
         <v>2.73</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CH17" t="n">
         <v>1.41</v>
@@ -7678,13 +7678,13 @@
         <v>1.96</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CK17" t="n">
         <v>1.58</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM17" t="n">
         <v>2.29</v>
@@ -7696,10 +7696,10 @@
         <v>1.28</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
@@ -7717,19 +7717,19 @@
         <v>2.1</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB17" t="n">
         <v>1.3</v>
@@ -7741,79 +7741,79 @@
         <v>3.33</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.62</v>
+        <v>3.43</v>
       </c>
       <c r="DH17" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="DK17" t="n">
-        <v>6.39</v>
+        <v>6.14</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="DM17" t="n">
-        <v>39.38</v>
+        <v>38.72</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="DP17" t="n">
-        <v>14.46</v>
+        <v>15.43</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.85</v>
+        <v>10.93</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.23</v>
+        <v>7.93</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.77</v>
+        <v>50.86</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.77</v>
+        <v>13.28</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.31</v>
+        <v>9.07</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.46</v>
+        <v>4.21</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.62</v>
+        <v>19.14</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="18">
@@ -8373,7 +8373,7 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>60.25</v>
+        <v>60.12</v>
       </c>
       <c r="AZ19" t="n">
         <v>0.25</v>
@@ -8598,7 +8598,7 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.93</v>
+        <v>55.86</v>
       </c>
       <c r="DW19" t="n">
         <v>0.22</v>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -3797,61 +3797,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="F8" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="H8" t="n">
-        <v>99</v>
+        <v>98.38</v>
       </c>
       <c r="I8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J8" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="K8" t="n">
-        <v>6.14</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="M8" t="n">
-        <v>59.29</v>
+        <v>55.75</v>
       </c>
       <c r="N8" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O8" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>11.29</v>
+        <v>10.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.14</v>
+        <v>10.12</v>
       </c>
       <c r="R8" t="n">
-        <v>6.29</v>
+        <v>7</v>
       </c>
       <c r="S8" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,25 +3863,25 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>64.86</v>
+        <v>63.88</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.29</v>
+        <v>20.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>14</v>
+        <v>13.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.29</v>
+        <v>7.12</v>
       </c>
       <c r="AC8" t="n">
-        <v>22.29</v>
+        <v>21.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -3968,70 +3968,70 @@
         <v>2.71</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="BH8" t="n">
-        <v>9</v>
+        <v>8.67</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL8" t="n">
         <v>0.93</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.07</v>
+        <v>3.87</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.93</v>
+        <v>4.8</v>
       </c>
       <c r="BR8" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS8" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT8" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BU8" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BV8" t="n">
-        <v>7.14</v>
+        <v>13.33</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.42</v>
+        <v>5.37</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.75</v>
+        <v>5.69</v>
       </c>
       <c r="CC8" t="n">
         <v>1.62</v>
@@ -4040,13 +4040,13 @@
         <v>1.71</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CF8" t="n">
         <v>2.13</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CH8" t="n">
         <v>1.69</v>
@@ -4061,36 +4061,36 @@
         <v>1.49</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CM8" t="n">
         <v>2.47</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX8" t="n">
         <v>1.51</v>
@@ -4099,10 +4099,10 @@
         <v>1.8</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB8" t="n">
         <v>1.15</v>
@@ -4114,46 +4114,46 @@
         <v>2.22</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DF8" t="n">
         <v>0.93</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="DH8" t="n">
-        <v>94.34999999999999</v>
+        <v>94.33</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="DK8" t="n">
-        <v>5</v>
+        <v>4.73</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DM8" t="n">
-        <v>52.43</v>
+        <v>51</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.22</v>
+        <v>11.87</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.86</v>
+        <v>10.8</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.64</v>
+        <v>7.93</v>
       </c>
       <c r="DS8" t="n">
         <v>0.14</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>61.72</v>
+        <v>61.4</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX8" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.36</v>
+        <v>11.06</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6.14</v>
+        <v>6.13</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.08</v>
+        <v>19.87</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
         <v>0.12</v>
@@ -7510,139 +7510,139 @@
         <v>1.88</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AI17" t="n">
-        <v>78.67</v>
+        <v>79.14</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="AL17" t="n">
-        <v>6.17</v>
+        <v>5.71</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AN17" t="n">
-        <v>31.83</v>
+        <v>34.43</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.33</v>
+        <v>2.86</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15.17</v>
+        <v>14.43</v>
       </c>
       <c r="AR17" t="n">
-        <v>9</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AS17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>43.43</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO17" t="n">
         <v>1</v>
       </c>
-      <c r="AU17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>15.83</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>10.57</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>0.93</v>
-      </c>
       <c r="BP17" t="n">
-        <v>4.64</v>
+        <v>4.4</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BR17" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS17" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT17" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BU17" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BV17" t="n">
-        <v>7.14</v>
+        <v>13.33</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BY17" t="n">
         <v>2.14</v>
@@ -7651,40 +7651,40 @@
         <v>2.14</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.14</v>
+        <v>3.55</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.3</v>
+        <v>3.76</v>
       </c>
       <c r="CE17" t="n">
         <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CM17" t="n">
         <v>2.29</v>
@@ -7693,127 +7693,127 @@
         <v>1.8</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="CT17" t="n">
         <v>3.12</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="DH17" t="n">
-        <v>95</v>
+        <v>94.13</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="DK17" t="n">
-        <v>6.14</v>
+        <v>5.93</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="DM17" t="n">
-        <v>38.72</v>
+        <v>39.47</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="DP17" t="n">
-        <v>15.43</v>
+        <v>15.06</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.93</v>
+        <v>10.67</v>
       </c>
       <c r="DR17" t="n">
         <v>7.93</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.86</v>
+        <v>50.34</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.28</v>
+        <v>13.27</v>
       </c>
       <c r="DY17" t="n">
         <v>9.07</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.14</v>
+        <v>18.93</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -2588,61 +2588,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="G5" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>77.43000000000001</v>
+        <v>78.75</v>
       </c>
       <c r="I5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="K5" t="n">
-        <v>5.43</v>
+        <v>5.12</v>
       </c>
       <c r="L5" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>40.71</v>
+        <v>40.88</v>
       </c>
       <c r="N5" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="O5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="P5" t="n">
-        <v>10.43</v>
+        <v>10.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.86</v>
+        <v>14</v>
       </c>
       <c r="R5" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>53</v>
+        <v>53.75</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.57</v>
+        <v>12.12</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.43</v>
+        <v>7.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.14</v>
+        <v>4.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.57</v>
+        <v>18.62</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AF5" t="n">
         <v>0.14</v>
@@ -2759,70 +2759,70 @@
         <v>2.86</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BH5" t="n">
-        <v>11.07</v>
+        <v>10.6</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.57</v>
+        <v>4.47</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.43</v>
+        <v>6.07</v>
       </c>
       <c r="BR5" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS5" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BT5" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BU5" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BV5" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.13</v>
+        <v>2.99</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.43</v>
+        <v>3.26</v>
       </c>
       <c r="CA5" t="n">
         <v>3.66</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="CC5" t="n">
         <v>4.15</v>
@@ -2837,37 +2837,37 @@
         <v>2.68</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CH5" t="n">
         <v>1.44</v>
       </c>
       <c r="CI5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK5" t="n">
         <v>1.56</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CM5" t="n">
         <v>2.31</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CO5" t="n">
         <v>1.26</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="CR5" t="n">
         <v>1.39</v>
@@ -2888,16 +2888,16 @@
         <v>1.75</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB5" t="n">
         <v>1.27</v>
@@ -2909,46 +2909,46 @@
         <v>3.14</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="DH5" t="n">
-        <v>76.72</v>
+        <v>77.47</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.36</v>
+        <v>4.27</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DM5" t="n">
-        <v>37.57</v>
+        <v>37.87</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="DO5" t="n">
         <v>1.86</v>
       </c>
       <c r="DP5" t="n">
-        <v>12</v>
+        <v>11.93</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.5</v>
+        <v>15.47</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.36</v>
+        <v>7.46</v>
       </c>
       <c r="DS5" t="n">
         <v>0.07000000000000001</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.57</v>
+        <v>51.13</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.78</v>
+        <v>12.06</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.93</v>
+        <v>8</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.86</v>
+        <v>4.07</v>
       </c>
       <c r="EA5" t="n">
-        <v>17.93</v>
+        <v>18</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AI6" t="n">
-        <v>79</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AL6" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>37.71</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>44.86</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BP6" t="n">
         <v>4.67</v>
       </c>
-      <c r="AM6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>13.83</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>42.33</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>21.67</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>4.64</v>
-      </c>
       <c r="BQ6" t="n">
-        <v>5.21</v>
+        <v>5.27</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BU6" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX6" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY6" t="n">
         <v>3.37</v>
@@ -3222,31 +3222,31 @@
         <v>3.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.07</v>
+        <v>4.03</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
       <c r="CC6" t="n">
-        <v>7.39</v>
+        <v>6.8</v>
       </c>
       <c r="CD6" t="n">
-        <v>8.039999999999999</v>
+        <v>7.42</v>
       </c>
       <c r="CE6" t="n">
         <v>1.34</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CH6" t="n">
         <v>1.47</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.75</v>
@@ -3255,22 +3255,22 @@
         <v>1.57</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CM6" t="n">
         <v>2.29</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CR6" t="n">
         <v>1.4</v>
@@ -3285,7 +3285,7 @@
         <v>1.51</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CW6" t="n">
         <v>1.8</v>
@@ -3306,82 +3306,82 @@
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DG6" t="n">
         <v>2.14</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.14</v>
+        <v>88.73</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="DM6" t="n">
-        <v>37</v>
+        <v>36.93</v>
       </c>
       <c r="DN6" t="n">
         <v>1.07</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.43</v>
+        <v>14.2</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.5</v>
+        <v>14.46</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.359999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.78</v>
+        <v>47.67</v>
       </c>
       <c r="DW6" t="n">
         <v>0.14</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.22</v>
+        <v>11</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.43</v>
+        <v>8.27</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.93</v>
+        <v>20.6</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="EC6" t="n">
         <v>2.14</v>
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0.14</v>
@@ -3484,52 +3484,52 @@
         <v>2.29</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG7" t="n">
         <v>2</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="n">
-        <v>103</v>
+        <v>98.88</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.86</v>
+        <v>6.12</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AN7" t="n">
-        <v>44</v>
+        <v>43.75</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP7" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.71</v>
+        <v>13.62</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.14</v>
+        <v>12.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.29</v>
+        <v>6.38</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>58.43</v>
+        <v>57.12</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA7" t="n">
-        <v>15.86</v>
+        <v>15.12</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.43</v>
+        <v>9.25</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.43</v>
+        <v>5.88</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.57</v>
+        <v>17.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.5</v>
+        <v>10.07</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.93</v>
+        <v>5.07</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.57</v>
+        <v>5</v>
       </c>
       <c r="BR7" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS7" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT7" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU7" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BV7" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW7" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX7" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY7" t="n">
         <v>1.41</v>
@@ -3625,40 +3625,40 @@
         <v>1.41</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.93</v>
+        <v>4.87</v>
       </c>
       <c r="CB7" t="n">
-        <v>5.13</v>
+        <v>5.04</v>
       </c>
       <c r="CC7" t="n">
         <v>1.68</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CE7" t="n">
         <v>1.28</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="CH7" t="n">
         <v>1.57</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CK7" t="n">
         <v>1.55</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CM7" t="n">
         <v>2.32</v>
@@ -3673,31 +3673,31 @@
         <v>1.62</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="CX7" t="n">
         <v>1.55</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.38</v>
@@ -3712,49 +3712,49 @@
         <v>1.68</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF7" t="n">
         <v>1.93</v>
       </c>
       <c r="DG7" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="DH7" t="n">
-        <v>112.57</v>
+        <v>109.73</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.43</v>
+        <v>6.53</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.93</v>
+        <v>52.2</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
       <c r="DP7" t="n">
-        <v>13.14</v>
+        <v>13.13</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.92</v>
+        <v>13.53</v>
       </c>
       <c r="DR7" t="n">
-        <v>5</v>
+        <v>5.13</v>
       </c>
       <c r="DS7" t="n">
         <v>0.14</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>60.36</v>
+        <v>59.53</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>18.93</v>
+        <v>18.33</v>
       </c>
       <c r="DY7" t="n">
-        <v>11.93</v>
+        <v>11.67</v>
       </c>
       <c r="DZ7" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.78</v>
+        <v>18.67</v>
       </c>
       <c r="EB7" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="8">
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
@@ -4611,82 +4611,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="H10" t="n">
-        <v>70.5</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>5.29</v>
       </c>
       <c r="L10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M10" t="n">
-        <v>30.5</v>
+        <v>31.14</v>
       </c>
       <c r="N10" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="P10" t="n">
-        <v>12.67</v>
+        <v>12.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>13</v>
+        <v>12.71</v>
       </c>
       <c r="R10" t="n">
-        <v>10.83</v>
+        <v>11.14</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="T10" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="U10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>42</v>
+        <v>41.71</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.5</v>
+        <v>13.43</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.33</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.17</v>
+        <v>4.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.33</v>
+        <v>17.57</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AF10" t="n">
         <v>0.12</v>
@@ -4770,70 +4770,70 @@
         <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.289999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BO10" t="n">
         <v>1.07</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.71</v>
+        <v>4.73</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BU10" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV10" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.68</v>
+        <v>3.45</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.13</v>
+        <v>4.08</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.14</v>
+        <v>4.1</v>
       </c>
       <c r="CC10" t="n">
         <v>6.05</v>
@@ -4854,10 +4854,10 @@
         <v>1.44</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK10" t="n">
         <v>1.58</v>
@@ -4866,7 +4866,7 @@
         <v>1.98</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CN10" t="n">
         <v>1.78</v>
@@ -4878,7 +4878,7 @@
         <v>1.87</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CR10" t="n">
         <v>1.41</v>
@@ -4893,10 +4893,10 @@
         <v>1.44</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX10" t="n">
         <v>1.6</v>
@@ -4914,52 +4914,52 @@
         <v>1.29</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="DH10" t="n">
-        <v>64.84999999999999</v>
+        <v>65.13</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.86</v>
+        <v>4.07</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM10" t="n">
-        <v>28</v>
+        <v>28.46</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.93</v>
+        <v>13</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.36</v>
+        <v>14.13</v>
       </c>
       <c r="DR10" t="n">
-        <v>10.86</v>
+        <v>11</v>
       </c>
       <c r="DS10" t="n">
         <v>0.14</v>
@@ -4974,25 +4974,25 @@
         <v>39.93</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.07</v>
+        <v>10.67</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.93</v>
+        <v>7.27</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.36</v>
+        <v>18</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="11">
@@ -5002,58 +5002,58 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="H11" t="n">
-        <v>95</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>5.29</v>
       </c>
       <c r="L11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M11" t="n">
-        <v>42.67</v>
+        <v>44.43</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>18.17</v>
+        <v>18.29</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.33</v>
+        <v>9</v>
       </c>
       <c r="R11" t="n">
-        <v>8.17</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
@@ -5068,28 +5068,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>37.33</v>
+        <v>37.43</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.5</v>
+        <v>13.71</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.17</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.83</v>
+        <v>19.43</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="AF11" t="n">
         <v>0.12</v>
@@ -5173,49 +5173,49 @@
         <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.43</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.07</v>
+        <v>5.13</v>
       </c>
       <c r="BR11" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS11" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BT11" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BU11" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5224,19 +5224,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CC11" t="n">
         <v>2.92</v>
@@ -5251,10 +5251,10 @@
         <v>2.81</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI11" t="n">
         <v>1.94</v>
@@ -5266,7 +5266,7 @@
         <v>1.57</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CM11" t="n">
         <v>2.26</v>
@@ -5275,7 +5275,7 @@
         <v>1.8</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP11" t="n">
         <v>1.97</v>
@@ -5287,25 +5287,25 @@
         <v>1.42</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CU11" t="n">
         <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX11" t="n">
         <v>1.54</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.38</v>
@@ -5320,49 +5320,49 @@
         <v>2.03</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="DH11" t="n">
-        <v>94.78</v>
+        <v>95.87</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DM11" t="n">
-        <v>43.36</v>
+        <v>44.14</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DP11" t="n">
-        <v>17.72</v>
+        <v>17.8</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.07</v>
+        <v>8.94</v>
       </c>
       <c r="DR11" t="n">
-        <v>8</v>
+        <v>8.07</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>38.14</v>
+        <v>38.13</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.07</v>
+        <v>13.6</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.789999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.28</v>
+        <v>4.53</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.07</v>
+        <v>19.87</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="12">
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5498,49 +5498,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="AI12" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>39.43</v>
+        <v>36.75</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.71</v>
+        <v>16.12</v>
       </c>
       <c r="AR12" t="n">
         <v>10</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.86</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5552,82 +5552,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>43.14</v>
+        <v>41.88</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.14</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.29</v>
+        <v>6.88</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>20.29</v>
+        <v>20.62</v>
       </c>
       <c r="BE12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN12" t="n">
         <v>1.13</v>
       </c>
-      <c r="BF12" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BO12" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="BQ12" t="n">
         <v>6.07</v>
       </c>
       <c r="BR12" t="n">
-        <v>92.86</v>
+        <v>86.67</v>
       </c>
       <c r="BS12" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT12" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU12" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV12" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY12" t="n">
         <v>3.61</v>
@@ -5639,133 +5639,133 @@
         <v>3.58</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.12</v>
+        <v>3.26</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="CH12" t="n">
         <v>1.44</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CK12" t="n">
         <v>1.53</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="CR12" t="n">
         <v>1.4</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CX12" t="n">
         <v>1.54</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB12" t="n">
         <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="DH12" t="n">
-        <v>90.06999999999999</v>
+        <v>88.87</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.43</v>
+        <v>5.27</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DM12" t="n">
-        <v>43.86</v>
+        <v>42.14</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.86</v>
+        <v>15.13</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.64</v>
+        <v>12.47</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.58</v>
+        <v>7.73</v>
       </c>
       <c r="DS12" t="n">
         <v>0.07000000000000001</v>
@@ -5777,28 +5777,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46</v>
+        <v>45.14</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.86</v>
+        <v>11.34</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.859999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.07</v>
+        <v>20.27</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="13">
@@ -5808,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5901,49 +5901,49 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AI13" t="n">
-        <v>85.70999999999999</v>
+        <v>84.25</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.86</v>
+        <v>4.38</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN13" t="n">
-        <v>35.29</v>
+        <v>35.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14.43</v>
+        <v>14.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.71</v>
+        <v>13.38</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.710000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5955,82 +5955,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>46.71</v>
+        <v>46</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.43</v>
+        <v>11</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.57</v>
+        <v>6.38</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.86</v>
+        <v>4.62</v>
       </c>
       <c r="BD13" t="n">
-        <v>18.71</v>
+        <v>18.38</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.21</v>
+        <v>3.13</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.640000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.21</v>
+        <v>3.13</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BN13" t="n">
         <v>2.07</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.21</v>
+        <v>4.93</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU13" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BV13" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX13" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY13" t="n">
         <v>3.4</v>
@@ -6039,46 +6039,46 @@
         <v>3.7</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.16</v>
+        <v>4.11</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.18</v>
+        <v>4.96</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.65</v>
+        <v>5.44</v>
       </c>
       <c r="CE13" t="n">
         <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CK13" t="n">
         <v>1.47</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CO13" t="n">
         <v>1.21</v>
@@ -6087,25 +6087,25 @@
         <v>1.72</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CR13" t="n">
         <v>1.37</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX13" t="n">
         <v>1.51</v>
@@ -6117,58 +6117,58 @@
         <v>2.44</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB13" t="n">
         <v>1.22</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="DH13" t="n">
-        <v>85.14</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.78</v>
+        <v>2.93</v>
       </c>
       <c r="DK13" t="n">
-        <v>5</v>
+        <v>4.73</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="DM13" t="n">
-        <v>41.72</v>
+        <v>41.4</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.57</v>
+        <v>13.66</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.42</v>
+        <v>13.27</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.57</v>
+        <v>8.4</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6180,28 +6180,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.36</v>
+        <v>48.8</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.78</v>
+        <v>11.53</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.71</v>
+        <v>7.54</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.36</v>
+        <v>21</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="14">
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
@@ -6223,82 +6223,82 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="G14" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>90.70999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.29</v>
+        <v>-0.25</v>
       </c>
       <c r="J14" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="K14" t="n">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
       <c r="L14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M14" t="n">
-        <v>33.14</v>
+        <v>35.12</v>
       </c>
       <c r="N14" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="O14" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="P14" t="n">
-        <v>13.71</v>
+        <v>13.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.57</v>
+        <v>14.25</v>
       </c>
       <c r="R14" t="n">
-        <v>9.57</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="U14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>46.43</v>
+        <v>49</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z14" t="n">
-        <v>12.29</v>
+        <v>11.88</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.86</v>
+        <v>7.62</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>22.43</v>
+        <v>23.62</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6382,67 +6382,67 @@
         <v>3</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.57</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.64</v>
+        <v>4.47</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="BR14" t="n">
-        <v>92.86</v>
+        <v>86.67</v>
       </c>
       <c r="BS14" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BT14" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BU14" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV14" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.98</v>
+        <v>2.83</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.01</v>
+        <v>2.85</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CB14" t="n">
         <v>3.88</v>
@@ -6454,31 +6454,31 @@
         <v>5.84</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK14" t="n">
         <v>1.61</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN14" t="n">
         <v>1.76</v>
@@ -6487,31 +6487,31 @@
         <v>1.28</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.16</v>
+        <v>3.21</v>
       </c>
       <c r="CR14" t="n">
         <v>1.41</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CU14" t="n">
         <v>1.44</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY14" t="n">
         <v>2.02</v>
@@ -6523,88 +6523,88 @@
         <v>1.79</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC14" t="n">
         <v>1.98</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="DG14" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DH14" t="n">
-        <v>85.84999999999999</v>
+        <v>87.67</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.43</v>
+        <v>4.47</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DM14" t="n">
-        <v>34.07</v>
+        <v>35.06</v>
       </c>
       <c r="DN14" t="n">
         <v>1</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.71</v>
+        <v>14.4</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.07</v>
+        <v>14.4</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.640000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47.57</v>
+        <v>48.86</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.22</v>
+        <v>10.13</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.72</v>
+        <v>6.66</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="EA14" t="n">
-        <v>21</v>
+        <v>21.73</v>
       </c>
       <c r="EB14" t="n">
         <v>1.14</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="15">
@@ -6614,10 +6614,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -6626,82 +6626,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="G15" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="H15" t="n">
-        <v>104.71</v>
+        <v>104.38</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>6.62</v>
       </c>
       <c r="L15" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="M15" t="n">
-        <v>52.14</v>
+        <v>49.62</v>
       </c>
       <c r="N15" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O15" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>13.71</v>
+        <v>12.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>11.88</v>
       </c>
       <c r="R15" t="n">
-        <v>7.43</v>
+        <v>7.88</v>
       </c>
       <c r="S15" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="U15" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="V15" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>15.71</v>
+        <v>15.12</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.29</v>
+        <v>10.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>22.29</v>
+        <v>21.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AF15" t="n">
         <v>0.14</v>
@@ -6785,70 +6785,70 @@
         <v>1.71</v>
       </c>
       <c r="BG15" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.93</v>
+        <v>10.6</v>
       </c>
       <c r="BI15" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.64</v>
+        <v>4.53</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.29</v>
+        <v>6.07</v>
       </c>
       <c r="BR15" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS15" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT15" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU15" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="CC15" t="n">
         <v>4.59</v>
@@ -6860,25 +6860,25 @@
         <v>1.36</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CH15" t="n">
         <v>1.45</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK15" t="n">
         <v>1.52</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CM15" t="n">
         <v>2.41</v>
@@ -6893,7 +6893,7 @@
         <v>1.86</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
@@ -6908,10 +6908,10 @@
         <v>1.47</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX15" t="n">
         <v>1.54</v>
@@ -6938,76 +6938,76 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="DH15" t="n">
-        <v>97.5</v>
+        <v>97.8</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.14</v>
+        <v>6</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DM15" t="n">
-        <v>45.92</v>
+        <v>45</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.21</v>
+        <v>11.87</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.22</v>
+        <v>13.07</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.359999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>53.22</v>
+        <v>52.87</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.28</v>
+        <v>14.07</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.859999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.79</v>
+        <v>20.34</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0.12</v>
@@ -7107,16 +7107,16 @@
         <v>2.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AI16" t="n">
-        <v>77</v>
+        <v>78.14</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
@@ -7125,34 +7125,34 @@
         <v>3</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN16" t="n">
-        <v>26.5</v>
+        <v>27.71</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ16" t="n">
-        <v>14.5</v>
+        <v>14.14</v>
       </c>
       <c r="AR16" t="n">
-        <v>12.83</v>
+        <v>12</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.67</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7164,82 +7164,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>44.67</v>
+        <v>45.71</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.5</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.33</v>
+        <v>6.57</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="BD16" t="n">
-        <v>15</v>
+        <v>15.29</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BF16" t="n">
         <v>3</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.5</v>
+        <v>8.33</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.36</v>
+        <v>4.27</v>
       </c>
       <c r="BR16" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS16" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU16" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV16" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW16" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX16" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY16" t="n">
         <v>2.46</v>
@@ -7248,16 +7248,16 @@
         <v>2.64</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="CC16" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="CD16" t="n">
         <v>4.54</v>
-      </c>
-      <c r="CD16" t="n">
-        <v>4.88</v>
       </c>
       <c r="CE16" t="n">
         <v>1.34</v>
@@ -7266,7 +7266,7 @@
         <v>2.55</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CH16" t="n">
         <v>1.49</v>
@@ -7275,7 +7275,7 @@
         <v>2.11</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CK16" t="n">
         <v>1.56</v>
@@ -7296,34 +7296,34 @@
         <v>1.82</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="CR16" t="n">
         <v>1.38</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CU16" t="n">
         <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CX16" t="n">
         <v>1.58</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DA16" t="n">
         <v>1.85</v>
@@ -7335,82 +7335,82 @@
         <v>1.83</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DH16" t="n">
-        <v>84.70999999999999</v>
+        <v>84.73</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.43</v>
+        <v>3.34</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM16" t="n">
-        <v>36.43</v>
+        <v>36.33</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.72</v>
+        <v>14.53</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.5</v>
+        <v>12.13</v>
       </c>
       <c r="DR16" t="n">
+        <v>9</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>12</v>
+      </c>
+      <c r="DY16" t="n">
         <v>8.93</v>
-      </c>
-      <c r="DS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV16" t="n">
-        <v>49.93</v>
-      </c>
-      <c r="DW16" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DX16" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="DY16" t="n">
-        <v>9</v>
       </c>
       <c r="DZ16" t="n">
         <v>3.07</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.57</v>
+        <v>17.54</v>
       </c>
       <c r="EB16" t="n">
         <v>1.24</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="17">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7913,139 +7913,139 @@
         <v>1.38</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AI18" t="n">
-        <v>75.83</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.17</v>
+        <v>2.57</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AN18" t="n">
-        <v>31.33</v>
+        <v>29.86</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12</v>
+        <v>11.29</v>
       </c>
       <c r="AR18" t="n">
-        <v>16.17</v>
+        <v>16.57</v>
       </c>
       <c r="AS18" t="n">
-        <v>10.5</v>
+        <v>10.43</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>48.33</v>
+        <v>50.29</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BA18" t="n">
-        <v>12.17</v>
+        <v>13</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.83</v>
+        <v>7.57</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.33</v>
+        <v>5.43</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.17</v>
+        <v>17.14</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.210000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.29</v>
+        <v>4.33</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.93</v>
+        <v>5</v>
       </c>
       <c r="BR18" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS18" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT18" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU18" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV18" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW18" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX18" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY18" t="n">
         <v>1.63</v>
@@ -8054,31 +8054,31 @@
         <v>1.62</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="CD18" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CH18" t="n">
         <v>1.49</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.73</v>
@@ -8087,10 +8087,10 @@
         <v>1.53</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CN18" t="n">
         <v>1.85</v>
@@ -8099,22 +8099,22 @@
         <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV18" t="n">
         <v>2.17</v>
@@ -8129,94 +8129,94 @@
         <v>1.92</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB18" t="n">
         <v>1.24</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="DE18" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="DH18" t="n">
-        <v>89.5</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="DK18" t="n">
         <v>4.07</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DM18" t="n">
-        <v>37.14</v>
+        <v>36.07</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.35</v>
+        <v>12</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.85</v>
+        <v>8.93</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>51.43</v>
+        <v>52.14</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DX18" t="n">
-        <v>15.07</v>
+        <v>15.27</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.57</v>
+        <v>9.73</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.29</v>
+        <v>19.13</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="19">
@@ -8226,10 +8226,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
@@ -8241,79 +8241,79 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>2.67</v>
+        <v>3.29</v>
       </c>
       <c r="H19" t="n">
-        <v>76.67</v>
+        <v>79.14</v>
       </c>
       <c r="I19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J19" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="K19" t="n">
-        <v>4.33</v>
+        <v>5.14</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="M19" t="n">
-        <v>40.83</v>
+        <v>41.57</v>
       </c>
       <c r="N19" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="O19" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="P19" t="n">
-        <v>16.17</v>
+        <v>15</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.5</v>
+        <v>12.57</v>
       </c>
       <c r="R19" t="n">
-        <v>8</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T19" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="U19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>50.17</v>
+        <v>50.43</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.33</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.5</v>
+        <v>17.71</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8397,67 +8397,67 @@
         <v>2.38</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.07</v>
+        <v>11.53</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BM19" t="n">
         <v>1</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO19" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="BR19" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS19" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV19" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX19" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.44</v>
+        <v>2.74</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="CB19" t="n">
         <v>3.59</v>
@@ -8469,19 +8469,19 @@
         <v>3.01</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF19" t="n">
         <v>2.69</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.73</v>
@@ -8490,7 +8490,7 @@
         <v>1.56</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CM19" t="n">
         <v>2.3</v>
@@ -8502,28 +8502,28 @@
         <v>1.24</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="CR19" t="n">
         <v>1.39</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CU19" t="n">
         <v>1.46</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CX19" t="n">
         <v>1.55</v>
@@ -8538,55 +8538,55 @@
         <v>1.86</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.93</v>
+        <v>3.2</v>
       </c>
       <c r="DH19" t="n">
-        <v>91.78</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.43</v>
+        <v>5.73</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DM19" t="n">
-        <v>44.29</v>
+        <v>44.4</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.5</v>
+        <v>13.13</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.07</v>
+        <v>14</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.07</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DS19" t="n">
         <v>0.14</v>
@@ -8598,28 +8598,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.86</v>
+        <v>55.6</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.36</v>
+        <v>12.74</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.35</v>
+        <v>8.73</v>
       </c>
       <c r="DZ19" t="n">
         <v>4</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.15</v>
+        <v>17.27</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
@@ -1394,79 +1394,79 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="H2" t="n">
-        <v>94.5</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>6.43</v>
       </c>
       <c r="L2" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="M2" t="n">
-        <v>45.83</v>
+        <v>47.57</v>
       </c>
       <c r="N2" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O2" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>11.17</v>
+        <v>12.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.83</v>
+        <v>15.43</v>
       </c>
       <c r="R2" t="n">
-        <v>6.33</v>
+        <v>5.71</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="T2" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="U2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>51.33</v>
+        <v>51.71</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.33</v>
+        <v>12.71</v>
       </c>
       <c r="AA2" t="n">
-        <v>9</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.83</v>
+        <v>18.43</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,49 +1550,49 @@
         <v>2.38</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.07</v>
+        <v>8.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.14</v>
+        <v>3.53</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.93</v>
+        <v>4.87</v>
       </c>
       <c r="BR2" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS2" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU2" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,19 +1601,19 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.27</v>
+        <v>3.05</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CC2" t="n">
         <v>4.21</v>
@@ -1622,19 +1622,19 @@
         <v>5.1</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CH2" t="n">
         <v>1.45</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.75</v>
@@ -1673,19 +1673,19 @@
         <v>1.45</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DA2" t="n">
         <v>1.65</v>
@@ -1697,82 +1697,82 @@
         <v>1.91</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="DH2" t="n">
-        <v>84.20999999999999</v>
+        <v>85.33</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.35</v>
+        <v>4.66</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DM2" t="n">
-        <v>38.72</v>
+        <v>40</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="DP2" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="DQ2" t="n">
-        <v>16.21</v>
+        <v>16.4</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.35</v>
+        <v>7</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47.5</v>
+        <v>47.93</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.28</v>
+        <v>12.06</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.43</v>
+        <v>8.33</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.86</v>
+        <v>3.73</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.85</v>
+        <v>19.06</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,49 +1875,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AI3" t="n">
-        <v>64.14</v>
+        <v>65.12</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN3" t="n">
-        <v>24</v>
+        <v>23.62</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.14</v>
+        <v>12.12</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.57</v>
+        <v>12.38</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.43</v>
+        <v>11.38</v>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>40.86</v>
+        <v>41.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.14</v>
+        <v>6.12</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="BD3" t="n">
-        <v>20</v>
+        <v>19.88</v>
       </c>
       <c r="BE3" t="n">
         <v>0.76</v>
       </c>
       <c r="BF3" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.140000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.71</v>
+        <v>5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="BR3" t="n">
-        <v>92.86</v>
+        <v>86.67</v>
       </c>
       <c r="BS3" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU3" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX3" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY3" t="n">
         <v>3.01</v>
@@ -2013,16 +2013,16 @@
         <v>3.33</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.59</v>
+        <v>5.47</v>
       </c>
       <c r="CD3" t="n">
-        <v>6.09</v>
+        <v>5.97</v>
       </c>
       <c r="CE3" t="n">
         <v>1.38</v>
@@ -2031,28 +2031,28 @@
         <v>2.82</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CH3" t="n">
         <v>1.41</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.85</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL3" t="n">
         <v>2.08</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO3" t="n">
         <v>1.28</v>
@@ -2061,7 +2061,7 @@
         <v>1.92</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CR3" t="n">
         <v>1.42</v>
@@ -2082,16 +2082,16 @@
         <v>1.88</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="DB3" t="n">
         <v>1.32</v>
@@ -2106,43 +2106,43 @@
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DH3" t="n">
-        <v>71.36</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="DI3" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="DM3" t="n">
-        <v>28.64</v>
+        <v>28.13</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DO3" t="n">
         <v>2</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.5</v>
+        <v>14.74</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.43</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.28</v>
+        <v>43.46</v>
       </c>
       <c r="DW3" t="n">
         <v>0.14</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.42</v>
+        <v>8.26</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.78</v>
+        <v>4.67</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="EA3" t="n">
         <v>19.07</v>
       </c>
       <c r="EB3" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="G4" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>86.33</v>
+        <v>91</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>6.14</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>42.17</v>
+        <v>45.43</v>
       </c>
       <c r="N4" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>13.83</v>
+        <v>14.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.83</v>
+        <v>12.86</v>
       </c>
       <c r="R4" t="n">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="T4" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>50.67</v>
+        <v>51.71</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.33</v>
+        <v>16.43</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.33</v>
+        <v>10.29</v>
       </c>
       <c r="AB4" t="n">
-        <v>5</v>
+        <v>6.14</v>
       </c>
       <c r="AC4" t="n">
-        <v>15.83</v>
+        <v>15.71</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
         <v>0.25</v>
@@ -2356,37 +2356,37 @@
         <v>2.25</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.36</v>
+        <v>10.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.29</v>
+        <v>5.13</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -2395,31 +2395,31 @@
         <v>100</v>
       </c>
       <c r="BT4" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BU4" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BV4" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.12</v>
+        <v>4.18</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.29</v>
+        <v>4.36</v>
       </c>
       <c r="CC4" t="n">
         <v>2.4</v>
@@ -2428,16 +2428,16 @@
         <v>2.3</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CI4" t="n">
         <v>2.2</v>
@@ -2449,7 +2449,7 @@
         <v>1.5</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CM4" t="n">
         <v>2.41</v>
@@ -2461,22 +2461,22 @@
         <v>1.18</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="CT4" t="n">
         <v>3.32</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CV4" t="n">
         <v>2.32</v>
@@ -2497,55 +2497,55 @@
         <v>1.92</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.36</v>
+        <v>2.67</v>
       </c>
       <c r="DH4" t="n">
-        <v>86.64</v>
+        <v>88.8</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.15</v>
+        <v>5.47</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DM4" t="n">
-        <v>40.86</v>
+        <v>42.47</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.14</v>
+        <v>14.6</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12</v>
+        <v>12.07</v>
       </c>
       <c r="DR4" t="n">
-        <v>8</v>
+        <v>7.73</v>
       </c>
       <c r="DS4" t="n">
         <v>0.14</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>53.08</v>
+        <v>53.4</v>
       </c>
       <c r="DW4" t="n">
         <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>14.78</v>
+        <v>15.73</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.279999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="EA4" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="EC4" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="5">
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>63.88</v>
+        <v>64</v>
       </c>
       <c r="Y8" t="n">
         <v>0.25</v>
@@ -4165,7 +4165,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>61.4</v>
+        <v>61.47</v>
       </c>
       <c r="DW8" t="n">
         <v>0.13</v>
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>0.25</v>
@@ -4286,139 +4286,139 @@
         <v>2.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AI9" t="n">
-        <v>64.33</v>
+        <v>64.86</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AN9" t="n">
-        <v>30.83</v>
+        <v>29.71</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.17</v>
+        <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>14.67</v>
+        <v>15.57</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>47.5</v>
+        <v>46.71</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>11</v>
+        <v>10.71</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="BD9" t="n">
-        <v>15.33</v>
+        <v>15.57</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.640000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK9" t="n">
         <v>1.07</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.21</v>
+        <v>4.13</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.43</v>
+        <v>5.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS9" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT9" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BU9" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BV9" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY9" t="n">
         <v>3.05</v>
@@ -4427,34 +4427,34 @@
         <v>3.2</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.62</v>
+        <v>3.71</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.68</v>
+        <v>3.79</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.47</v>
+        <v>3.92</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.69</v>
+        <v>4.23</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CK9" t="n">
         <v>1.54</v>
@@ -4463,34 +4463,34 @@
         <v>2.08</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO9" t="n">
         <v>1.23</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="CT9" t="n">
         <v>3.22</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CW9" t="n">
         <v>1.69</v>
@@ -4508,88 +4508,88 @@
         <v>1.88</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.42</v>
+        <v>3.26</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.43000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.43</v>
+        <v>5.13</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM9" t="n">
-        <v>37.78</v>
+        <v>36.8</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DO9" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.22</v>
+        <v>13.2</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16</v>
+        <v>16.33</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.71</v>
+        <v>7.87</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>54.43</v>
+        <v>53.6</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.14</v>
+        <v>13.8</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.359999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.78</v>
+        <v>4.73</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.5</v>
+        <v>17.46</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.72</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="10">
@@ -7567,7 +7567,7 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>43.43</v>
+        <v>43.29</v>
       </c>
       <c r="AZ17" t="n">
         <v>0.14</v>
@@ -7792,7 +7792,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.34</v>
+        <v>50.27</v>
       </c>
       <c r="DW17" t="n">
         <v>0.13</v>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>51.71</v>
+        <v>51.86</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47.93</v>
+        <v>48</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>41.5</v>
+        <v>41.38</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.46</v>
+        <v>43.4</v>
       </c>
       <c r="DW3" t="n">
         <v>0.14</v>
@@ -2260,16 +2260,16 @@
         <v>16.43</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.29</v>
+        <v>10.43</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.14</v>
+        <v>6</v>
       </c>
       <c r="AC4" t="n">
         <v>15.71</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -2566,16 +2566,16 @@
         <v>15.73</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.74</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6</v>
+        <v>5.94</v>
       </c>
       <c r="EA4" t="n">
         <v>17.8</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="EC4" t="n">
         <v>2.13</v>
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4689,139 +4689,139 @@
         <v>1.71</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG10" t="n">
         <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" t="n">
-        <v>60.62</v>
+        <v>64.89</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AL10" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN10" t="n">
-        <v>26.12</v>
+        <v>26.33</v>
       </c>
       <c r="AO10" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ10" t="n">
         <v>0.5</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="BK10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN10" t="n">
         <v>1.38</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>13.12</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>15.38</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>38.38</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>18.38</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1.47</v>
-      </c>
       <c r="BO10" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.73</v>
+        <v>4.56</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR10" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="BS10" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU10" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV10" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY10" t="n">
         <v>3.35</v>
@@ -4830,25 +4830,25 @@
         <v>3.45</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="CC10" t="n">
-        <v>6.05</v>
+        <v>5.7</v>
       </c>
       <c r="CD10" t="n">
-        <v>7.24</v>
+        <v>6.75</v>
       </c>
       <c r="CE10" t="n">
         <v>1.35</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="CH10" t="n">
         <v>1.44</v>
@@ -4866,7 +4866,7 @@
         <v>1.98</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN10" t="n">
         <v>1.78</v>
@@ -4875,10 +4875,10 @@
         <v>1.26</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="CR10" t="n">
         <v>1.41</v>
@@ -4893,22 +4893,22 @@
         <v>1.44</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CX10" t="n">
         <v>1.6</v>
       </c>
       <c r="CY10" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="DB10" t="n">
         <v>1.29</v>
@@ -4923,76 +4923,76 @@
         <v>0.06</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DH10" t="n">
-        <v>65.13</v>
+        <v>67.25</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.07</v>
+        <v>3.94</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM10" t="n">
-        <v>28.46</v>
+        <v>28.43</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="DP10" t="n">
-        <v>13</v>
+        <v>13.19</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.13</v>
+        <v>14</v>
       </c>
       <c r="DR10" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>39.93</v>
+        <v>40.62</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.67</v>
+        <v>10.38</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.27</v>
+        <v>7.13</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="EA10" t="n">
-        <v>18</v>
+        <v>18.13</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="11">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
@@ -5417,82 +5417,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="G12" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="H12" t="n">
-        <v>92.14</v>
+        <v>90.12</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="K12" t="n">
-        <v>6.29</v>
+        <v>5.88</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="M12" t="n">
-        <v>48.29</v>
+        <v>46.25</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="O12" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>15.29</v>
+        <v>15.38</v>
       </c>
       <c r="R12" t="n">
-        <v>7.29</v>
+        <v>6.75</v>
       </c>
       <c r="S12" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="U12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>48.86</v>
+        <v>48.88</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.57</v>
+        <v>13.12</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.43</v>
+        <v>10</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.86</v>
+        <v>19.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5576,70 +5576,70 @@
         <v>2.25</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.869999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.8</v>
+        <v>3.69</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.07</v>
+        <v>5.88</v>
       </c>
       <c r="BR12" t="n">
-        <v>86.67</v>
+        <v>81.25</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BT12" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV12" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY12" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="CB12" t="n">
         <v>3.61</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="CB12" t="n">
-        <v>3.63</v>
       </c>
       <c r="CC12" t="n">
         <v>3.26</v>
@@ -5651,28 +5651,28 @@
         <v>1.36</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI12" t="n">
         <v>2.06</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL12" t="n">
         <v>2.01</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN12" t="n">
         <v>1.87</v>
@@ -5681,10 +5681,10 @@
         <v>1.26</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="CR12" t="n">
         <v>1.4</v>
@@ -5699,22 +5699,22 @@
         <v>1.44</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CY12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="DA12" t="n">
         <v>1.89</v>
-      </c>
-      <c r="CZ12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="DA12" t="n">
-        <v>1.91</v>
       </c>
       <c r="DB12" t="n">
         <v>1.29</v>
@@ -5729,76 +5729,76 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="DH12" t="n">
-        <v>88.87</v>
+        <v>88.06</v>
       </c>
       <c r="DI12" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.27</v>
+        <v>5.13</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM12" t="n">
-        <v>42.14</v>
+        <v>41.5</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.13</v>
+        <v>14.94</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.47</v>
+        <v>12.69</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.73</v>
+        <v>7.44</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.14</v>
+        <v>45.38</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.34</v>
+        <v>11.25</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.539999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.27</v>
+        <v>20</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="13">

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1472,127 +1472,127 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AH2" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AI2" t="n">
-        <v>76.5</v>
+        <v>79.22</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.12</v>
+        <v>3.67</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="AN2" t="n">
-        <v>33.38</v>
+        <v>36.78</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.12</v>
+        <v>1.56</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.62</v>
+        <v>12.56</v>
       </c>
       <c r="AR2" t="n">
-        <v>17.25</v>
+        <v>16.33</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.119999999999999</v>
+        <v>7.67</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>44.62</v>
+        <v>46.22</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.5</v>
+        <v>11.78</v>
       </c>
       <c r="BB2" t="n">
-        <v>8</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="BD2" t="n">
-        <v>19.62</v>
+        <v>20.11</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.4</v>
+        <v>8.56</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.53</v>
+        <v>3.69</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.87</v>
+        <v>4.88</v>
       </c>
       <c r="BR2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BU2" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
         <v>3.05</v>
@@ -1610,22 +1610,22 @@
         <v>3.1</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CC2" t="n">
-        <v>4.21</v>
+        <v>4.03</v>
       </c>
       <c r="CD2" t="n">
-        <v>5.1</v>
+        <v>4.82</v>
       </c>
       <c r="CE2" t="n">
         <v>1.36</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CG2" t="n">
         <v>2.95</v>
@@ -1634,28 +1634,28 @@
         <v>1.45</v>
       </c>
       <c r="CI2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CO2" t="n">
         <v>1.25</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CQ2" t="n">
         <v>3.04</v>
@@ -1664,28 +1664,28 @@
         <v>1.4</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CU2" t="n">
         <v>1.45</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DA2" t="n">
         <v>1.65</v>
@@ -1694,85 +1694,85 @@
         <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="DH2" t="n">
-        <v>85.33</v>
+        <v>86.31</v>
       </c>
       <c r="DI2" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.66</v>
+        <v>4.88</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="DM2" t="n">
-        <v>40</v>
+        <v>41.5</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DO2" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.4</v>
+        <v>12.38</v>
       </c>
       <c r="DQ2" t="n">
-        <v>16.4</v>
+        <v>15.94</v>
       </c>
       <c r="DR2" t="n">
-        <v>7</v>
+        <v>6.81</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>48</v>
+        <v>48.69</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.06</v>
+        <v>12.19</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.33</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.73</v>
+        <v>3.81</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.06</v>
+        <v>19.38</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="H3" t="n">
-        <v>78.56999999999999</v>
+        <v>79.12</v>
       </c>
       <c r="I3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M3" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="O3" t="n">
         <v>2</v>
       </c>
-      <c r="K3" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="M3" t="n">
-        <v>33.29</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.14</v>
-      </c>
       <c r="P3" t="n">
-        <v>11.86</v>
+        <v>11.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>17.43</v>
+        <v>17</v>
       </c>
       <c r="R3" t="n">
-        <v>7.43</v>
+        <v>7.75</v>
       </c>
       <c r="S3" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="T3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>45.71</v>
+        <v>44.62</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.71</v>
+        <v>10.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.14</v>
+        <v>6.38</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.14</v>
+        <v>18.38</v>
       </c>
       <c r="AD3" t="n">
         <v>1.24</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>2.75</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.4</v>
+        <v>9.31</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="BM3" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BP3" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.4</v>
+        <v>4.44</v>
       </c>
       <c r="BR3" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT3" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU3" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BV3" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX3" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.01</v>
+        <v>3.45</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.33</v>
+        <v>3.84</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.74</v>
+        <v>3.82</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.85</v>
+        <v>3.96</v>
       </c>
       <c r="CC3" t="n">
         <v>5.47</v>
@@ -2025,124 +2025,124 @@
         <v>5.97</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="CR3" t="n">
         <v>1.42</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="CT3" t="n">
         <v>2.98</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="CV3" t="n">
         <v>2</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.47</v>
+        <v>3.39</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DG3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>72.12</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>4</v>
+      </c>
+      <c r="DL3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DO3" t="n">
         <v>1.94</v>
       </c>
-      <c r="DH3" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="DI3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DJ3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="DK3" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="DL3" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DM3" t="n">
-        <v>28.13</v>
-      </c>
-      <c r="DN3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="DO3" t="n">
-        <v>2</v>
-      </c>
       <c r="DP3" t="n">
-        <v>12</v>
+        <v>11.75</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.74</v>
+        <v>14.69</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.539999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.4</v>
+        <v>43</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.26</v>
+        <v>8.44</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.67</v>
+        <v>4.88</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.07</v>
+        <v>19.13</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0.43</v>
@@ -2275,118 +2275,118 @@
         <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AI4" t="n">
-        <v>86.88</v>
+        <v>81.44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.25</v>
+        <v>2.78</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.88</v>
+        <v>4.44</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AN4" t="n">
-        <v>39.88</v>
+        <v>36.44</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.38</v>
+        <v>13.67</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.38</v>
+        <v>10.89</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.25</v>
+        <v>10.11</v>
       </c>
       <c r="AT4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BK4" t="n">
         <v>1</v>
       </c>
-      <c r="AU4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>54.88</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>19.62</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.87</v>
-      </c>
       <c r="BL4" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.13</v>
+        <v>4.94</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -2395,19 +2395,19 @@
         <v>100</v>
       </c>
       <c r="BT4" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BV4" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BX4" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BY4" t="n">
         <v>1.71</v>
@@ -2416,31 +2416,31 @@
         <v>1.8</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.18</v>
+        <v>4.13</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.36</v>
+        <v>4.3</v>
       </c>
       <c r="CC4" t="n">
         <v>2.4</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF4" t="n">
         <v>2.34</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="CH4" t="n">
         <v>1.54</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.64</v>
@@ -2455,22 +2455,22 @@
         <v>2.41</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO4" t="n">
         <v>1.18</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CT4" t="n">
         <v>3.32</v>
@@ -2479,10 +2479,10 @@
         <v>1.57</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CX4" t="n">
         <v>1.53</v>
@@ -2500,85 +2500,85 @@
         <v>1.2</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.8</v>
+        <v>85.62</v>
       </c>
       <c r="DI4" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.47</v>
+        <v>5.18</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DM4" t="n">
-        <v>42.47</v>
+        <v>40.37</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.66</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.6</v>
+        <v>14.19</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.07</v>
+        <v>11.75</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.73</v>
+        <v>8.31</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>53.4</v>
+        <v>51.56</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="DX4" t="n">
-        <v>15.73</v>
+        <v>15.31</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.94</v>
+        <v>5.88</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.8</v>
+        <v>17.56</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0.12</v>
@@ -2678,139 +2678,139 @@
         <v>2.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>76</v>
+        <v>75.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AN5" t="n">
-        <v>34.43</v>
+        <v>33.62</v>
       </c>
       <c r="AO5" t="n">
         <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.57</v>
+        <v>13.88</v>
       </c>
       <c r="AR5" t="n">
-        <v>17.14</v>
+        <v>17.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.71</v>
+        <v>7.38</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>48.14</v>
+        <v>49</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>12</v>
+        <v>11.38</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.43</v>
+        <v>8.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.57</v>
+        <v>3.12</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.29</v>
+        <v>17.62</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.6</v>
+        <v>10.31</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.47</v>
+        <v>4.44</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.07</v>
+        <v>5.81</v>
       </c>
       <c r="BR5" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS5" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BU5" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BV5" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY5" t="n">
         <v>2.99</v>
@@ -2825,40 +2825,40 @@
         <v>3.77</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CH5" t="n">
         <v>1.44</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.74</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO5" t="n">
         <v>1.26</v>
@@ -2867,7 +2867,7 @@
         <v>1.85</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CR5" t="n">
         <v>1.39</v>
@@ -2876,25 +2876,25 @@
         <v>2.79</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="CU5" t="n">
         <v>1.48</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="DA5" t="n">
         <v>1.86</v>
@@ -2903,85 +2903,85 @@
         <v>1.27</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="DH5" t="n">
-        <v>77.47</v>
+        <v>77.12</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.27</v>
+        <v>4.19</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DM5" t="n">
-        <v>37.87</v>
+        <v>37.25</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.93</v>
+        <v>12.19</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.47</v>
+        <v>15.75</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.46</v>
+        <v>7.32</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.13</v>
+        <v>51.38</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.06</v>
+        <v>11.75</v>
       </c>
       <c r="DY5" t="n">
-        <v>8</v>
+        <v>7.94</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.07</v>
+        <v>3.81</v>
       </c>
       <c r="EA5" t="n">
-        <v>18</v>
+        <v>18.12</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
@@ -3003,13 +3003,13 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="G6" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="H6" t="n">
-        <v>95</v>
+        <v>93.11</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3018,64 +3018,64 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="L6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M6" t="n">
-        <v>36.25</v>
+        <v>35.44</v>
       </c>
       <c r="N6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="n">
-        <v>0.88</v>
-      </c>
       <c r="P6" t="n">
-        <v>14.88</v>
+        <v>14.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.12</v>
+        <v>14.78</v>
       </c>
       <c r="R6" t="n">
-        <v>8</v>
+        <v>8.44</v>
       </c>
       <c r="S6" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="T6" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="U6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>50.12</v>
+        <v>48.44</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.5</v>
+        <v>10.22</v>
       </c>
       <c r="AA6" t="n">
-        <v>8</v>
+        <v>7.78</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.38</v>
+        <v>20.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -3162,70 +3162,70 @@
         <v>2.29</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.93</v>
+        <v>9.81</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.67</v>
+        <v>4.69</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.27</v>
+        <v>5.12</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU6" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV6" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX6" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.24</v>
+        <v>4.18</v>
       </c>
       <c r="CC6" t="n">
         <v>6.8</v>
@@ -3234,31 +3234,31 @@
         <v>7.42</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CN6" t="n">
         <v>1.78</v>
@@ -3267,91 +3267,91 @@
         <v>1.24</v>
       </c>
       <c r="CP6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CW6" t="n">
         <v>1.82</v>
       </c>
-      <c r="CQ6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>1.8</v>
-      </c>
       <c r="CX6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.12</v>
+        <v>3.21</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.73</v>
+        <v>88.06</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.87</v>
+        <v>3.75</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM6" t="n">
-        <v>36.93</v>
+        <v>36.43</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.2</v>
+        <v>14.25</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.46</v>
+        <v>14.31</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.4</v>
+        <v>9.56</v>
       </c>
       <c r="DS6" t="n">
         <v>0.06</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47.67</v>
+        <v>46.87</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX6" t="n">
-        <v>11</v>
+        <v>10.81</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.27</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.6</v>
+        <v>20.56</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="7">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0.25</v>
@@ -3887,139 +3887,139 @@
         <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AI8" t="n">
-        <v>89.70999999999999</v>
+        <v>92</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AN8" t="n">
-        <v>45.57</v>
+        <v>44.75</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.14</v>
+        <v>13.25</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.57</v>
+        <v>11.12</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>58.57</v>
+        <v>59.12</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.71</v>
+        <v>13.62</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.710000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.86</v>
+        <v>17.25</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.67</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.87</v>
+        <v>3.81</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
       <c r="BR8" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS8" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT8" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BV8" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY8" t="n">
         <v>1.3</v>
@@ -4028,28 +4028,28 @@
         <v>1.34</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.37</v>
+        <v>5.35</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.69</v>
+        <v>5.68</v>
       </c>
       <c r="CC8" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="CD8" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="CE8" t="n">
         <v>1.23</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CG8" t="n">
         <v>3.77</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CI8" t="n">
         <v>2.06</v>
@@ -4067,7 +4067,7 @@
         <v>2.47</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CO8" t="n">
         <v>1.13</v>
@@ -4076,18 +4076,18 @@
         <v>1.46</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="n">
         <v>1.73</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CW8" t="n">
         <v>1.76</v>
@@ -4096,7 +4096,7 @@
         <v>1.51</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.48</v>
@@ -4111,19 +4111,19 @@
         <v>1.48</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="DH8" t="n">
-        <v>94.33</v>
+        <v>95.19</v>
       </c>
       <c r="DI8" t="n">
         <v>0.06</v>
@@ -4132,61 +4132,61 @@
         <v>2</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.73</v>
+        <v>4.62</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DM8" t="n">
-        <v>51</v>
+        <v>50.25</v>
       </c>
       <c r="DN8" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.87</v>
+        <v>12</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.8</v>
+        <v>10.62</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.93</v>
+        <v>7.75</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>61.47</v>
+        <v>61.56</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX8" t="n">
-        <v>17.2</v>
+        <v>16.93</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.06</v>
+        <v>10.81</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6.13</v>
+        <v>6.12</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.87</v>
+        <v>19.44</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="9">
@@ -4196,94 +4196,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="G9" t="n">
-        <v>4.62</v>
+        <v>4.78</v>
       </c>
       <c r="H9" t="n">
-        <v>92.5</v>
+        <v>93.89</v>
       </c>
       <c r="I9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="J9" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="K9" t="n">
-        <v>6.88</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M9" t="n">
-        <v>43</v>
+        <v>43.78</v>
       </c>
       <c r="N9" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="O9" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="P9" t="n">
-        <v>12.5</v>
+        <v>12.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>17</v>
+        <v>16.56</v>
       </c>
       <c r="R9" t="n">
-        <v>6.75</v>
+        <v>6.89</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="U9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>59.62</v>
+        <v>59.44</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.5</v>
+        <v>16.78</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.88</v>
+        <v>11.44</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.62</v>
+        <v>5.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.12</v>
+        <v>19.67</v>
       </c>
       <c r="AD9" t="n">
         <v>1.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AF9" t="n">
         <v>0.14</v>
@@ -4367,70 +4367,70 @@
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.73</v>
+        <v>10</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.13</v>
+        <v>4.19</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.6</v>
+        <v>5.81</v>
       </c>
       <c r="BR9" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS9" t="n">
-        <v>93.33</v>
+        <v>87.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BU9" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="CC9" t="n">
         <v>3.92</v>
@@ -4439,28 +4439,28 @@
         <v>4.23</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="CH9" t="n">
         <v>1.47</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CK9" t="n">
         <v>1.54</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM9" t="n">
         <v>2.31</v>
@@ -4472,28 +4472,28 @@
         <v>1.23</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CU9" t="n">
         <v>1.5</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CX9" t="n">
         <v>1.59</v>
@@ -4508,88 +4508,88 @@
         <v>1.88</v>
       </c>
       <c r="DB9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>81.19</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="DN9" t="n">
         <v>1.25</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="DD9" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="DE9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DF9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DG9" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="DH9" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="DJ9" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="DK9" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="DL9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DM9" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>1.2</v>
       </c>
       <c r="DO9" t="n">
         <v>1.87</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.2</v>
+        <v>13.12</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.33</v>
+        <v>16.13</v>
       </c>
       <c r="DR9" t="n">
         <v>7.87</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>53.6</v>
+        <v>53.87</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.8</v>
+        <v>14.12</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.07</v>
+        <v>9.5</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.73</v>
+        <v>4.62</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.46</v>
+        <v>17.88</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="10">
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>0.14</v>
@@ -5092,52 +5092,52 @@
         <v>2.43</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG11" t="n">
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AI11" t="n">
-        <v>94.62</v>
+        <v>92.67</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.12</v>
+        <v>4.33</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN11" t="n">
-        <v>43.88</v>
+        <v>43.11</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ11" t="n">
-        <v>17.38</v>
+        <v>17</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.880000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.88</v>
+        <v>8.33</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5149,73 +5149,73 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>38.75</v>
+        <v>39.11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA11" t="n">
-        <v>13.5</v>
+        <v>13.67</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.5</v>
+        <v>8.67</v>
       </c>
       <c r="BC11" t="n">
         <v>5</v>
       </c>
       <c r="BD11" t="n">
-        <v>20.25</v>
+        <v>20.11</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BF11" t="n">
         <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.529999999999999</v>
+        <v>9.81</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.4</v>
+        <v>4.44</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.13</v>
+        <v>5.38</v>
       </c>
       <c r="BR11" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS11" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BT11" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BY11" t="n">
         <v>2.21</v>
@@ -5233,16 +5233,16 @@
         <v>2.29</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="CE11" t="n">
         <v>1.39</v>
@@ -5251,7 +5251,7 @@
         <v>2.81</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CH11" t="n">
         <v>1.39</v>
@@ -5260,7 +5260,7 @@
         <v>1.94</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CK11" t="n">
         <v>1.57</v>
@@ -5269,10 +5269,10 @@
         <v>1.98</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO11" t="n">
         <v>1.29</v>
@@ -5281,16 +5281,16 @@
         <v>1.97</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
       </c>
       <c r="CS11" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CU11" t="n">
         <v>1.41</v>
@@ -5320,49 +5320,49 @@
         <v>2.03</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="DH11" t="n">
-        <v>95.87</v>
+        <v>94.69</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.67</v>
+        <v>4.75</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.14</v>
+        <v>43.69</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="DP11" t="n">
-        <v>17.8</v>
+        <v>17.56</v>
       </c>
       <c r="DQ11" t="n">
-        <v>8.94</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.07</v>
+        <v>8.31</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>38.13</v>
+        <v>38.38</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.6</v>
+        <v>13.69</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.06</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.53</v>
+        <v>4.56</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.87</v>
+        <v>19.81</v>
       </c>
       <c r="EB11" t="n">
         <v>1.5</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="12">
@@ -5808,10 +5808,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
@@ -5820,49 +5820,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="G13" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="H13" t="n">
-        <v>84.56999999999999</v>
+        <v>82.25</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="K13" t="n">
-        <v>5.14</v>
+        <v>4.88</v>
       </c>
       <c r="L13" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="M13" t="n">
-        <v>48.14</v>
+        <v>46.25</v>
       </c>
       <c r="N13" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>12.71</v>
+        <v>12.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.14</v>
+        <v>13</v>
       </c>
       <c r="R13" t="n">
-        <v>8.43</v>
+        <v>8.75</v>
       </c>
       <c r="S13" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="T13" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5874,28 +5874,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>52</v>
+        <v>50.62</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.14</v>
+        <v>11.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.859999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="AC13" t="n">
-        <v>24</v>
+        <v>22.38</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5979,70 +5979,70 @@
         <v>2.75</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.13</v>
+        <v>2.94</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.27</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.13</v>
+        <v>2.94</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.93</v>
+        <v>4.94</v>
       </c>
       <c r="BR13" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="BS13" t="n">
-        <v>93.33</v>
+        <v>87.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BV13" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX13" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.7</v>
+        <v>3.59</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.11</v>
+        <v>4.06</v>
       </c>
       <c r="CC13" t="n">
         <v>4.96</v>
@@ -6051,124 +6051,124 @@
         <v>5.44</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CH13" t="n">
         <v>1.51</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.68</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL13" t="n">
         <v>1.87</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CR13" t="n">
         <v>1.37</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV13" t="n">
         <v>2.26</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DH13" t="n">
-        <v>84.40000000000001</v>
+        <v>83.25</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.73</v>
+        <v>4.63</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DM13" t="n">
-        <v>41.4</v>
+        <v>40.88</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.66</v>
+        <v>13.38</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.27</v>
+        <v>13.19</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.4</v>
+        <v>8.57</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6180,28 +6180,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.8</v>
+        <v>48.31</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.53</v>
+        <v>11.44</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.54</v>
+        <v>7.44</v>
       </c>
       <c r="DZ13" t="n">
         <v>4</v>
       </c>
       <c r="EA13" t="n">
-        <v>21</v>
+        <v>20.38</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="14">
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6304,49 +6304,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AI14" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.57</v>
+        <v>4.75</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AN14" t="n">
-        <v>35</v>
+        <v>40.62</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15.71</v>
+        <v>15.25</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.57</v>
+        <v>14.62</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.710000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6358,82 +6358,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>48.71</v>
+        <v>50.75</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.140000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.57</v>
+        <v>6.25</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="BD14" t="n">
-        <v>19.57</v>
+        <v>19.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.95</v>
+        <v>1.08</v>
       </c>
       <c r="BF14" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.529999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="BR14" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS14" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BT14" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BU14" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV14" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BY14" t="n">
         <v>2.83</v>
@@ -6442,25 +6442,25 @@
         <v>2.85</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.77</v>
+        <v>3.73</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="CC14" t="n">
-        <v>5.65</v>
+        <v>5.2</v>
       </c>
       <c r="CD14" t="n">
-        <v>5.84</v>
+        <v>5.39</v>
       </c>
       <c r="CE14" t="n">
         <v>1.37</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CH14" t="n">
         <v>1.42</v>
@@ -6475,7 +6475,7 @@
         <v>1.61</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CM14" t="n">
         <v>2.2</v>
@@ -6484,127 +6484,127 @@
         <v>1.76</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DA14" t="n">
         <v>1.79</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="DH14" t="n">
-        <v>87.67</v>
+        <v>90.25</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.47</v>
+        <v>4.56</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="DM14" t="n">
-        <v>35.06</v>
+        <v>37.87</v>
       </c>
       <c r="DN14" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.4</v>
+        <v>14.25</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.4</v>
+        <v>14.43</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.4</v>
+        <v>9.06</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.86</v>
+        <v>49.88</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.13</v>
+        <v>10.5</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.66</v>
+        <v>6.94</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.47</v>
+        <v>3.56</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.73</v>
+        <v>21.56</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="15">
@@ -7017,94 +7017,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="G16" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="H16" t="n">
-        <v>90.5</v>
+        <v>83.22</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="K16" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="L16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M16" t="n">
-        <v>43.88</v>
+        <v>40.67</v>
       </c>
       <c r="N16" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="P16" t="n">
-        <v>14.88</v>
+        <v>15.44</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.25</v>
+        <v>12.56</v>
       </c>
       <c r="R16" t="n">
-        <v>9.119999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="S16" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="T16" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>53.88</v>
+        <v>52.89</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z16" t="n">
         <v>14</v>
       </c>
       <c r="AA16" t="n">
-        <v>11</v>
+        <v>10.67</v>
       </c>
       <c r="AB16" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.5</v>
+        <v>18.56</v>
       </c>
       <c r="AD16" t="n">
         <v>1.41</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AF16" t="n">
         <v>0.29</v>
@@ -7188,70 +7188,70 @@
         <v>3</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.33</v>
+        <v>8.19</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="BM16" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BP16" t="n">
         <v>4</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.27</v>
+        <v>4.12</v>
       </c>
       <c r="BR16" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS16" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT16" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV16" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW16" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX16" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="CC16" t="n">
         <v>4.32</v>
@@ -7272,22 +7272,22 @@
         <v>1.49</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.69</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CO16" t="n">
         <v>1.24</v>
@@ -7296,7 +7296,7 @@
         <v>1.82</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CR16" t="n">
         <v>1.38</v>
@@ -7305,7 +7305,7 @@
         <v>2.75</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CU16" t="n">
         <v>1.5</v>
@@ -7317,16 +7317,16 @@
         <v>1.71</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY16" t="n">
         <v>1.95</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB16" t="n">
         <v>1.26</v>
@@ -7338,79 +7338,79 @@
         <v>3.02</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="DG16" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DH16" t="n">
-        <v>84.73</v>
+        <v>81</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DM16" t="n">
-        <v>36.33</v>
+        <v>35</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.53</v>
+        <v>14.87</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.13</v>
+        <v>12.32</v>
       </c>
       <c r="DR16" t="n">
-        <v>9</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DS16" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DT16" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>50.07</v>
+        <v>49.75</v>
       </c>
       <c r="DW16" t="n">
         <v>0.06</v>
       </c>
       <c r="DX16" t="n">
-        <v>12</v>
+        <v>12.12</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.93</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.07</v>
+        <v>3.25</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.54</v>
+        <v>17.13</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="17">
@@ -7420,94 +7420,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="G17" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>107.25</v>
+        <v>104.44</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="J17" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="K17" t="n">
-        <v>6.12</v>
+        <v>6.22</v>
       </c>
       <c r="L17" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="M17" t="n">
-        <v>43.88</v>
+        <v>44.56</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O17" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="P17" t="n">
-        <v>15.62</v>
+        <v>15.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.38</v>
+        <v>12</v>
       </c>
       <c r="R17" t="n">
-        <v>5.25</v>
+        <v>5.67</v>
       </c>
       <c r="S17" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>56.38</v>
+        <v>56</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z17" t="n">
-        <v>14</v>
+        <v>13.89</v>
       </c>
       <c r="AA17" t="n">
-        <v>9.880000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="AC17" t="n">
-        <v>21.62</v>
+        <v>20.89</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AF17" t="n">
         <v>0.29</v>
@@ -7591,70 +7591,70 @@
         <v>2.86</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.13</v>
+        <v>10.06</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="BR17" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS17" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT17" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU17" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV17" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CC17" t="n">
         <v>3.55</v>
@@ -7666,7 +7666,7 @@
         <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CG17" t="n">
         <v>2.96</v>
@@ -7675,31 +7675,31 @@
         <v>1.43</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO17" t="n">
         <v>1.27</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
@@ -7708,79 +7708,79 @@
         <v>2.84</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CU17" t="n">
         <v>1.46</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY17" t="n">
         <v>1.95</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB17" t="n">
         <v>1.29</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="DH17" t="n">
-        <v>94.13</v>
+        <v>93.37</v>
       </c>
       <c r="DI17" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.93</v>
+        <v>6</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DM17" t="n">
-        <v>39.47</v>
+        <v>40.13</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DP17" t="n">
-        <v>15.06</v>
+        <v>15.19</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.67</v>
+        <v>10.56</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.93</v>
+        <v>8</v>
       </c>
       <c r="DS17" t="n">
         <v>0.06</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.27</v>
+        <v>50.44</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.27</v>
+        <v>13.25</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.07</v>
+        <v>9.06</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.93</v>
+        <v>18.69</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="18">
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
         <v>7</v>
@@ -7835,82 +7835,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="G18" t="n">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="H18" t="n">
-        <v>99.75</v>
+        <v>106.11</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="L18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M18" t="n">
-        <v>41.5</v>
+        <v>50.89</v>
       </c>
       <c r="N18" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O18" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="P18" t="n">
-        <v>12.62</v>
+        <v>12</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.25</v>
+        <v>12.67</v>
       </c>
       <c r="R18" t="n">
-        <v>7.62</v>
+        <v>7.22</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="T18" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="U18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>53.75</v>
+        <v>56.22</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>17.25</v>
+        <v>19.11</v>
       </c>
       <c r="AA18" t="n">
-        <v>11.62</v>
+        <v>12.67</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.62</v>
+        <v>6.44</v>
       </c>
       <c r="AC18" t="n">
-        <v>20.88</v>
+        <v>21.78</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.78</v>
+        <v>2.03</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AF18" t="n">
         <v>0.14</v>
@@ -7994,70 +7994,70 @@
         <v>1.71</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.33</v>
+        <v>9.25</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.53</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="BR18" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS18" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT18" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU18" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BV18" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BW18" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BX18" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="CB18" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="CC18" t="n">
         <v>3.72</v>
@@ -8069,7 +8069,7 @@
         <v>1.34</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CG18" t="n">
         <v>3.15</v>
@@ -8078,19 +8078,19 @@
         <v>1.49</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.73</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL18" t="n">
         <v>2.03</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CN18" t="n">
         <v>1.85</v>
@@ -8102,25 +8102,25 @@
         <v>1.77</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS18" t="n">
         <v>2.67</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CU18" t="n">
         <v>1.51</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CX18" t="n">
         <v>1.55</v>
@@ -8144,79 +8144,79 @@
         <v>2.9</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="DH18" t="n">
-        <v>87.93000000000001</v>
+        <v>92.25</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.07</v>
+        <v>4.25</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM18" t="n">
-        <v>36.07</v>
+        <v>41.69</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DP18" t="n">
-        <v>12</v>
+        <v>11.69</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.8</v>
+        <v>14.38</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.93</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>52.14</v>
+        <v>53.63</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX18" t="n">
-        <v>15.27</v>
+        <v>16.44</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.73</v>
+        <v>10.44</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.53</v>
+        <v>6</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.13</v>
+        <v>19.75</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="19">
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8319,136 +8319,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="AI19" t="n">
-        <v>103.12</v>
+        <v>104.22</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="AL19" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>75</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BV19" t="n">
         <v>6.25</v>
       </c>
-      <c r="AM19" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>46.88</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>60.12</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>16.88</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>11.53</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>86.67</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>73.33</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>46.67</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>20</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>6.67</v>
-      </c>
       <c r="BW19" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX19" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY19" t="n">
         <v>2.74</v>
@@ -8463,16 +8463,16 @@
         <v>3.59</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="CE19" t="n">
         <v>1.34</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CG19" t="n">
         <v>3</v>
@@ -8484,28 +8484,28 @@
         <v>2.06</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CN19" t="n">
         <v>1.82</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="CR19" t="n">
         <v>1.39</v>
@@ -8514,7 +8514,7 @@
         <v>2.81</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CU19" t="n">
         <v>1.46</v>
@@ -8541,85 +8541,85 @@
         <v>1.27</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DG19" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="DH19" t="n">
-        <v>91.93000000000001</v>
+        <v>93.25</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.73</v>
+        <v>5.5</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="DM19" t="n">
-        <v>44.4</v>
+        <v>44.38</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.13</v>
+        <v>12.87</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14</v>
+        <v>14.18</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.130000000000001</v>
+        <v>7.94</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.6</v>
+        <v>55.06</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.74</v>
+        <v>12.75</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.73</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.27</v>
+        <v>17.69</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>46.22</v>
+        <v>46.11</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>3.67</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.11</v>
+        <v>20.22</v>
       </c>
       <c r="BE2" t="n">
         <v>1.27</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>48.69</v>
+        <v>48.63</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
@@ -1766,7 +1766,7 @@
         <v>3.81</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.38</v>
+        <v>19.44</v>
       </c>
       <c r="EB2" t="n">
         <v>1.34</v>
@@ -3033,7 +3033,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>14.89</v>
+        <v>14.78</v>
       </c>
       <c r="Q6" t="n">
         <v>14.78</v>
@@ -3345,7 +3345,7 @@
         <v>1.75</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.25</v>
+        <v>14.19</v>
       </c>
       <c r="DQ6" t="n">
         <v>14.31</v>
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F7" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="G7" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="H7" t="n">
-        <v>122.14</v>
+        <v>117.38</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>6.62</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="M7" t="n">
-        <v>61.86</v>
+        <v>58.12</v>
       </c>
       <c r="N7" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="O7" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>12.57</v>
+        <v>12.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.71</v>
+        <v>13.88</v>
       </c>
       <c r="R7" t="n">
-        <v>3.71</v>
+        <v>4.25</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="T7" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="U7" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="V7" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>62.29</v>
+        <v>61.12</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>21.38</v>
       </c>
       <c r="AA7" t="n">
-        <v>14.43</v>
+        <v>13.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.57</v>
+        <v>7.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>20</v>
+        <v>20.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AF7" t="n">
         <v>0.25</v>
@@ -3565,70 +3565,70 @@
         <v>2.75</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.07</v>
+        <v>3.12</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.07</v>
+        <v>9.94</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.07</v>
+        <v>3.12</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.07</v>
+        <v>5.06</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="BR7" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS7" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT7" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU7" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BV7" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW7" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.87</v>
+        <v>4.97</v>
       </c>
       <c r="CB7" t="n">
-        <v>5.04</v>
+        <v>5.17</v>
       </c>
       <c r="CC7" t="n">
         <v>1.68</v>
@@ -3640,40 +3640,40 @@
         <v>1.28</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="CH7" t="n">
         <v>1.57</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CL7" t="n">
         <v>1.95</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CO7" t="n">
         <v>1.17</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
@@ -3688,10 +3688,10 @@
         <v>1.57</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CX7" t="n">
         <v>1.55</v>
@@ -3706,88 +3706,88 @@
         <v>1.89</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.07</v>
+        <v>2.94</v>
       </c>
       <c r="DH7" t="n">
-        <v>109.73</v>
+        <v>108.13</v>
       </c>
       <c r="DI7" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.53</v>
+        <v>6.37</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.2</v>
+        <v>50.94</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="DP7" t="n">
-        <v>13.13</v>
+        <v>13.25</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.53</v>
+        <v>13.19</v>
       </c>
       <c r="DR7" t="n">
-        <v>5.13</v>
+        <v>5.32</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.53</v>
+        <v>59.12</v>
       </c>
       <c r="DW7" t="n">
         <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>18.33</v>
+        <v>18.25</v>
       </c>
       <c r="DY7" t="n">
-        <v>11.67</v>
+        <v>11.43</v>
       </c>
       <c r="DZ7" t="n">
-        <v>6.67</v>
+        <v>6.82</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.67</v>
+        <v>19.19</v>
       </c>
       <c r="EB7" t="n">
         <v>2</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
@@ -5874,7 +5874,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50.62</v>
+        <v>50.75</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.31</v>
+        <v>48.38</v>
       </c>
       <c r="DW13" t="n">
         <v>0.12</v>
@@ -6337,7 +6337,7 @@
         <v>15.25</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.62</v>
+        <v>14.5</v>
       </c>
       <c r="AS14" t="n">
         <v>9</v>
@@ -6373,7 +6373,7 @@
         <v>2.88</v>
       </c>
       <c r="BD14" t="n">
-        <v>19.5</v>
+        <v>19.62</v>
       </c>
       <c r="BE14" t="n">
         <v>1.08</v>
@@ -6568,7 +6568,7 @@
         <v>14.25</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.43</v>
+        <v>14.38</v>
       </c>
       <c r="DR14" t="n">
         <v>9.06</v>
@@ -6598,7 +6598,7 @@
         <v>3.56</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.56</v>
+        <v>21.62</v>
       </c>
       <c r="EB14" t="n">
         <v>1.2</v>
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6704,139 +6704,139 @@
         <v>2.25</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>90.29000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.29</v>
+        <v>5.12</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN15" t="n">
-        <v>39.71</v>
+        <v>40</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.71</v>
+        <v>10.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.43</v>
+        <v>14.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.289999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>50.43</v>
+        <v>50</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>12.86</v>
+        <v>13.38</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.43</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>19.29</v>
+        <v>18.62</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.6</v>
+        <v>10.44</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.53</v>
+        <v>4.56</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.07</v>
+        <v>5.88</v>
       </c>
       <c r="BR15" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS15" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT15" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BV15" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BY15" t="n">
         <v>2.21</v>
@@ -6845,55 +6845,55 @@
         <v>2.31</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.65</v>
+        <v>3.82</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.71</v>
+        <v>3.92</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.59</v>
+        <v>5.39</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.91</v>
+        <v>5.74</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL15" t="n">
         <v>1.99</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
@@ -6908,10 +6908,10 @@
         <v>1.47</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CX15" t="n">
         <v>1.54</v>
@@ -6926,85 +6926,85 @@
         <v>1.9</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.27</v>
+        <v>3.19</v>
       </c>
       <c r="DH15" t="n">
-        <v>97.8</v>
+        <v>97.44</v>
       </c>
       <c r="DI15" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DK15" t="n">
-        <v>6</v>
+        <v>5.87</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM15" t="n">
-        <v>45</v>
+        <v>44.81</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.87</v>
+        <v>11.69</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.07</v>
+        <v>13.19</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.539999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>52.87</v>
+        <v>52.5</v>
       </c>
       <c r="DW15" t="n">
         <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.07</v>
+        <v>14.25</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.74</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.34</v>
+        <v>19.94</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="EC15" t="n">
         <v>2</v>
@@ -7492,10 +7492,10 @@
         <v>0.11</v>
       </c>
       <c r="Z17" t="n">
-        <v>13.89</v>
+        <v>14</v>
       </c>
       <c r="AA17" t="n">
-        <v>9.779999999999999</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AB17" t="n">
         <v>4.11</v>
@@ -7504,7 +7504,7 @@
         <v>20.89</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
         <v>1.67</v>
@@ -7798,10 +7798,10 @@
         <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.25</v>
+        <v>13.31</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.06</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DZ17" t="n">
         <v>4.19</v>
@@ -7810,7 +7810,7 @@
         <v>18.69</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="EC17" t="n">
         <v>2.19</v>
@@ -8379,10 +8379,10 @@
         <v>0.22</v>
       </c>
       <c r="BA19" t="n">
-        <v>13.33</v>
+        <v>13.22</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.890000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BC19" t="n">
         <v>4.44</v>
@@ -8391,7 +8391,7 @@
         <v>17.67</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="BF19" t="n">
         <v>2.11</v>
@@ -8604,10 +8604,10 @@
         <v>0.18</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.75</v>
+        <v>12.69</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.630000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="DZ19" t="n">
         <v>4.12</v>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
@@ -1391,82 +1391,82 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M2" t="n">
+        <v>45.62</v>
+      </c>
+      <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="H2" t="n">
-        <v>95.43000000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="K2" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="M2" t="n">
-        <v>47.57</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.71</v>
-      </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="P2" t="n">
-        <v>12.14</v>
+        <v>13</v>
       </c>
       <c r="Q2" t="n">
-        <v>15.43</v>
+        <v>15.5</v>
       </c>
       <c r="R2" t="n">
-        <v>5.71</v>
+        <v>5.62</v>
       </c>
       <c r="S2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="T2" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="U2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>51.86</v>
+        <v>50.88</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.71</v>
+        <v>12.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.710000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>18.43</v>
+        <v>18.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,49 +1550,49 @@
         <v>2.33</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.56</v>
+        <v>8.35</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.69</v>
+        <v>3.59</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.88</v>
+        <v>4.76</v>
       </c>
       <c r="BR2" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BS2" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BU2" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,19 +1601,19 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CC2" t="n">
         <v>4.03</v>
@@ -1628,28 +1628,28 @@
         <v>2.7</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CH2" t="n">
         <v>1.45</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK2" t="n">
         <v>1.71</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CO2" t="n">
         <v>1.25</v>
@@ -1664,115 +1664,115 @@
         <v>1.4</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.08</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="DH2" t="n">
-        <v>86.31</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="DI2" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.88</v>
+        <v>4.71</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DM2" t="n">
-        <v>41.5</v>
+        <v>40.94</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.38</v>
+        <v>12.77</v>
       </c>
       <c r="DQ2" t="n">
         <v>15.94</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.81</v>
+        <v>6.71</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>48.63</v>
+        <v>48.35</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.19</v>
+        <v>12.12</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.369999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.81</v>
+        <v>3.94</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.44</v>
+        <v>19.29</v>
       </c>
       <c r="EB2" t="n">
         <v>1.34</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,49 +1875,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AI3" t="n">
-        <v>65.12</v>
+        <v>69.89</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.62</v>
+        <v>25.44</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.12</v>
+        <v>12.89</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.38</v>
+        <v>13.44</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.38</v>
+        <v>11.11</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>41.38</v>
+        <v>42.78</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.38</v>
+        <v>3.56</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.88</v>
+        <v>20.44</v>
       </c>
       <c r="BE3" t="n">
         <v>0.76</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.31</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.88</v>
+        <v>4.82</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.44</v>
+        <v>4.29</v>
       </c>
       <c r="BR3" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT3" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU3" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV3" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX3" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY3" t="n">
         <v>3.45</v>
@@ -2013,55 +2013,55 @@
         <v>3.84</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.47</v>
+        <v>5.44</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.97</v>
+        <v>5.98</v>
       </c>
       <c r="CE3" t="n">
         <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CH3" t="n">
         <v>1.42</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="CR3" t="n">
         <v>1.42</v>
@@ -2076,10 +2076,10 @@
         <v>1.43</v>
       </c>
       <c r="CV3" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CX3" t="n">
         <v>1.61</v>
@@ -2094,40 +2094,40 @@
         <v>1.79</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.39</v>
+        <v>3.45</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="DH3" t="n">
-        <v>72.12</v>
+        <v>74.23</v>
       </c>
       <c r="DI3" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="DK3" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM3" t="n">
-        <v>28.94</v>
+        <v>29.59</v>
       </c>
       <c r="DN3" t="n">
         <v>1.06</v>
@@ -2136,13 +2136,13 @@
         <v>1.94</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.75</v>
+        <v>12.18</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.69</v>
+        <v>15.12</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.57</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43</v>
+        <v>43.65</v>
       </c>
       <c r="DW3" t="n">
         <v>0.12</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.44</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.13</v>
+        <v>19.47</v>
       </c>
       <c r="EB3" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F4" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="H4" t="n">
-        <v>91</v>
+        <v>91.5</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="J4" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="K4" t="n">
-        <v>6.14</v>
+        <v>5.88</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>45.43</v>
+        <v>46.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>14.86</v>
+        <v>14.62</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.86</v>
+        <v>13</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S4" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="U4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>51.71</v>
+        <v>52.88</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.43</v>
+        <v>16.38</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.43</v>
+        <v>10.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>6</v>
+        <v>5.88</v>
       </c>
       <c r="AC4" t="n">
-        <v>15.71</v>
+        <v>14.88</v>
       </c>
       <c r="AD4" t="n">
         <v>1.78</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AF4" t="n">
         <v>0.22</v>
@@ -2356,70 +2356,70 @@
         <v>2.56</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.19</v>
+        <v>3.06</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.19</v>
+        <v>3.06</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK4" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.94</v>
+        <v>4.88</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>100</v>
+        <v>94.12</v>
       </c>
       <c r="BT4" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BU4" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV4" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX4" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="CC4" t="n">
         <v>2.4</v>
@@ -2434,16 +2434,16 @@
         <v>2.34</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="CH4" t="n">
         <v>1.54</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK4" t="n">
         <v>1.5</v>
@@ -2452,7 +2452,7 @@
         <v>1.94</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CN4" t="n">
         <v>1.9</v>
@@ -2464,7 +2464,7 @@
         <v>1.63</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
@@ -2473,112 +2473,112 @@
         <v>2.52</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CU4" t="n">
         <v>1.57</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CW4" t="n">
         <v>1.65</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB4" t="n">
         <v>1.2</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="DH4" t="n">
-        <v>85.62</v>
+        <v>86.17</v>
       </c>
       <c r="DI4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>41.17</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="DS4" t="n">
         <v>0.12</v>
       </c>
-      <c r="DJ4" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="DK4" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="DL4" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="DM4" t="n">
-        <v>40.37</v>
-      </c>
-      <c r="DN4" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="DO4" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="DP4" t="n">
-        <v>14.19</v>
-      </c>
-      <c r="DQ4" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="DR4" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="DS4" t="n">
-        <v>0.13</v>
-      </c>
       <c r="DT4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>51.56</v>
+        <v>52.12</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX4" t="n">
-        <v>15.31</v>
+        <v>15.35</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.44</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.88</v>
+        <v>5.83</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.56</v>
+        <v>17.06</v>
       </c>
       <c r="EB4" t="n">
         <v>1.67</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="5">
@@ -2588,61 +2588,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F5" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="H5" t="n">
-        <v>78.75</v>
+        <v>77.11</v>
       </c>
       <c r="I5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J5" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="K5" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M5" t="n">
-        <v>40.88</v>
+        <v>39.89</v>
       </c>
       <c r="N5" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="O5" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="P5" t="n">
-        <v>10.5</v>
+        <v>10.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>13.89</v>
       </c>
       <c r="R5" t="n">
-        <v>7.25</v>
+        <v>7.44</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="T5" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>53.75</v>
+        <v>52.56</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>12.12</v>
+        <v>11.67</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.62</v>
+        <v>7.33</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.62</v>
+        <v>18.67</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AF5" t="n">
         <v>0.12</v>
@@ -2759,70 +2759,70 @@
         <v>2.75</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.31</v>
+        <v>10.24</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.81</v>
+        <v>5.82</v>
       </c>
       <c r="BR5" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BU5" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BV5" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.99</v>
+        <v>3.49</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.26</v>
+        <v>3.73</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.66</v>
+        <v>3.73</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.77</v>
+        <v>3.84</v>
       </c>
       <c r="CC5" t="n">
         <v>4.1</v>
@@ -2834,13 +2834,13 @@
         <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI5" t="n">
         <v>2.03</v>
@@ -2852,7 +2852,7 @@
         <v>1.55</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CM5" t="n">
         <v>2.32</v>
@@ -2861,19 +2861,19 @@
         <v>1.81</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="CR5" t="n">
         <v>1.39</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="CT5" t="n">
         <v>3.09</v>
@@ -2882,10 +2882,10 @@
         <v>1.48</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CX5" t="n">
         <v>1.57</v>
@@ -2897,58 +2897,58 @@
         <v>2.35</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB5" t="n">
         <v>1.27</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="DH5" t="n">
-        <v>77.12</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM5" t="n">
-        <v>37.25</v>
+        <v>36.94</v>
       </c>
       <c r="DN5" t="n">
         <v>0.88</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.19</v>
+        <v>12.18</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.75</v>
+        <v>15.59</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.32</v>
+        <v>7.41</v>
       </c>
       <c r="DS5" t="n">
         <v>0.06</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.38</v>
+        <v>50.88</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.75</v>
+        <v>11.53</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.94</v>
+        <v>7.76</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.81</v>
+        <v>3.76</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.12</v>
+        <v>18.18</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,49 +3084,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AI6" t="n">
-        <v>81.56999999999999</v>
+        <v>83.12</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>37.71</v>
+        <v>38.75</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13.43</v>
+        <v>13.75</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.71</v>
+        <v>14.38</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>10.12</v>
       </c>
       <c r="AT6" t="n">
         <v>2</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>44.86</v>
+        <v>46.25</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.57</v>
+        <v>11.25</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.57</v>
+        <v>8.25</v>
       </c>
       <c r="BC6" t="n">
         <v>3</v>
       </c>
       <c r="BD6" t="n">
-        <v>20.86</v>
+        <v>20.62</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.81</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="BO6" t="n">
         <v>1.06</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.69</v>
+        <v>4.53</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU6" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV6" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX6" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY6" t="n">
         <v>3.4</v>
@@ -3222,22 +3222,22 @@
         <v>3.52</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.18</v>
+        <v>4.14</v>
       </c>
       <c r="CC6" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="CD6" t="n">
-        <v>7.42</v>
+        <v>7.12</v>
       </c>
       <c r="CE6" t="n">
         <v>1.35</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CG6" t="n">
         <v>3.1</v>
@@ -3246,7 +3246,7 @@
         <v>1.46</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.76</v>
@@ -3255,13 +3255,13 @@
         <v>1.58</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CO6" t="n">
         <v>1.24</v>
@@ -3270,88 +3270,88 @@
         <v>1.85</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CR6" t="n">
         <v>1.41</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CX6" t="n">
         <v>1.61</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DB6" t="n">
         <v>1.28</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DG6" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.06</v>
+        <v>88.41</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM6" t="n">
-        <v>36.43</v>
+        <v>37</v>
       </c>
       <c r="DN6" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.19</v>
+        <v>14.3</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.31</v>
+        <v>14.59</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.56</v>
+        <v>9.23</v>
       </c>
       <c r="DS6" t="n">
         <v>0.06</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.87</v>
+        <v>47.41</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.81</v>
+        <v>10.7</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.130000000000001</v>
+        <v>8</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.56</v>
+        <v>20.47</v>
       </c>
       <c r="EB6" t="n">
         <v>1.14</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0.12</v>
@@ -3484,52 +3484,52 @@
         <v>2.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG7" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AH7" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AI7" t="n">
-        <v>98.88</v>
+        <v>98.78</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AN7" t="n">
-        <v>43.75</v>
+        <v>43.56</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.62</v>
+        <v>13.56</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.5</v>
+        <v>12.44</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.38</v>
+        <v>6.44</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>57.12</v>
+        <v>57.11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA7" t="n">
-        <v>15.12</v>
+        <v>16</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.25</v>
+        <v>10</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.88</v>
+        <v>6</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.5</v>
+        <v>17.67</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="BG7" t="n">
         <v>3.12</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.94</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI7" t="n">
         <v>3.12</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.06</v>
+        <v>4.94</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.88</v>
+        <v>4.94</v>
       </c>
       <c r="BR7" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU7" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BV7" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW7" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX7" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY7" t="n">
         <v>1.39</v>
@@ -3625,16 +3625,16 @@
         <v>1.39</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.97</v>
+        <v>4.96</v>
       </c>
       <c r="CB7" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="CE7" t="n">
         <v>1.28</v>
@@ -3658,7 +3658,7 @@
         <v>1.54</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM7" t="n">
         <v>2.34</v>
@@ -3673,7 +3673,7 @@
         <v>1.61</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
@@ -3688,7 +3688,7 @@
         <v>1.57</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CW7" t="n">
         <v>1.87</v>
@@ -3697,7 +3697,7 @@
         <v>1.55</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.38</v>
@@ -3706,7 +3706,7 @@
         <v>1.89</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC7" t="n">
         <v>1.67</v>
@@ -3715,79 +3715,79 @@
         <v>2.65</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="DH7" t="n">
-        <v>108.13</v>
+        <v>107.53</v>
       </c>
       <c r="DI7" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.37</v>
+        <v>6.29</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DM7" t="n">
-        <v>50.94</v>
+        <v>50.41</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="DP7" t="n">
-        <v>13.25</v>
+        <v>13.24</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.19</v>
+        <v>13.12</v>
       </c>
       <c r="DR7" t="n">
-        <v>5.32</v>
+        <v>5.41</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.12</v>
+        <v>59</v>
       </c>
       <c r="DW7" t="n">
         <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>18.25</v>
+        <v>18.53</v>
       </c>
       <c r="DY7" t="n">
-        <v>11.43</v>
+        <v>11.7</v>
       </c>
       <c r="DZ7" t="n">
         <v>6.82</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.19</v>
+        <v>19.18</v>
       </c>
       <c r="EB7" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="8">
@@ -3797,61 +3797,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="F8" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="G8" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="H8" t="n">
-        <v>98.38</v>
+        <v>97.44</v>
       </c>
       <c r="I8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J8" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="K8" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="M8" t="n">
-        <v>55.75</v>
+        <v>55.22</v>
       </c>
       <c r="N8" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="P8" t="n">
-        <v>10.75</v>
+        <v>10.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.12</v>
+        <v>10.44</v>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>6.56</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="T8" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>64</v>
+        <v>64.89</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.25</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>13.12</v>
+        <v>13.89</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.12</v>
+        <v>7.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.62</v>
+        <v>21.56</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
         <v>0.12</v>
@@ -3971,67 +3971,67 @@
         <v>3</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.619999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="BI8" t="n">
         <v>3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.81</v>
+        <v>3.88</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.81</v>
+        <v>4.88</v>
       </c>
       <c r="BR8" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS8" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU8" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV8" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.35</v>
+        <v>5.44</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.68</v>
+        <v>5.81</v>
       </c>
       <c r="CC8" t="n">
         <v>1.58</v>
@@ -4040,16 +4040,16 @@
         <v>1.67</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.77</v>
+        <v>3.8</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CI8" t="n">
         <v>2.06</v>
@@ -4058,10 +4058,10 @@
         <v>1.71</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CM8" t="n">
         <v>2.47</v>
@@ -4073,33 +4073,33 @@
         <v>1.13</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CV8" t="n">
         <v>2.18</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="DA8" t="n">
         <v>2.01</v>
@@ -4108,22 +4108,22 @@
         <v>1.15</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DF8" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="DH8" t="n">
-        <v>95.19</v>
+        <v>94.88</v>
       </c>
       <c r="DI8" t="n">
         <v>0.06</v>
@@ -4132,28 +4132,28 @@
         <v>2</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.62</v>
+        <v>4.94</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="DM8" t="n">
-        <v>50.25</v>
+        <v>50.29</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="DP8" t="n">
-        <v>12</v>
+        <v>11.94</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.62</v>
+        <v>10.76</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.75</v>
+        <v>7.47</v>
       </c>
       <c r="DS8" t="n">
         <v>0.12</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>61.56</v>
+        <v>62.17</v>
       </c>
       <c r="DW8" t="n">
         <v>0.12</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.93</v>
+        <v>17.53</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.81</v>
+        <v>11.35</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6.12</v>
+        <v>6.17</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.44</v>
+        <v>19.53</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="9">
@@ -5002,61 +5002,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="H11" t="n">
-        <v>97.29000000000001</v>
+        <v>95.88</v>
       </c>
       <c r="I11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J11" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="K11" t="n">
-        <v>5.29</v>
+        <v>5.12</v>
       </c>
       <c r="L11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M11" t="n">
-        <v>44.43</v>
+        <v>42.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>18.29</v>
+        <v>18.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="R11" t="n">
-        <v>8.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="S11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5068,28 +5068,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>37.43</v>
+        <v>37.25</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.71</v>
+        <v>13.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.710000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.43</v>
+        <v>20.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AF11" t="n">
         <v>0.11</v>
@@ -5173,49 +5173,49 @@
         <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.81</v>
+        <v>9.65</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BK11" t="n">
         <v>0.12</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.44</v>
+        <v>4.29</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.38</v>
+        <v>5.35</v>
       </c>
       <c r="BR11" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BT11" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BY11" t="n">
         <v>2.21</v>
@@ -5233,10 +5233,10 @@
         <v>2.29</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="CC11" t="n">
         <v>2.84</v>
@@ -5245,13 +5245,13 @@
         <v>3.05</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="CH11" t="n">
         <v>1.39</v>
@@ -5260,109 +5260,109 @@
         <v>1.94</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CO11" t="n">
         <v>1.29</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.34</v>
+        <v>3.39</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="CU11" t="n">
         <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY11" t="n">
         <v>1.95</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.52</v>
+        <v>3.63</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="DH11" t="n">
-        <v>94.69</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DM11" t="n">
-        <v>43.69</v>
+        <v>42.71</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="DP11" t="n">
-        <v>17.56</v>
+        <v>17.59</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.119999999999999</v>
+        <v>9</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.31</v>
+        <v>8.17</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>38.38</v>
+        <v>38.23</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.69</v>
+        <v>13.47</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.119999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.56</v>
+        <v>4.41</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.81</v>
+        <v>20.11</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="12">
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5498,136 +5498,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AI12" t="n">
-        <v>86</v>
+        <v>81.78</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>36.75</v>
+        <v>35.56</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AP12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BN12" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>16.12</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>41.88</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>6.88</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>20.62</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>9.56</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1.06</v>
       </c>
       <c r="BO12" t="n">
         <v>1.12</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.69</v>
+        <v>3.76</v>
       </c>
       <c r="BQ12" t="n">
         <v>5.88</v>
       </c>
       <c r="BR12" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT12" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU12" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV12" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY12" t="n">
         <v>3.44</v>
@@ -5636,28 +5636,28 @@
         <v>3.95</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.56</v>
+        <v>3.76</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.61</v>
+        <v>3.86</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.26</v>
+        <v>3.87</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.8</v>
+        <v>4.65</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CI12" t="n">
         <v>2.06</v>
@@ -5666,106 +5666,106 @@
         <v>1.72</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CN12" t="n">
         <v>1.87</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.06</v>
+        <v>2.99</v>
       </c>
       <c r="CR12" t="n">
         <v>1.4</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="CT12" t="n">
         <v>3.06</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CW12" t="n">
         <v>1.76</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.27</v>
+        <v>3.19</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="DH12" t="n">
-        <v>88.06</v>
+        <v>85.7</v>
       </c>
       <c r="DI12" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.13</v>
+        <v>4.88</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DM12" t="n">
-        <v>41.5</v>
+        <v>40.59</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.94</v>
+        <v>14.82</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.69</v>
+        <v>12.59</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.44</v>
+        <v>7.77</v>
       </c>
       <c r="DS12" t="n">
         <v>0.06</v>
@@ -5777,28 +5777,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.38</v>
+        <v>44.35</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.25</v>
+        <v>10.64</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.44</v>
+        <v>8</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.81</v>
+        <v>2.64</v>
       </c>
       <c r="EA12" t="n">
-        <v>20</v>
+        <v>19.71</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="13">
@@ -5808,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5901,49 +5901,49 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AI13" t="n">
-        <v>84.25</v>
+        <v>83.67</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.38</v>
+        <v>4.11</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN13" t="n">
-        <v>35.5</v>
+        <v>36.56</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14.5</v>
+        <v>14.11</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.38</v>
+        <v>13.33</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.380000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5955,46 +5955,46 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>46</v>
+        <v>45.56</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA13" t="n">
-        <v>11</v>
+        <v>11.22</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.38</v>
+        <v>6.67</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
       <c r="BD13" t="n">
-        <v>18.38</v>
+        <v>17.44</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.380000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM13" t="n">
         <v>1.12</v>
@@ -6003,34 +6003,34 @@
         <v>1.94</v>
       </c>
       <c r="BO13" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.94</v>
+        <v>4.82</v>
       </c>
       <c r="BR13" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS13" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU13" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV13" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX13" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY13" t="n">
         <v>3.34</v>
@@ -6039,16 +6039,16 @@
         <v>3.59</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.06</v>
+        <v>4.03</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.96</v>
+        <v>4.82</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.44</v>
+        <v>5.24</v>
       </c>
       <c r="CE13" t="n">
         <v>1.32</v>
@@ -6057,10 +6057,10 @@
         <v>2.52</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI13" t="n">
         <v>2.13</v>
@@ -6072,7 +6072,7 @@
         <v>1.48</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CM13" t="n">
         <v>2.53</v>
@@ -6084,10 +6084,10 @@
         <v>1.22</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CR13" t="n">
         <v>1.37</v>
@@ -6096,7 +6096,7 @@
         <v>2.62</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CU13" t="n">
         <v>1.53</v>
@@ -6132,43 +6132,43 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DH13" t="n">
-        <v>83.25</v>
+        <v>83</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.63</v>
+        <v>4.47</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="DM13" t="n">
-        <v>40.88</v>
+        <v>41.12</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.38</v>
+        <v>13.23</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.19</v>
+        <v>13.17</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.57</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6180,28 +6180,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.38</v>
+        <v>48</v>
       </c>
       <c r="DW13" t="n">
         <v>0.12</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.44</v>
+        <v>11.53</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.44</v>
+        <v>7.53</v>
       </c>
       <c r="DZ13" t="n">
         <v>4</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.38</v>
+        <v>19.76</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="14">
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
@@ -6223,82 +6223,82 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>93.5</v>
+        <v>93.11</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="J14" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="K14" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="L14" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="M14" t="n">
-        <v>35.12</v>
+        <v>36</v>
       </c>
       <c r="N14" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O14" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="P14" t="n">
-        <v>13.25</v>
+        <v>14.22</v>
       </c>
       <c r="Q14" t="n">
-        <v>14.25</v>
+        <v>14.78</v>
       </c>
       <c r="R14" t="n">
-        <v>9.119999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="S14" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="T14" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>49</v>
+        <v>48.67</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.88</v>
+        <v>11.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.62</v>
+        <v>7.22</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="AC14" t="n">
-        <v>23.62</v>
+        <v>23.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6382,70 +6382,70 @@
         <v>2.88</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.5</v>
+        <v>8.35</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.94</v>
+        <v>3.82</v>
       </c>
       <c r="BR14" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BT14" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BU14" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV14" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="CA14" t="n">
         <v>3.73</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="CC14" t="n">
         <v>5.2</v>
@@ -6454,43 +6454,43 @@
         <v>5.39</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CH14" t="n">
         <v>1.42</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CO14" t="n">
         <v>1.29</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.26</v>
+        <v>3.29</v>
       </c>
       <c r="CR14" t="n">
         <v>1.42</v>
@@ -6505,10 +6505,10 @@
         <v>1.43</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CX14" t="n">
         <v>1.62</v>
@@ -6526,52 +6526,52 @@
         <v>1.32</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.46</v>
+        <v>3.51</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DH14" t="n">
-        <v>90.25</v>
+        <v>90.23</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="DM14" t="n">
-        <v>37.87</v>
+        <v>38.17</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.25</v>
+        <v>14.7</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.38</v>
+        <v>14.65</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.06</v>
+        <v>8.83</v>
       </c>
       <c r="DS14" t="n">
         <v>0.12</v>
@@ -6583,28 +6583,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.88</v>
+        <v>49.65</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.5</v>
+        <v>10.29</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.94</v>
+        <v>6.76</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.62</v>
+        <v>21.58</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="15">
@@ -6614,10 +6614,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>8</v>
@@ -6626,82 +6626,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="H15" t="n">
+        <v>104.67</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M15" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>55.33</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.62</v>
       </c>
-      <c r="G15" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="H15" t="n">
-        <v>104.38</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="K15" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M15" t="n">
-        <v>49.62</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P15" t="n">
-        <v>12.88</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>55</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AE15" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AF15" t="n">
         <v>0.12</v>
@@ -6785,70 +6785,70 @@
         <v>1.75</v>
       </c>
       <c r="BG15" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.44</v>
+        <v>10.12</v>
       </c>
       <c r="BI15" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL15" t="n">
         <v>0.88</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.56</v>
+        <v>4.41</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.88</v>
+        <v>5.71</v>
       </c>
       <c r="BR15" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS15" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT15" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BU15" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV15" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CA15" t="n">
         <v>3.82</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="CC15" t="n">
         <v>5.39</v>
@@ -6863,7 +6863,7 @@
         <v>2.65</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CH15" t="n">
         <v>1.46</v>
@@ -6872,7 +6872,7 @@
         <v>2.05</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK15" t="n">
         <v>1.51</v>
@@ -6881,10 +6881,10 @@
         <v>1.99</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CO15" t="n">
         <v>1.25</v>
@@ -6893,25 +6893,25 @@
         <v>1.83</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CU15" t="n">
         <v>1.47</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX15" t="n">
         <v>1.54</v>
@@ -6929,85 +6929,85 @@
         <v>1.27</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="DE15" t="n">
         <v>0.06</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="DH15" t="n">
-        <v>97.44</v>
+        <v>98</v>
       </c>
       <c r="DI15" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.87</v>
+        <v>5.7</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DM15" t="n">
-        <v>44.81</v>
+        <v>45.47</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.69</v>
+        <v>11.77</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.19</v>
+        <v>13.06</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.32</v>
+        <v>8.24</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>52.5</v>
+        <v>52.82</v>
       </c>
       <c r="DW15" t="n">
         <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.25</v>
+        <v>14.35</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.880000000000001</v>
+        <v>10.06</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.38</v>
+        <v>4.29</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.94</v>
+        <v>19.53</v>
       </c>
       <c r="EB15" t="n">
         <v>1.54</v>
       </c>
       <c r="EC15" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="16">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0.11</v>
@@ -7107,16 +7107,16 @@
         <v>2.56</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>78.14</v>
+        <v>78.88</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
@@ -7125,34 +7125,34 @@
         <v>3</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN16" t="n">
-        <v>27.71</v>
+        <v>30.12</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AQ16" t="n">
-        <v>14.14</v>
+        <v>14.12</v>
       </c>
       <c r="AR16" t="n">
-        <v>12</v>
+        <v>12.12</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.859999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7164,82 +7164,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>45.71</v>
+        <v>44.88</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.710000000000001</v>
+        <v>10.62</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.57</v>
+        <v>7.75</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="BD16" t="n">
-        <v>15.29</v>
+        <v>16</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BF16" t="n">
         <v>3</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.19</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BP16" t="n">
         <v>4</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.12</v>
+        <v>4.24</v>
       </c>
       <c r="BR16" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU16" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV16" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW16" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX16" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY16" t="n">
         <v>2.4</v>
@@ -7248,40 +7248,40 @@
         <v>2.55</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.77</v>
+        <v>3.79</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.54</v>
+        <v>4.5</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CH16" t="n">
         <v>1.49</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CK16" t="n">
         <v>1.55</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CM16" t="n">
         <v>2.31</v>
@@ -7293,10 +7293,10 @@
         <v>1.24</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="CR16" t="n">
         <v>1.38</v>
@@ -7311,10 +7311,10 @@
         <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CX16" t="n">
         <v>1.57</v>
@@ -7326,58 +7326,58 @@
         <v>2.33</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="DH16" t="n">
-        <v>81</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.31</v>
+        <v>3.47</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM16" t="n">
-        <v>35</v>
+        <v>35.71</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.87</v>
+        <v>14.82</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.32</v>
+        <v>12.35</v>
       </c>
       <c r="DR16" t="n">
-        <v>9.119999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="DS16" t="n">
         <v>0.06</v>
@@ -7389,28 +7389,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>49.75</v>
+        <v>49.12</v>
       </c>
       <c r="DW16" t="n">
         <v>0.06</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.12</v>
+        <v>12.41</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.880000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.13</v>
+        <v>17.36</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="17">
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>0.11</v>
@@ -7510,139 +7510,139 @@
         <v>1.67</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AI17" t="n">
-        <v>79.14</v>
+        <v>79.25</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.71</v>
+        <v>5.38</v>
       </c>
       <c r="AM17" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>33.62</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BL17" t="n">
         <v>0.71</v>
       </c>
-      <c r="AN17" t="n">
-        <v>34.43</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>43.29</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>15.86</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0.6899999999999999</v>
-      </c>
       <c r="BM17" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BO17" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.38</v>
+        <v>4.24</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.75</v>
+        <v>5.71</v>
       </c>
       <c r="BR17" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT17" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU17" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV17" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY17" t="n">
         <v>2.13</v>
@@ -7651,136 +7651,136 @@
         <v>2.13</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.55</v>
+        <v>3.46</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="CE17" t="n">
         <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI17" t="n">
         <v>1.98</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK17" t="n">
         <v>1.56</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.13</v>
+        <v>3.07</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY17" t="n">
         <v>1.95</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="DH17" t="n">
-        <v>93.37</v>
+        <v>92.59</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DK17" t="n">
-        <v>6</v>
+        <v>5.82</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="DM17" t="n">
-        <v>40.13</v>
+        <v>39.41</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="DP17" t="n">
-        <v>15.19</v>
+        <v>14.71</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.56</v>
+        <v>11</v>
       </c>
       <c r="DR17" t="n">
-        <v>8</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DS17" t="n">
         <v>0.06</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.44</v>
+        <v>51.24</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.31</v>
+        <v>12.82</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.119999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.19</v>
+        <v>3.94</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.69</v>
+        <v>19</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -4192,17 +4192,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>0.22</v>
@@ -4286,139 +4286,139 @@
         <v>2.78</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AI9" t="n">
-        <v>64.86</v>
+        <v>66.5</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>29.71</v>
+        <v>30.25</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ9" t="n">
         <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>15.57</v>
+        <v>16</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.140000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.14</v>
+        <v>1.62</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>46.71</v>
+        <v>46.12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BA9" t="n">
-        <v>10.71</v>
+        <v>11.12</v>
       </c>
       <c r="BB9" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="BD9" t="n">
-        <v>15.57</v>
+        <v>15</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="BF9" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="BG9" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="BH9" t="n">
-        <v>10</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BK9" t="n">
         <v>1</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.19</v>
+        <v>4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.81</v>
+        <v>5.71</v>
       </c>
       <c r="BR9" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS9" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BU9" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BV9" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY9" t="n">
         <v>3.09</v>
@@ -4427,25 +4427,25 @@
         <v>3.23</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.92</v>
+        <v>3.99</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.23</v>
+        <v>4.36</v>
       </c>
       <c r="CE9" t="n">
         <v>1.33</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CH9" t="n">
         <v>1.47</v>
@@ -4454,34 +4454,34 @@
         <v>2.11</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CK9" t="n">
         <v>1.54</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CO9" t="n">
         <v>1.23</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CT9" t="n">
         <v>3.2</v>
@@ -4496,100 +4496,100 @@
         <v>1.7</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="DA9" t="n">
         <v>1.88</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="DH9" t="n">
-        <v>81.19</v>
+        <v>81</v>
       </c>
       <c r="DI9" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.12</v>
+        <v>3.23</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.31</v>
+        <v>5.17</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM9" t="n">
-        <v>37.62</v>
+        <v>37.41</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.12</v>
+        <v>13.17</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.13</v>
+        <v>16.3</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.87</v>
+        <v>7.94</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>53.87</v>
+        <v>53.17</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DX9" t="n">
         <v>14.12</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.5</v>
+        <v>9.59</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.62</v>
+        <v>4.53</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.88</v>
+        <v>17.47</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="10">
@@ -4599,94 +4599,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="F10" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="H10" t="n">
-        <v>70.29000000000001</v>
+        <v>70.88</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="J10" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="K10" t="n">
-        <v>5.29</v>
+        <v>5.38</v>
       </c>
       <c r="L10" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="M10" t="n">
-        <v>31.14</v>
+        <v>31.12</v>
       </c>
       <c r="N10" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="O10" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="P10" t="n">
-        <v>12.86</v>
+        <v>12</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.71</v>
+        <v>13</v>
       </c>
       <c r="R10" t="n">
-        <v>11.14</v>
+        <v>11</v>
       </c>
       <c r="S10" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="U10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>41.71</v>
+        <v>41.12</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.43</v>
+        <v>14</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.859999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.57</v>
+        <v>5.12</v>
       </c>
       <c r="AC10" t="n">
-        <v>17.57</v>
+        <v>18.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AF10" t="n">
         <v>0.11</v>
@@ -4770,70 +4770,70 @@
         <v>2.11</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.119999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="BO10" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.56</v>
+        <v>4.88</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="BR10" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS10" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU10" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BV10" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="BX10" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.04</v>
+        <v>3.99</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="CC10" t="n">
         <v>5.7</v>
@@ -4845,28 +4845,28 @@
         <v>1.35</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CH10" t="n">
         <v>1.44</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK10" t="n">
         <v>1.58</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CN10" t="n">
         <v>1.78</v>
@@ -4875,28 +4875,28 @@
         <v>1.26</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CU10" t="n">
         <v>1.44</v>
       </c>
       <c r="CV10" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX10" t="n">
         <v>1.6</v>
@@ -4908,7 +4908,7 @@
         <v>2.3</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DB10" t="n">
         <v>1.29</v>
@@ -4917,82 +4917,82 @@
         <v>1.94</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="DG10" t="n">
         <v>2</v>
       </c>
       <c r="DH10" t="n">
-        <v>67.25</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.06</v>
+        <v>-0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.94</v>
+        <v>4.06</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="DM10" t="n">
-        <v>28.43</v>
+        <v>28.58</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.19</v>
+        <v>12.76</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14</v>
+        <v>14.06</v>
       </c>
       <c r="DR10" t="n">
-        <v>11.25</v>
+        <v>11.17</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>40.62</v>
+        <v>40.41</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.38</v>
+        <v>10.82</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.13</v>
+        <v>7.24</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.13</v>
+        <v>18.53</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="11">
@@ -5955,7 +5955,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>45.56</v>
+        <v>45.67</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.22</v>
@@ -6180,7 +6180,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48</v>
+        <v>48.06</v>
       </c>
       <c r="DW13" t="n">
         <v>0.12</v>
@@ -6680,7 +6680,7 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>55.33</v>
+        <v>55.22</v>
       </c>
       <c r="Y15" t="n">
         <v>0.11</v>
@@ -6986,7 +6986,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>52.82</v>
+        <v>52.76</v>
       </c>
       <c r="DW15" t="n">
         <v>0.06</v>
@@ -7173,16 +7173,16 @@
         <v>10.62</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.75</v>
+        <v>7.62</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BD16" t="n">
         <v>16</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BF16" t="n">
         <v>3</v>
@@ -7398,10 +7398,10 @@
         <v>12.41</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.300000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="EA16" t="n">
         <v>17.36</v>
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
         <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7913,139 +7913,139 @@
         <v>1.44</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="n">
-        <v>74.43000000000001</v>
+        <v>78.12</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.14</v>
+        <v>4.38</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>29.86</v>
+        <v>32.25</v>
       </c>
       <c r="AO18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>51.88</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BK18" t="n">
         <v>0.71</v>
       </c>
-      <c r="AP18" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>11.29</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>50.29</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>17.14</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0.6899999999999999</v>
-      </c>
       <c r="BL18" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.19</v>
+        <v>4.53</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.06</v>
+        <v>4.88</v>
       </c>
       <c r="BR18" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS18" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT18" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU18" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BV18" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BW18" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BX18" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY18" t="n">
         <v>1.75</v>
@@ -8054,16 +8054,16 @@
         <v>1.75</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.87</v>
+        <v>3.83</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.97</v>
+        <v>3.93</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.72</v>
+        <v>3.52</v>
       </c>
       <c r="CD18" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="CE18" t="n">
         <v>1.34</v>
@@ -8072,25 +8072,25 @@
         <v>2.53</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI18" t="n">
         <v>2.06</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CN18" t="n">
         <v>1.85</v>
@@ -8102,13 +8102,13 @@
         <v>1.77</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CT18" t="n">
         <v>3.22</v>
@@ -8117,7 +8117,7 @@
         <v>1.51</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CW18" t="n">
         <v>1.74</v>
@@ -8135,13 +8135,13 @@
         <v>1.88</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="DE18" t="n">
         <v>0.06</v>
@@ -8150,73 +8150,73 @@
         <v>1.06</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="DH18" t="n">
-        <v>92.25</v>
+        <v>92.94</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.69</v>
+        <v>42.12</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.69</v>
+        <v>11.88</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.38</v>
+        <v>13.82</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.619999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>53.63</v>
+        <v>54.18</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX18" t="n">
-        <v>16.44</v>
+        <v>16.29</v>
       </c>
       <c r="DY18" t="n">
-        <v>10.44</v>
+        <v>10.24</v>
       </c>
       <c r="DZ18" t="n">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.75</v>
+        <v>19.77</v>
       </c>
       <c r="EB18" t="n">
         <v>1.76</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="19">
@@ -8226,10 +8226,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -8241,79 +8241,79 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>79.14</v>
+        <v>81.38</v>
       </c>
       <c r="I19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J19" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="K19" t="n">
-        <v>5.14</v>
+        <v>4.75</v>
       </c>
       <c r="L19" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="M19" t="n">
-        <v>41.57</v>
+        <v>40.5</v>
       </c>
       <c r="N19" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="P19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.57</v>
+        <v>12.75</v>
       </c>
       <c r="R19" t="n">
-        <v>8.140000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="S19" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>1.14</v>
+        <v>1.62</v>
       </c>
       <c r="U19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>50.43</v>
+        <v>51.38</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z19" t="n">
-        <v>12</v>
+        <v>12.62</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.289999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.71</v>
+        <v>4.12</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.71</v>
+        <v>17.62</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8397,70 +8397,70 @@
         <v>2.11</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.38</v>
+        <v>11</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.62</v>
+        <v>4.41</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.69</v>
+        <v>6.53</v>
       </c>
       <c r="BR19" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT19" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU19" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BV19" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BW19" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BX19" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.74</v>
+        <v>2.61</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.59</v>
+        <v>3.62</v>
       </c>
       <c r="CC19" t="n">
         <v>2.96</v>
@@ -8472,16 +8472,16 @@
         <v>1.34</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CG19" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CH19" t="n">
         <v>1.45</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.72</v>
@@ -8490,34 +8490,34 @@
         <v>1.55</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CO19" t="n">
         <v>1.23</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CR19" t="n">
         <v>1.39</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CT19" t="n">
         <v>3.13</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CV19" t="n">
         <v>2.2</v>
@@ -8529,97 +8529,97 @@
         <v>1.55</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB19" t="n">
         <v>1.27</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DG19" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.25</v>
+        <v>93.47</v>
       </c>
       <c r="DI19" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="DN19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DO19" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="DP19" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="DQ19" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="DR19" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="DS19" t="n">
         <v>0.12</v>
       </c>
-      <c r="DJ19" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="DK19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="DL19" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="DM19" t="n">
-        <v>44.38</v>
-      </c>
-      <c r="DN19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="DO19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DP19" t="n">
-        <v>12.87</v>
-      </c>
-      <c r="DQ19" t="n">
-        <v>14.18</v>
-      </c>
-      <c r="DR19" t="n">
-        <v>7.94</v>
-      </c>
-      <c r="DS19" t="n">
-        <v>0.13</v>
-      </c>
       <c r="DT19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.06</v>
+        <v>55.24</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.69</v>
+        <v>12.94</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.57</v>
+        <v>8.65</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.12</v>
+        <v>4.29</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.69</v>
+        <v>17.65</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>64.89</v>
+        <v>64.78</v>
       </c>
       <c r="Y8" t="n">
         <v>0.22</v>
@@ -4165,7 +4165,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>62.17</v>
+        <v>62.12</v>
       </c>
       <c r="DW8" t="n">
         <v>0.12</v>
@@ -5552,7 +5552,7 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>40.33</v>
+        <v>40.44</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.11</v>
@@ -5777,7 +5777,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>44.35</v>
+        <v>44.41</v>
       </c>
       <c r="DW12" t="n">
         <v>0.11</v>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1875,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="n">
         <v>1.22</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="AL3" t="n">
         <v>3.11</v>
@@ -1950,7 +1950,7 @@
         <v>0.76</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="BG3" t="n">
         <v>2.76</v>
@@ -2106,7 +2106,7 @@
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="DG3" t="n">
         <v>1.94</v>
@@ -2118,7 +2118,7 @@
         <v>0.12</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="DK3" t="n">
         <v>3.88</v>
@@ -2175,7 +2175,7 @@
         <v>0.99</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="4">
@@ -4208,7 +4208,7 @@
         <v>0.22</v>
       </c>
       <c r="F9" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="G9" t="n">
         <v>4.78</v>
@@ -4220,7 +4220,7 @@
         <v>0.22</v>
       </c>
       <c r="J9" t="n">
-        <v>3.22</v>
+        <v>3.33</v>
       </c>
       <c r="K9" t="n">
         <v>7</v>
@@ -4283,7 +4283,7 @@
         <v>1.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="AF9" t="n">
         <v>0.12</v>
@@ -4520,7 +4520,7 @@
         <v>0.17</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="DG9" t="n">
         <v>3.42</v>
@@ -4532,7 +4532,7 @@
         <v>0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="DK9" t="n">
         <v>5.17</v>
@@ -4589,7 +4589,7 @@
         <v>1.48</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -5823,7 +5823,7 @@
         <v>1.62</v>
       </c>
       <c r="G13" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="H13" t="n">
         <v>82.25</v>
@@ -5838,7 +5838,7 @@
         <v>4.88</v>
       </c>
       <c r="L13" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="M13" t="n">
         <v>46.25</v>
@@ -5847,7 +5847,7 @@
         <v>0.75</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
         <v>12.25</v>
@@ -6006,10 +6006,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="BP13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ13" t="n">
         <v>4.35</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>4.82</v>
       </c>
       <c r="BR13" t="n">
         <v>94.12</v>
@@ -6135,7 +6135,7 @@
         <v>1.88</v>
       </c>
       <c r="DG13" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DH13" t="n">
         <v>83</v>
@@ -6150,7 +6150,7 @@
         <v>4.47</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.65</v>
+        <v>0.53</v>
       </c>
       <c r="DM13" t="n">
         <v>41.12</v>
@@ -6159,7 +6159,7 @@
         <v>0.71</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.53</v>
+        <v>2.17</v>
       </c>
       <c r="DP13" t="n">
         <v>13.23</v>
@@ -7110,7 +7110,7 @@
         <v>0.25</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="n">
         <v>2</v>
@@ -7122,7 +7122,7 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AL16" t="n">
         <v>2.75</v>
@@ -7185,7 +7185,7 @@
         <v>1.1</v>
       </c>
       <c r="BF16" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BG16" t="n">
         <v>2.59</v>
@@ -7341,7 +7341,7 @@
         <v>0.18</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="DG16" t="n">
         <v>2.12</v>
@@ -7353,7 +7353,7 @@
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="DK16" t="n">
         <v>3.47</v>
@@ -7410,7 +7410,7 @@
         <v>1.26</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="17">
@@ -7492,10 +7492,10 @@
         <v>0.11</v>
       </c>
       <c r="Z17" t="n">
-        <v>14</v>
+        <v>14.11</v>
       </c>
       <c r="AA17" t="n">
-        <v>9.890000000000001</v>
+        <v>10</v>
       </c>
       <c r="AB17" t="n">
         <v>4.11</v>
@@ -7504,7 +7504,7 @@
         <v>20.89</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE17" t="n">
         <v>1.67</v>
@@ -7516,7 +7516,7 @@
         <v>1.75</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.88</v>
+        <v>2.12</v>
       </c>
       <c r="AI17" t="n">
         <v>79.25</v>
@@ -7531,7 +7531,7 @@
         <v>5.38</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="AN17" t="n">
         <v>33.62</v>
@@ -7540,7 +7540,7 @@
         <v>1.12</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ17" t="n">
         <v>13.5</v>
@@ -7618,10 +7618,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.24</v>
+        <v>3.88</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.71</v>
+        <v>5.24</v>
       </c>
       <c r="BR17" t="n">
         <v>88.23999999999999</v>
@@ -7747,7 +7747,7 @@
         <v>1.53</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.47</v>
+        <v>3.12</v>
       </c>
       <c r="DH17" t="n">
         <v>92.59</v>
@@ -7762,7 +7762,7 @@
         <v>5.82</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="DM17" t="n">
         <v>39.41</v>
@@ -7771,7 +7771,7 @@
         <v>0.76</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="DP17" t="n">
         <v>14.71</v>
@@ -7798,10 +7798,10 @@
         <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.82</v>
+        <v>12.88</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.880000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="DZ17" t="n">
         <v>3.94</v>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F2" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="H2" t="n">
-        <v>93.25</v>
+        <v>92.11</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="K2" t="n">
-        <v>5.88</v>
+        <v>5.89</v>
       </c>
       <c r="L2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M2" t="n">
-        <v>45.62</v>
+        <v>45.22</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="O2" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="P2" t="n">
-        <v>13</v>
+        <v>12.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>15.5</v>
+        <v>14.89</v>
       </c>
       <c r="R2" t="n">
-        <v>5.62</v>
+        <v>5.78</v>
       </c>
       <c r="S2" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="T2" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="U2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>50.88</v>
+        <v>50.22</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.5</v>
+        <v>12.11</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="AC2" t="n">
-        <v>18.25</v>
+        <v>17.22</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2.33</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.35</v>
+        <v>8.56</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.65</v>
+        <v>0.78</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.59</v>
+        <v>3.67</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.76</v>
+        <v>4.89</v>
       </c>
       <c r="BR2" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BS2" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BU2" t="n">
-        <v>11.76</v>
+        <v>16.67</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.89</v>
+        <v>3.17</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.94</v>
+        <v>3.31</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="CC2" t="n">
         <v>4.03</v>
@@ -1631,22 +1631,22 @@
         <v>2.96</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CL2" t="n">
         <v>2.12</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CN2" t="n">
         <v>1.64</v>
@@ -1673,10 +1673,10 @@
         <v>1.44</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX2" t="n">
         <v>1.73</v>
@@ -1700,46 +1700,46 @@
         <v>3.26</v>
       </c>
       <c r="DE2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="DH2" t="n">
-        <v>85.81999999999999</v>
+        <v>85.66</v>
       </c>
       <c r="DI2" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.71</v>
+        <v>4.78</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM2" t="n">
-        <v>40.94</v>
+        <v>41</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.77</v>
+        <v>12.62</v>
       </c>
       <c r="DQ2" t="n">
-        <v>15.94</v>
+        <v>15.61</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.71</v>
+        <v>6.72</v>
       </c>
       <c r="DS2" t="n">
         <v>0.11</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>48.35</v>
+        <v>48.16</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.12</v>
+        <v>11.94</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.18</v>
+        <v>8.06</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.29</v>
+        <v>18.72</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,49 +1875,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" t="n">
-        <v>69.89</v>
+        <v>70.3</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN3" t="n">
-        <v>25.44</v>
+        <v>26.6</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.89</v>
+        <v>12.7</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.44</v>
+        <v>13.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.11</v>
+        <v>10.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>42.78</v>
+        <v>42.6</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.11</v>
+        <v>6.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>20.44</v>
+        <v>20.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.119999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BM3" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.82</v>
+        <v>4.94</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.29</v>
+        <v>4.44</v>
       </c>
       <c r="BR3" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS3" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU3" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV3" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX3" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY3" t="n">
         <v>3.45</v>
@@ -2013,16 +2013,16 @@
         <v>3.84</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.44</v>
+        <v>5.22</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.98</v>
+        <v>5.77</v>
       </c>
       <c r="CE3" t="n">
         <v>1.37</v>
@@ -2058,22 +2058,22 @@
         <v>1.28</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CR3" t="n">
         <v>1.42</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV3" t="n">
         <v>1.98</v>
@@ -2097,52 +2097,52 @@
         <v>1.32</v>
       </c>
       <c r="DC3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="DG3" t="n">
         <v>1.94</v>
       </c>
       <c r="DH3" t="n">
-        <v>74.23</v>
+        <v>74.22</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM3" t="n">
-        <v>29.59</v>
+        <v>30</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DO3" t="n">
         <v>1.94</v>
       </c>
       <c r="DP3" t="n">
-        <v>12.18</v>
+        <v>12.11</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.12</v>
+        <v>15.28</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.529999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.65</v>
+        <v>43.5</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.289999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DY3" t="n">
         <v>4.89</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.47</v>
+        <v>19.45</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="4">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0.11</v>
@@ -2678,139 +2678,139 @@
         <v>2.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>75.5</v>
+        <v>72.33</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>33.62</v>
+        <v>31.89</v>
       </c>
       <c r="AO5" t="n">
         <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.88</v>
+        <v>13.89</v>
       </c>
       <c r="AR5" t="n">
-        <v>17.5</v>
+        <v>16.33</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.38</v>
+        <v>7.78</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>49</v>
+        <v>46.89</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.38</v>
+        <v>11.22</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.25</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.62</v>
+        <v>17.33</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="BG5" t="n">
         <v>2</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.24</v>
+        <v>10.06</v>
       </c>
       <c r="BI5" t="n">
         <v>2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.35</v>
+        <v>4.44</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.82</v>
+        <v>5.56</v>
       </c>
       <c r="BR5" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS5" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BV5" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BY5" t="n">
         <v>3.49</v>
@@ -2819,22 +2819,22 @@
         <v>3.73</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.1</v>
+        <v>4.31</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.3</v>
+        <v>4.66</v>
       </c>
       <c r="CE5" t="n">
         <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CG5" t="n">
         <v>2.98</v>
@@ -2843,7 +2843,7 @@
         <v>1.45</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.74</v>
@@ -2855,7 +2855,7 @@
         <v>2.03</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CN5" t="n">
         <v>1.81</v>
@@ -2867,25 +2867,25 @@
         <v>1.83</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS5" t="n">
         <v>2.76</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CU5" t="n">
         <v>1.48</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX5" t="n">
         <v>1.57</v>
@@ -2906,49 +2906,49 @@
         <v>1.86</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="DE5" t="n">
         <v>0.11</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="DH5" t="n">
-        <v>76.34999999999999</v>
+        <v>74.72</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.18</v>
+        <v>4.06</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="DM5" t="n">
-        <v>36.94</v>
+        <v>35.89</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.18</v>
+        <v>12.28</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.59</v>
+        <v>15.11</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.41</v>
+        <v>7.61</v>
       </c>
       <c r="DS5" t="n">
         <v>0.06</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.88</v>
+        <v>49.72</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.53</v>
+        <v>11.44</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.76</v>
+        <v>7.78</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.76</v>
+        <v>3.66</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.18</v>
+        <v>18</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,49 +3084,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AI6" t="n">
-        <v>83.12</v>
+        <v>82.67</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>38.75</v>
+        <v>36.89</v>
       </c>
       <c r="AO6" t="n">
         <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13.75</v>
+        <v>13.11</v>
       </c>
       <c r="AR6" t="n">
-        <v>14.38</v>
+        <v>14.67</v>
       </c>
       <c r="AS6" t="n">
-        <v>10.12</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AT6" t="n">
         <v>2</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>46.25</v>
+        <v>45.33</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.25</v>
+        <v>11.22</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="BC6" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="BD6" t="n">
-        <v>20.62</v>
+        <v>20.33</v>
       </c>
       <c r="BE6" t="n">
         <v>1.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.529999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BO6" t="n">
         <v>1.06</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.53</v>
+        <v>4.39</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT6" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU6" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV6" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX6" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY6" t="n">
         <v>3.4</v>
@@ -3222,34 +3222,34 @@
         <v>3.52</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.14</v>
+        <v>4.18</v>
       </c>
       <c r="CC6" t="n">
-        <v>6.5</v>
+        <v>6.44</v>
       </c>
       <c r="CD6" t="n">
         <v>7.12</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CH6" t="n">
         <v>1.46</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CK6" t="n">
         <v>1.58</v>
@@ -3258,19 +3258,19 @@
         <v>2.11</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CO6" t="n">
         <v>1.24</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="CR6" t="n">
         <v>1.41</v>
@@ -3291,13 +3291,13 @@
         <v>1.83</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY6" t="n">
         <v>1.98</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="DA6" t="n">
         <v>1.83</v>
@@ -3306,52 +3306,52 @@
         <v>1.28</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.41</v>
+        <v>87.89</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.71</v>
+        <v>3.56</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM6" t="n">
-        <v>37</v>
+        <v>36.16</v>
       </c>
       <c r="DN6" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.3</v>
+        <v>13.94</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.59</v>
+        <v>14.72</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.23</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DS6" t="n">
         <v>0.06</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47.41</v>
+        <v>46.88</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.7</v>
+        <v>10.72</v>
       </c>
       <c r="DY6" t="n">
-        <v>8</v>
+        <v>7.89</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.47</v>
+        <v>20.33</v>
       </c>
       <c r="EB6" t="n">
         <v>1.14</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0.12</v>
@@ -3484,139 +3484,139 @@
         <v>2.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="AI7" t="n">
-        <v>98.78</v>
+        <v>98.7</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
       </c>
       <c r="AM7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>43</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BK7" t="n">
         <v>0.78</v>
       </c>
-      <c r="AN7" t="n">
-        <v>43.56</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>13.56</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>12.44</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>57.11</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>17.67</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.76</v>
-      </c>
       <c r="BL7" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="BP7" t="n">
         <v>4.94</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.94</v>
+        <v>5.06</v>
       </c>
       <c r="BR7" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS7" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT7" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU7" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BV7" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BW7" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX7" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY7" t="n">
         <v>1.39</v>
@@ -3625,31 +3625,31 @@
         <v>1.39</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.96</v>
+        <v>4.92</v>
       </c>
       <c r="CB7" t="n">
-        <v>5.16</v>
+        <v>5.1</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CE7" t="n">
         <v>1.28</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.8</v>
@@ -3658,22 +3658,22 @@
         <v>1.54</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CN7" t="n">
         <v>1.83</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
@@ -3709,85 +3709,85 @@
         <v>1.22</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.89</v>
+        <v>3.06</v>
       </c>
       <c r="DH7" t="n">
-        <v>107.53</v>
+        <v>107</v>
       </c>
       <c r="DI7" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.29</v>
+        <v>6.28</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="DM7" t="n">
-        <v>50.41</v>
+        <v>49.72</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.41</v>
+        <v>3.22</v>
       </c>
       <c r="DP7" t="n">
-        <v>13.24</v>
+        <v>13.06</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.12</v>
+        <v>12.95</v>
       </c>
       <c r="DR7" t="n">
-        <v>5.41</v>
+        <v>5.33</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59</v>
+        <v>58.78</v>
       </c>
       <c r="DW7" t="n">
         <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>18.53</v>
+        <v>18.17</v>
       </c>
       <c r="DY7" t="n">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="DZ7" t="n">
-        <v>6.82</v>
+        <v>6.67</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.18</v>
+        <v>19.22</v>
       </c>
       <c r="EB7" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="8">
@@ -3797,61 +3797,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F8" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="H8" t="n">
-        <v>97.44</v>
+        <v>102.8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J8" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="L8" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M8" t="n">
-        <v>55.22</v>
+        <v>55.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>10.78</v>
+        <v>11.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.44</v>
+        <v>10.6</v>
       </c>
       <c r="R8" t="n">
-        <v>6.56</v>
+        <v>6.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>64.78</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>13.89</v>
+        <v>13.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.11</v>
+        <v>6.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.56</v>
+        <v>21.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AF8" t="n">
         <v>0.12</v>
@@ -3968,70 +3968,70 @@
         <v>2.62</v>
       </c>
       <c r="BG8" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.76</v>
+        <v>8.94</v>
       </c>
       <c r="BI8" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.88</v>
+        <v>4.06</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="BR8" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS8" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU8" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV8" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.44</v>
+        <v>5.56</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.81</v>
+        <v>5.93</v>
       </c>
       <c r="CC8" t="n">
         <v>1.58</v>
@@ -4043,51 +4043,51 @@
         <v>1.22</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK8" t="n">
         <v>1.48</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CN8" t="n">
         <v>1.92</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="CP8" t="n">
         <v>1.45</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CW8" t="n">
         <v>1.77</v>
@@ -4111,82 +4111,82 @@
         <v>1.47</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="DH8" t="n">
-        <v>94.88</v>
+        <v>98</v>
       </c>
       <c r="DI8" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.94</v>
+        <v>5.22</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM8" t="n">
-        <v>50.29</v>
+        <v>50.67</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.94</v>
+        <v>12.22</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.76</v>
+        <v>10.83</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.47</v>
+        <v>7.39</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>62.12</v>
+        <v>62.44</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX8" t="n">
-        <v>17.53</v>
+        <v>17.5</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.35</v>
+        <v>11.5</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6.17</v>
+        <v>6</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.53</v>
+        <v>19.83</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="9">
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0.22</v>
@@ -4286,139 +4286,139 @@
         <v>2.89</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AI9" t="n">
-        <v>66.5</v>
+        <v>64.89</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN9" t="n">
-        <v>30.25</v>
+        <v>29</v>
       </c>
       <c r="AO9" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14</v>
+        <v>13.78</v>
       </c>
       <c r="AR9" t="n">
-        <v>16</v>
+        <v>16.11</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.119999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AU9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO9" t="n">
         <v>1.5</v>
       </c>
-      <c r="AV9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>46.12</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.59</v>
-      </c>
       <c r="BP9" t="n">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS9" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT9" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BU9" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV9" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX9" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY9" t="n">
         <v>3.09</v>
@@ -4427,73 +4427,73 @@
         <v>3.23</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.78</v>
+        <v>4.02</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.36</v>
+        <v>5.36</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.07</v>
+        <v>3.15</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="CT9" t="n">
         <v>3.2</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CX9" t="n">
         <v>1.58</v>
@@ -4511,85 +4511,85 @@
         <v>1.25</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="DD9" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="DH9" t="n">
-        <v>81</v>
+        <v>79.39</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.29</v>
+        <v>3.22</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="DM9" t="n">
-        <v>37.41</v>
+        <v>36.39</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.17</v>
+        <v>13.11</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.3</v>
+        <v>16.33</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.94</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>53.17</v>
+        <v>52</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.12</v>
+        <v>13.89</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.59</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.47</v>
+        <v>17.89</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="EC9" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="10">
@@ -4599,94 +4599,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="G10" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="H10" t="n">
-        <v>70.88</v>
+        <v>71.89</v>
       </c>
       <c r="I10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J10" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="K10" t="n">
-        <v>5.38</v>
+        <v>5.22</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M10" t="n">
-        <v>31.12</v>
+        <v>30.22</v>
       </c>
       <c r="N10" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O10" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="P10" t="n">
-        <v>12</v>
+        <v>11.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>13</v>
+        <v>13.11</v>
       </c>
       <c r="R10" t="n">
         <v>11</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T10" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="U10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>41.12</v>
+        <v>42.33</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>14</v>
+        <v>13.22</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.880000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.12</v>
+        <v>4.89</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.5</v>
+        <v>18.44</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AF10" t="n">
         <v>0.11</v>
@@ -4770,70 +4770,70 @@
         <v>2.11</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.289999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL10" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.88</v>
+        <v>4.83</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.35</v>
+        <v>4.44</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS10" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU10" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV10" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX10" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.99</v>
+        <v>3.73</v>
       </c>
       <c r="CB10" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="CC10" t="n">
         <v>5.7</v>
@@ -4842,52 +4842,52 @@
         <v>6.75</v>
       </c>
       <c r="CE10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="CH10" t="n">
         <v>1.35</v>
       </c>
-      <c r="CF10" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="CG10" t="n">
-        <v>3</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>1.44</v>
-      </c>
       <c r="CI10" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.27</v>
+        <v>2.13</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.12</v>
+        <v>3.02</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="CU10" t="n">
         <v>1.44</v>
@@ -4911,88 +4911,88 @@
         <v>1.81</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.29</v>
+        <v>3.34</v>
       </c>
       <c r="DE10" t="n">
         <v>0.11</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="DG10" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DH10" t="n">
-        <v>67.70999999999999</v>
+        <v>68.39</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="DK10" t="n">
         <v>4.06</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM10" t="n">
-        <v>28.58</v>
+        <v>28.28</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DO10" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.76</v>
+        <v>12.56</v>
       </c>
       <c r="DQ10" t="n">
         <v>14.06</v>
       </c>
       <c r="DR10" t="n">
-        <v>11.17</v>
+        <v>11.16</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>40.41</v>
+        <v>41.06</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.82</v>
+        <v>10.61</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.24</v>
+        <v>7.06</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.53</v>
+        <v>18.5</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="11">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
@@ -5417,82 +5417,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="G12" t="n">
-        <v>3.38</v>
+        <v>3.56</v>
       </c>
       <c r="H12" t="n">
-        <v>90.12</v>
+        <v>90.56</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="J12" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="K12" t="n">
-        <v>5.88</v>
+        <v>6.33</v>
       </c>
       <c r="L12" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="M12" t="n">
-        <v>46.25</v>
+        <v>46.56</v>
       </c>
       <c r="N12" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="P12" t="n">
-        <v>13.75</v>
+        <v>14.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>15.38</v>
+        <v>14.89</v>
       </c>
       <c r="R12" t="n">
-        <v>6.75</v>
+        <v>6.78</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="T12" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="U12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>48.88</v>
+        <v>50</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.12</v>
+        <v>12.89</v>
       </c>
       <c r="AA12" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.38</v>
+        <v>20.11</v>
       </c>
       <c r="AD12" t="n">
         <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5576,70 +5576,70 @@
         <v>2.11</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.65</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BP12" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>77.78</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>38.89</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="BZ12" t="n">
         <v>3.76</v>
       </c>
-      <c r="BQ12" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>82.34999999999999</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>70.59</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>41.18</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>17.65</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>52.94</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>3.95</v>
-      </c>
       <c r="CA12" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="CC12" t="n">
         <v>3.87</v>
@@ -5651,22 +5651,22 @@
         <v>1.35</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CH12" t="n">
         <v>1.45</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.72</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL12" t="n">
         <v>2</v>
@@ -5681,28 +5681,28 @@
         <v>1.25</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX12" t="n">
         <v>1.55</v>
@@ -5711,61 +5711,61 @@
         <v>1.91</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="DH12" t="n">
-        <v>85.7</v>
+        <v>86.17</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.88</v>
+        <v>5.16</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.53</v>
+        <v>0.66</v>
       </c>
       <c r="DM12" t="n">
-        <v>40.59</v>
+        <v>41.06</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.82</v>
+        <v>15</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.59</v>
+        <v>12.5</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.77</v>
+        <v>7.72</v>
       </c>
       <c r="DS12" t="n">
         <v>0.06</v>
@@ -5777,28 +5777,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>44.41</v>
+        <v>45.22</v>
       </c>
       <c r="DW12" t="n">
         <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.64</v>
+        <v>10.66</v>
       </c>
       <c r="DY12" t="n">
-        <v>8</v>
+        <v>7.94</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.71</v>
+        <v>20.06</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="13">
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
@@ -6223,82 +6223,82 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H14" t="n">
-        <v>93.11</v>
+        <v>94.5</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="J14" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="K14" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M14" t="n">
-        <v>36</v>
+        <v>37.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O14" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="P14" t="n">
-        <v>14.22</v>
+        <v>14.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>14.78</v>
+        <v>14.7</v>
       </c>
       <c r="R14" t="n">
-        <v>8.67</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>48.67</v>
+        <v>48.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.33</v>
+        <v>11.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.22</v>
+        <v>7.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>23.33</v>
+        <v>23.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6382,70 +6382,70 @@
         <v>2.88</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.35</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.47</v>
+        <v>4.28</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.82</v>
+        <v>3.94</v>
       </c>
       <c r="BR14" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS14" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BT14" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BU14" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV14" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="CC14" t="n">
         <v>5.2</v>
@@ -6457,13 +6457,13 @@
         <v>1.38</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="CG14" t="n">
         <v>2.9</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI14" t="n">
         <v>1.91</v>
@@ -6475,7 +6475,7 @@
         <v>1.62</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CM14" t="n">
         <v>2.19</v>
@@ -6487,28 +6487,28 @@
         <v>1.29</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="CR14" t="n">
         <v>1.42</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX14" t="n">
         <v>1.62</v>
@@ -6520,91 +6520,91 @@
         <v>2.25</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB14" t="n">
         <v>1.32</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="DH14" t="n">
-        <v>90.23</v>
+        <v>91.17</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM14" t="n">
-        <v>38.17</v>
+        <v>38.66</v>
       </c>
       <c r="DN14" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.7</v>
+        <v>14.78</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.65</v>
+        <v>14.61</v>
       </c>
       <c r="DR14" t="n">
         <v>8.83</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.65</v>
+        <v>49.28</v>
       </c>
       <c r="DW14" t="n">
         <v>0.11</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.29</v>
+        <v>10.55</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.76</v>
+        <v>6.94</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.53</v>
+        <v>3.61</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.58</v>
+        <v>21.83</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="15">
@@ -6614,10 +6614,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>8</v>
@@ -6626,82 +6626,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>104.67</v>
+        <v>109.2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="K15" t="n">
-        <v>6.22</v>
+        <v>6.1</v>
       </c>
       <c r="L15" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="M15" t="n">
-        <v>50.33</v>
+        <v>52.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>12.89</v>
+        <v>12.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.78</v>
+        <v>12</v>
       </c>
       <c r="R15" t="n">
-        <v>7.78</v>
+        <v>7.7</v>
       </c>
       <c r="S15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>55.22</v>
+        <v>56.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>15.22</v>
+        <v>15.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.11</v>
+        <v>11.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.33</v>
+        <v>22.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AF15" t="n">
         <v>0.12</v>
@@ -6785,70 +6785,70 @@
         <v>1.75</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.12</v>
+        <v>9.94</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.41</v>
+        <v>4.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.71</v>
+        <v>5.44</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS15" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT15" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU15" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
       <c r="CC15" t="n">
         <v>5.39</v>
@@ -6869,10 +6869,10 @@
         <v>1.46</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK15" t="n">
         <v>1.51</v>
@@ -6893,25 +6893,25 @@
         <v>1.83</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CU15" t="n">
         <v>1.47</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CX15" t="n">
         <v>1.54</v>
@@ -6929,85 +6929,85 @@
         <v>1.27</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="DH15" t="n">
-        <v>98</v>
+        <v>100.89</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.7</v>
+        <v>5.66</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="DM15" t="n">
-        <v>45.47</v>
+        <v>46.83</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.77</v>
+        <v>11.5</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.06</v>
+        <v>13.11</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.24</v>
+        <v>8.17</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>52.76</v>
+        <v>53.72</v>
       </c>
       <c r="DW15" t="n">
         <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.35</v>
+        <v>14.56</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.06</v>
+        <v>10.28</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.53</v>
+        <v>20.72</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="16">
@@ -7242,13 +7242,13 @@
         <v>52.94</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="BZ16" t="n">
         <v>2.55</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.79</v>
+        <v>3.56</v>
       </c>
       <c r="CB16" t="n">
         <v>3.9</v>
@@ -7260,43 +7260,43 @@
         <v>4.5</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="CR16" t="n">
         <v>1.38</v>
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>0.11</v>
@@ -7510,139 +7510,139 @@
         <v>1.67</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AI17" t="n">
-        <v>79.25</v>
+        <v>79.56</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.38</v>
+        <v>5.44</v>
       </c>
       <c r="AM17" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>35.11</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>46.11</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BK17" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN17" t="n">
-        <v>33.62</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>45.88</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>16.88</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.47</v>
-      </c>
       <c r="BL17" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO17" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.24</v>
+        <v>5.28</v>
       </c>
       <c r="BR17" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS17" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT17" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU17" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV17" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY17" t="n">
         <v>2.13</v>
@@ -7651,31 +7651,31 @@
         <v>2.13</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.46</v>
+        <v>3.39</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.77</v>
+        <v>3.73</v>
       </c>
       <c r="CE17" t="n">
         <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="CH17" t="n">
         <v>1.42</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.76</v>
@@ -7684,7 +7684,7 @@
         <v>1.56</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CM17" t="n">
         <v>2.29</v>
@@ -7696,91 +7696,91 @@
         <v>1.28</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX17" t="n">
         <v>1.58</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DA17" t="n">
         <v>1.85</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.59</v>
+        <v>92</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.82</v>
+        <v>5.83</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="DM17" t="n">
-        <v>39.41</v>
+        <v>39.84</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="DP17" t="n">
-        <v>14.71</v>
+        <v>14.67</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11</v>
+        <v>10.89</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.119999999999999</v>
+        <v>8</v>
       </c>
       <c r="DS17" t="n">
         <v>0.06</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>51.24</v>
+        <v>51.06</v>
       </c>
       <c r="DW17" t="n">
         <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.88</v>
+        <v>13.16</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.94</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DZ17" t="n">
         <v>3.94</v>
       </c>
       <c r="EA17" t="n">
-        <v>19</v>
+        <v>19.11</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="18">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
         <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7913,139 +7913,139 @@
         <v>1.44</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AH18" t="n">
         <v>2</v>
       </c>
       <c r="AI18" t="n">
-        <v>78.12</v>
+        <v>80.67</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN18" t="n">
-        <v>32.25</v>
+        <v>31.22</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11.75</v>
+        <v>12</v>
       </c>
       <c r="AR18" t="n">
-        <v>15.12</v>
+        <v>15.22</v>
       </c>
       <c r="AS18" t="n">
-        <v>10.38</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AU18" t="n">
         <v>2</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>51.88</v>
+        <v>52.44</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BA18" t="n">
-        <v>13.12</v>
+        <v>12.78</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.5</v>
+        <v>7.44</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.62</v>
+        <v>5.33</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.5</v>
+        <v>17.22</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.41</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.53</v>
+        <v>4.33</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.88</v>
+        <v>4.94</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS18" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT18" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU18" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV18" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW18" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BX18" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY18" t="n">
         <v>1.75</v>
@@ -8054,25 +8054,25 @@
         <v>1.75</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="CE18" t="n">
         <v>1.34</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CH18" t="n">
         <v>1.48</v>
@@ -8084,7 +8084,7 @@
         <v>1.72</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL18" t="n">
         <v>2.04</v>
@@ -8093,67 +8093,67 @@
         <v>2.38</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CW18" t="n">
         <v>1.74</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB18" t="n">
         <v>1.25</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="DE18" t="n">
         <v>0.06</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DH18" t="n">
-        <v>92.94</v>
+        <v>93.39</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
@@ -8162,61 +8162,61 @@
         <v>1.94</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.35</v>
+        <v>4.27</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DM18" t="n">
-        <v>42.12</v>
+        <v>41.06</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DO18" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.88</v>
+        <v>12</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.82</v>
+        <v>13.94</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.710000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>54.18</v>
+        <v>54.33</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX18" t="n">
-        <v>16.29</v>
+        <v>15.94</v>
       </c>
       <c r="DY18" t="n">
-        <v>10.24</v>
+        <v>10.06</v>
       </c>
       <c r="DZ18" t="n">
-        <v>6.05</v>
+        <v>5.89</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.77</v>
+        <v>19.5</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="19">
@@ -8226,10 +8226,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -8238,82 +8238,82 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="G19" t="n">
         <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>81.38</v>
+        <v>83.44</v>
       </c>
       <c r="I19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J19" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="K19" t="n">
-        <v>4.75</v>
+        <v>4.78</v>
       </c>
       <c r="L19" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>40.5</v>
+        <v>40.78</v>
       </c>
       <c r="N19" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="O19" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="P19" t="n">
-        <v>15.5</v>
+        <v>15.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.75</v>
+        <v>12.22</v>
       </c>
       <c r="R19" t="n">
-        <v>7.88</v>
+        <v>8</v>
       </c>
       <c r="S19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T19" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="U19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>51.38</v>
+        <v>52.56</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.62</v>
+        <v>12.56</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.5</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.12</v>
+        <v>4.33</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.62</v>
+        <v>17.44</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8397,70 +8397,70 @@
         <v>2.11</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BH19" t="n">
-        <v>11</v>
+        <v>10.72</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM19" t="n">
         <v>1</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BO19" t="n">
         <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.41</v>
+        <v>4.28</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.53</v>
+        <v>6.39</v>
       </c>
       <c r="BR19" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS19" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT19" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU19" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV19" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW19" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX19" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.61</v>
+        <v>2.49</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
       <c r="CC19" t="n">
         <v>2.96</v>
@@ -8472,25 +8472,25 @@
         <v>1.34</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI19" t="n">
         <v>2.07</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CL19" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CM19" t="n">
         <v>2.32</v>
@@ -8502,10 +8502,10 @@
         <v>1.23</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CR19" t="n">
         <v>1.39</v>
@@ -8520,10 +8520,10 @@
         <v>1.47</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX19" t="n">
         <v>1.55</v>
@@ -8532,7 +8532,7 @@
         <v>1.94</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DA19" t="n">
         <v>1.87</v>
@@ -8541,85 +8541,85 @@
         <v>1.27</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.47</v>
+        <v>93.83</v>
       </c>
       <c r="DI19" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.3</v>
+        <v>5.28</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="DM19" t="n">
-        <v>43.71</v>
+        <v>43.67</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.23</v>
+        <v>13.44</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.17</v>
+        <v>13.83</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.83</v>
+        <v>7.89</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.24</v>
+        <v>55.61</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.94</v>
+        <v>12.89</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.65</v>
+        <v>8.5</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.29</v>
+        <v>4.39</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.65</v>
+        <v>17.56</v>
       </c>
       <c r="EB19" t="n">
         <v>1.44</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BC3" t="n">
         <v>2.5</v>
@@ -1947,7 +1947,7 @@
         <v>20.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="BF3" t="n">
         <v>2.7</v>
@@ -2160,10 +2160,10 @@
         <v>0.11</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.220000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.89</v>
+        <v>4.84</v>
       </c>
       <c r="DZ3" t="n">
         <v>3.34</v>
@@ -2172,7 +2172,7 @@
         <v>19.45</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="EC3" t="n">
         <v>2.22</v>
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F4" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="G4" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>91.5</v>
+        <v>99.44</v>
       </c>
       <c r="I4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J4" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="K4" t="n">
-        <v>5.88</v>
+        <v>6.22</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="M4" t="n">
-        <v>46.5</v>
+        <v>50.56</v>
       </c>
       <c r="N4" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="P4" t="n">
-        <v>14.62</v>
+        <v>14.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>13.22</v>
       </c>
       <c r="R4" t="n">
-        <v>7</v>
+        <v>6.89</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T4" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="U4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>52.88</v>
+        <v>54.67</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.38</v>
+        <v>18</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.5</v>
+        <v>11.78</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.88</v>
+        <v>6.22</v>
       </c>
       <c r="AC4" t="n">
-        <v>14.88</v>
+        <v>14.89</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AF4" t="n">
         <v>0.22</v>
@@ -2356,70 +2356,70 @@
         <v>2.56</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.24</v>
+        <v>10.28</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.88</v>
+        <v>4.94</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.29</v>
+        <v>5.28</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>94.12</v>
+        <v>88.89</v>
       </c>
       <c r="BT4" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU4" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV4" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX4" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.12</v>
+        <v>4.17</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.28</v>
+        <v>4.34</v>
       </c>
       <c r="CC4" t="n">
         <v>2.4</v>
@@ -2431,10 +2431,10 @@
         <v>1.28</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="CH4" t="n">
         <v>1.54</v>
@@ -2443,16 +2443,16 @@
         <v>2.22</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK4" t="n">
         <v>1.5</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CN4" t="n">
         <v>1.9</v>
@@ -2461,10 +2461,10 @@
         <v>1.18</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
@@ -2473,7 +2473,7 @@
         <v>2.52</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="CU4" t="n">
         <v>1.57</v>
@@ -2488,97 +2488,97 @@
         <v>1.54</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.41</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB4" t="n">
         <v>1.2</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.47</v>
+        <v>2.61</v>
       </c>
       <c r="DH4" t="n">
-        <v>86.17</v>
+        <v>90.44</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.12</v>
+        <v>5.33</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.17</v>
+        <v>43.5</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.12</v>
+        <v>14</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.88</v>
+        <v>12.06</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.65</v>
+        <v>8.5</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>52.12</v>
+        <v>53.06</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>15.35</v>
+        <v>16.22</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.529999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.83</v>
+        <v>6</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.06</v>
+        <v>16.94</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="5">
@@ -2822,13 +2822,13 @@
         <v>3.76</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="CC5" t="n">
         <v>4.31</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.66</v>
+        <v>4.71</v>
       </c>
       <c r="CE5" t="n">
         <v>1.35</v>
@@ -2870,13 +2870,13 @@
         <v>3</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS5" t="n">
         <v>2.76</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CU5" t="n">
         <v>1.48</v>
@@ -5002,61 +5002,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G11" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="H11" t="n">
-        <v>95.88</v>
+        <v>94.67</v>
       </c>
       <c r="I11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J11" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="K11" t="n">
-        <v>5.12</v>
+        <v>4.89</v>
       </c>
       <c r="L11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M11" t="n">
-        <v>42.25</v>
+        <v>40.33</v>
       </c>
       <c r="N11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>18.25</v>
+        <v>17.89</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.75</v>
+        <v>8.67</v>
       </c>
       <c r="R11" t="n">
         <v>8</v>
       </c>
       <c r="S11" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="T11" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5068,28 +5068,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>37.25</v>
+        <v>36.78</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.25</v>
+        <v>13.22</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.5</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.75</v>
+        <v>4.11</v>
       </c>
       <c r="AC11" t="n">
-        <v>20.12</v>
+        <v>19.56</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AF11" t="n">
         <v>0.11</v>
@@ -5173,49 +5173,49 @@
         <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.65</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.29</v>
+        <v>4.33</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.35</v>
+        <v>5.44</v>
       </c>
       <c r="BR11" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS11" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BT11" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.88</v>
+        <v>11.11</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5224,19 +5224,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CC11" t="n">
         <v>2.84</v>
@@ -5248,16 +5248,16 @@
         <v>1.4</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CH11" t="n">
         <v>1.39</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.8</v>
@@ -5266,7 +5266,7 @@
         <v>1.56</v>
       </c>
       <c r="CL11" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CM11" t="n">
         <v>2.26</v>
@@ -5275,31 +5275,31 @@
         <v>1.8</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CX11" t="n">
         <v>1.55</v>
@@ -5317,52 +5317,52 @@
         <v>1.34</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.63</v>
+        <v>3.68</v>
       </c>
       <c r="DE11" t="n">
         <v>0.11</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="DH11" t="n">
-        <v>94.18000000000001</v>
+        <v>93.67</v>
       </c>
       <c r="DI11" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.7</v>
+        <v>4.61</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM11" t="n">
-        <v>42.71</v>
+        <v>41.72</v>
       </c>
       <c r="DN11" t="n">
         <v>1.11</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DP11" t="n">
-        <v>17.59</v>
+        <v>17.44</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9</v>
+        <v>8.94</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.17</v>
+        <v>8.16</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>38.23</v>
+        <v>37.94</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.47</v>
+        <v>13.44</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.06</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.41</v>
+        <v>4.56</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.11</v>
+        <v>19.83</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="12">
@@ -5808,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5901,136 +5901,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AI13" t="n">
-        <v>83.67</v>
+        <v>81.5</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AL13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BP13" t="n">
         <v>4.11</v>
       </c>
-      <c r="AM13" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>36.56</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>14.11</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>45.67</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>11.22</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>17.44</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>4</v>
-      </c>
       <c r="BQ13" t="n">
-        <v>4.35</v>
+        <v>4.39</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS13" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU13" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX13" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY13" t="n">
         <v>3.34</v>
@@ -6039,55 +6039,55 @@
         <v>3.59</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.03</v>
+        <v>4.11</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.82</v>
+        <v>5.03</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.24</v>
+        <v>5.46</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.68</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="CR13" t="n">
         <v>1.37</v>
@@ -6102,7 +6102,7 @@
         <v>1.53</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CW13" t="n">
         <v>1.68</v>
@@ -6111,7 +6111,7 @@
         <v>1.53</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.42</v>
@@ -6120,55 +6120,55 @@
         <v>1.95</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="DH13" t="n">
-        <v>83</v>
+        <v>81.83</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.47</v>
+        <v>4.34</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM13" t="n">
-        <v>41.12</v>
+        <v>40.11</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="DO13" t="n">
         <v>2.17</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.23</v>
+        <v>13.33</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.17</v>
+        <v>13.11</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.710000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6180,28 +6180,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.06</v>
+        <v>47.11</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.53</v>
+        <v>11.39</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.53</v>
+        <v>7.44</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.76</v>
+        <v>19.22</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -6277,16 +6277,16 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="Y14" t="n">
         <v>0.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AB14" t="n">
         <v>4.2</v>
@@ -6295,7 +6295,7 @@
         <v>23.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE14" t="n">
         <v>1.9</v>
@@ -6583,16 +6583,16 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.28</v>
+        <v>49.33</v>
       </c>
       <c r="DW14" t="n">
         <v>0.11</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.55</v>
+        <v>10.66</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.94</v>
+        <v>7.06</v>
       </c>
       <c r="DZ14" t="n">
         <v>3.61</v>
@@ -6842,13 +6842,13 @@
         <v>2.11</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CA15" t="n">
         <v>3.84</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.96</v>
+        <v>3.97</v>
       </c>
       <c r="CC15" t="n">
         <v>5.39</v>
@@ -6896,19 +6896,19 @@
         <v>2.98</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CU15" t="n">
         <v>1.47</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CW15" t="n">
         <v>1.78</v>
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0.11</v>
@@ -7107,139 +7107,139 @@
         <v>2.56</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="AI16" t="n">
-        <v>78.88</v>
+        <v>80.56</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.75</v>
+        <v>3.44</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN16" t="n">
-        <v>30.12</v>
+        <v>31.89</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>14.12</v>
+        <v>13.44</v>
       </c>
       <c r="AR16" t="n">
-        <v>12.12</v>
+        <v>12.33</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.75</v>
+        <v>8.44</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>44.88</v>
+        <v>47.33</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.62</v>
+        <v>11.22</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.62</v>
+        <v>8</v>
       </c>
       <c r="BC16" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="BD16" t="n">
         <v>16</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.59</v>
+        <v>2.67</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.289999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.59</v>
+        <v>2.67</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="BO16" t="n">
         <v>1.06</v>
       </c>
       <c r="BP16" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.24</v>
+        <v>4.39</v>
       </c>
       <c r="BR16" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS16" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT16" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BV16" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW16" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX16" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY16" t="n">
         <v>2.21</v>
@@ -7248,40 +7248,40 @@
         <v>2.55</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CH16" t="n">
         <v>1.4</v>
       </c>
       <c r="CI16" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CK16" t="n">
         <v>1.46</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CM16" t="n">
         <v>2.17</v>
@@ -7290,37 +7290,37 @@
         <v>1.71</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CX16" t="n">
         <v>1.57</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.33</v>
@@ -7329,88 +7329,88 @@
         <v>1.85</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.98</v>
+        <v>3.07</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="DH16" t="n">
-        <v>81.18000000000001</v>
+        <v>81.89</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.47</v>
+        <v>3.78</v>
       </c>
       <c r="DL16" t="n">
         <v>0.11</v>
       </c>
       <c r="DM16" t="n">
-        <v>35.71</v>
+        <v>36.28</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.82</v>
+        <v>14.44</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.35</v>
+        <v>12.44</v>
       </c>
       <c r="DR16" t="n">
-        <v>9.06</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>49.12</v>
+        <v>50.11</v>
       </c>
       <c r="DW16" t="n">
         <v>0.06</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.41</v>
+        <v>12.61</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.23</v>
+        <v>9.34</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.36</v>
+        <v>17.28</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="17">
@@ -7970,7 +7970,7 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>52.44</v>
+        <v>52.33</v>
       </c>
       <c r="AZ18" t="n">
         <v>0.33</v>
@@ -8195,7 +8195,7 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>54.33</v>
+        <v>54.28</v>
       </c>
       <c r="DW18" t="n">
         <v>0.16</v>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5498,49 +5498,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AI12" t="n">
-        <v>81.78</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AL12" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN12" t="n">
-        <v>35.56</v>
+        <v>34.4</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AP12" t="n">
         <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.78</v>
+        <v>15.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>10.11</v>
+        <v>10.9</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.67</v>
+        <v>8.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5552,82 +5552,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>40.44</v>
+        <v>40.7</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.22</v>
+        <v>6</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.890000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.94</v>
+        <v>5.74</v>
       </c>
       <c r="BR12" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT12" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BU12" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV12" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY12" t="n">
         <v>3.31</v>
@@ -5636,25 +5636,25 @@
         <v>3.76</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.73</v>
+        <v>3.77</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.87</v>
+        <v>4.03</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.65</v>
+        <v>4.73</v>
       </c>
       <c r="CE12" t="n">
         <v>1.35</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CH12" t="n">
         <v>1.45</v>
@@ -5666,13 +5666,13 @@
         <v>1.72</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL12" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CN12" t="n">
         <v>1.87</v>
@@ -5681,10 +5681,10 @@
         <v>1.25</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CR12" t="n">
         <v>1.41</v>
@@ -5699,106 +5699,106 @@
         <v>1.47</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CW12" t="n">
         <v>1.77</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY12" t="n">
         <v>1.91</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.23</v>
+        <v>3.19</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="DH12" t="n">
-        <v>86.17</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.16</v>
+        <v>5.05</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="DM12" t="n">
-        <v>41.06</v>
+        <v>40.16</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="DP12" t="n">
-        <v>15</v>
+        <v>14.89</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.5</v>
+        <v>12.79</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.72</v>
+        <v>7.9</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.22</v>
+        <v>45.11</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.66</v>
+        <v>10.42</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.94</v>
+        <v>7.74</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.06</v>
+        <v>19.79</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="13">
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
         <v>9</v>
@@ -7835,82 +7835,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="G18" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="H18" t="n">
-        <v>106.11</v>
+        <v>107</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="K18" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="M18" t="n">
-        <v>50.89</v>
+        <v>51.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="P18" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.67</v>
+        <v>12.7</v>
       </c>
       <c r="R18" t="n">
-        <v>7.22</v>
+        <v>6.7</v>
       </c>
       <c r="S18" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="T18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>56.22</v>
+        <v>56.3</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.11</v>
+        <v>18.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>12.67</v>
+        <v>12.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.44</v>
+        <v>6.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>21.78</v>
+        <v>21.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
         <v>0.11</v>
@@ -7997,67 +7997,67 @@
         <v>3.11</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.279999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI18" t="n">
         <v>3.11</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.94</v>
+        <v>4.79</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT18" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU18" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV18" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW18" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BX18" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="CC18" t="n">
         <v>3.44</v>
@@ -8069,10 +8069,10 @@
         <v>1.34</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CH18" t="n">
         <v>1.48</v>
@@ -8084,25 +8084,25 @@
         <v>1.72</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CR18" t="n">
         <v>1.37</v>
@@ -8123,100 +8123,100 @@
         <v>1.74</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB18" t="n">
         <v>1.25</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="DH18" t="n">
-        <v>93.39</v>
+        <v>94.53</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.27</v>
+        <v>4.21</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.06</v>
+        <v>41.84</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DP18" t="n">
-        <v>12</v>
+        <v>12.32</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.94</v>
+        <v>13.89</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.56</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>54.28</v>
+        <v>54.42</v>
       </c>
       <c r="DW18" t="n">
         <v>0.16</v>
       </c>
       <c r="DX18" t="n">
-        <v>15.94</v>
+        <v>15.84</v>
       </c>
       <c r="DY18" t="n">
-        <v>10.06</v>
+        <v>10.1</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.89</v>
+        <v>5.74</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.5</v>
+        <v>19.58</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0.11</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AI2" t="n">
-        <v>79.22</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.67</v>
+        <v>4.1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN2" t="n">
-        <v>36.78</v>
+        <v>39.9</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.56</v>
+        <v>12.1</v>
       </c>
       <c r="AR2" t="n">
-        <v>16.33</v>
+        <v>16.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.67</v>
+        <v>7.1</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>46.11</v>
+        <v>47.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.78</v>
+        <v>12.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.109999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.22</v>
+        <v>19.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="BG2" t="n">
         <v>2</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.56</v>
+        <v>8.74</v>
       </c>
       <c r="BI2" t="n">
         <v>2</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.67</v>
+        <v>3.79</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.89</v>
+        <v>4.95</v>
       </c>
       <c r="BR2" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT2" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BU2" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV2" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY2" t="n">
         <v>3.17</v>
@@ -1610,25 +1610,25 @@
         <v>3.31</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CC2" t="n">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.82</v>
+        <v>4.8</v>
       </c>
       <c r="CE2" t="n">
         <v>1.36</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CH2" t="n">
         <v>1.44</v>
@@ -1640,25 +1640,25 @@
         <v>1.76</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CL2" t="n">
         <v>2.12</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CN2" t="n">
         <v>1.64</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="CR2" t="n">
         <v>1.4</v>
@@ -1673,10 +1673,10 @@
         <v>1.44</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CX2" t="n">
         <v>1.73</v>
@@ -1694,85 +1694,85 @@
         <v>1.29</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="DH2" t="n">
-        <v>85.66</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.11</v>
+        <v>2.26</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.78</v>
+        <v>4.95</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM2" t="n">
-        <v>41</v>
+        <v>42.42</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.62</v>
+        <v>12.37</v>
       </c>
       <c r="DQ2" t="n">
-        <v>15.61</v>
+        <v>15.53</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.72</v>
+        <v>6.47</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>48.16</v>
+        <v>48.95</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>11.94</v>
+        <v>12.53</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.06</v>
+        <v>8.68</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.89</v>
+        <v>3.84</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.72</v>
+        <v>18.31</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="G3" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="H3" t="n">
-        <v>79.12</v>
+        <v>78.89</v>
       </c>
       <c r="I3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="K3" t="n">
-        <v>4.75</v>
+        <v>5.11</v>
       </c>
       <c r="L3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M3" t="n">
-        <v>34.25</v>
+        <v>35.78</v>
       </c>
       <c r="N3" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="P3" t="n">
-        <v>11.38</v>
+        <v>11.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>17</v>
+        <v>17.33</v>
       </c>
       <c r="R3" t="n">
-        <v>7.75</v>
+        <v>7.78</v>
       </c>
       <c r="S3" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="T3" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>44.62</v>
+        <v>45</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.75</v>
+        <v>10.78</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.38</v>
+        <v>6.56</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.38</v>
+        <v>18.33</v>
       </c>
       <c r="AD3" t="n">
         <v>1.24</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>2.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.390000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.94</v>
+        <v>5.05</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.44</v>
+        <v>4.37</v>
       </c>
       <c r="BR3" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT3" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU3" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV3" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX3" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.84</v>
+        <v>3.73</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="CC3" t="n">
         <v>5.22</v>
@@ -2025,13 +2025,13 @@
         <v>5.77</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CH3" t="n">
         <v>1.42</v>
@@ -2040,16 +2040,16 @@
         <v>1.92</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK3" t="n">
         <v>1.59</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CN3" t="n">
         <v>1.78</v>
@@ -2058,19 +2058,19 @@
         <v>1.28</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CR3" t="n">
         <v>1.42</v>
       </c>
       <c r="CS3" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CU3" t="n">
         <v>1.42</v>
@@ -2088,7 +2088,7 @@
         <v>2.02</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DA3" t="n">
         <v>1.79</v>
@@ -2097,52 +2097,52 @@
         <v>1.32</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DH3" t="n">
-        <v>74.22</v>
+        <v>74.37</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM3" t="n">
-        <v>30</v>
+        <v>30.95</v>
       </c>
       <c r="DN3" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="DP3" t="n">
-        <v>12.11</v>
+        <v>12.32</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.28</v>
+        <v>15.52</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.279999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.5</v>
+        <v>43.74</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.17</v>
+        <v>8.32</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.84</v>
+        <v>5</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.45</v>
+        <v>19.37</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="4">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>93.11</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>35.44</v>
+        <v>35.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>14.78</v>
+        <v>14.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.78</v>
+        <v>14.6</v>
       </c>
       <c r="R6" t="n">
-        <v>8.44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="T6" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="U6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>48.44</v>
+        <v>47.2</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.22</v>
+        <v>10.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.78</v>
+        <v>7.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.33</v>
+        <v>20.6</v>
       </c>
       <c r="AD6" t="n">
         <v>1.08</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>2.11</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.33</v>
+        <v>9.26</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.94</v>
+        <v>4.89</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT6" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BU6" t="n">
-        <v>16.67</v>
+        <v>21.05</v>
       </c>
       <c r="BV6" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX6" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.52</v>
+        <v>4.19</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.98</v>
+        <v>4.16</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.18</v>
+        <v>4.31</v>
       </c>
       <c r="CC6" t="n">
         <v>6.44</v>
@@ -3234,25 +3234,25 @@
         <v>7.12</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CL6" t="n">
         <v>2.11</v>
@@ -3264,13 +3264,13 @@
         <v>1.78</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="CR6" t="n">
         <v>1.41</v>
@@ -3294,97 +3294,97 @@
         <v>1.6</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="DG6" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DH6" t="n">
-        <v>87.89</v>
+        <v>87</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM6" t="n">
-        <v>36.16</v>
+        <v>35.95</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.94</v>
+        <v>13.63</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.72</v>
+        <v>14.63</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.109999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.88</v>
+        <v>46.31</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.72</v>
+        <v>10.68</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.89</v>
+        <v>7.84</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.33</v>
+        <v>20.47</v>
       </c>
       <c r="EB6" t="n">
         <v>1.14</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F7" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="G7" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>117.38</v>
+        <v>120.78</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="J7" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="K7" t="n">
-        <v>6.62</v>
+        <v>6.78</v>
       </c>
       <c r="L7" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="M7" t="n">
-        <v>58.12</v>
+        <v>62.78</v>
       </c>
       <c r="N7" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="P7" t="n">
-        <v>12.88</v>
+        <v>12.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.88</v>
+        <v>14.78</v>
       </c>
       <c r="R7" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="S7" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="T7" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="U7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>61.12</v>
+        <v>63.44</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.38</v>
+        <v>21.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>13.62</v>
+        <v>13.89</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.75</v>
+        <v>7.44</v>
       </c>
       <c r="AC7" t="n">
-        <v>20.88</v>
+        <v>22</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AF7" t="n">
         <v>0.3</v>
@@ -3565,70 +3565,70 @@
         <v>2.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="BH7" t="n">
-        <v>10</v>
+        <v>10.11</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.94</v>
+        <v>5.05</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="BR7" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS7" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BU7" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BV7" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW7" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX7" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>1.39</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.92</v>
+        <v>4.89</v>
       </c>
       <c r="CB7" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="CC7" t="n">
         <v>1.64</v>
@@ -3640,25 +3640,25 @@
         <v>1.28</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK7" t="n">
         <v>1.54</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CM7" t="n">
         <v>2.32</v>
@@ -3673,25 +3673,25 @@
         <v>1.63</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CX7" t="n">
         <v>1.55</v>
@@ -3712,82 +3712,82 @@
         <v>1.69</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="DH7" t="n">
-        <v>107</v>
+        <v>109.16</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.28</v>
+        <v>6.37</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DM7" t="n">
-        <v>49.72</v>
+        <v>52.37</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="DP7" t="n">
-        <v>13.06</v>
+        <v>12.79</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.95</v>
+        <v>13.42</v>
       </c>
       <c r="DR7" t="n">
-        <v>5.33</v>
+        <v>5.26</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>58.78</v>
+        <v>60</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX7" t="n">
-        <v>18.17</v>
+        <v>18.31</v>
       </c>
       <c r="DY7" t="n">
-        <v>11.5</v>
+        <v>11.74</v>
       </c>
       <c r="DZ7" t="n">
-        <v>6.67</v>
+        <v>6.58</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.22</v>
+        <v>19.84</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0.3</v>
@@ -3887,139 +3887,139 @@
         <v>1.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AI8" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN8" t="n">
-        <v>44.75</v>
+        <v>45.22</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.25</v>
+        <v>13.22</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.12</v>
+        <v>10.78</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>59.12</v>
+        <v>59.67</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.62</v>
+        <v>13.33</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.5</v>
+        <v>8.33</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.25</v>
+        <v>17.11</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.94</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL8" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.89</v>
+        <v>4.84</v>
       </c>
       <c r="BR8" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU8" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BV8" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY8" t="n">
         <v>1.28</v>
@@ -4028,16 +4028,16 @@
         <v>1.31</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.56</v>
+        <v>5.65</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.93</v>
+        <v>5.98</v>
       </c>
       <c r="CC8" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="CD8" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="CE8" t="n">
         <v>1.22</v>
@@ -4046,13 +4046,13 @@
         <v>2.11</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="CH8" t="n">
         <v>1.7</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.72</v>
@@ -4061,10 +4061,10 @@
         <v>1.48</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CN8" t="n">
         <v>1.92</v>
@@ -4073,10 +4073,10 @@
         <v>1.12</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
@@ -4087,106 +4087,106 @@
         <v>1.75</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DB8" t="n">
         <v>1.15</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="DD8" t="n">
         <v>2.19</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="DH8" t="n">
-        <v>98</v>
+        <v>98.16</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
         <v>2.05</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.22</v>
+        <v>5.26</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM8" t="n">
-        <v>50.67</v>
+        <v>50.58</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.22</v>
+        <v>12.26</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.83</v>
+        <v>10.69</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.39</v>
+        <v>7.21</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>62.44</v>
+        <v>62.53</v>
       </c>
       <c r="DW8" t="n">
         <v>0.11</v>
       </c>
       <c r="DX8" t="n">
-        <v>17.5</v>
+        <v>17.16</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.5</v>
+        <v>11.26</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.83</v>
+        <v>19.63</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="9">
@@ -4196,94 +4196,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F9" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G9" t="n">
-        <v>4.78</v>
+        <v>4.9</v>
       </c>
       <c r="H9" t="n">
-        <v>93.89</v>
+        <v>91.7</v>
       </c>
       <c r="I9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="L9" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="M9" t="n">
-        <v>43.78</v>
+        <v>43.2</v>
       </c>
       <c r="N9" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="O9" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="P9" t="n">
-        <v>12.44</v>
+        <v>12.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.56</v>
+        <v>16.4</v>
       </c>
       <c r="R9" t="n">
-        <v>6.89</v>
+        <v>6.6</v>
       </c>
       <c r="S9" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>59.44</v>
+        <v>57.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.78</v>
+        <v>16.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.44</v>
+        <v>11.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.67</v>
+        <v>19.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="AF9" t="n">
         <v>0.11</v>
@@ -4367,70 +4367,70 @@
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.83</v>
+        <v>10.05</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.67</v>
+        <v>5.84</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT9" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BU9" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV9" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX9" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.09</v>
+        <v>3.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="CC9" t="n">
         <v>4.99</v>
@@ -4445,25 +4445,25 @@
         <v>2.55</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CH9" t="n">
         <v>1.49</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CK9" t="n">
         <v>1.53</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CN9" t="n">
         <v>1.83</v>
@@ -4472,7 +4472,7 @@
         <v>1.22</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ9" t="n">
         <v>2.85</v>
@@ -4481,7 +4481,7 @@
         <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CT9" t="n">
         <v>3.2</v>
@@ -4490,7 +4490,7 @@
         <v>1.52</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CW9" t="n">
         <v>1.71</v>
@@ -4502,7 +4502,7 @@
         <v>1.92</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DA9" t="n">
         <v>1.88</v>
@@ -4523,40 +4523,40 @@
         <v>1.89</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.22</v>
+        <v>3.37</v>
       </c>
       <c r="DH9" t="n">
-        <v>79.39</v>
+        <v>79</v>
       </c>
       <c r="DI9" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.22</v>
+        <v>3.37</v>
       </c>
       <c r="DK9" t="n">
-        <v>5</v>
+        <v>5.26</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="DM9" t="n">
-        <v>36.39</v>
+        <v>36.47</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.11</v>
+        <v>13.26</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.33</v>
+        <v>16.26</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.279999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS9" t="n">
         <v>0.16</v>
@@ -4568,28 +4568,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>52</v>
+        <v>51.48</v>
       </c>
       <c r="DW9" t="n">
         <v>0.16</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.89</v>
+        <v>13.95</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.380000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.5</v>
+        <v>4.37</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.89</v>
+        <v>17.84</v>
       </c>
       <c r="EB9" t="n">
         <v>1.45</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.94</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="10">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0.11</v>
@@ -4689,52 +4689,52 @@
         <v>1.44</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>64.89</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN10" t="n">
-        <v>26.33</v>
+        <v>26.4</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.44</v>
+        <v>14.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="AS10" t="n">
-        <v>11.33</v>
+        <v>11</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4746,82 +4746,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>39.78</v>
+        <v>41</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.78</v>
+        <v>6.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.56</v>
+        <v>18.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.33</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.83</v>
+        <v>4.95</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.44</v>
+        <v>4.37</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT10" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU10" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV10" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX10" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY10" t="n">
         <v>3.26</v>
@@ -4830,40 +4830,40 @@
         <v>3.31</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.7</v>
+        <v>5.39</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.75</v>
+        <v>6.34</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CH10" t="n">
         <v>1.35</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK10" t="n">
         <v>1.5</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="CM10" t="n">
         <v>2.13</v>
@@ -4872,25 +4872,25 @@
         <v>1.68</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV10" t="n">
         <v>2.01</v>
@@ -4905,94 +4905,94 @@
         <v>2.01</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DB10" t="n">
         <v>1.3</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="DH10" t="n">
-        <v>68.39</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="DI10" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.06</v>
+        <v>3.95</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM10" t="n">
-        <v>28.28</v>
+        <v>28.21</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.56</v>
+        <v>12.95</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.06</v>
+        <v>14.16</v>
       </c>
       <c r="DR10" t="n">
-        <v>11.16</v>
+        <v>11</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>41.06</v>
+        <v>41.63</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.61</v>
+        <v>10.68</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.06</v>
+        <v>7.21</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.5</v>
+        <v>18.42</v>
       </c>
       <c r="EB10" t="n">
         <v>1.12</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="11">
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0.11</v>
@@ -5092,52 +5092,52 @@
         <v>2.33</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AI11" t="n">
-        <v>92.67</v>
+        <v>90.7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AN11" t="n">
-        <v>43.11</v>
+        <v>40.8</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.220000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.33</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5149,73 +5149,73 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>39.11</v>
+        <v>37</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>13.67</v>
+        <v>13.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.67</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BD11" t="n">
-        <v>20.11</v>
+        <v>18.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="BG11" t="n">
         <v>1.89</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.779999999999999</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI11" t="n">
         <v>1.89</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.33</v>
+        <v>4.47</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.44</v>
+        <v>5.42</v>
       </c>
       <c r="BR11" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT11" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BU11" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BY11" t="n">
         <v>2.18</v>
@@ -5233,22 +5233,22 @@
         <v>2.27</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.52</v>
+        <v>3.59</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.84</v>
+        <v>3.26</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="CE11" t="n">
         <v>1.4</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CG11" t="n">
         <v>2.78</v>
@@ -5257,16 +5257,16 @@
         <v>1.39</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK11" t="n">
         <v>1.56</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CM11" t="n">
         <v>2.26</v>
@@ -5275,25 +5275,25 @@
         <v>1.8</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CV11" t="n">
         <v>1.99</v>
@@ -5317,52 +5317,52 @@
         <v>1.34</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="DH11" t="n">
-        <v>93.67</v>
+        <v>92.58</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.61</v>
+        <v>4.58</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="DM11" t="n">
-        <v>41.72</v>
+        <v>40.58</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="DP11" t="n">
-        <v>17.44</v>
+        <v>17.68</v>
       </c>
       <c r="DQ11" t="n">
-        <v>8.94</v>
+        <v>8.9</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.16</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>37.94</v>
+        <v>36.9</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.44</v>
+        <v>13.47</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.890000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.83</v>
+        <v>19.16</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="12">
@@ -5808,10 +5808,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
@@ -5820,49 +5820,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="G13" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="H13" t="n">
-        <v>82.25</v>
+        <v>79.67</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="K13" t="n">
-        <v>4.88</v>
+        <v>5.44</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M13" t="n">
-        <v>46.25</v>
+        <v>45.89</v>
       </c>
       <c r="N13" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="P13" t="n">
-        <v>12.25</v>
+        <v>11.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>13.56</v>
       </c>
       <c r="R13" t="n">
-        <v>8.75</v>
+        <v>8.67</v>
       </c>
       <c r="S13" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="T13" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5874,28 +5874,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50.75</v>
+        <v>50.11</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>11.88</v>
+        <v>11.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.5</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.38</v>
+        <v>22.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5979,25 +5979,25 @@
         <v>2.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.220000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BN13" t="n">
         <v>1.89</v>
@@ -6006,43 +6006,43 @@
         <v>0.89</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.11</v>
+        <v>4.26</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.39</v>
+        <v>4.53</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BU13" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX13" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.11</v>
+        <v>4.08</v>
       </c>
       <c r="CC13" t="n">
         <v>5.03</v>
@@ -6054,10 +6054,10 @@
         <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CH13" t="n">
         <v>1.51</v>
@@ -6066,19 +6066,19 @@
         <v>2.14</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO13" t="n">
         <v>1.21</v>
@@ -6093,10 +6093,10 @@
         <v>1.37</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CU13" t="n">
         <v>1.53</v>
@@ -6111,64 +6111,64 @@
         <v>1.53</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB13" t="n">
         <v>1.22</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="DH13" t="n">
-        <v>81.83</v>
+        <v>80.63</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.34</v>
+        <v>4.63</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM13" t="n">
-        <v>40.11</v>
+        <v>40.26</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.17</v>
+        <v>2.37</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.33</v>
+        <v>13.05</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.11</v>
+        <v>13.37</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.109999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6180,28 +6180,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.11</v>
+        <v>47</v>
       </c>
       <c r="DW13" t="n">
         <v>0.11</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.39</v>
+        <v>11.16</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.44</v>
+        <v>7.32</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.95</v>
+        <v>3.84</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.22</v>
+        <v>19.37</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="14">
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6304,49 +6304,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AI14" t="n">
-        <v>87</v>
+        <v>86.78</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AN14" t="n">
-        <v>40.62</v>
+        <v>38.56</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15.25</v>
+        <v>15.11</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.5</v>
+        <v>14.33</v>
       </c>
       <c r="AS14" t="n">
-        <v>9</v>
+        <v>9.33</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6358,82 +6358,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>50.75</v>
+        <v>49.22</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.119999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.25</v>
+        <v>6.22</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="BD14" t="n">
-        <v>19.62</v>
+        <v>18.44</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.279999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.28</v>
+        <v>4.42</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="BR14" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BT14" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BU14" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV14" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BY14" t="n">
         <v>2.66</v>
@@ -6442,55 +6442,55 @@
         <v>2.7</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="CC14" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="CD14" t="n">
-        <v>5.39</v>
+        <v>5.17</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI14" t="n">
         <v>1.91</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="CR14" t="n">
         <v>1.42</v>
@@ -6505,73 +6505,73 @@
         <v>1.42</v>
       </c>
       <c r="CV14" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.53</v>
+        <v>3.64</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="DH14" t="n">
-        <v>91.17</v>
+        <v>90.84</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.5</v>
+        <v>4.31</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="DM14" t="n">
-        <v>38.66</v>
+        <v>37.79</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.78</v>
+        <v>14.74</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.61</v>
+        <v>14.52</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.83</v>
+        <v>9</v>
       </c>
       <c r="DS14" t="n">
         <v>0.11</v>
@@ -6583,28 +6583,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.33</v>
+        <v>48.68</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.66</v>
+        <v>10.47</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.06</v>
+        <v>7</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.61</v>
+        <v>3.48</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.83</v>
+        <v>21.16</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="15">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6704,139 +6704,139 @@
         <v>2.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AH15" t="n">
         <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>90.5</v>
+        <v>92.78</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN15" t="n">
-        <v>40</v>
+        <v>39.78</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.5</v>
+        <v>14.67</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.75</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AT15" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>50</v>
+        <v>50.89</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>13.38</v>
+        <v>13.11</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.880000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="BD15" t="n">
-        <v>18.62</v>
+        <v>18.78</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.94</v>
+        <v>10.16</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.44</v>
+        <v>5.63</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS15" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU15" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV15" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BY15" t="n">
         <v>2.11</v>
@@ -6845,16 +6845,16 @@
         <v>2.19</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="CC15" t="n">
-        <v>5.39</v>
+        <v>5.11</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.74</v>
+        <v>5.47</v>
       </c>
       <c r="CE15" t="n">
         <v>1.35</v>
@@ -6863,55 +6863,55 @@
         <v>2.65</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CH15" t="n">
         <v>1.46</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK15" t="n">
         <v>1.51</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CM15" t="n">
         <v>2.43</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO15" t="n">
         <v>1.25</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CU15" t="n">
         <v>1.47</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX15" t="n">
         <v>1.54</v>
@@ -6932,49 +6932,49 @@
         <v>1.86</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="DE15" t="n">
         <v>0.05</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DG15" t="n">
         <v>3</v>
       </c>
       <c r="DH15" t="n">
-        <v>100.89</v>
+        <v>101.42</v>
       </c>
       <c r="DI15" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.66</v>
+        <v>5.58</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DM15" t="n">
-        <v>46.83</v>
+        <v>46.37</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.66</v>
+        <v>0.74</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.5</v>
+        <v>11.68</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.11</v>
+        <v>13.26</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.17</v>
+        <v>8.26</v>
       </c>
       <c r="DS15" t="n">
         <v>0.16</v>
@@ -6986,28 +6986,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>53.72</v>
+        <v>53.95</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.56</v>
+        <v>14.37</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.28</v>
+        <v>10</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.28</v>
+        <v>4.37</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.72</v>
+        <v>20.69</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -7017,94 +7017,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F16" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="H16" t="n">
-        <v>83.22</v>
+        <v>80</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J16" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="K16" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="M16" t="n">
-        <v>40.67</v>
+        <v>38.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="P16" t="n">
-        <v>15.44</v>
+        <v>15.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.56</v>
+        <v>12.1</v>
       </c>
       <c r="R16" t="n">
-        <v>9.33</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>52.89</v>
+        <v>51.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>14</v>
+        <v>13.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>10.67</v>
+        <v>9.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>18.56</v>
+        <v>17.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AF16" t="n">
         <v>0.22</v>
@@ -7188,70 +7188,70 @@
         <v>2.67</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.5</v>
+        <v>8.68</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BM16" t="n">
         <v>0.89</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.06</v>
+        <v>4.16</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.39</v>
+        <v>4.47</v>
       </c>
       <c r="BR16" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS16" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU16" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV16" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW16" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX16" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="CC16" t="n">
         <v>4.27</v>
@@ -7260,43 +7260,43 @@
         <v>4.47</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CH16" t="n">
         <v>1.4</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CN16" t="n">
         <v>1.71</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="CR16" t="n">
         <v>1.39</v>
@@ -7311,106 +7311,106 @@
         <v>1.49</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="DE16" t="n">
         <v>0.16</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="DH16" t="n">
-        <v>81.89</v>
+        <v>80.27</v>
       </c>
       <c r="DI16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="DL16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>35.32</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="DW16" t="n">
         <v>0.11</v>
       </c>
-      <c r="DM16" t="n">
-        <v>36.28</v>
-      </c>
-      <c r="DN16" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="DO16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="DP16" t="n">
-        <v>14.44</v>
-      </c>
-      <c r="DQ16" t="n">
-        <v>12.44</v>
-      </c>
-      <c r="DR16" t="n">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="DS16" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DT16" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV16" t="n">
-        <v>50.11</v>
-      </c>
-      <c r="DW16" t="n">
-        <v>0.06</v>
-      </c>
       <c r="DX16" t="n">
-        <v>12.61</v>
+        <v>12.26</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.34</v>
+        <v>9</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.28</v>
+        <v>16.74</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="17">
@@ -7420,94 +7420,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H17" t="n">
-        <v>104.44</v>
+        <v>104.7</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J17" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="K17" t="n">
-        <v>6.22</v>
+        <v>6.5</v>
       </c>
       <c r="L17" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="M17" t="n">
-        <v>44.56</v>
+        <v>45.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O17" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="P17" t="n">
-        <v>15.78</v>
+        <v>15.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="R17" t="n">
-        <v>5.67</v>
+        <v>5.9</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="U17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>56</v>
+        <v>56.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.11</v>
+        <v>14.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.11</v>
+        <v>3.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>20.89</v>
+        <v>21.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
         <v>0.22</v>
@@ -7591,70 +7591,70 @@
         <v>2.67</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="BH17" t="n">
         <v>9.890000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.89</v>
+        <v>4.05</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.28</v>
+        <v>5.16</v>
       </c>
       <c r="BR17" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BU17" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV17" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="CC17" t="n">
         <v>3.39</v>
@@ -7663,43 +7663,43 @@
         <v>3.73</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="CR17" t="n">
         <v>1.41</v>
@@ -7714,106 +7714,106 @@
         <v>1.44</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.42</v>
+        <v>3.53</v>
       </c>
       <c r="DE17" t="n">
         <v>0.16</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="DH17" t="n">
-        <v>92</v>
+        <v>92.79000000000001</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.83</v>
+        <v>6</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="DM17" t="n">
-        <v>39.84</v>
+        <v>40.63</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="DP17" t="n">
-        <v>14.67</v>
+        <v>14.58</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.89</v>
+        <v>11.05</v>
       </c>
       <c r="DR17" t="n">
         <v>8</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>51.06</v>
+        <v>51.68</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.16</v>
+        <v>13.31</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.220000000000001</v>
+        <v>9.52</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.94</v>
+        <v>3.79</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.11</v>
+        <v>19.58</v>
       </c>
       <c r="EB17" t="n">
         <v>1.4</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="18">
@@ -7895,10 +7895,10 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="AB18" t="n">
         <v>6.1</v>
@@ -7907,7 +7907,7 @@
         <v>21.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AE18" t="n">
         <v>1.5</v>
@@ -8201,10 +8201,10 @@
         <v>0.16</v>
       </c>
       <c r="DX18" t="n">
-        <v>15.84</v>
+        <v>15.9</v>
       </c>
       <c r="DY18" t="n">
-        <v>10.1</v>
+        <v>10.16</v>
       </c>
       <c r="DZ18" t="n">
         <v>5.74</v>
@@ -8213,7 +8213,7 @@
         <v>19.58</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="EC18" t="n">
         <v>1.63</v>
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
         <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8319,136 +8319,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AI19" t="n">
-        <v>104.22</v>
+        <v>102.2</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.78</v>
+        <v>5.6</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN19" t="n">
-        <v>46.56</v>
+        <v>46</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP19" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11.22</v>
+        <v>11.9</v>
       </c>
       <c r="AR19" t="n">
-        <v>15.44</v>
+        <v>14.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.78</v>
+        <v>7.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>58.67</v>
+        <v>58.3</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA19" t="n">
-        <v>13.22</v>
+        <v>13.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.779999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.44</v>
+        <v>4.7</v>
       </c>
       <c r="BD19" t="n">
-        <v>17.67</v>
+        <v>19</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.72</v>
+        <v>10.89</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BM19" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BO19" t="n">
         <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.28</v>
+        <v>4.42</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.39</v>
+        <v>6.42</v>
       </c>
       <c r="BR19" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS19" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU19" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV19" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW19" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX19" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY19" t="n">
         <v>2.49</v>
@@ -8460,22 +8460,22 @@
         <v>3.64</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="CE19" t="n">
         <v>1.34</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CH19" t="n">
         <v>1.46</v>
@@ -8490,7 +8490,7 @@
         <v>1.54</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CM19" t="n">
         <v>2.32</v>
@@ -8505,25 +8505,25 @@
         <v>1.81</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="CU19" t="n">
         <v>1.47</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CX19" t="n">
         <v>1.55</v>
@@ -8532,94 +8532,94 @@
         <v>1.94</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DA19" t="n">
         <v>1.87</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="DG19" t="n">
         <v>2.89</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.83</v>
+        <v>93.31</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.28</v>
+        <v>5.21</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DM19" t="n">
-        <v>43.67</v>
+        <v>43.53</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.44</v>
+        <v>13.69</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.83</v>
+        <v>13.47</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.89</v>
+        <v>7.74</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.61</v>
+        <v>55.58</v>
       </c>
       <c r="DW19" t="n">
         <v>0.16</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.89</v>
+        <v>12.9</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.5</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.39</v>
+        <v>4.52</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.56</v>
+        <v>18.26</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0.33</v>
@@ -2275,52 +2275,52 @@
         <v>2.11</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="AI4" t="n">
-        <v>81.44</v>
+        <v>86</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AN4" t="n">
-        <v>36.44</v>
+        <v>39.4</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.67</v>
+        <v>13.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.89</v>
+        <v>10.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.11</v>
+        <v>9.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>51.44</v>
+        <v>52.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA4" t="n">
-        <v>14.44</v>
+        <v>14.7</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.78</v>
+        <v>6.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>19</v>
+        <v>20.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.28</v>
+        <v>10.16</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK4" t="n">
         <v>0.89</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.94</v>
+        <v>4.89</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.28</v>
+        <v>5.21</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT4" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU4" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BV4" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX4" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY4" t="n">
         <v>1.67</v>
@@ -2416,55 +2416,55 @@
         <v>1.76</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.17</v>
+        <v>4.25</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.34</v>
+        <v>4.44</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.64</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CM4" t="n">
         <v>2.42</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
@@ -2479,13 +2479,13 @@
         <v>1.57</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CW4" t="n">
         <v>1.65</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY4" t="n">
         <v>1.89</v>
@@ -2497,88 +2497,88 @@
         <v>1.92</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="DH4" t="n">
-        <v>90.44</v>
+        <v>92.37</v>
       </c>
       <c r="DI4" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.33</v>
+        <v>5.31</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.5</v>
+        <v>44.69</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="DP4" t="n">
         <v>14</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.06</v>
+        <v>11.95</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.5</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>53.06</v>
+        <v>53.48</v>
       </c>
       <c r="DW4" t="n">
         <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.22</v>
+        <v>16.26</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.23</v>
+        <v>10.11</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6</v>
+        <v>6.16</v>
       </c>
       <c r="EA4" t="n">
-        <v>16.94</v>
+        <v>17.68</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="G5" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="H5" t="n">
-        <v>77.11</v>
+        <v>76.7</v>
       </c>
       <c r="I5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J5" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>39.89</v>
+        <v>38.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>10.67</v>
+        <v>10.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.89</v>
+        <v>13.8</v>
       </c>
       <c r="R5" t="n">
-        <v>7.44</v>
+        <v>7.8</v>
       </c>
       <c r="S5" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>52.56</v>
+        <v>51.2</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.67</v>
+        <v>12</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.33</v>
+        <v>7.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.67</v>
+        <v>18.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
         <v>0.11</v>
@@ -2759,70 +2759,70 @@
         <v>2.67</v>
       </c>
       <c r="BG5" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.06</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.56</v>
+        <v>5.47</v>
       </c>
       <c r="BR5" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS5" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT5" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.56</v>
+        <v>10.53</v>
       </c>
       <c r="BV5" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.49</v>
+        <v>4.02</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.73</v>
+        <v>4.38</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.76</v>
+        <v>3.87</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.91</v>
+        <v>4.03</v>
       </c>
       <c r="CC5" t="n">
         <v>4.31</v>
@@ -2831,16 +2831,16 @@
         <v>4.71</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI5" t="n">
         <v>2.01</v>
@@ -2849,25 +2849,25 @@
         <v>1.74</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CL5" t="n">
         <v>2.03</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CO5" t="n">
         <v>1.25</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="CR5" t="n">
         <v>1.39</v>
@@ -2888,100 +2888,100 @@
         <v>1.76</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.09</v>
+        <v>3.03</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="DH5" t="n">
-        <v>74.72</v>
+        <v>74.63</v>
       </c>
       <c r="DI5" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DM5" t="n">
-        <v>35.89</v>
+        <v>35.53</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.28</v>
+        <v>12.16</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.11</v>
+        <v>15</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.61</v>
+        <v>7.79</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.72</v>
+        <v>49.16</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.44</v>
+        <v>11.63</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.78</v>
+        <v>7.95</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="EA5" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="6">

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="G3" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="H3" t="n">
-        <v>78.89</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="K3" t="n">
-        <v>5.11</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M3" t="n">
-        <v>35.78</v>
+        <v>35.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="P3" t="n">
-        <v>11.89</v>
+        <v>12.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>17.33</v>
+        <v>16.8</v>
       </c>
       <c r="R3" t="n">
-        <v>7.78</v>
+        <v>8</v>
       </c>
       <c r="S3" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>45</v>
+        <v>43.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.78</v>
+        <v>10.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.56</v>
+        <v>6.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.33</v>
+        <v>18.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>2.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.42</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.37</v>
+        <v>4.45</v>
       </c>
       <c r="BR3" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS3" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT3" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU3" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX3" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.73</v>
+        <v>3.8</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CC3" t="n">
         <v>5.22</v>
@@ -2025,7 +2025,7 @@
         <v>5.77</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF3" t="n">
         <v>2.81</v>
@@ -2043,16 +2043,16 @@
         <v>1.85</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CO3" t="n">
         <v>1.28</v>
@@ -2067,31 +2067,31 @@
         <v>1.42</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CU3" t="n">
         <v>1.42</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB3" t="n">
         <v>1.32</v>
@@ -2106,43 +2106,43 @@
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="DG3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DH3" t="n">
-        <v>74.37</v>
+        <v>73.7</v>
       </c>
       <c r="DI3" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM3" t="n">
         <v>30.95</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="DP3" t="n">
-        <v>12.32</v>
+        <v>12.65</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.52</v>
+        <v>15.35</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.210000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.74</v>
+        <v>43.1</v>
       </c>
       <c r="DW3" t="n">
         <v>0.1</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.32</v>
+        <v>8.1</v>
       </c>
       <c r="DY3" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.37</v>
+        <v>19.35</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="4">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
@@ -5417,82 +5417,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G12" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>90.56</v>
+        <v>90.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J12" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="K12" t="n">
-        <v>6.33</v>
+        <v>6.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="M12" t="n">
-        <v>46.56</v>
+        <v>45</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O12" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>14.22</v>
+        <v>14.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.89</v>
+        <v>15.6</v>
       </c>
       <c r="R12" t="n">
-        <v>6.78</v>
+        <v>6.6</v>
       </c>
       <c r="S12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="U12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>50</v>
+        <v>50.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.89</v>
+        <v>12.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.67</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.11</v>
+        <v>19.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5576,70 +5576,70 @@
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.68</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BO12" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.74</v>
+        <v>5.55</v>
       </c>
       <c r="BR12" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BS12" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BT12" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BU12" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV12" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CC12" t="n">
         <v>4.03</v>
@@ -5654,7 +5654,7 @@
         <v>2.62</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="CH12" t="n">
         <v>1.45</v>
@@ -5663,40 +5663,40 @@
         <v>2.05</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO12" t="n">
         <v>1.25</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CR12" t="n">
         <v>1.41</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV12" t="n">
         <v>2.13</v>
@@ -5705,67 +5705,67 @@
         <v>1.77</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="DH12" t="n">
-        <v>85.73999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="DI12" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="DM12" t="n">
-        <v>40.16</v>
+        <v>39.7</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.89</v>
+        <v>15.2</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.79</v>
+        <v>13.25</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.9</v>
+        <v>7.75</v>
       </c>
       <c r="DS12" t="n">
         <v>0.05</v>
@@ -5777,28 +5777,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.11</v>
+        <v>45.45</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.42</v>
+        <v>10.45</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.74</v>
+        <v>7.85</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.79</v>
+        <v>19.55</v>
       </c>
       <c r="EB12" t="n">
         <v>1.14</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>0.1</v>
@@ -7510,52 +7510,52 @@
         <v>1.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AI17" t="n">
-        <v>79.56</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.44</v>
+        <v>5</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AN17" t="n">
-        <v>35.11</v>
+        <v>34.2</v>
       </c>
       <c r="AO17" t="n">
         <v>1</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.56</v>
+        <v>14.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.779999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="AS17" t="n">
-        <v>10.33</v>
+        <v>9.9</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7567,82 +7567,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>46.11</v>
+        <v>46.3</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA17" t="n">
-        <v>12.22</v>
+        <v>11.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.44</v>
+        <v>8.1</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="BD17" t="n">
-        <v>17.33</v>
+        <v>16.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.890000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.16</v>
+        <v>5</v>
       </c>
       <c r="BR17" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS17" t="n">
-        <v>73.68000000000001</v>
+        <v>70</v>
       </c>
       <c r="BT17" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BU17" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV17" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY17" t="n">
         <v>2.14</v>
@@ -7651,28 +7651,28 @@
         <v>2.17</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.39</v>
+        <v>3.29</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.73</v>
+        <v>3.59</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF17" t="n">
         <v>2.78</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI17" t="n">
         <v>1.96</v>
@@ -7681,34 +7681,34 @@
         <v>1.77</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO17" t="n">
         <v>1.29</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="CR17" t="n">
         <v>1.41</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CU17" t="n">
         <v>1.44</v>
@@ -7723,64 +7723,64 @@
         <v>1.6</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.79000000000001</v>
+        <v>92.05</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="DK17" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="DM17" t="n">
-        <v>40.63</v>
+        <v>39.9</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="DP17" t="n">
-        <v>14.58</v>
+        <v>14.95</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.05</v>
+        <v>11.55</v>
       </c>
       <c r="DR17" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="DS17" t="n">
         <v>0.05</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>51.68</v>
+        <v>51.5</v>
       </c>
       <c r="DW17" t="n">
         <v>0.1</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.31</v>
+        <v>13.05</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.52</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.58</v>
+        <v>19.2</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="18">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7913,139 +7913,139 @@
         <v>1.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>80.67</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.22</v>
+        <v>4.7</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AN18" t="n">
-        <v>31.22</v>
+        <v>32.2</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ18" t="n">
         <v>12</v>
       </c>
       <c r="AR18" t="n">
-        <v>15.22</v>
+        <v>15.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.890000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>52.33</v>
+        <v>54</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BA18" t="n">
-        <v>12.78</v>
+        <v>12.9</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.44</v>
+        <v>7.7</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.22</v>
+        <v>17.3</v>
       </c>
       <c r="BE18" t="n">
         <v>1.41</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.109999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.32</v>
+        <v>4.4</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.79</v>
+        <v>4.85</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS18" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT18" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU18" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV18" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW18" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BX18" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY18" t="n">
         <v>1.72</v>
@@ -8054,25 +8054,25 @@
         <v>1.73</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.44</v>
+        <v>3.27</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="CE18" t="n">
         <v>1.34</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CH18" t="n">
         <v>1.48</v>
@@ -8084,16 +8084,16 @@
         <v>1.72</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO18" t="n">
         <v>1.22</v>
@@ -8102,16 +8102,16 @@
         <v>1.78</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CR18" t="n">
         <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CU18" t="n">
         <v>1.5</v>
@@ -8123,16 +8123,16 @@
         <v>1.74</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB18" t="n">
         <v>1.25</v>
@@ -8147,13 +8147,13 @@
         <v>0.05</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="DH18" t="n">
-        <v>94.53</v>
+        <v>95.05</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
@@ -8162,61 +8162,61 @@
         <v>1.95</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.21</v>
+        <v>4.45</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.84</v>
+        <v>41.8</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="DO18" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.32</v>
+        <v>12.3</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.89</v>
+        <v>14.05</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.210000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>54.42</v>
+        <v>55.15</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX18" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="DY18" t="n">
-        <v>10.16</v>
+        <v>10.15</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.74</v>
+        <v>5.65</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.58</v>
+        <v>19.5</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F2" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="G2" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="H2" t="n">
-        <v>92.11</v>
+        <v>91.3</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="K2" t="n">
-        <v>5.89</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>45.22</v>
+        <v>44.6</v>
       </c>
       <c r="N2" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>12.67</v>
+        <v>12.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.89</v>
+        <v>14</v>
       </c>
       <c r="R2" t="n">
-        <v>5.78</v>
+        <v>6.1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="T2" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="U2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>50.22</v>
+        <v>49.4</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.11</v>
+        <v>12.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.11</v>
+        <v>4.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.22</v>
+        <v>17.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.74</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="BR2" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BS2" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT2" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BU2" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BV2" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.17</v>
+        <v>3.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.31</v>
+        <v>3.14</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="CC2" t="n">
         <v>4</v>
@@ -1625,25 +1625,25 @@
         <v>1.36</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="CH2" t="n">
         <v>1.44</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CM2" t="n">
         <v>2.04</v>
@@ -1655,10 +1655,10 @@
         <v>1.26</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="CR2" t="n">
         <v>1.4</v>
@@ -1685,7 +1685,7 @@
         <v>2.18</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DA2" t="n">
         <v>1.66</v>
@@ -1694,52 +1694,52 @@
         <v>1.29</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="DH2" t="n">
-        <v>86.31999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="DI2" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM2" t="n">
-        <v>42.42</v>
+        <v>42.25</v>
       </c>
       <c r="DN2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.37</v>
+        <v>12.25</v>
       </c>
       <c r="DQ2" t="n">
-        <v>15.53</v>
+        <v>15.05</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.47</v>
+        <v>6.6</v>
       </c>
       <c r="DS2" t="n">
         <v>0.1</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>48.95</v>
+        <v>48.6</v>
       </c>
       <c r="DW2" t="n">
         <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.53</v>
+        <v>12.75</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.68</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.31</v>
+        <v>18.6</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="3">
@@ -2097,10 +2097,10 @@
         <v>1.32</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F4" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H4" t="n">
-        <v>99.44</v>
+        <v>100.6</v>
       </c>
       <c r="I4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="K4" t="n">
-        <v>6.22</v>
+        <v>6.4</v>
       </c>
       <c r="L4" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="M4" t="n">
-        <v>50.56</v>
+        <v>51.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O4" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>14.33</v>
+        <v>14.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.22</v>
+        <v>14.1</v>
       </c>
       <c r="R4" t="n">
-        <v>6.89</v>
+        <v>6.9</v>
       </c>
       <c r="S4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>54.67</v>
+        <v>55.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.78</v>
+        <v>11.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.22</v>
+        <v>6.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>14.89</v>
+        <v>15.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AF4" t="n">
         <v>0.3</v>
@@ -2359,64 +2359,64 @@
         <v>3</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.16</v>
+        <v>10.15</v>
       </c>
       <c r="BI4" t="n">
         <v>3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT4" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU4" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV4" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX4" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.25</v>
+        <v>4.27</v>
       </c>
       <c r="CB4" t="n">
         <v>4.44</v>
@@ -2434,7 +2434,7 @@
         <v>2.32</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="CH4" t="n">
         <v>1.55</v>
@@ -2446,7 +2446,7 @@
         <v>1.64</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL4" t="n">
         <v>1.94</v>
@@ -2455,7 +2455,7 @@
         <v>2.42</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO4" t="n">
         <v>1.17</v>
@@ -2464,16 +2464,16 @@
         <v>1.6</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CU4" t="n">
         <v>1.57</v>
@@ -2491,10 +2491,10 @@
         <v>1.89</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DB4" t="n">
         <v>1.19</v>
@@ -2503,49 +2503,49 @@
         <v>1.62</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="DH4" t="n">
-        <v>92.37</v>
+        <v>93.3</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.31</v>
+        <v>5.45</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.69</v>
+        <v>45.55</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="DP4" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.95</v>
+        <v>12.45</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.210000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="DS4" t="n">
         <v>0.1</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>53.48</v>
+        <v>53.8</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.26</v>
+        <v>16.55</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.11</v>
+        <v>10.2</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6.16</v>
+        <v>6.35</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.68</v>
+        <v>17.75</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0.1</v>
@@ -2678,139 +2678,139 @@
         <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>72.33</v>
+        <v>74.3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>31.89</v>
+        <v>32.3</v>
       </c>
       <c r="AO5" t="n">
         <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.89</v>
+        <v>13.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>16.33</v>
+        <v>15.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.78</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>46.89</v>
+        <v>48</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.22</v>
+        <v>11.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.220000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.33</v>
+        <v>17.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.949999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.58</v>
+        <v>0.7</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.42</v>
+        <v>4.45</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.47</v>
+        <v>5.2</v>
       </c>
       <c r="BR5" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS5" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT5" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BU5" t="n">
-        <v>10.53</v>
+        <v>15</v>
       </c>
       <c r="BV5" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BY5" t="n">
         <v>4.02</v>
@@ -2819,43 +2819,43 @@
         <v>4.38</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.31</v>
+        <v>4.48</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.71</v>
+        <v>4.83</v>
       </c>
       <c r="CE5" t="n">
         <v>1.34</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CH5" t="n">
         <v>1.46</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CN5" t="n">
         <v>1.82</v>
@@ -2867,7 +2867,7 @@
         <v>1.81</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CR5" t="n">
         <v>1.39</v>
@@ -2882,22 +2882,22 @@
         <v>1.48</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="DB5" t="n">
         <v>1.26</v>
@@ -2906,49 +2906,49 @@
         <v>1.83</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="DE5" t="n">
         <v>0.1</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="DH5" t="n">
-        <v>74.63</v>
+        <v>75.5</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="DK5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM5" t="n">
-        <v>35.53</v>
+        <v>35.55</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.16</v>
+        <v>11.85</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15</v>
+        <v>14.75</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.79</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS5" t="n">
         <v>0.1</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.16</v>
+        <v>49.6</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.63</v>
+        <v>11.7</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.95</v>
+        <v>7.9</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.1</v>
+        <v>17.95</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,49 +3084,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AI6" t="n">
-        <v>82.67</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="AL6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AN6" t="n">
-        <v>36.89</v>
+        <v>37.2</v>
       </c>
       <c r="AO6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13.11</v>
+        <v>13.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>14.67</v>
+        <v>15.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.779999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT6" t="n">
         <v>2</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>45.33</v>
+        <v>46.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.22</v>
+        <v>10.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>20.33</v>
+        <v>21.9</v>
       </c>
       <c r="BE6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO6" t="n">
         <v>1.2</v>
       </c>
-      <c r="BF6" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>9.26</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.11</v>
-      </c>
       <c r="BP6" t="n">
-        <v>4.37</v>
+        <v>4.4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.89</v>
+        <v>4.85</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT6" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX6" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
         <v>4.15</v>
@@ -3222,43 +3222,43 @@
         <v>4.19</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="CB6" t="n">
         <v>4.31</v>
       </c>
       <c r="CC6" t="n">
-        <v>6.44</v>
+        <v>6.54</v>
       </c>
       <c r="CD6" t="n">
-        <v>7.12</v>
+        <v>7.07</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF6" t="n">
         <v>2.57</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CK6" t="n">
         <v>1.57</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CN6" t="n">
         <v>1.78</v>
@@ -3270,28 +3270,28 @@
         <v>1.81</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="CR6" t="n">
         <v>1.41</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CT6" t="n">
         <v>3.03</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY6" t="n">
         <v>1.97</v>
@@ -3309,49 +3309,49 @@
         <v>1.87</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="DH6" t="n">
-        <v>87</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DM6" t="n">
-        <v>35.95</v>
+        <v>36.15</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.63</v>
+        <v>13.65</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.63</v>
+        <v>14.9</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.949999999999999</v>
+        <v>9</v>
       </c>
       <c r="DS6" t="n">
         <v>0.05</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.31</v>
+        <v>46.8</v>
       </c>
       <c r="DW6" t="n">
         <v>0.1</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.68</v>
+        <v>10.55</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.84</v>
+        <v>7.7</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.47</v>
+        <v>21.25</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="7">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="H8" t="n">
-        <v>102.8</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="K8" t="n">
-        <v>6.4</v>
+        <v>6.36</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M8" t="n">
-        <v>55.4</v>
+        <v>56.09</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="P8" t="n">
-        <v>11.4</v>
+        <v>11.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.6</v>
+        <v>10.45</v>
       </c>
       <c r="R8" t="n">
-        <v>6.5</v>
+        <v>6.09</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="T8" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>65.09999999999999</v>
+        <v>65.27</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.6</v>
+        <v>20.82</v>
       </c>
       <c r="AA8" t="n">
-        <v>13.9</v>
+        <v>13.91</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.7</v>
+        <v>6.91</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.9</v>
+        <v>20.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF8" t="n">
         <v>0.22</v>
@@ -3968,70 +3968,70 @@
         <v>2.56</v>
       </c>
       <c r="BG8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.890000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="BR8" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS8" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT8" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU8" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BV8" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY8" t="n">
         <v>1.28</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.65</v>
+        <v>5.67</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.98</v>
+        <v>6.08</v>
       </c>
       <c r="CC8" t="n">
         <v>1.54</v>
@@ -4040,13 +4040,13 @@
         <v>1.62</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CF8" t="n">
         <v>2.11</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.85</v>
+        <v>3.89</v>
       </c>
       <c r="CH8" t="n">
         <v>1.7</v>
@@ -4058,16 +4058,16 @@
         <v>1.72</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO8" t="n">
         <v>1.12</v>
@@ -4076,15 +4076,15 @@
         <v>1.44</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CV8" t="n">
         <v>2.15</v>
@@ -4096,13 +4096,13 @@
         <v>1.51</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DA8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB8" t="n">
         <v>1.15</v>
@@ -4111,19 +4111,19 @@
         <v>1.46</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="DH8" t="n">
-        <v>98.16</v>
+        <v>96.75</v>
       </c>
       <c r="DI8" t="n">
         <v>0.05</v>
@@ -4132,58 +4132,58 @@
         <v>2.05</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.26</v>
+        <v>5.3</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM8" t="n">
-        <v>50.58</v>
+        <v>51.2</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.26</v>
+        <v>12.3</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.69</v>
+        <v>10.6</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.21</v>
+        <v>6.95</v>
       </c>
       <c r="DS8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="DW8" t="n">
         <v>0.1</v>
       </c>
-      <c r="DT8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV8" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="DW8" t="n">
-        <v>0.11</v>
-      </c>
       <c r="DX8" t="n">
-        <v>17.16</v>
+        <v>17.45</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.26</v>
+        <v>11.4</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.89</v>
+        <v>6.05</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.63</v>
+        <v>19.1</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="EC8" t="n">
         <v>1.9</v>
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>0.2</v>
@@ -4286,139 +4286,139 @@
         <v>3.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AI9" t="n">
-        <v>64.89</v>
+        <v>64.8</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="AL9" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.78</v>
+        <v>13.7</v>
       </c>
       <c r="AR9" t="n">
-        <v>16.11</v>
+        <v>16.3</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.67</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>44.56</v>
+        <v>46.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA9" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>16.11</v>
+        <v>16.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BF9" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="BG9" t="n">
         <v>3.05</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.05</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI9" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.84</v>
+        <v>5.7</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS9" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT9" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU9" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV9" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX9" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY9" t="n">
         <v>3.01</v>
@@ -4427,16 +4427,16 @@
         <v>3.14</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.99</v>
+        <v>4.8</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.36</v>
+        <v>5.16</v>
       </c>
       <c r="CE9" t="n">
         <v>1.32</v>
@@ -4445,37 +4445,37 @@
         <v>2.55</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="CH9" t="n">
         <v>1.49</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.69</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP9" t="n">
         <v>1.76</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
@@ -4484,16 +4484,16 @@
         <v>2.67</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CU9" t="n">
         <v>1.52</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CX9" t="n">
         <v>1.58</v>
@@ -4514,82 +4514,82 @@
         <v>1.8</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="DH9" t="n">
-        <v>79</v>
+        <v>78.25</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.26</v>
+        <v>5.1</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM9" t="n">
-        <v>36.47</v>
+        <v>36.15</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.26</v>
+        <v>13.25</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.26</v>
+        <v>16.35</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.050000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.48</v>
+        <v>52.05</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX9" t="n">
         <v>13.95</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.58</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.37</v>
+        <v>4.4</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.84</v>
+        <v>18.1</v>
       </c>
       <c r="EB9" t="n">
         <v>1.45</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -4599,94 +4599,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F10" t="n">
-        <v>0.89</v>
+        <v>1.2</v>
       </c>
       <c r="G10" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="n">
-        <v>71.89</v>
+        <v>69.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J10" t="n">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>5.22</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M10" t="n">
-        <v>30.22</v>
+        <v>28.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="P10" t="n">
-        <v>11.67</v>
+        <v>12.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.11</v>
+        <v>13.1</v>
       </c>
       <c r="R10" t="n">
         <v>11</v>
       </c>
       <c r="S10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>42.33</v>
+        <v>41.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.22</v>
+        <v>13.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.33</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.89</v>
+        <v>5</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.44</v>
+        <v>18.4</v>
       </c>
       <c r="AD10" t="n">
         <v>1.39</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AF10" t="n">
         <v>0.1</v>
@@ -4770,70 +4770,70 @@
         <v>2.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.369999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BL10" t="n">
         <v>0.95</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.37</v>
+        <v>4.3</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS10" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT10" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU10" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV10" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX10" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CC10" t="n">
         <v>5.39</v>
@@ -4845,7 +4845,7 @@
         <v>1.29</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CG10" t="n">
         <v>2.79</v>
@@ -4854,49 +4854,49 @@
         <v>1.35</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.73</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ10" t="n">
         <v>3.05</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="CT10" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CU10" t="n">
         <v>1.43</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX10" t="n">
         <v>1.6</v>
@@ -4917,46 +4917,46 @@
         <v>1.97</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="DG10" t="n">
         <v>1.95</v>
       </c>
       <c r="DH10" t="n">
-        <v>68.73999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="DI10" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DM10" t="n">
-        <v>28.21</v>
+        <v>27.55</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.95</v>
+        <v>13.2</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.16</v>
+        <v>14.1</v>
       </c>
       <c r="DR10" t="n">
         <v>11</v>
@@ -4971,28 +4971,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>41.63</v>
+        <v>41.4</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.68</v>
+        <v>10.8</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.21</v>
+        <v>7.2</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.47</v>
+        <v>3.6</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.42</v>
+        <v>18.4</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="11">
@@ -5002,61 +5002,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F11" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G11" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="H11" t="n">
-        <v>94.67</v>
+        <v>95.3</v>
       </c>
       <c r="I11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J11" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="K11" t="n">
-        <v>4.89</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="M11" t="n">
-        <v>40.33</v>
+        <v>41.2</v>
       </c>
       <c r="N11" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="P11" t="n">
-        <v>17.89</v>
+        <v>18.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.67</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="S11" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5068,28 +5068,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>36.78</v>
+        <v>37.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.22</v>
+        <v>13.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.109999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.11</v>
+        <v>4.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.56</v>
+        <v>19.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AF11" t="n">
         <v>0.1</v>
@@ -5173,49 +5173,49 @@
         <v>2.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.890000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.42</v>
+        <v>5.35</v>
       </c>
       <c r="BR11" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS11" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT11" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BU11" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5224,19 +5224,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.59</v>
+        <v>3.62</v>
       </c>
       <c r="CC11" t="n">
         <v>3.26</v>
@@ -5248,19 +5248,19 @@
         <v>1.4</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH11" t="n">
         <v>1.39</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CK11" t="n">
         <v>1.56</v>
@@ -5269,19 +5269,19 @@
         <v>2.02</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO11" t="n">
         <v>1.29</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="CR11" t="n">
         <v>1.43</v>
@@ -5290,16 +5290,16 @@
         <v>3.03</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CU11" t="n">
         <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX11" t="n">
         <v>1.55</v>
@@ -5320,49 +5320,49 @@
         <v>2.08</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="DE11" t="n">
         <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="DH11" t="n">
-        <v>92.58</v>
+        <v>93</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.58</v>
+        <v>4.65</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="DM11" t="n">
-        <v>40.58</v>
+        <v>41</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="DP11" t="n">
-        <v>17.68</v>
+        <v>17.8</v>
       </c>
       <c r="DQ11" t="n">
-        <v>8.9</v>
+        <v>9.15</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.369999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>36.9</v>
+        <v>37.25</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.47</v>
+        <v>13.75</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.949999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.53</v>
+        <v>4.65</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.16</v>
+        <v>19.35</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="12">
@@ -5808,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5901,136 +5901,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AI13" t="n">
-        <v>81.5</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.9</v>
+        <v>3.09</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="AM13" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>35.09</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>43.18</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BK13" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN13" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.53</v>
-      </c>
       <c r="BL13" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.26</v>
+        <v>4.3</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS13" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT13" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BV13" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX13" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY13" t="n">
         <v>3.33</v>
@@ -6039,70 +6039,70 @@
         <v>3.57</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.92</v>
+        <v>4.02</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.08</v>
+        <v>4.27</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.03</v>
+        <v>5.34</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.46</v>
+        <v>6.09</v>
       </c>
       <c r="CE13" t="n">
         <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CK13" t="n">
         <v>1.48</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="CR13" t="n">
         <v>1.37</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="CT13" t="n">
         <v>3.22</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CW13" t="n">
         <v>1.68</v>
@@ -6111,10 +6111,10 @@
         <v>1.53</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DA13" t="n">
         <v>1.94</v>
@@ -6123,52 +6123,52 @@
         <v>1.22</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="DH13" t="n">
-        <v>80.63</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM13" t="n">
-        <v>40.26</v>
+        <v>39.95</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.05</v>
+        <v>12.95</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.37</v>
+        <v>13.35</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.050000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6180,28 +6180,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47</v>
+        <v>46.3</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.16</v>
+        <v>11.05</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.32</v>
+        <v>7.25</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.37</v>
+        <v>18.9</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="14">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6704,139 +6704,139 @@
         <v>2.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="AH15" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AI15" t="n">
-        <v>92.78</v>
+        <v>90</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="AL15" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN15" t="n">
-        <v>39.78</v>
+        <v>38.2</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AP15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11</v>
+        <v>12.1</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.67</v>
+        <v>14.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.890000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>50.89</v>
+        <v>49.8</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>13.11</v>
+        <v>12.7</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.44</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.67</v>
+        <v>4.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>18.78</v>
+        <v>19.1</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.16</v>
+        <v>10.15</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.63</v>
+        <v>5.6</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS15" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BT15" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU15" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV15" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BY15" t="n">
         <v>2.11</v>
@@ -6845,31 +6845,31 @@
         <v>2.19</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="CC15" t="n">
-        <v>5.11</v>
+        <v>5.18</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.47</v>
+        <v>5.65</v>
       </c>
       <c r="CE15" t="n">
         <v>1.35</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.72</v>
@@ -6878,136 +6878,136 @@
         <v>1.51</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CN15" t="n">
         <v>1.86</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="CR15" t="n">
         <v>1.38</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="CT15" t="n">
         <v>3.13</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX15" t="n">
         <v>1.54</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DA15" t="n">
         <v>1.9</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="DE15" t="n">
         <v>0.05</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="DG15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="DH15" t="n">
-        <v>101.42</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="DI15" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.58</v>
+        <v>5.4</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DM15" t="n">
-        <v>46.37</v>
+        <v>45.25</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.68</v>
+        <v>12.2</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.26</v>
+        <v>13.4</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.26</v>
+        <v>8.15</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>53.95</v>
+        <v>53.25</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.37</v>
+        <v>14.1</v>
       </c>
       <c r="DY15" t="n">
-        <v>10</v>
+        <v>9.85</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.37</v>
+        <v>4.25</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.69</v>
+        <v>20.75</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="EC15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="16">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0.1</v>
@@ -7107,139 +7107,139 @@
         <v>2.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>80.56</v>
+        <v>81.3</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>31.89</v>
+        <v>32.2</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP16" t="n">
         <v>1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.44</v>
+        <v>13.1</v>
       </c>
       <c r="AR16" t="n">
-        <v>12.33</v>
+        <v>12.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.44</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>47.33</v>
+        <v>46.9</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.22</v>
+        <v>11.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.68</v>
+        <v>8.65</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="BO16" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.16</v>
+        <v>4.05</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.47</v>
+        <v>4.55</v>
       </c>
       <c r="BR16" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS16" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT16" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BV16" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW16" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX16" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY16" t="n">
         <v>2.19</v>
@@ -7248,16 +7248,16 @@
         <v>2.49</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="CB16" t="n">
         <v>3.83</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.27</v>
+        <v>4.23</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.47</v>
+        <v>4.46</v>
       </c>
       <c r="CE16" t="n">
         <v>1.28</v>
@@ -7266,19 +7266,19 @@
         <v>2.45</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CH16" t="n">
         <v>1.4</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.62</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL16" t="n">
         <v>1.94</v>
@@ -7296,25 +7296,25 @@
         <v>1.74</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CU16" t="n">
         <v>1.49</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CX16" t="n">
         <v>1.58</v>
@@ -7329,55 +7329,55 @@
         <v>1.84</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF16" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="DH16" t="n">
-        <v>80.27</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="DI16" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DM16" t="n">
-        <v>35.32</v>
+        <v>35.3</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.42</v>
+        <v>14.2</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.21</v>
+        <v>12.35</v>
       </c>
       <c r="DR16" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="DS16" t="n">
         <v>0.1</v>
@@ -7389,28 +7389,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>49.42</v>
+        <v>49.1</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.26</v>
+        <v>12.3</v>
       </c>
       <c r="DY16" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.74</v>
+        <v>16.65</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="17">
@@ -8141,7 +8141,7 @@
         <v>1.8</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="DE18" t="n">
         <v>0.05</v>
@@ -8226,10 +8226,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -8238,82 +8238,82 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="G19" t="n">
         <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>83.44</v>
+        <v>85.2</v>
       </c>
       <c r="I19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J19" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M19" t="n">
-        <v>40.78</v>
+        <v>41.7</v>
       </c>
       <c r="N19" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="P19" t="n">
-        <v>15.67</v>
+        <v>15.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.22</v>
+        <v>12</v>
       </c>
       <c r="R19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>53</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AA19" t="n">
         <v>8</v>
       </c>
-      <c r="S19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>52.56</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>12.56</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>8.220000000000001</v>
-      </c>
       <c r="AB19" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.44</v>
+        <v>17.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8397,67 +8397,67 @@
         <v>1.9</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.89</v>
+        <v>10.75</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BM19" t="n">
         <v>1.05</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="BO19" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.42</v>
+        <v>4.3</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.42</v>
+        <v>6.4</v>
       </c>
       <c r="BR19" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS19" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT19" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU19" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BV19" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW19" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX19" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="CB19" t="n">
         <v>3.67</v>
@@ -8472,55 +8472,55 @@
         <v>1.34</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CH19" t="n">
         <v>1.46</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL19" t="n">
         <v>2.02</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CN19" t="n">
         <v>1.83</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CR19" t="n">
         <v>1.38</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CU19" t="n">
         <v>1.47</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CW19" t="n">
         <v>1.72</v>
@@ -8544,82 +8544,82 @@
         <v>1.86</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.31</v>
+        <v>93.7</v>
       </c>
       <c r="DI19" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.21</v>
+        <v>5.15</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DM19" t="n">
-        <v>43.53</v>
+        <v>43.85</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.69</v>
+        <v>13.75</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.47</v>
+        <v>13.3</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.74</v>
+        <v>7.5</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.58</v>
+        <v>55.65</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.9</v>
+        <v>12.75</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.369999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="EA19" t="n">
-        <v>18.26</v>
+        <v>18.2</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1421,7 +1421,7 @@
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="Q2" t="n">
         <v>14</v>
@@ -1733,7 +1733,7 @@
         <v>2.45</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.25</v>
+        <v>12.3</v>
       </c>
       <c r="DQ2" t="n">
         <v>15.05</v>
@@ -2714,7 +2714,7 @@
         <v>13.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="AS5" t="n">
         <v>8.300000000000001</v>
@@ -2945,7 +2945,7 @@
         <v>11.85</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.75</v>
+        <v>14.8</v>
       </c>
       <c r="DR5" t="n">
         <v>8.050000000000001</v>
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0.11</v>
@@ -3484,52 +3484,52 @@
         <v>2.33</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="n">
-        <v>98.7</v>
+        <v>96.64</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AL7" t="n">
-        <v>6</v>
+        <v>5.73</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AN7" t="n">
-        <v>43</v>
+        <v>41.27</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.2</v>
+        <v>13.27</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.2</v>
+        <v>12.64</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.2</v>
+        <v>6.73</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>56.9</v>
+        <v>55.45</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA7" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.8</v>
+        <v>5.73</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.9</v>
+        <v>18.09</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.11</v>
+        <v>10.15</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="BP7" t="n">
         <v>5.05</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="BR7" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS7" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT7" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU7" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BV7" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW7" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX7" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY7" t="n">
         <v>1.4</v>
@@ -3625,55 +3625,55 @@
         <v>1.39</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.89</v>
+        <v>4.84</v>
       </c>
       <c r="CB7" t="n">
-        <v>5.09</v>
+        <v>5.02</v>
       </c>
       <c r="CC7" t="n">
         <v>1.64</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="CH7" t="n">
         <v>1.55</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.81</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CO7" t="n">
         <v>1.18</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
@@ -3694,100 +3694,100 @@
         <v>1.88</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="DH7" t="n">
-        <v>109.16</v>
+        <v>107.5</v>
       </c>
       <c r="DI7" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.37</v>
+        <v>6.2</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.37</v>
+        <v>50.95</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.79</v>
+        <v>12.85</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.42</v>
+        <v>13.6</v>
       </c>
       <c r="DR7" t="n">
-        <v>5.26</v>
+        <v>5.6</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>60</v>
+        <v>59.05</v>
       </c>
       <c r="DW7" t="n">
         <v>0.05</v>
       </c>
       <c r="DX7" t="n">
-        <v>18.31</v>
+        <v>17.85</v>
       </c>
       <c r="DY7" t="n">
-        <v>11.74</v>
+        <v>11.35</v>
       </c>
       <c r="DZ7" t="n">
-        <v>6.58</v>
+        <v>6.5</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.84</v>
+        <v>19.85</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="8">
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>9</v>
@@ -6223,82 +6223,82 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="H14" t="n">
-        <v>94.5</v>
+        <v>95.91</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3</v>
+        <v>4.64</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M14" t="n">
-        <v>37.1</v>
+        <v>38.64</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="O14" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="P14" t="n">
-        <v>14.4</v>
+        <v>14.64</v>
       </c>
       <c r="Q14" t="n">
-        <v>14.7</v>
+        <v>14.64</v>
       </c>
       <c r="R14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>48.2</v>
+        <v>49.18</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.9</v>
+        <v>11.91</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.2</v>
+        <v>3.91</v>
       </c>
       <c r="AC14" t="n">
-        <v>23.6</v>
+        <v>24.27</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6382,70 +6382,70 @@
         <v>2.78</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.369999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.42</v>
+        <v>4.45</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="BR14" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS14" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BT14" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BU14" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV14" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CC14" t="n">
         <v>5</v>
@@ -6457,7 +6457,7 @@
         <v>1.39</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CG14" t="n">
         <v>2.87</v>
@@ -6472,13 +6472,13 @@
         <v>1.84</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CL14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CM14" t="n">
         <v>2.17</v>
-      </c>
-      <c r="CM14" t="n">
-        <v>2.18</v>
       </c>
       <c r="CN14" t="n">
         <v>1.74</v>
@@ -6490,7 +6490,7 @@
         <v>1.98</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="CR14" t="n">
         <v>1.42</v>
@@ -6508,7 +6508,7 @@
         <v>1.98</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX14" t="n">
         <v>1.64</v>
@@ -6517,94 +6517,94 @@
         <v>2.05</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB14" t="n">
         <v>1.34</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="DH14" t="n">
-        <v>90.84</v>
+        <v>91.8</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.31</v>
+        <v>4.5</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM14" t="n">
-        <v>37.79</v>
+        <v>38.6</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.74</v>
+        <v>14.85</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.52</v>
+        <v>14.5</v>
       </c>
       <c r="DR14" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.68</v>
+        <v>49.2</v>
       </c>
       <c r="DW14" t="n">
         <v>0.1</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.47</v>
+        <v>10.55</v>
       </c>
       <c r="DY14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.16</v>
+        <v>21.65</v>
       </c>
       <c r="EB14" t="n">
         <v>1.18</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,49 +1875,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AI3" t="n">
-        <v>70.3</v>
+        <v>73</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN3" t="n">
-        <v>26.6</v>
+        <v>27.27</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.7</v>
+        <v>11.73</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.9</v>
+        <v>14.64</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.5</v>
+        <v>10.18</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>42.6</v>
+        <v>44</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.1</v>
+        <v>6.36</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.6</v>
+        <v>3.91</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="BD3" t="n">
-        <v>20.3</v>
+        <v>20.64</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.550000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.1</v>
+        <v>5.14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.45</v>
+        <v>4.57</v>
       </c>
       <c r="BR3" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV3" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW3" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX3" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY3" t="n">
         <v>3.5</v>
@@ -2013,28 +2013,28 @@
         <v>3.8</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.22</v>
+        <v>5.02</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.77</v>
+        <v>5.55</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI3" t="n">
         <v>1.92</v>
@@ -2049,19 +2049,19 @@
         <v>2.09</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="CR3" t="n">
         <v>1.42</v>
@@ -2079,7 +2079,7 @@
         <v>1.99</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX3" t="n">
         <v>1.62</v>
@@ -2094,55 +2094,55 @@
         <v>1.78</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="DG3" t="n">
         <v>1.9</v>
       </c>
       <c r="DH3" t="n">
-        <v>73.7</v>
+        <v>74.95</v>
       </c>
       <c r="DI3" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DK3" t="n">
         <v>4.05</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM3" t="n">
-        <v>30.95</v>
+        <v>31.09</v>
       </c>
       <c r="DN3" t="n">
         <v>0.9</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DP3" t="n">
-        <v>12.65</v>
+        <v>12.14</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.35</v>
+        <v>15.67</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.25</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.1</v>
+        <v>43.81</v>
       </c>
       <c r="DW3" t="n">
         <v>0.1</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.1</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.85</v>
+        <v>4.95</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.35</v>
+        <v>19.57</v>
       </c>
       <c r="EB3" t="n">
         <v>0.97</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="4">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="H5" t="n">
-        <v>76.7</v>
+        <v>75.73</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="K5" t="n">
-        <v>4.8</v>
+        <v>4.36</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M5" t="n">
-        <v>38.8</v>
+        <v>37.55</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="P5" t="n">
-        <v>10.6</v>
+        <v>10.27</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.8</v>
+        <v>13.91</v>
       </c>
       <c r="R5" t="n">
-        <v>7.8</v>
+        <v>7.91</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>51.2</v>
+        <v>50.64</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>12</v>
+        <v>11.45</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.7</v>
+        <v>7.36</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.3</v>
+        <v>4.09</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.8</v>
+        <v>18.64</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AF5" t="n">
         <v>0.1</v>
@@ -2759,70 +2759,70 @@
         <v>2.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.699999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BR5" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS5" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU5" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV5" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY5" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="CB5" t="n">
         <v>4.02</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>4.04</v>
       </c>
       <c r="CC5" t="n">
         <v>4.48</v>
@@ -2834,7 +2834,7 @@
         <v>1.34</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CG5" t="n">
         <v>3.04</v>
@@ -2843,7 +2843,7 @@
         <v>1.46</v>
       </c>
       <c r="CI5" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.75</v>
@@ -2858,34 +2858,34 @@
         <v>2.32</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX5" t="n">
         <v>1.57</v>
@@ -2897,7 +2897,7 @@
         <v>2.35</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB5" t="n">
         <v>1.26</v>
@@ -2906,82 +2906,82 @@
         <v>1.83</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DG5" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DH5" t="n">
-        <v>75.5</v>
+        <v>75.05</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.95</v>
+        <v>3.76</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM5" t="n">
-        <v>35.55</v>
+        <v>35.05</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.85</v>
+        <v>11.62</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.8</v>
+        <v>14.81</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.050000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.6</v>
+        <v>49.38</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.7</v>
+        <v>11.43</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.9</v>
+        <v>7.71</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="EA5" t="n">
-        <v>17.95</v>
+        <v>17.91</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="H6" t="n">
-        <v>90.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M6" t="n">
-        <v>35.1</v>
+        <v>34.73</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>14.1</v>
+        <v>13.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.6</v>
+        <v>14.45</v>
       </c>
       <c r="R6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>47.2</v>
+        <v>46.73</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.2</v>
+        <v>10.73</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.6</v>
+        <v>20.45</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>2.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.25</v>
+        <v>9.43</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.4</v>
+        <v>4.48</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.85</v>
+        <v>4.95</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>90</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU6" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV6" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW6" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="BZ6" t="n">
-        <v>4.19</v>
+        <v>4.03</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.31</v>
+        <v>4.25</v>
       </c>
       <c r="CC6" t="n">
         <v>6.54</v>
@@ -3237,16 +3237,16 @@
         <v>1.34</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI6" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.78</v>
@@ -3255,22 +3255,22 @@
         <v>1.57</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CN6" t="n">
         <v>1.78</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="CR6" t="n">
         <v>1.41</v>
@@ -3288,7 +3288,7 @@
         <v>2.05</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX6" t="n">
         <v>1.59</v>
@@ -3303,55 +3303,55 @@
         <v>1.84</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="DE6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="DH6" t="n">
-        <v>87.15000000000001</v>
+        <v>86.86</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.45</v>
+        <v>3.72</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM6" t="n">
-        <v>36.15</v>
+        <v>35.91</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.65</v>
+        <v>13.19</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.9</v>
+        <v>14.81</v>
       </c>
       <c r="DR6" t="n">
-        <v>9</v>
+        <v>9.15</v>
       </c>
       <c r="DS6" t="n">
         <v>0.05</v>
@@ -3363,25 +3363,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.8</v>
+        <v>46.57</v>
       </c>
       <c r="DW6" t="n">
         <v>0.1</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.55</v>
+        <v>10.81</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.7</v>
+        <v>7.86</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.25</v>
+        <v>21.14</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="EC6" t="n">
         <v>2.1</v>
@@ -7420,94 +7420,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="G17" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>104.7</v>
+        <v>104.55</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="K17" t="n">
-        <v>6.5</v>
+        <v>6.64</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="M17" t="n">
-        <v>45.6</v>
+        <v>45.27</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="O17" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="P17" t="n">
-        <v>15.5</v>
+        <v>15.09</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.2</v>
+        <v>12.18</v>
       </c>
       <c r="R17" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>56.7</v>
+        <v>56.27</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.5</v>
+        <v>10.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="AC17" t="n">
-        <v>21.6</v>
+        <v>20.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AF17" t="n">
         <v>0.2</v>
@@ -7591,31 +7591,31 @@
         <v>2.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.65</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BP17" t="n">
         <v>4</v>
@@ -7624,37 +7624,37 @@
         <v>5</v>
       </c>
       <c r="BR17" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BU17" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV17" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CC17" t="n">
         <v>3.29</v>
@@ -7666,10 +7666,10 @@
         <v>1.38</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CH17" t="n">
         <v>1.4</v>
@@ -7684,7 +7684,7 @@
         <v>1.58</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CM17" t="n">
         <v>2.26</v>
@@ -7699,7 +7699,7 @@
         <v>1.95</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CR17" t="n">
         <v>1.41</v>
@@ -7708,10 +7708,10 @@
         <v>2.94</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV17" t="n">
         <v>2.07</v>
@@ -7726,7 +7726,7 @@
         <v>1.99</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DA17" t="n">
         <v>1.82</v>
@@ -7741,46 +7741,46 @@
         <v>3.55</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DG17" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.05</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.75</v>
+        <v>5.86</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DM17" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="DP17" t="n">
-        <v>14.95</v>
+        <v>14.76</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.55</v>
+        <v>11.57</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.9</v>
+        <v>7.86</v>
       </c>
       <c r="DS17" t="n">
         <v>0.05</v>
@@ -7792,25 +7792,25 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>51.5</v>
+        <v>51.52</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.05</v>
+        <v>12.95</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.300000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.75</v>
+        <v>3.57</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.2</v>
+        <v>18.76</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="EC17" t="n">
         <v>2.05</v>
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7913,139 +7913,139 @@
         <v>1.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AI18" t="n">
-        <v>83.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.7</v>
+        <v>4.36</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN18" t="n">
-        <v>32.2</v>
+        <v>31</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ18" t="n">
         <v>12</v>
       </c>
       <c r="AR18" t="n">
-        <v>15.4</v>
+        <v>15.18</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.6</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>54</v>
+        <v>53.45</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA18" t="n">
-        <v>12.9</v>
+        <v>13.27</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.7</v>
+        <v>7.73</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.2</v>
+        <v>5.55</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.3</v>
+        <v>17.18</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="BG18" t="n">
         <v>3.05</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.25</v>
+        <v>9.24</v>
       </c>
       <c r="BI18" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="BR18" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT18" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU18" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV18" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW18" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BX18" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY18" t="n">
         <v>1.72</v>
@@ -8054,31 +8054,31 @@
         <v>1.73</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.27</v>
+        <v>3.23</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CE18" t="n">
         <v>1.34</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CG18" t="n">
         <v>3.11</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.72</v>
@@ -8090,31 +8090,31 @@
         <v>2.01</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CN18" t="n">
         <v>1.84</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="CR18" t="n">
         <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV18" t="n">
         <v>2.18</v>
@@ -8126,97 +8126,97 @@
         <v>1.56</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.36</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DB18" t="n">
         <v>1.25</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="DE18" t="n">
         <v>0.05</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="DH18" t="n">
-        <v>95.05</v>
+        <v>95.48</v>
       </c>
       <c r="DI18" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.45</v>
+        <v>4.28</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.8</v>
+        <v>40.71</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.3</v>
+        <v>12.29</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.05</v>
+        <v>14</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.15</v>
+        <v>8.24</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>55.15</v>
+        <v>54.81</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX18" t="n">
-        <v>15.8</v>
+        <v>15.86</v>
       </c>
       <c r="DY18" t="n">
-        <v>10.15</v>
+        <v>10.05</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.65</v>
+        <v>5.81</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.5</v>
+        <v>19.33</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="19">
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8319,136 +8319,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AI19" t="n">
-        <v>102.2</v>
+        <v>102</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.6</v>
+        <v>5.73</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN19" t="n">
-        <v>46</v>
+        <v>46.64</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11.9</v>
+        <v>12.18</v>
       </c>
       <c r="AR19" t="n">
-        <v>14.6</v>
+        <v>14.09</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.5</v>
+        <v>7.18</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>58.3</v>
+        <v>58</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA19" t="n">
-        <v>13.2</v>
+        <v>14.36</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.5</v>
+        <v>9.09</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.7</v>
+        <v>5.27</v>
       </c>
       <c r="BD19" t="n">
-        <v>19</v>
+        <v>19.09</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.75</v>
+        <v>10.57</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM19" t="n">
         <v>1.05</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BO19" t="n">
         <v>1.05</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.4</v>
+        <v>6.24</v>
       </c>
       <c r="BR19" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS19" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT19" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU19" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV19" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW19" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX19" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY19" t="n">
         <v>2.43</v>
@@ -8457,22 +8457,22 @@
         <v>2.43</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.01</v>
+        <v>2.89</v>
       </c>
       <c r="CE19" t="n">
         <v>1.34</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CG19" t="n">
         <v>3.05</v>
@@ -8493,37 +8493,37 @@
         <v>2.02</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CO19" t="n">
         <v>1.22</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CR19" t="n">
         <v>1.38</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CV19" t="n">
         <v>2.21</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CX19" t="n">
         <v>1.55</v>
@@ -8541,85 +8541,85 @@
         <v>1.26</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.7</v>
+        <v>94</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.15</v>
+        <v>5.24</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DM19" t="n">
-        <v>43.85</v>
+        <v>44.29</v>
       </c>
       <c r="DN19" t="n">
         <v>1.1</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.75</v>
+        <v>13.81</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.3</v>
+        <v>13.09</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.5</v>
+        <v>7.33</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.65</v>
+        <v>55.62</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.75</v>
+        <v>13.38</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.25</v>
+        <v>8.57</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.5</v>
+        <v>4.81</v>
       </c>
       <c r="EA19" t="n">
-        <v>18.2</v>
+        <v>18.29</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>0.2</v>
@@ -1469,139 +1469,139 @@
         <v>1.9</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>81.09999999999999</v>
+        <v>77.73</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN2" t="n">
-        <v>39.9</v>
+        <v>37.55</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.1</v>
+        <v>12.27</v>
       </c>
       <c r="AR2" t="n">
-        <v>16.1</v>
+        <v>15.82</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.1</v>
+        <v>7.36</v>
       </c>
       <c r="AT2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>46.27</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="BE2" t="n">
         <v>1.3</v>
       </c>
-      <c r="AU2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BF2" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.550000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.7</v>
+        <v>4.57</v>
       </c>
       <c r="BR2" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BS2" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BU2" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BV2" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY2" t="n">
         <v>3.01</v>
@@ -1610,34 +1610,34 @@
         <v>3.14</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="CC2" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.8</v>
+        <v>4.94</v>
       </c>
       <c r="CE2" t="n">
         <v>1.36</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CK2" t="n">
         <v>1.7</v>
@@ -1646,19 +1646,19 @@
         <v>2.13</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="CR2" t="n">
         <v>1.4</v>
@@ -1679,100 +1679,100 @@
         <v>1.82</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DB2" t="n">
         <v>1.29</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="DH2" t="n">
-        <v>86.2</v>
+        <v>84.19</v>
       </c>
       <c r="DI2" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.8</v>
+        <v>4.71</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM2" t="n">
-        <v>42.25</v>
+        <v>40.91</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.3</v>
+        <v>12.38</v>
       </c>
       <c r="DQ2" t="n">
-        <v>15.05</v>
+        <v>14.95</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.6</v>
+        <v>6.76</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>48.6</v>
+        <v>47.76</v>
       </c>
       <c r="DW2" t="n">
         <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.75</v>
+        <v>12.47</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.6</v>
+        <v>18.62</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="3">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>100.6</v>
+        <v>101.18</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="K4" t="n">
-        <v>6.4</v>
+        <v>6.09</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="M4" t="n">
-        <v>51.7</v>
+        <v>52</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>14.5</v>
+        <v>14.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.1</v>
+        <v>14.09</v>
       </c>
       <c r="R4" t="n">
-        <v>6.9</v>
+        <v>6.91</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>55.2</v>
+        <v>56.45</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.4</v>
+        <v>18.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.8</v>
+        <v>11.82</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.6</v>
+        <v>6.73</v>
       </c>
       <c r="AC4" t="n">
-        <v>15.3</v>
+        <v>15.27</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AF4" t="n">
         <v>0.3</v>
@@ -2356,70 +2356,70 @@
         <v>2.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.15</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BL4" t="n">
         <v>0.9</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.9</v>
+        <v>4.86</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.2</v>
+        <v>5.05</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BT4" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU4" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BV4" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW4" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX4" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.27</v>
+        <v>4.28</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.44</v>
+        <v>4.45</v>
       </c>
       <c r="CC4" t="n">
         <v>2.29</v>
@@ -2440,7 +2440,7 @@
         <v>1.55</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.64</v>
@@ -2449,10 +2449,10 @@
         <v>1.5</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CN4" t="n">
         <v>1.9</v>
@@ -2461,10 +2461,10 @@
         <v>1.17</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
@@ -2473,16 +2473,16 @@
         <v>2.5</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="CU4" t="n">
         <v>1.57</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX4" t="n">
         <v>1.53</v>
@@ -2491,10 +2491,10 @@
         <v>1.89</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DB4" t="n">
         <v>1.19</v>
@@ -2506,79 +2506,79 @@
         <v>2.53</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="DH4" t="n">
-        <v>93.3</v>
+        <v>93.95</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.45</v>
+        <v>5.33</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="DM4" t="n">
-        <v>45.55</v>
+        <v>46</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.1</v>
+        <v>14.09</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.45</v>
+        <v>12.52</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.15</v>
+        <v>8.1</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>53.8</v>
+        <v>54.52</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.55</v>
+        <v>16.72</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.2</v>
+        <v>10.29</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6.35</v>
+        <v>6.43</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.75</v>
+        <v>17.62</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="5">
@@ -2816,13 +2816,13 @@
         <v>4.07</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4.48</v>
+        <v>4.52</v>
       </c>
       <c r="CA5" t="n">
         <v>3.9</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.02</v>
+        <v>4.03</v>
       </c>
       <c r="CC5" t="n">
         <v>4.48</v>
@@ -2870,22 +2870,22 @@
         <v>2.92</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV5" t="n">
         <v>2.12</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX5" t="n">
         <v>1.57</v>
@@ -2903,7 +2903,7 @@
         <v>1.26</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DD5" t="n">
         <v>3.02</v>
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F7" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H7" t="n">
-        <v>120.78</v>
+        <v>118.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="K7" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="L7" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>62.78</v>
+        <v>64.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>12.33</v>
+        <v>12</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.78</v>
+        <v>14.4</v>
       </c>
       <c r="R7" t="n">
-        <v>4.22</v>
+        <v>4.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U7" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="V7" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>63.44</v>
+        <v>63.4</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.33</v>
+        <v>21.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>13.89</v>
+        <v>13.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.44</v>
+        <v>7.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AF7" t="n">
         <v>0.27</v>
@@ -3565,70 +3565,70 @@
         <v>2.36</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.15</v>
+        <v>10.43</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.05</v>
+        <v>5.19</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.1</v>
+        <v>5.24</v>
       </c>
       <c r="BR7" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS7" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU7" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BV7" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW7" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX7" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.84</v>
+        <v>4.89</v>
       </c>
       <c r="CB7" t="n">
-        <v>5.02</v>
+        <v>5.09</v>
       </c>
       <c r="CC7" t="n">
         <v>1.64</v>
@@ -3637,31 +3637,31 @@
         <v>1.7</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="CH7" t="n">
         <v>1.55</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK7" t="n">
         <v>1.55</v>
       </c>
       <c r="CL7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CN7" t="n">
         <v>1.82</v>
@@ -3673,7 +3673,7 @@
         <v>1.65</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
@@ -3688,106 +3688,106 @@
         <v>1.56</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CW7" t="n">
         <v>1.88</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY7" t="n">
         <v>1.94</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB7" t="n">
         <v>1.23</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="DG7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="DH7" t="n">
-        <v>107.5</v>
+        <v>106.95</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.2</v>
+        <v>6.24</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DM7" t="n">
-        <v>50.95</v>
+        <v>52.33</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.85</v>
+        <v>12.67</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.6</v>
+        <v>13.48</v>
       </c>
       <c r="DR7" t="n">
-        <v>5.6</v>
+        <v>5.57</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.05</v>
+        <v>59.24</v>
       </c>
       <c r="DW7" t="n">
         <v>0.05</v>
       </c>
       <c r="DX7" t="n">
-        <v>17.85</v>
+        <v>17.9</v>
       </c>
       <c r="DY7" t="n">
-        <v>11.35</v>
+        <v>11.38</v>
       </c>
       <c r="DZ7" t="n">
-        <v>6.5</v>
+        <v>6.53</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.85</v>
+        <v>19.48</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0.36</v>
@@ -3887,139 +3887,139 @@
         <v>1.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AI8" t="n">
-        <v>93</v>
+        <v>94.2</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AL8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="AN8" t="n">
-        <v>45.22</v>
+        <v>45.4</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.22</v>
+        <v>12.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>10.78</v>
+        <v>10.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>59.67</v>
+        <v>59.7</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.33</v>
+        <v>13.9</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.33</v>
+        <v>8.9</v>
       </c>
       <c r="BC8" t="n">
         <v>5</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.11</v>
+        <v>16.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="BG8" t="n">
         <v>3.05</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.949999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="BI8" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL8" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP8" t="n">
         <v>4.1</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.85</v>
+        <v>4.71</v>
       </c>
       <c r="BR8" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BV8" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY8" t="n">
         <v>1.28</v>
@@ -4028,43 +4028,43 @@
         <v>1.3</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.67</v>
+        <v>5.61</v>
       </c>
       <c r="CB8" t="n">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="CC8" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CD8" t="n">
         <v>1.62</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CF8" t="n">
         <v>2.11</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="CH8" t="n">
         <v>1.7</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CK8" t="n">
         <v>1.49</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CN8" t="n">
         <v>1.91</v>
@@ -4073,36 +4073,36 @@
         <v>1.12</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB8" t="n">
         <v>1.15</v>
@@ -4114,79 +4114,79 @@
         <v>2.18</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="DH8" t="n">
-        <v>96.75</v>
+        <v>97.14</v>
       </c>
       <c r="DI8" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.3</v>
+        <v>5.19</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="DM8" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.6</v>
+        <v>10.62</v>
       </c>
       <c r="DR8" t="n">
         <v>6.95</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>62.75</v>
+        <v>62.62</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>17.45</v>
+        <v>17.52</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.4</v>
+        <v>11.52</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.1</v>
+        <v>18.76</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="9">
@@ -4196,94 +4196,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="G9" t="n">
-        <v>4.9</v>
+        <v>4.45</v>
       </c>
       <c r="H9" t="n">
-        <v>91.7</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="K9" t="n">
-        <v>7.3</v>
+        <v>6.73</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M9" t="n">
-        <v>43.2</v>
+        <v>41.82</v>
       </c>
       <c r="N9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="O9" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="P9" t="n">
-        <v>12.8</v>
+        <v>12.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.4</v>
+        <v>16.82</v>
       </c>
       <c r="R9" t="n">
-        <v>6.6</v>
+        <v>6.91</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>57.7</v>
+        <v>56.64</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.6</v>
+        <v>15.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.6</v>
+        <v>10.73</v>
       </c>
       <c r="AB9" t="n">
-        <v>5</v>
+        <v>4.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.4</v>
+        <v>18.82</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AF9" t="n">
         <v>0.1</v>
@@ -4370,67 +4370,67 @@
         <v>3.05</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI9" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.7</v>
+        <v>5.57</v>
       </c>
       <c r="BR9" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BT9" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU9" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW9" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX9" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CC9" t="n">
         <v>4.8</v>
@@ -4439,16 +4439,16 @@
         <v>5.16</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI9" t="n">
         <v>2.1</v>
@@ -4460,19 +4460,19 @@
         <v>1.54</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CM9" t="n">
         <v>2.32</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CO9" t="n">
         <v>1.23</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CQ9" t="n">
         <v>2.86</v>
@@ -4496,7 +4496,7 @@
         <v>1.7</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY9" t="n">
         <v>1.92</v>
@@ -4505,7 +4505,7 @@
         <v>2.33</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DB9" t="n">
         <v>1.25</v>
@@ -4514,79 +4514,79 @@
         <v>1.8</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.25</v>
+        <v>78.62</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.1</v>
+        <v>4.91</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM9" t="n">
-        <v>36.15</v>
+        <v>35.76</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.25</v>
+        <v>13.29</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.35</v>
+        <v>16.57</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.95</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>52.05</v>
+        <v>51.76</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.95</v>
+        <v>13.47</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.550000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.4</v>
+        <v>4.29</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.1</v>
+        <v>17.86</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="EC9" t="n">
         <v>3</v>
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>0.2</v>
@@ -4689,52 +4689,52 @@
         <v>1.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AI10" t="n">
-        <v>65.90000000000001</v>
+        <v>66.36</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.8</v>
+        <v>3.36</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AN10" t="n">
-        <v>26.4</v>
+        <v>29.91</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.1</v>
+        <v>13.82</v>
       </c>
       <c r="AR10" t="n">
-        <v>15.1</v>
+        <v>14.55</v>
       </c>
       <c r="AS10" t="n">
-        <v>11</v>
+        <v>10.36</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4746,82 +4746,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>41</v>
+        <v>40.64</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.4</v>
+        <v>8.82</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.2</v>
+        <v>6.55</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.4</v>
+        <v>18.82</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.15</v>
+        <v>9.48</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.3</v>
+        <v>4.48</v>
       </c>
       <c r="BR10" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU10" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BV10" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW10" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX10" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY10" t="n">
         <v>3.17</v>
@@ -4830,55 +4830,55 @@
         <v>3.21</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.68</v>
+        <v>3.79</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.9</v>
+        <v>4.02</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.39</v>
+        <v>5.81</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.34</v>
+        <v>6.79</v>
       </c>
       <c r="CE10" t="n">
         <v>1.29</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK10" t="n">
         <v>1.52</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CM10" t="n">
         <v>2.12</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="CR10" t="n">
         <v>1.41</v>
@@ -4893,73 +4893,73 @@
         <v>1.43</v>
       </c>
       <c r="CV10" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CY10" t="n">
         <v>2.02</v>
       </c>
-      <c r="CW10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CX10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CY10" t="n">
-        <v>2.01</v>
-      </c>
       <c r="CZ10" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DA10" t="n">
         <v>1.8</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="DH10" t="n">
-        <v>67.7</v>
+        <v>67.86</v>
       </c>
       <c r="DI10" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.9</v>
+        <v>4.14</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DM10" t="n">
-        <v>27.55</v>
+        <v>29.33</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.1</v>
+        <v>13.86</v>
       </c>
       <c r="DR10" t="n">
-        <v>11</v>
+        <v>10.66</v>
       </c>
       <c r="DS10" t="n">
         <v>0.1</v>
@@ -4971,25 +4971,25 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>41.4</v>
+        <v>41.19</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.8</v>
+        <v>10.91</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.2</v>
+        <v>7.34</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.4</v>
+        <v>18.62</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="EC10" t="n">
         <v>2.05</v>
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>0.1</v>
@@ -5092,52 +5092,52 @@
         <v>2.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AI11" t="n">
-        <v>90.7</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.3</v>
+        <v>4.18</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AN11" t="n">
-        <v>40.8</v>
+        <v>38.64</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AQ11" t="n">
-        <v>17.5</v>
+        <v>16.45</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5149,73 +5149,73 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>37</v>
+        <v>36.91</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA11" t="n">
-        <v>13.7</v>
+        <v>13.09</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.9</v>
+        <v>4.55</v>
       </c>
       <c r="BD11" t="n">
-        <v>18.8</v>
+        <v>18.64</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.85</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.35</v>
+        <v>5.14</v>
       </c>
       <c r="BR11" t="n">
-        <v>85</v>
+        <v>80.95</v>
       </c>
       <c r="BS11" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BT11" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BU11" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BY11" t="n">
         <v>2.11</v>
@@ -5233,16 +5233,16 @@
         <v>2.2</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.55</v>
+        <v>3.47</v>
       </c>
       <c r="CE11" t="n">
         <v>1.4</v>
@@ -5251,7 +5251,7 @@
         <v>2.82</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CH11" t="n">
         <v>1.39</v>
@@ -5263,34 +5263,34 @@
         <v>1.83</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="CR11" t="n">
         <v>1.43</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CU11" t="n">
         <v>1.41</v>
@@ -5302,67 +5302,67 @@
         <v>1.89</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB11" t="n">
         <v>1.34</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="DH11" t="n">
-        <v>93</v>
+        <v>92.62</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.65</v>
+        <v>4.57</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DM11" t="n">
-        <v>41</v>
+        <v>39.86</v>
       </c>
       <c r="DN11" t="n">
         <v>1.05</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DP11" t="n">
-        <v>17.8</v>
+        <v>17.24</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.15</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.15</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>37.25</v>
+        <v>37.19</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.75</v>
+        <v>13.43</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.1</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.65</v>
+        <v>4.48</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.35</v>
+        <v>19.24</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="12">
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5498,49 +5498,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="AI12" t="n">
-        <v>81.40000000000001</v>
+        <v>83.64</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.9</v>
+        <v>4.18</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="AN12" t="n">
-        <v>34.4</v>
+        <v>35.73</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AP12" t="n">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.5</v>
+        <v>15.82</v>
       </c>
       <c r="AR12" t="n">
-        <v>10.9</v>
+        <v>11.27</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.9</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5552,82 +5552,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>40.7</v>
+        <v>41.91</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="BB12" t="n">
-        <v>6</v>
+        <v>6.18</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="BD12" t="n">
-        <v>19.5</v>
+        <v>20.09</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF12" t="n">
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.449999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.55</v>
+        <v>5.43</v>
       </c>
       <c r="BR12" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BS12" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU12" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV12" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY12" t="n">
         <v>3.29</v>
@@ -5636,46 +5636,46 @@
         <v>3.74</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.73</v>
+        <v>4.62</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI12" t="n">
         <v>2.05</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK12" t="n">
         <v>1.54</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM12" t="n">
         <v>2.36</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CO12" t="n">
         <v>1.25</v>
@@ -5684,7 +5684,7 @@
         <v>1.85</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CR12" t="n">
         <v>1.41</v>
@@ -5720,52 +5720,52 @@
         <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="DG12" t="n">
         <v>3.1</v>
       </c>
       <c r="DH12" t="n">
-        <v>85.8</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DK12" t="n">
-        <v>5</v>
+        <v>5.09</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="DM12" t="n">
-        <v>39.7</v>
+        <v>40.14</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.2</v>
+        <v>15.38</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.25</v>
+        <v>13.33</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.75</v>
+        <v>7.57</v>
       </c>
       <c r="DS12" t="n">
         <v>0.05</v>
@@ -5777,28 +5777,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.45</v>
+        <v>45.86</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.45</v>
+        <v>10.38</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.85</v>
+        <v>7.86</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.55</v>
+        <v>19.86</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="13">
@@ -5808,10 +5808,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
@@ -5820,49 +5820,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="H13" t="n">
-        <v>79.67</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="K13" t="n">
-        <v>5.44</v>
+        <v>5.7</v>
       </c>
       <c r="L13" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M13" t="n">
-        <v>45.89</v>
+        <v>47.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="O13" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="P13" t="n">
-        <v>11.78</v>
+        <v>11.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.56</v>
+        <v>13.6</v>
       </c>
       <c r="R13" t="n">
-        <v>8.67</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="T13" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5874,28 +5874,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50.11</v>
+        <v>50.8</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>11.33</v>
+        <v>12.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.109999999999999</v>
+        <v>9</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.33</v>
+        <v>22.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5979,70 +5979,70 @@
         <v>2.82</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.5</v>
+        <v>9.52</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.55</v>
+        <v>4.57</v>
       </c>
       <c r="BR13" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU13" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV13" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW13" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX13" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="BZ13" t="n">
         <v>3.57</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
       <c r="CC13" t="n">
         <v>5.34</v>
@@ -6051,61 +6051,61 @@
         <v>6.09</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.27</v>
+        <v>3.23</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="CW13" t="n">
         <v>1.7</v>
-      </c>
-      <c r="CQ13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CS13" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="CU13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CV13" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="CW13" t="n">
-        <v>1.68</v>
       </c>
       <c r="CX13" t="n">
         <v>1.53</v>
@@ -6120,55 +6120,55 @@
         <v>1.94</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="DH13" t="n">
-        <v>78.09999999999999</v>
+        <v>78.86</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.6</v>
+        <v>4.76</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM13" t="n">
-        <v>39.95</v>
+        <v>40.86</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.95</v>
+        <v>12.67</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.35</v>
+        <v>13.38</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6180,28 +6180,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>46.3</v>
+        <v>46.81</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.05</v>
+        <v>11.48</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.25</v>
+        <v>7.72</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.9</v>
+        <v>19.14</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="14">
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6304,49 +6304,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AI14" t="n">
-        <v>86.78</v>
+        <v>85.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AN14" t="n">
-        <v>38.56</v>
+        <v>37.4</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15.11</v>
+        <v>14.2</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.33</v>
+        <v>14.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.33</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6358,82 +6358,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>49.22</v>
+        <v>48.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.890000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.22</v>
+        <v>6.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>18.44</v>
+        <v>17.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.5</v>
+        <v>8.57</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="BR14" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BT14" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BU14" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV14" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BY14" t="n">
         <v>2.9</v>
@@ -6442,25 +6442,25 @@
         <v>2.95</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CC14" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="CD14" t="n">
-        <v>5.17</v>
+        <v>4.88</v>
       </c>
       <c r="CE14" t="n">
         <v>1.39</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CH14" t="n">
         <v>1.4</v>
@@ -6475,31 +6475,31 @@
         <v>1.64</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CM14" t="n">
         <v>2.17</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO14" t="n">
         <v>1.3</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="CU14" t="n">
         <v>1.42</v>
@@ -6508,7 +6508,7 @@
         <v>1.98</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CX14" t="n">
         <v>1.64</v>
@@ -6526,85 +6526,85 @@
         <v>1.34</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.63</v>
+        <v>3.66</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="DH14" t="n">
-        <v>91.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.5</v>
+        <v>4.38</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM14" t="n">
-        <v>38.6</v>
+        <v>38.05</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.85</v>
+        <v>14.43</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.5</v>
+        <v>14.62</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.2</v>
+        <v>48.9</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.55</v>
+        <v>10.52</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.2</v>
+        <v>7.14</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.65</v>
+        <v>21.19</v>
       </c>
       <c r="EB14" t="n">
         <v>1.18</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="15">
@@ -6614,10 +6614,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
@@ -6626,82 +6626,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="H15" t="n">
-        <v>109.2</v>
+        <v>108.45</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="K15" t="n">
-        <v>6.1</v>
+        <v>5.91</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="M15" t="n">
-        <v>52.3</v>
+        <v>51.45</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="P15" t="n">
-        <v>12.3</v>
+        <v>11.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>12.27</v>
       </c>
       <c r="R15" t="n">
-        <v>7.7</v>
+        <v>7.82</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>56.7</v>
+        <v>57.36</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z15" t="n">
-        <v>15.5</v>
+        <v>15.09</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="AC15" t="n">
-        <v>22.4</v>
+        <v>22.36</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AF15" t="n">
         <v>0.1</v>
@@ -6785,70 +6785,70 @@
         <v>2.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.15</v>
+        <v>10</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.55</v>
+        <v>4.62</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.6</v>
+        <v>5.38</v>
       </c>
       <c r="BR15" t="n">
-        <v>95</v>
+        <v>90.48</v>
       </c>
       <c r="BS15" t="n">
-        <v>95</v>
+        <v>90.48</v>
       </c>
       <c r="BT15" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU15" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV15" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="CC15" t="n">
         <v>5.18</v>
@@ -6860,154 +6860,154 @@
         <v>1.35</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="CH15" t="n">
         <v>1.47</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.72</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="CU15" t="n">
         <v>1.48</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="DE15" t="n">
         <v>0.05</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="DH15" t="n">
-        <v>99.59999999999999</v>
+        <v>99.66</v>
       </c>
       <c r="DI15" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.4</v>
+        <v>5.33</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="DM15" t="n">
-        <v>45.25</v>
+        <v>45.14</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.2</v>
+        <v>11.81</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.4</v>
+        <v>13.47</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.15</v>
+        <v>8.19</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>53.25</v>
+        <v>53.76</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.1</v>
+        <v>13.95</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.85</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.75</v>
+        <v>20.81</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="16">
@@ -7017,94 +7017,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="H16" t="n">
-        <v>80</v>
+        <v>78.36</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M16" t="n">
-        <v>38.4</v>
+        <v>38.27</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="O16" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="P16" t="n">
-        <v>15.3</v>
+        <v>14.27</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.1</v>
+        <v>12.18</v>
       </c>
       <c r="R16" t="n">
-        <v>9.699999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>51.3</v>
+        <v>50.27</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.2</v>
+        <v>13.36</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.4</v>
+        <v>17.27</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AF16" t="n">
         <v>0.2</v>
@@ -7188,28 +7188,28 @@
         <v>2.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.65</v>
+        <v>8.52</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BO16" t="n">
         <v>1.05</v>
@@ -7218,40 +7218,40 @@
         <v>4.05</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.55</v>
+        <v>4.43</v>
       </c>
       <c r="BR16" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS16" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU16" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV16" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW16" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX16" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.19</v>
+        <v>2.44</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.53</v>
+        <v>3.57</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.83</v>
+        <v>3.87</v>
       </c>
       <c r="CC16" t="n">
         <v>4.23</v>
@@ -7263,25 +7263,25 @@
         <v>1.28</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CK16" t="n">
         <v>1.49</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CM16" t="n">
         <v>2.16</v>
@@ -7293,25 +7293,25 @@
         <v>1.19</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="CR16" t="n">
         <v>1.38</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="CT16" t="n">
         <v>3.16</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CW16" t="n">
         <v>1.72</v>
@@ -7323,7 +7323,7 @@
         <v>1.97</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DA16" t="n">
         <v>1.84</v>
@@ -7338,79 +7338,79 @@
         <v>3.07</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DH16" t="n">
-        <v>80.65000000000001</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM16" t="n">
-        <v>35.3</v>
+        <v>35.38</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.2</v>
+        <v>13.71</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.35</v>
+        <v>12.38</v>
       </c>
       <c r="DR16" t="n">
         <v>9</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>49.1</v>
+        <v>48.67</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.3</v>
+        <v>12.43</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.65</v>
+        <v>16.62</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="17">
@@ -7486,7 +7486,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>56.27</v>
+        <v>56.36</v>
       </c>
       <c r="Y17" t="n">
         <v>0.09</v>
@@ -7792,7 +7792,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>51.52</v>
+        <v>51.57</v>
       </c>
       <c r="DW17" t="n">
         <v>0.09</v>
@@ -7970,7 +7970,7 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>53.45</v>
+        <v>53.36</v>
       </c>
       <c r="AZ18" t="n">
         <v>0.27</v>
@@ -8195,7 +8195,7 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>54.81</v>
+        <v>54.76</v>
       </c>
       <c r="DW18" t="n">
         <v>0.14</v>
@@ -8466,7 +8466,7 @@
         <v>2.77</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CE19" t="n">
         <v>1.34</v>
@@ -8511,13 +8511,13 @@
         <v>1.38</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV19" t="n">
         <v>2.21</v>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="H2" t="n">
-        <v>91.3</v>
+        <v>91.55</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>5.36</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>44.6</v>
+        <v>46.82</v>
       </c>
       <c r="N2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="P2" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="R2" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>14</v>
-      </c>
-      <c r="R2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.9</v>
-      </c>
       <c r="U2" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>49.4</v>
+        <v>48.64</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.6</v>
+        <v>13.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.9</v>
+        <v>17.82</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AF2" t="n">
         <v>0.09</v>
@@ -1550,70 +1550,70 @@
         <v>2.64</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.43</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BO2" t="n">
         <v>0.86</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.57</v>
+        <v>4.36</v>
       </c>
       <c r="BR2" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT2" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BU2" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV2" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.01</v>
+        <v>2.96</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CC2" t="n">
         <v>4.15</v>
@@ -1625,13 +1625,13 @@
         <v>1.36</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI2" t="n">
         <v>1.99</v>
@@ -1640,25 +1640,25 @@
         <v>1.76</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CN2" t="n">
         <v>1.65</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CR2" t="n">
         <v>1.4</v>
@@ -1676,13 +1676,13 @@
         <v>2.07</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CX2" t="n">
         <v>1.72</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.1</v>
@@ -1697,82 +1697,82 @@
         <v>1.92</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="DH2" t="n">
-        <v>84.19</v>
+        <v>84.64</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.71</v>
+        <v>4.68</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="DM2" t="n">
-        <v>40.91</v>
+        <v>42.18</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.38</v>
+        <v>12.18</v>
       </c>
       <c r="DQ2" t="n">
-        <v>14.95</v>
+        <v>15</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.76</v>
+        <v>6.91</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47.76</v>
+        <v>47.46</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.47</v>
+        <v>12.77</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.57</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.62</v>
+        <v>18.55</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="3">
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="H3" t="n">
-        <v>77.09999999999999</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9</v>
+        <v>4.82</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="M3" t="n">
-        <v>35.3</v>
+        <v>34</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="O3" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="P3" t="n">
-        <v>12.6</v>
+        <v>12.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>16.8</v>
+        <v>16.18</v>
       </c>
       <c r="R3" t="n">
-        <v>8</v>
+        <v>8.18</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>43.6</v>
+        <v>42.82</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.1</v>
+        <v>10.36</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.1</v>
+        <v>6.27</v>
       </c>
       <c r="AB3" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.4</v>
+        <v>18.36</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>2.82</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.710000000000001</v>
+        <v>9.91</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BM3" t="n">
         <v>0.86</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="BP3" t="n">
         <v>5.14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.57</v>
+        <v>4.77</v>
       </c>
       <c r="BR3" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS3" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BV3" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX3" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="CC3" t="n">
         <v>5.02</v>
@@ -2028,19 +2028,19 @@
         <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CK3" t="n">
         <v>1.6</v>
@@ -2058,10 +2058,10 @@
         <v>1.29</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="CR3" t="n">
         <v>1.42</v>
@@ -2076,7 +2076,7 @@
         <v>1.42</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW3" t="n">
         <v>1.89</v>
@@ -2088,61 +2088,61 @@
         <v>2.04</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DB3" t="n">
         <v>1.33</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DH3" t="n">
-        <v>74.95</v>
+        <v>75.09</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="DK3" t="n">
         <v>4.05</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="DM3" t="n">
-        <v>31.09</v>
+        <v>30.64</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DP3" t="n">
-        <v>12.14</v>
+        <v>12.32</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.67</v>
+        <v>15.41</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.140000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.81</v>
+        <v>43.41</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.140000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.95</v>
+        <v>5.09</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.19</v>
+        <v>3.27</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.57</v>
+        <v>19.5</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.24</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="4">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0.09</v>
@@ -2678,139 +2678,139 @@
         <v>2.09</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI5" t="n">
-        <v>74.3</v>
+        <v>71.55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN5" t="n">
-        <v>32.3</v>
+        <v>31.27</v>
       </c>
       <c r="AO5" t="n">
         <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.8</v>
+        <v>15.55</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.300000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>48</v>
+        <v>47.09</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.4</v>
+        <v>10.91</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.1</v>
+        <v>7.64</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.1</v>
+        <v>16.82</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.24</v>
+        <v>2.41</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.57</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.24</v>
+        <v>2.41</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.43</v>
+        <v>4.64</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.1</v>
+        <v>5.18</v>
       </c>
       <c r="BR5" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS5" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT5" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU5" t="n">
-        <v>14.29</v>
+        <v>18.18</v>
       </c>
       <c r="BV5" t="n">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BX5" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
         <v>4.07</v>
@@ -2819,67 +2819,67 @@
         <v>4.52</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.9</v>
+        <v>4.12</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.03</v>
+        <v>4.27</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.48</v>
+        <v>5.67</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.83</v>
+        <v>6.03</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.75</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="CR5" t="n">
         <v>1.39</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="CT5" t="n">
         <v>3.09</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="CV5" t="n">
         <v>2.12</v>
@@ -2888,67 +2888,67 @@
         <v>1.77</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="DB5" t="n">
         <v>1.26</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="DE5" t="n">
         <v>0.09</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="DH5" t="n">
-        <v>75.05</v>
+        <v>73.64</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM5" t="n">
-        <v>35.05</v>
+        <v>34.41</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.62</v>
+        <v>11.64</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.81</v>
+        <v>14.73</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.1</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS5" t="n">
         <v>0.09</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.38</v>
+        <v>48.86</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.43</v>
+        <v>11.18</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.71</v>
+        <v>7.5</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="EA5" t="n">
-        <v>17.91</v>
+        <v>17.73</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="6">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>0.1</v>
@@ -3484,139 +3484,139 @@
         <v>2.3</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH7" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AI7" t="n">
-        <v>96.64</v>
+        <v>93.92</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.73</v>
+        <v>5.83</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AN7" t="n">
-        <v>41.27</v>
+        <v>40.17</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.73</v>
+        <v>2.92</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.27</v>
+        <v>13.42</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.64</v>
+        <v>12.92</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.73</v>
+        <v>6.92</v>
       </c>
       <c r="AT7" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BK7" t="n">
         <v>0.82</v>
       </c>
-      <c r="AU7" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>55.45</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>9.27</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>18.09</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.76</v>
-      </c>
       <c r="BL7" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM7" t="n">
         <v>0.86</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.19</v>
+        <v>5.27</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.24</v>
+        <v>5.32</v>
       </c>
       <c r="BR7" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS7" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT7" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU7" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BV7" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX7" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY7" t="n">
         <v>1.38</v>
@@ -3625,34 +3625,34 @@
         <v>1.38</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.89</v>
+        <v>4.83</v>
       </c>
       <c r="CB7" t="n">
-        <v>5.09</v>
+        <v>5.03</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CH7" t="n">
         <v>1.55</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK7" t="n">
         <v>1.55</v>
@@ -3661,10 +3661,10 @@
         <v>2.02</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CO7" t="n">
         <v>1.18</v>
@@ -3673,13 +3673,13 @@
         <v>1.65</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CT7" t="n">
         <v>3.26</v>
@@ -3688,7 +3688,7 @@
         <v>1.56</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CW7" t="n">
         <v>1.88</v>
@@ -3697,97 +3697,97 @@
         <v>1.57</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DB7" t="n">
         <v>1.23</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="DH7" t="n">
-        <v>106.95</v>
+        <v>105</v>
       </c>
       <c r="DI7" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.24</v>
+        <v>6.27</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.33</v>
+        <v>51.23</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.19</v>
+        <v>3.27</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.67</v>
+        <v>12.77</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.48</v>
+        <v>13.59</v>
       </c>
       <c r="DR7" t="n">
-        <v>5.57</v>
+        <v>5.73</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.24</v>
+        <v>58.45</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX7" t="n">
-        <v>17.9</v>
+        <v>17.5</v>
       </c>
       <c r="DY7" t="n">
-        <v>11.38</v>
+        <v>11.14</v>
       </c>
       <c r="DZ7" t="n">
-        <v>6.53</v>
+        <v>6.36</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.48</v>
+        <v>19.32</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="F8" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="G8" t="n">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="H8" t="n">
-        <v>99.81999999999999</v>
+        <v>100.33</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="K8" t="n">
-        <v>6.36</v>
+        <v>6.83</v>
       </c>
       <c r="L8" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="M8" t="n">
-        <v>56.09</v>
+        <v>57.33</v>
       </c>
       <c r="N8" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O8" t="n">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="P8" t="n">
-        <v>11.55</v>
+        <v>11.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.45</v>
+        <v>10.67</v>
       </c>
       <c r="R8" t="n">
-        <v>6.09</v>
+        <v>5.83</v>
       </c>
       <c r="S8" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="T8" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="U8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>65.27</v>
+        <v>65</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.82</v>
+        <v>20.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>13.91</v>
+        <v>13.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.91</v>
+        <v>7.08</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.73</v>
+        <v>20.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AF8" t="n">
         <v>0.2</v>
@@ -3968,70 +3968,70 @@
         <v>2.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.81</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="BM8" t="n">
         <v>0.86</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.1</v>
+        <v>4.32</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.71</v>
+        <v>4.82</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS8" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT8" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU8" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BV8" t="n">
-        <v>14.29</v>
+        <v>18.18</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BX8" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.61</v>
+        <v>5.75</v>
       </c>
       <c r="CB8" t="n">
-        <v>6.01</v>
+        <v>6.16</v>
       </c>
       <c r="CC8" t="n">
         <v>1.55</v>
@@ -4040,16 +4040,16 @@
         <v>1.62</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.87</v>
+        <v>3.91</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CI8" t="n">
         <v>2.05</v>
@@ -4058,33 +4058,33 @@
         <v>1.71</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CM8" t="n">
         <v>2.45</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CO8" t="n">
         <v>1.12</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CV8" t="n">
         <v>2.16</v>
@@ -4096,97 +4096,97 @@
         <v>1.52</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.45</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="DB8" t="n">
         <v>1.15</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="DH8" t="n">
-        <v>97.14</v>
+        <v>97.54000000000001</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.19</v>
+        <v>5.5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM8" t="n">
-        <v>51</v>
+        <v>51.91</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.1</v>
+        <v>12.14</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.62</v>
+        <v>10.73</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.95</v>
+        <v>6.77</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>62.62</v>
+        <v>62.59</v>
       </c>
       <c r="DW8" t="n">
         <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>17.52</v>
+        <v>17.68</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.52</v>
+        <v>11.55</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6</v>
+        <v>6.13</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.76</v>
+        <v>18.86</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="9">
@@ -4599,94 +4599,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="H10" t="n">
-        <v>69.5</v>
+        <v>70</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J10" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M10" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="P10" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="R10" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>41.45</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE10" t="n">
         <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>11</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.9</v>
       </c>
       <c r="AF10" t="n">
         <v>0.09</v>
@@ -4770,70 +4770,70 @@
         <v>2.18</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.71</v>
+        <v>2.77</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.48</v>
+        <v>9.73</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.71</v>
+        <v>2.77</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.48</v>
+        <v>4.64</v>
       </c>
       <c r="BR10" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS10" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT10" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU10" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BV10" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX10" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="CC10" t="n">
         <v>5.81</v>
@@ -4842,22 +4842,22 @@
         <v>6.79</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CH10" t="n">
         <v>1.37</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK10" t="n">
         <v>1.52</v>
@@ -4878,7 +4878,7 @@
         <v>1.81</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CR10" t="n">
         <v>1.41</v>
@@ -4893,10 +4893,10 @@
         <v>1.43</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX10" t="n">
         <v>1.61</v>
@@ -4911,88 +4911,88 @@
         <v>1.8</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC10" t="n">
         <v>1.95</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="DG10" t="n">
         <v>2.05</v>
       </c>
       <c r="DH10" t="n">
-        <v>67.86</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="DK10" t="n">
         <v>4.14</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM10" t="n">
-        <v>29.33</v>
+        <v>29.5</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.1</v>
+        <v>13.23</v>
       </c>
       <c r="DQ10" t="n">
         <v>13.86</v>
       </c>
       <c r="DR10" t="n">
-        <v>10.66</v>
+        <v>10.5</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>41.19</v>
+        <v>41.04</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.91</v>
+        <v>10.96</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.34</v>
+        <v>7.36</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.57</v>
+        <v>3.59</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.62</v>
+        <v>18.95</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="11">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6704,139 +6704,139 @@
         <v>2.09</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AI15" t="n">
-        <v>90</v>
+        <v>91.64</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.2</v>
+        <v>41.09</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12.1</v>
+        <v>11.73</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.8</v>
+        <v>14.36</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.6</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>49.8</v>
+        <v>50.64</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>12.7</v>
+        <v>12.36</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.300000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.4</v>
+        <v>4.18</v>
       </c>
       <c r="BD15" t="n">
-        <v>19.1</v>
+        <v>18.45</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="BH15" t="n">
-        <v>10</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.62</v>
+        <v>4.73</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.38</v>
+        <v>5.14</v>
       </c>
       <c r="BR15" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS15" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BT15" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU15" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV15" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BY15" t="n">
         <v>2.18</v>
@@ -6845,22 +6845,22 @@
         <v>2.26</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="CC15" t="n">
-        <v>5.18</v>
+        <v>4.99</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.65</v>
+        <v>5.45</v>
       </c>
       <c r="CE15" t="n">
         <v>1.35</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CG15" t="n">
         <v>3.05</v>
@@ -6878,22 +6878,22 @@
         <v>1.52</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO15" t="n">
         <v>1.25</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
@@ -6914,100 +6914,100 @@
         <v>1.77</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB15" t="n">
         <v>1.27</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="DH15" t="n">
-        <v>99.66</v>
+        <v>100.04</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.33</v>
+        <v>5.23</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="DM15" t="n">
-        <v>45.14</v>
+        <v>46.27</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.81</v>
+        <v>11.64</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.47</v>
+        <v>13.31</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.19</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>53.76</v>
+        <v>54</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.95</v>
+        <v>13.72</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.710000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.24</v>
+        <v>4.14</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.81</v>
+        <v>20.4</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="16">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
         <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0.09</v>
@@ -7107,139 +7107,139 @@
         <v>2.36</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="AI16" t="n">
-        <v>81.3</v>
+        <v>81.09</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.5</v>
+        <v>4.18</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AN16" t="n">
-        <v>32.2</v>
+        <v>34.18</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="AP16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>48.27</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BM16" t="n">
         <v>1</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0.95</v>
-      </c>
       <c r="BN16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.05</v>
+        <v>4.18</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.43</v>
+        <v>4.59</v>
       </c>
       <c r="BR16" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS16" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT16" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU16" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BV16" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW16" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX16" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY16" t="n">
         <v>2.44</v>
@@ -7248,37 +7248,37 @@
         <v>2.75</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.23</v>
+        <v>4.12</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.46</v>
+        <v>4.34</v>
       </c>
       <c r="CE16" t="n">
         <v>1.28</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CH16" t="n">
         <v>1.41</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.61</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL16" t="n">
         <v>1.96</v>
@@ -7296,19 +7296,19 @@
         <v>1.73</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="CR16" t="n">
         <v>1.38</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV16" t="n">
         <v>2.22</v>
@@ -7329,55 +7329,55 @@
         <v>1.84</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="DH16" t="n">
-        <v>79.76000000000001</v>
+        <v>79.73</v>
       </c>
       <c r="DI16" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.76</v>
+        <v>4.09</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DM16" t="n">
-        <v>35.38</v>
+        <v>36.22</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.71</v>
+        <v>13.68</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.38</v>
+        <v>12.59</v>
       </c>
       <c r="DR16" t="n">
-        <v>9</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DS16" t="n">
         <v>0.09</v>
@@ -7389,28 +7389,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>48.67</v>
+        <v>49.27</v>
       </c>
       <c r="DW16" t="n">
         <v>0.09</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.43</v>
+        <v>12.54</v>
       </c>
       <c r="DY16" t="n">
         <v>9</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.43</v>
+        <v>3.55</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.62</v>
+        <v>16.64</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="17">
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
         <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
         <v>0.09</v>
@@ -7510,139 +7510,139 @@
         <v>1.64</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AI17" t="n">
-        <v>79.40000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AL17" t="n">
-        <v>5</v>
+        <v>5.45</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AN17" t="n">
-        <v>34.2</v>
+        <v>36.91</v>
       </c>
       <c r="AO17" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.9</v>
+        <v>11.36</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.9</v>
+        <v>9.27</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>46.3</v>
+        <v>48</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.8</v>
+        <v>11.91</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.1</v>
+        <v>8.27</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="BD17" t="n">
-        <v>16.8</v>
+        <v>17.55</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.619999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BP17" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5</v>
+        <v>5.18</v>
       </c>
       <c r="BR17" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS17" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT17" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BU17" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BV17" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY17" t="n">
         <v>2.17</v>
@@ -7651,40 +7651,40 @@
         <v>2.19</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.29</v>
+        <v>3.18</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.59</v>
+        <v>3.46</v>
       </c>
       <c r="CE17" t="n">
         <v>1.38</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CH17" t="n">
         <v>1.4</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CK17" t="n">
         <v>1.58</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM17" t="n">
         <v>2.26</v>
@@ -7693,13 +7693,13 @@
         <v>1.78</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="CR17" t="n">
         <v>1.41</v>
@@ -7714,106 +7714,106 @@
         <v>1.43</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CW17" t="n">
         <v>1.83</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DB17" t="n">
         <v>1.33</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.56999999999999</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.86</v>
+        <v>6.05</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DM17" t="n">
-        <v>40</v>
+        <v>41.09</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="DP17" t="n">
-        <v>14.76</v>
+        <v>14.54</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.57</v>
+        <v>11.77</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.86</v>
+        <v>7.64</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>51.57</v>
+        <v>52.18</v>
       </c>
       <c r="DW17" t="n">
         <v>0.09</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.95</v>
+        <v>12.96</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.380000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.76</v>
+        <v>19.05</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="18">
@@ -7823,94 +7823,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
         <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="H18" t="n">
-        <v>107</v>
+        <v>104.82</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="M18" t="n">
-        <v>51.4</v>
+        <v>50.73</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="O18" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="P18" t="n">
-        <v>12.6</v>
+        <v>12.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.7</v>
+        <v>12.82</v>
       </c>
       <c r="R18" t="n">
-        <v>6.7</v>
+        <v>6.55</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>56.3</v>
+        <v>56.45</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>18.7</v>
+        <v>18.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>12.6</v>
+        <v>12.27</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.1</v>
+        <v>6.27</v>
       </c>
       <c r="AC18" t="n">
-        <v>21.7</v>
+        <v>21.45</v>
       </c>
       <c r="AD18" t="n">
         <v>1.98</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AF18" t="n">
         <v>0.09</v>
@@ -7994,70 +7994,70 @@
         <v>1.73</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.24</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.38</v>
+        <v>4.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.86</v>
+        <v>4.95</v>
       </c>
       <c r="BR18" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS18" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT18" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU18" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BV18" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BW18" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BX18" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="CC18" t="n">
         <v>3.23</v>
@@ -8078,7 +8078,7 @@
         <v>1.47</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.72</v>
@@ -8090,10 +8090,10 @@
         <v>2.01</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CO18" t="n">
         <v>1.23</v>
@@ -8102,7 +8102,7 @@
         <v>1.79</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CR18" t="n">
         <v>1.37</v>
@@ -8111,7 +8111,7 @@
         <v>2.73</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CU18" t="n">
         <v>1.49</v>
@@ -8123,100 +8123,100 @@
         <v>1.74</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY18" t="n">
         <v>1.95</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DB18" t="n">
         <v>1.25</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DD18" t="n">
         <v>2.98</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DF18" t="n">
         <v>1.14</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="DH18" t="n">
-        <v>95.48</v>
+        <v>94.91</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.28</v>
+        <v>4.4</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="DM18" t="n">
-        <v>40.71</v>
+        <v>40.86</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="DO18" t="n">
         <v>2</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.29</v>
+        <v>12.41</v>
       </c>
       <c r="DQ18" t="n">
         <v>14</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.24</v>
+        <v>8.1</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>54.76</v>
+        <v>54.9</v>
       </c>
       <c r="DW18" t="n">
         <v>0.14</v>
       </c>
       <c r="DX18" t="n">
-        <v>15.86</v>
+        <v>15.91</v>
       </c>
       <c r="DY18" t="n">
-        <v>10.05</v>
+        <v>10</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.81</v>
+        <v>5.91</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.33</v>
+        <v>19.31</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>0.27</v>
@@ -2275,52 +2275,52 @@
         <v>2.09</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AI4" t="n">
-        <v>86</v>
+        <v>83.36</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.5</v>
+        <v>4.36</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN4" t="n">
-        <v>39.4</v>
+        <v>38.45</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.7</v>
+        <v>13.45</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.8</v>
+        <v>10.91</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.4</v>
+        <v>9.27</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>52.4</v>
+        <v>51.55</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA4" t="n">
-        <v>14.7</v>
+        <v>14.55</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.6</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.1</v>
+        <v>5.91</v>
       </c>
       <c r="BD4" t="n">
-        <v>20.2</v>
+        <v>20.18</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK4" t="n">
         <v>0.95</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.86</v>
+        <v>4.64</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.05</v>
+        <v>5.23</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BT4" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU4" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BV4" t="n">
-        <v>9.52</v>
+        <v>13.64</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX4" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY4" t="n">
         <v>1.65</v>
@@ -2416,16 +2416,16 @@
         <v>1.71</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CE4" t="n">
         <v>1.27</v>
@@ -2434,13 +2434,13 @@
         <v>2.32</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CH4" t="n">
         <v>1.55</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.64</v>
@@ -2455,16 +2455,16 @@
         <v>2.41</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CO4" t="n">
         <v>1.17</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
@@ -2479,10 +2479,10 @@
         <v>1.57</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CX4" t="n">
         <v>1.53</v>
@@ -2503,49 +2503,49 @@
         <v>1.62</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="DH4" t="n">
-        <v>93.95</v>
+        <v>92.27</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.33</v>
+        <v>5.22</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DM4" t="n">
-        <v>46</v>
+        <v>45.22</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.09</v>
+        <v>13.95</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.52</v>
+        <v>12.5</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.1</v>
+        <v>8.09</v>
       </c>
       <c r="DS4" t="n">
         <v>0.14</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>54.52</v>
+        <v>54</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.72</v>
+        <v>16.55</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.29</v>
+        <v>10.23</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6.43</v>
+        <v>6.32</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.62</v>
+        <v>17.72</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="5">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0.09</v>
@@ -3084,49 +3084,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" t="n">
-        <v>83.40000000000001</v>
+        <v>86.73</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN6" t="n">
-        <v>37.2</v>
+        <v>38.18</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.2</v>
+        <v>15.64</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AT6" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>46.4</v>
+        <v>47.36</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.9</v>
+        <v>10.91</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.7</v>
+        <v>7.64</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="BD6" t="n">
-        <v>21.9</v>
+        <v>21.55</v>
       </c>
       <c r="BE6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO6" t="n">
         <v>1.18</v>
       </c>
-      <c r="BF6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.19</v>
-      </c>
       <c r="BP6" t="n">
-        <v>4.48</v>
+        <v>4.41</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.95</v>
+        <v>4.82</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT6" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.52</v>
+        <v>13.64</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX6" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
         <v>3.99</v>
@@ -3222,25 +3222,25 @@
         <v>4.03</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.11</v>
+        <v>4.07</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.25</v>
+        <v>4.21</v>
       </c>
       <c r="CC6" t="n">
-        <v>6.54</v>
+        <v>6.3</v>
       </c>
       <c r="CD6" t="n">
-        <v>7.07</v>
+        <v>6.76</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CH6" t="n">
         <v>1.46</v>
@@ -3267,10 +3267,10 @@
         <v>1.24</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CR6" t="n">
         <v>1.41</v>
@@ -3285,7 +3285,7 @@
         <v>1.47</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CW6" t="n">
         <v>1.85</v>
@@ -3297,94 +3297,94 @@
         <v>1.97</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DA6" t="n">
         <v>1.84</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DH6" t="n">
-        <v>86.86</v>
+        <v>88.36</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM6" t="n">
-        <v>35.91</v>
+        <v>36.46</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.19</v>
+        <v>13.09</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.81</v>
+        <v>15.04</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.15</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.57</v>
+        <v>47.04</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.81</v>
+        <v>10.82</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.86</v>
+        <v>7.82</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.14</v>
+        <v>21</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>0.18</v>
@@ -4286,139 +4286,139 @@
         <v>3.18</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" t="n">
-        <v>64.8</v>
+        <v>63.73</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.9</v>
+        <v>3.27</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AN9" t="n">
-        <v>29.1</v>
+        <v>28.09</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.7</v>
+        <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>16.3</v>
+        <v>17.09</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>46.4</v>
+        <v>45.82</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.3</v>
+        <v>10.91</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.5</v>
+        <v>7.18</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="BD9" t="n">
-        <v>16.8</v>
+        <v>16.91</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="BG9" t="n">
         <v>3.05</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.710000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BI9" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BL9" t="n">
         <v>0.86</v>
       </c>
-      <c r="BL9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
       <c r="BM9" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.14</v>
+        <v>4.23</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.57</v>
+        <v>5.32</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS9" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BT9" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BV9" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX9" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY9" t="n">
         <v>2.93</v>
@@ -4427,34 +4427,34 @@
         <v>3.06</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.8</v>
+        <v>4.73</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.16</v>
+        <v>5.1</v>
       </c>
       <c r="CE9" t="n">
         <v>1.33</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CH9" t="n">
         <v>1.48</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CK9" t="n">
         <v>1.54</v>
@@ -4466,130 +4466,130 @@
         <v>2.32</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CO9" t="n">
         <v>1.23</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="DB9" t="n">
         <v>1.25</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.09</v>
+        <v>2.95</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.62</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="DI9" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.91</v>
+        <v>4.77</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.76</v>
+        <v>34.96</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.29</v>
+        <v>13.46</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.57</v>
+        <v>16.95</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.050000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.76</v>
+        <v>51.23</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.47</v>
+        <v>13.18</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.19</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.29</v>
+        <v>4.23</v>
       </c>
       <c r="EA9" t="n">
         <v>17.86</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="EC9" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="10">
@@ -5002,61 +5002,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="G11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>95.3</v>
+        <v>96.91</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J11" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>5.09</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M11" t="n">
-        <v>41.2</v>
+        <v>43.36</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="P11" t="n">
-        <v>18.1</v>
+        <v>17.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="R11" t="n">
-        <v>7.7</v>
+        <v>7.27</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5068,28 +5068,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>37.5</v>
+        <v>39.09</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.8</v>
+        <v>14.09</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.4</v>
+        <v>9.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.9</v>
+        <v>20.36</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AF11" t="n">
         <v>0.09</v>
@@ -5173,49 +5173,49 @@
         <v>2.36</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.710000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.57</v>
+        <v>4.55</v>
       </c>
       <c r="BQ11" t="n">
         <v>5.14</v>
       </c>
       <c r="BR11" t="n">
-        <v>80.95</v>
+        <v>77.27</v>
       </c>
       <c r="BS11" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BT11" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BU11" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5224,16 +5224,16 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="CB11" t="n">
         <v>3.59</v>
@@ -5248,7 +5248,7 @@
         <v>1.4</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CG11" t="n">
         <v>2.76</v>
@@ -5257,19 +5257,19 @@
         <v>1.39</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.83</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CN11" t="n">
         <v>1.8</v>
@@ -5284,25 +5284,25 @@
         <v>3.43</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY11" t="n">
         <v>1.96</v>
@@ -5311,91 +5311,91 @@
         <v>2.35</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB11" t="n">
         <v>1.34</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="DE11" t="n">
         <v>0.09</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="DH11" t="n">
-        <v>92.62</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.57</v>
+        <v>4.64</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DM11" t="n">
-        <v>39.86</v>
+        <v>41</v>
       </c>
       <c r="DN11" t="n">
         <v>1.05</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DP11" t="n">
-        <v>17.24</v>
+        <v>17.09</v>
       </c>
       <c r="DQ11" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>38</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="DY11" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="DR11" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="DS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV11" t="n">
-        <v>37.19</v>
-      </c>
-      <c r="DW11" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="DX11" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="DY11" t="n">
-        <v>8.949999999999999</v>
-      </c>
       <c r="DZ11" t="n">
-        <v>4.48</v>
+        <v>4.45</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.24</v>
+        <v>19.5</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="12">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -5417,82 +5417,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="H12" t="n">
-        <v>90.2</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J12" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="K12" t="n">
-        <v>6.1</v>
+        <v>5.73</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>45</v>
+        <v>43.27</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="P12" t="n">
-        <v>14.9</v>
+        <v>15.45</v>
       </c>
       <c r="Q12" t="n">
-        <v>15.6</v>
+        <v>14.91</v>
       </c>
       <c r="R12" t="n">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>50.2</v>
+        <v>49.55</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.7</v>
+        <v>12.64</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AB12" t="n">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="AD12" t="n">
         <v>1.34</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5576,70 +5576,70 @@
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.380000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="BO12" t="n">
         <v>1.05</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.43</v>
+        <v>5.27</v>
       </c>
       <c r="BR12" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU12" t="n">
-        <v>14.29</v>
+        <v>18.18</v>
       </c>
       <c r="BV12" t="n">
-        <v>9.52</v>
+        <v>13.64</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.29</v>
+        <v>3.17</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CC12" t="n">
         <v>3.97</v>
@@ -5651,40 +5651,40 @@
         <v>1.36</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CH12" t="n">
         <v>1.44</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CM12" t="n">
         <v>2.36</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CR12" t="n">
         <v>1.41</v>
@@ -5720,85 +5720,85 @@
         <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="DH12" t="n">
-        <v>86.76000000000001</v>
+        <v>86.41</v>
       </c>
       <c r="DI12" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.09</v>
+        <v>4.95</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="DM12" t="n">
-        <v>40.14</v>
+        <v>39.5</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="DO12" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.38</v>
+        <v>15.64</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.33</v>
+        <v>13.09</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.57</v>
+        <v>7.5</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.86</v>
+        <v>45.73</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.38</v>
+        <v>10.46</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.86</v>
+        <v>7.77</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.86</v>
+        <v>19.55</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="13">
@@ -5808,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5901,49 +5901,49 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>76.81999999999999</v>
+        <v>76.92</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN13" t="n">
-        <v>35.09</v>
+        <v>34.67</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.91</v>
+        <v>13.42</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.18</v>
+        <v>13.25</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.449999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5955,82 +5955,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>43.18</v>
+        <v>43.33</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.82</v>
+        <v>10.75</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.55</v>
+        <v>6.58</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.27</v>
+        <v>4.17</v>
       </c>
       <c r="BD13" t="n">
-        <v>16.09</v>
+        <v>16.25</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.52</v>
+        <v>9.5</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BL13" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BO13" t="n">
         <v>0.86</v>
       </c>
-      <c r="BM13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>0.9</v>
-      </c>
       <c r="BP13" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.57</v>
+        <v>4.59</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="BS13" t="n">
-        <v>85.70999999999999</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV13" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX13" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY13" t="n">
         <v>3.3</v>
@@ -6042,37 +6042,37 @@
         <v>3.99</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.22</v>
+        <v>4.18</v>
       </c>
       <c r="CC13" t="n">
         <v>5.34</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.09</v>
+        <v>6.03</v>
       </c>
       <c r="CE13" t="n">
         <v>1.32</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CK13" t="n">
         <v>1.49</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CM13" t="n">
         <v>2.5</v>
@@ -6081,31 +6081,31 @@
         <v>1.93</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CX13" t="n">
         <v>1.53</v>
@@ -6114,61 +6114,61 @@
         <v>1.87</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DA13" t="n">
         <v>1.94</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="DH13" t="n">
-        <v>78.86</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.76</v>
+        <v>4.68</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM13" t="n">
-        <v>40.86</v>
+        <v>40.37</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.67</v>
+        <v>12.46</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.38</v>
+        <v>13.41</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.9</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6180,28 +6180,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>46.81</v>
+        <v>46.73</v>
       </c>
       <c r="DW13" t="n">
         <v>0.09</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.48</v>
+        <v>11.41</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.72</v>
+        <v>7.68</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.14</v>
+        <v>19.09</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="14">
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
@@ -6223,82 +6223,82 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="G14" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="H14" t="n">
-        <v>95.91</v>
+        <v>96.25</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="J14" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="K14" t="n">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
       <c r="L14" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="M14" t="n">
-        <v>38.64</v>
+        <v>39.58</v>
       </c>
       <c r="N14" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="O14" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="P14" t="n">
-        <v>14.64</v>
+        <v>15.58</v>
       </c>
       <c r="Q14" t="n">
-        <v>14.64</v>
+        <v>14.83</v>
       </c>
       <c r="R14" t="n">
-        <v>8.18</v>
+        <v>7.92</v>
       </c>
       <c r="S14" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="T14" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="U14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>49.18</v>
+        <v>50.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.91</v>
+        <v>12.08</v>
       </c>
       <c r="AA14" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.91</v>
+        <v>4.17</v>
       </c>
       <c r="AC14" t="n">
-        <v>24.27</v>
+        <v>23.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6382,70 +6382,70 @@
         <v>2.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.57</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.48</v>
+        <v>4.55</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.05</v>
+        <v>3.86</v>
       </c>
       <c r="BR14" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS14" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BT14" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BU14" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BV14" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CC14" t="n">
         <v>4.75</v>
@@ -6454,13 +6454,13 @@
         <v>4.88</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CH14" t="n">
         <v>1.4</v>
@@ -6475,10 +6475,10 @@
         <v>1.64</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CN14" t="n">
         <v>1.73</v>
@@ -6487,25 +6487,25 @@
         <v>1.3</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="CR14" t="n">
         <v>1.43</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CT14" t="n">
         <v>2.95</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW14" t="n">
         <v>1.9</v>
@@ -6514,7 +6514,7 @@
         <v>1.64</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.22</v>
@@ -6535,43 +6535,43 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="DH14" t="n">
-        <v>91.09999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.38</v>
+        <v>4.36</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DM14" t="n">
-        <v>38.05</v>
+        <v>38.59</v>
       </c>
       <c r="DN14" t="n">
         <v>0.91</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.43</v>
+        <v>14.95</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.62</v>
+        <v>14.73</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.67</v>
+        <v>8.5</v>
       </c>
       <c r="DS14" t="n">
         <v>0.09</v>
@@ -6583,28 +6583,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.9</v>
+        <v>49.41</v>
       </c>
       <c r="DW14" t="n">
         <v>0.09</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.52</v>
+        <v>10.68</v>
       </c>
       <c r="DY14" t="n">
         <v>7.14</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.19</v>
+        <v>20.91</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="15">
@@ -8226,10 +8226,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
         <v>11</v>
@@ -8238,82 +8238,82 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="H19" t="n">
-        <v>85.2</v>
+        <v>86.18000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="K19" t="n">
-        <v>4.7</v>
+        <v>4.82</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="M19" t="n">
-        <v>41.7</v>
+        <v>41.45</v>
       </c>
       <c r="N19" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="O19" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="P19" t="n">
-        <v>15.6</v>
+        <v>15.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>12.09</v>
       </c>
       <c r="R19" t="n">
-        <v>7.5</v>
+        <v>7.55</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>53</v>
+        <v>53.36</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.3</v>
+        <v>12.45</v>
       </c>
       <c r="AA19" t="n">
         <v>8</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.4</v>
+        <v>17.64</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8397,64 +8397,64 @@
         <v>1.82</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.57</v>
+        <v>10.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.29</v>
+        <v>4.09</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.24</v>
+        <v>6.36</v>
       </c>
       <c r="BR19" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS19" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU19" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BV19" t="n">
-        <v>9.52</v>
+        <v>13.64</v>
       </c>
       <c r="BW19" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX19" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="CA19" t="n">
         <v>3.67</v>
@@ -8472,7 +8472,7 @@
         <v>1.34</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CG19" t="n">
         <v>3.05</v>
@@ -8481,16 +8481,16 @@
         <v>1.46</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CK19" t="n">
         <v>1.55</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CM19" t="n">
         <v>2.32</v>
@@ -8505,7 +8505,7 @@
         <v>1.79</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CR19" t="n">
         <v>1.38</v>
@@ -8520,7 +8520,7 @@
         <v>1.47</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CW19" t="n">
         <v>1.71</v>
@@ -8541,79 +8541,79 @@
         <v>1.26</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="DH19" t="n">
-        <v>94</v>
+        <v>94.09</v>
       </c>
       <c r="DI19" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.24</v>
+        <v>5.28</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DM19" t="n">
-        <v>44.29</v>
+        <v>44.04</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.81</v>
+        <v>13.68</v>
       </c>
       <c r="DQ19" t="n">
         <v>13.09</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.33</v>
+        <v>7.36</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.62</v>
+        <v>55.68</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.38</v>
+        <v>13.4</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.57</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.81</v>
+        <v>4.86</v>
       </c>
       <c r="EA19" t="n">
-        <v>18.29</v>
+        <v>18.37</v>
       </c>
       <c r="EB19" t="n">
         <v>1.51</v>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -6286,16 +6286,16 @@
         <v>12.08</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.92</v>
+        <v>8</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="AC14" t="n">
         <v>23.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -6592,16 +6592,16 @@
         <v>10.68</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.14</v>
+        <v>7.18</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="EA14" t="n">
         <v>20.91</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="EC14" t="n">
         <v>2.27</v>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H2" t="n">
+        <v>91.17</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M2" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="H2" t="n">
-        <v>91.55</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="M2" t="n">
-        <v>46.82</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.91</v>
-      </c>
       <c r="O2" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="P2" t="n">
-        <v>12.09</v>
+        <v>12.17</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.18</v>
+        <v>14.5</v>
       </c>
       <c r="R2" t="n">
-        <v>6.45</v>
+        <v>6.75</v>
       </c>
       <c r="S2" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>48.64</v>
+        <v>49</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.18</v>
+        <v>13.17</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.73</v>
+        <v>8.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.82</v>
+        <v>17.67</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AF2" t="n">
         <v>0.09</v>
@@ -1550,70 +1550,70 @@
         <v>2.64</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.359999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BP2" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="BR2" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS2" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT2" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU2" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV2" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CC2" t="n">
         <v>4.15</v>
@@ -1643,13 +1643,13 @@
         <v>1.69</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CM2" t="n">
         <v>2.06</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CO2" t="n">
         <v>1.26</v>
@@ -1658,22 +1658,22 @@
         <v>1.88</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CR2" t="n">
         <v>1.4</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CU2" t="n">
         <v>1.44</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CW2" t="n">
         <v>1.81</v>
@@ -1697,49 +1697,49 @@
         <v>1.92</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="DE2" t="n">
         <v>0.13</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="DH2" t="n">
-        <v>84.64</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="DI2" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.68</v>
+        <v>4.74</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="DM2" t="n">
-        <v>42.18</v>
+        <v>42.44</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.18</v>
+        <v>12.22</v>
       </c>
       <c r="DQ2" t="n">
-        <v>15</v>
+        <v>15.13</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.91</v>
+        <v>7.04</v>
       </c>
       <c r="DS2" t="n">
         <v>0.13</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47.46</v>
+        <v>47.69</v>
       </c>
       <c r="DW2" t="n">
         <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.77</v>
+        <v>12.78</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.779999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.55</v>
+        <v>18.44</v>
       </c>
       <c r="EB2" t="n">
         <v>1.39</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
         <v>0.09</v>
@@ -1875,49 +1875,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>73</v>
+        <v>73.83</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.27</v>
+        <v>3.42</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN3" t="n">
-        <v>27.27</v>
+        <v>28.17</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.73</v>
+        <v>11.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.64</v>
+        <v>14.42</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.18</v>
+        <v>10.75</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>44</v>
+        <v>44.25</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.36</v>
+        <v>6.75</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.91</v>
+        <v>4.25</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>20.64</v>
+        <v>20.58</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="BH3" t="n">
         <v>9.91</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.14</v>
+        <v>5.22</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.77</v>
+        <v>4.7</v>
       </c>
       <c r="BR3" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BT3" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU3" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV3" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX3" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY3" t="n">
         <v>3.53</v>
@@ -2013,25 +2013,25 @@
         <v>3.79</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.02</v>
+        <v>4.91</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.55</v>
+        <v>5.42</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CH3" t="n">
         <v>1.4</v>
@@ -2043,13 +2043,13 @@
         <v>1.86</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CN3" t="n">
         <v>1.76</v>
@@ -2058,10 +2058,10 @@
         <v>1.29</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="CR3" t="n">
         <v>1.42</v>
@@ -2076,22 +2076,22 @@
         <v>1.42</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DB3" t="n">
         <v>1.33</v>
@@ -2106,43 +2106,43 @@
         <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="DH3" t="n">
-        <v>75.09</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="DI3" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM3" t="n">
-        <v>30.64</v>
+        <v>30.96</v>
       </c>
       <c r="DN3" t="n">
         <v>0.91</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="DP3" t="n">
-        <v>12.32</v>
+        <v>12.17</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.41</v>
+        <v>15.26</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.18</v>
+        <v>9.52</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.41</v>
+        <v>43.57</v>
       </c>
       <c r="DW3" t="n">
         <v>0.09</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.359999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.09</v>
+        <v>5.22</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.5</v>
+        <v>19.52</v>
       </c>
       <c r="EB3" t="n">
         <v>0.99</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="F4" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>101.18</v>
+        <v>98.17</v>
       </c>
       <c r="I4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J4" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="K4" t="n">
-        <v>6.09</v>
+        <v>6.33</v>
       </c>
       <c r="L4" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="M4" t="n">
-        <v>52</v>
+        <v>50.75</v>
       </c>
       <c r="N4" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>14.45</v>
+        <v>14.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.09</v>
+        <v>14.42</v>
       </c>
       <c r="R4" t="n">
-        <v>6.91</v>
+        <v>6.75</v>
       </c>
       <c r="S4" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="T4" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="U4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>56.45</v>
+        <v>56.67</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.55</v>
+        <v>18</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.82</v>
+        <v>11.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.73</v>
+        <v>6.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>15.27</v>
+        <v>15.92</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AF4" t="n">
         <v>0.27</v>
@@ -2356,70 +2356,70 @@
         <v>2.36</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.91</v>
+        <v>10.04</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.64</v>
+        <v>4.83</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.23</v>
+        <v>5.17</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BT4" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU4" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BV4" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX4" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="CC4" t="n">
         <v>2.31</v>
@@ -2428,19 +2428,19 @@
         <v>2.25</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CH4" t="n">
         <v>1.55</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.64</v>
@@ -2449,7 +2449,7 @@
         <v>1.5</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CM4" t="n">
         <v>2.41</v>
@@ -2461,28 +2461,28 @@
         <v>1.17</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CU4" t="n">
         <v>1.57</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX4" t="n">
         <v>1.53</v>
@@ -2497,88 +2497,88 @@
         <v>1.92</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="DH4" t="n">
-        <v>92.27</v>
+        <v>91.09</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.22</v>
+        <v>5.39</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="DM4" t="n">
-        <v>45.22</v>
+        <v>44.87</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.46</v>
+        <v>2.61</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.95</v>
+        <v>14</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.5</v>
+        <v>12.74</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.09</v>
+        <v>7.96</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>54</v>
+        <v>54.22</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.55</v>
+        <v>16.35</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.23</v>
+        <v>10</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6.32</v>
+        <v>6.35</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.72</v>
+        <v>17.96</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="G5" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="n">
-        <v>75.73</v>
+        <v>77.42</v>
       </c>
       <c r="I5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J5" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>4.36</v>
+        <v>4.25</v>
       </c>
       <c r="L5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>37.55</v>
+        <v>38.67</v>
       </c>
       <c r="N5" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="O5" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="P5" t="n">
-        <v>10.27</v>
+        <v>10.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.91</v>
+        <v>14.25</v>
       </c>
       <c r="R5" t="n">
-        <v>7.91</v>
+        <v>7.58</v>
       </c>
       <c r="S5" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="T5" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>50.64</v>
+        <v>51.25</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.45</v>
+        <v>11.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.36</v>
+        <v>7</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.09</v>
+        <v>4.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.64</v>
+        <v>18.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
         <v>0.09</v>
@@ -2759,70 +2759,70 @@
         <v>2.45</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.859999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.64</v>
+        <v>4.57</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.18</v>
+        <v>5.13</v>
       </c>
       <c r="BR5" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS5" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BU5" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV5" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.07</v>
+        <v>3.97</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4.52</v>
+        <v>4.4</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.12</v>
+        <v>4.09</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.27</v>
+        <v>4.23</v>
       </c>
       <c r="CC5" t="n">
         <v>5.67</v>
@@ -2834,10 +2834,10 @@
         <v>1.33</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CH5" t="n">
         <v>1.49</v>
@@ -2846,7 +2846,7 @@
         <v>2</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK5" t="n">
         <v>1.54</v>
@@ -2858,22 +2858,22 @@
         <v>2.33</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CR5" t="n">
         <v>1.39</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CT5" t="n">
         <v>3.09</v>
@@ -2885,103 +2885,103 @@
         <v>2.12</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB5" t="n">
         <v>1.26</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DH5" t="n">
-        <v>73.64</v>
+        <v>74.61</v>
       </c>
       <c r="DI5" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM5" t="n">
-        <v>34.41</v>
+        <v>35.13</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.64</v>
+        <v>11.7</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.73</v>
+        <v>14.87</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.140000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>48.86</v>
+        <v>49.26</v>
       </c>
       <c r="DW5" t="n">
         <v>0.04</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.18</v>
+        <v>11.13</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.5</v>
+        <v>7.31</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.68</v>
+        <v>3.82</v>
       </c>
       <c r="EA5" t="n">
-        <v>17.73</v>
+        <v>17.83</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="H6" t="n">
-        <v>90</v>
+        <v>88.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="L6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>34.73</v>
+        <v>33.67</v>
       </c>
       <c r="N6" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="O6" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="P6" t="n">
-        <v>13.18</v>
+        <v>12.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.45</v>
+        <v>14.5</v>
       </c>
       <c r="R6" t="n">
-        <v>8.550000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="S6" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="T6" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>46.73</v>
+        <v>45.75</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.73</v>
+        <v>10.83</v>
       </c>
       <c r="AA6" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.73</v>
+        <v>2.92</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.45</v>
+        <v>19.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>2.18</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.23</v>
+        <v>9.09</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.41</v>
+        <v>4.43</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.82</v>
+        <v>4.65</v>
       </c>
       <c r="BR6" t="n">
-        <v>100</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>86.36</v>
+        <v>82.61</v>
       </c>
       <c r="BT6" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU6" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV6" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="BZ6" t="n">
-        <v>4.03</v>
+        <v>3.95</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.07</v>
+        <v>4.04</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.21</v>
+        <v>4.16</v>
       </c>
       <c r="CC6" t="n">
         <v>6.3</v>
@@ -3237,13 +3237,13 @@
         <v>1.35</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI6" t="n">
         <v>1.99</v>
@@ -3264,25 +3264,25 @@
         <v>1.78</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV6" t="n">
         <v>2.04</v>
@@ -3306,52 +3306,52 @@
         <v>1.29</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="DE6" t="n">
         <v>0.04</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="DG6" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.36</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM6" t="n">
-        <v>36.46</v>
+        <v>35.83</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.09</v>
+        <v>12.57</v>
       </c>
       <c r="DQ6" t="n">
-        <v>15.04</v>
+        <v>15.05</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.960000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DS6" t="n">
         <v>0.04</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47.04</v>
+        <v>46.52</v>
       </c>
       <c r="DW6" t="n">
         <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.82</v>
+        <v>10.87</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.82</v>
+        <v>7.79</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="EA6" t="n">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="EC6" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="H7" t="n">
-        <v>118.3</v>
+        <v>118.82</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="K7" t="n">
-        <v>6.8</v>
+        <v>6.91</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="M7" t="n">
-        <v>64.5</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P7" t="n">
-        <v>12</v>
+        <v>11.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.4</v>
+        <v>14.55</v>
       </c>
       <c r="R7" t="n">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>63.4</v>
+        <v>63.82</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.1</v>
+        <v>21.09</v>
       </c>
       <c r="AA7" t="n">
-        <v>13.7</v>
+        <v>13.91</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.4</v>
+        <v>7.18</v>
       </c>
       <c r="AC7" t="n">
-        <v>21</v>
+        <v>21.73</v>
       </c>
       <c r="AD7" t="n">
         <v>2.31</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AF7" t="n">
         <v>0.25</v>
@@ -3565,70 +3565,70 @@
         <v>2.58</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.59</v>
+        <v>10.52</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.27</v>
+        <v>5.13</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.32</v>
+        <v>5.39</v>
       </c>
       <c r="BR7" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS7" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BU7" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BV7" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX7" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.83</v>
+        <v>4.88</v>
       </c>
       <c r="CB7" t="n">
-        <v>5.03</v>
+        <v>5.06</v>
       </c>
       <c r="CC7" t="n">
         <v>1.67</v>
@@ -3637,22 +3637,22 @@
         <v>1.73</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CH7" t="n">
         <v>1.55</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK7" t="n">
         <v>1.55</v>
@@ -3661,10 +3661,10 @@
         <v>2.02</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CO7" t="n">
         <v>1.18</v>
@@ -3673,7 +3673,7 @@
         <v>1.65</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
@@ -3688,7 +3688,7 @@
         <v>1.56</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CW7" t="n">
         <v>1.88</v>
@@ -3700,7 +3700,7 @@
         <v>1.95</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DA7" t="n">
         <v>1.86</v>
@@ -3712,82 +3712,82 @@
         <v>1.71</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="DG7" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="DH7" t="n">
-        <v>105</v>
+        <v>105.83</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.27</v>
+        <v>6.35</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="DM7" t="n">
-        <v>51.23</v>
+        <v>52.61</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.77</v>
+        <v>12.57</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.59</v>
+        <v>13.7</v>
       </c>
       <c r="DR7" t="n">
-        <v>5.73</v>
+        <v>5.65</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>58.45</v>
+        <v>58.87</v>
       </c>
       <c r="DW7" t="n">
         <v>0.04</v>
       </c>
       <c r="DX7" t="n">
-        <v>17.5</v>
+        <v>17.65</v>
       </c>
       <c r="DY7" t="n">
-        <v>11.14</v>
+        <v>11.35</v>
       </c>
       <c r="DZ7" t="n">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.32</v>
+        <v>19.74</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>0.42</v>
@@ -3887,139 +3887,139 @@
         <v>1.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AI8" t="n">
-        <v>94.2</v>
+        <v>93.36</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN8" t="n">
-        <v>45.4</v>
+        <v>43.73</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.7</v>
+        <v>12.45</v>
       </c>
       <c r="AR8" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.9</v>
+        <v>7.64</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>59.7</v>
+        <v>59.82</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.9</v>
+        <v>13.18</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.9</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>5</v>
+        <v>4.73</v>
       </c>
       <c r="BD8" t="n">
-        <v>16.6</v>
+        <v>17.18</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.140000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BN8" t="n">
         <v>1.91</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.32</v>
+        <v>4.22</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS8" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BU8" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BV8" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX8" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY8" t="n">
         <v>1.27</v>
@@ -4028,10 +4028,10 @@
         <v>1.29</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="CB8" t="n">
-        <v>6.16</v>
+        <v>6.07</v>
       </c>
       <c r="CC8" t="n">
         <v>1.55</v>
@@ -4043,48 +4043,48 @@
         <v>1.21</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="CH8" t="n">
         <v>1.71</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.71</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CM8" t="n">
         <v>2.45</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO8" t="n">
         <v>1.12</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CV8" t="n">
         <v>2.16</v>
@@ -4096,34 +4096,34 @@
         <v>1.52</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DA8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB8" t="n">
         <v>1.15</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DF8" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="DH8" t="n">
-        <v>97.54000000000001</v>
+        <v>97</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
@@ -4132,61 +4132,61 @@
         <v>1.91</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.5</v>
+        <v>5.43</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM8" t="n">
-        <v>51.91</v>
+        <v>50.83</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.14</v>
+        <v>12.04</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.73</v>
+        <v>10.83</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.77</v>
+        <v>6.7</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>62.59</v>
+        <v>62.52</v>
       </c>
       <c r="DW8" t="n">
         <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>17.68</v>
+        <v>17.17</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.55</v>
+        <v>11.22</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6.13</v>
+        <v>5.96</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.86</v>
+        <v>19.04</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="9">
@@ -4196,94 +4196,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F9" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="G9" t="n">
-        <v>4.45</v>
+        <v>4.83</v>
       </c>
       <c r="H9" t="n">
-        <v>91.18000000000001</v>
+        <v>90.75</v>
       </c>
       <c r="I9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J9" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>6.73</v>
+        <v>7.08</v>
       </c>
       <c r="L9" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="M9" t="n">
-        <v>41.82</v>
+        <v>44.08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O9" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="P9" t="n">
-        <v>12.91</v>
+        <v>12.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.82</v>
+        <v>16.75</v>
       </c>
       <c r="R9" t="n">
-        <v>6.91</v>
+        <v>6.92</v>
       </c>
       <c r="S9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="T9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="U9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>56.64</v>
+        <v>56.42</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>15.45</v>
+        <v>15.42</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.73</v>
+        <v>10.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.73</v>
+        <v>4.92</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.82</v>
+        <v>18.17</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="AF9" t="n">
         <v>0.09</v>
@@ -4367,70 +4367,70 @@
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.550000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.23</v>
+        <v>4.22</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.32</v>
+        <v>5.57</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS9" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BT9" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BU9" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV9" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX9" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.06</v>
+        <v>3.15</v>
       </c>
       <c r="CA9" t="n">
         <v>3.82</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="CC9" t="n">
         <v>4.73</v>
@@ -4445,13 +4445,13 @@
         <v>2.58</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CH9" t="n">
         <v>1.48</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.7</v>
@@ -4472,16 +4472,16 @@
         <v>1.23</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CT9" t="n">
         <v>3.19</v>
@@ -4499,13 +4499,13 @@
         <v>1.58</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB9" t="n">
         <v>1.25</v>
@@ -4514,49 +4514,49 @@
         <v>1.81</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="DE9" t="n">
         <v>0.13</v>
       </c>
       <c r="DF9" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.95</v>
+        <v>3.21</v>
       </c>
       <c r="DH9" t="n">
-        <v>77.45999999999999</v>
+        <v>77.83</v>
       </c>
       <c r="DI9" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.5</v>
+        <v>3.39</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.77</v>
+        <v>5.04</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.96</v>
+        <v>36.43</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DO9" t="n">
         <v>1.82</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.46</v>
+        <v>13.31</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.95</v>
+        <v>16.91</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.95</v>
+        <v>7.91</v>
       </c>
       <c r="DS9" t="n">
         <v>0.13</v>
@@ -4568,28 +4568,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.23</v>
+        <v>51.35</v>
       </c>
       <c r="DW9" t="n">
         <v>0.22</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.18</v>
+        <v>13.26</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.960000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.23</v>
+        <v>4.35</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.86</v>
+        <v>17.57</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>0.18</v>
@@ -4689,52 +4689,52 @@
         <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AI10" t="n">
-        <v>66.36</v>
+        <v>67.42</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>29.91</v>
+        <v>31.08</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.82</v>
+        <v>14.17</v>
       </c>
       <c r="AR10" t="n">
-        <v>14.55</v>
+        <v>14.42</v>
       </c>
       <c r="AS10" t="n">
-        <v>10.36</v>
+        <v>9.75</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4746,82 +4746,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>40.64</v>
+        <v>40.75</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.82</v>
+        <v>9.17</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.55</v>
+        <v>6.75</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.82</v>
+        <v>19.17</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.73</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.05</v>
+        <v>4.96</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.64</v>
+        <v>4.61</v>
       </c>
       <c r="BR10" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS10" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BU10" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV10" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX10" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BY10" t="n">
         <v>3.1</v>
@@ -4830,25 +4830,25 @@
         <v>3.14</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.81</v>
+        <v>5.54</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.79</v>
+        <v>6.43</v>
       </c>
       <c r="CE10" t="n">
         <v>1.3</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CH10" t="n">
         <v>1.37</v>
@@ -4860,31 +4860,31 @@
         <v>1.73</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL10" t="n">
         <v>1.97</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN10" t="n">
         <v>1.68</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CR10" t="n">
         <v>1.41</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CT10" t="n">
         <v>3.02</v>
@@ -4893,22 +4893,22 @@
         <v>1.43</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB10" t="n">
         <v>1.3</v>
@@ -4923,43 +4923,43 @@
         <v>0.13</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DH10" t="n">
-        <v>68.18000000000001</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="DI10" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DM10" t="n">
-        <v>29.5</v>
+        <v>30.13</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DO10" t="n">
         <v>2.04</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.23</v>
+        <v>13.44</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.86</v>
+        <v>13.83</v>
       </c>
       <c r="DR10" t="n">
-        <v>10.5</v>
+        <v>10.18</v>
       </c>
       <c r="DS10" t="n">
         <v>0.09</v>
@@ -4971,25 +4971,25 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>41.04</v>
+        <v>41.08</v>
       </c>
       <c r="DW10" t="n">
         <v>0.22</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.96</v>
+        <v>11.04</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.36</v>
+        <v>7.43</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.95</v>
+        <v>19.13</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="EC10" t="n">
         <v>2.09</v>
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
         <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>0.09</v>
@@ -5092,52 +5092,52 @@
         <v>2.27</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AI11" t="n">
-        <v>90.18000000000001</v>
+        <v>91.33</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AN11" t="n">
-        <v>38.64</v>
+        <v>39.17</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ11" t="n">
-        <v>16.45</v>
+        <v>16.58</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.09</v>
+        <v>9.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.550000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.64</v>
+        <v>0.92</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5149,73 +5149,73 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>36.91</v>
+        <v>37.25</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA11" t="n">
-        <v>13.09</v>
+        <v>12.67</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.550000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="BD11" t="n">
-        <v>18.64</v>
+        <v>19</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.68</v>
+        <v>9.83</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.55</v>
+        <v>4.74</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.14</v>
+        <v>5.09</v>
       </c>
       <c r="BR11" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BS11" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BT11" t="n">
-        <v>31.82</v>
+        <v>34.78</v>
       </c>
       <c r="BU11" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BY11" t="n">
         <v>2.07</v>
@@ -5233,16 +5233,16 @@
         <v>2.16</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.47</v>
+        <v>3.64</v>
       </c>
       <c r="CE11" t="n">
         <v>1.4</v>
@@ -5257,7 +5257,7 @@
         <v>1.39</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.83</v>
@@ -5269,31 +5269,31 @@
         <v>2.03</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP11" t="n">
         <v>1.98</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CV11" t="n">
         <v>1.97</v>
@@ -5305,10 +5305,10 @@
         <v>1.55</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA11" t="n">
         <v>1.85</v>
@@ -5317,52 +5317,52 @@
         <v>1.34</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="DH11" t="n">
-        <v>93.54000000000001</v>
+        <v>94</v>
       </c>
       <c r="DI11" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.64</v>
+        <v>4.61</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="DM11" t="n">
-        <v>41</v>
+        <v>41.17</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="DP11" t="n">
-        <v>17.09</v>
+        <v>17.13</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.130000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.91</v>
+        <v>7.74</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>38</v>
+        <v>38.13</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.59</v>
+        <v>13.35</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.140000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.5</v>
+        <v>19.65</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="12">
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5498,49 +5498,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.91</v>
+        <v>2.67</v>
       </c>
       <c r="AI12" t="n">
-        <v>83.64</v>
+        <v>81.92</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.18</v>
+        <v>2.58</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.18</v>
+        <v>3.92</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>35.73</v>
+        <v>34.67</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.82</v>
+        <v>15.83</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.27</v>
+        <v>11.08</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.449999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5552,82 +5552,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>41.91</v>
+        <v>41.08</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.27</v>
+        <v>8</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.18</v>
+        <v>5.83</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="BD12" t="n">
-        <v>20.09</v>
+        <v>19.75</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="BF12" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.18</v>
+        <v>9.17</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.27</v>
+        <v>5.35</v>
       </c>
       <c r="BR12" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS12" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BU12" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV12" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY12" t="n">
         <v>3.17</v>
@@ -5636,55 +5636,55 @@
         <v>3.6</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.72</v>
+        <v>3.82</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.78</v>
+        <v>3.87</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.97</v>
+        <v>4.56</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.62</v>
+        <v>4.96</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK12" t="n">
         <v>1.53</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CR12" t="n">
         <v>1.41</v>
@@ -5699,10 +5699,10 @@
         <v>1.46</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX12" t="n">
         <v>1.55</v>
@@ -5711,7 +5711,7 @@
         <v>1.92</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DA12" t="n">
         <v>1.89</v>
@@ -5720,52 +5720,52 @@
         <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="DG12" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="DH12" t="n">
-        <v>86.41</v>
+        <v>85.39</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.95</v>
+        <v>4.79</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DM12" t="n">
-        <v>39.5</v>
+        <v>38.78</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.68</v>
+        <v>0.78</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.64</v>
+        <v>15.65</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.09</v>
+        <v>12.91</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.5</v>
+        <v>7.61</v>
       </c>
       <c r="DS12" t="n">
         <v>0.04</v>
@@ -5777,28 +5777,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.73</v>
+        <v>45.13</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.46</v>
+        <v>10.22</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.77</v>
+        <v>7.52</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.55</v>
+        <v>19.39</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.22</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="13">
@@ -5808,10 +5808,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
@@ -5820,49 +5820,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="H13" t="n">
-        <v>81.09999999999999</v>
+        <v>82.64</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="K13" t="n">
-        <v>5.7</v>
+        <v>5.64</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="M13" t="n">
-        <v>47.2</v>
+        <v>46.18</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="O13" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="P13" t="n">
-        <v>11.3</v>
+        <v>11.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.6</v>
+        <v>13.18</v>
       </c>
       <c r="R13" t="n">
-        <v>8.300000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5874,28 +5874,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.2</v>
+        <v>12.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>9</v>
+        <v>9.09</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5979,70 +5979,70 @@
         <v>2.67</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.5</v>
+        <v>9.52</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.32</v>
+        <v>4.43</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.59</v>
+        <v>4.52</v>
       </c>
       <c r="BR13" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS13" t="n">
-        <v>81.81999999999999</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU13" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV13" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX13" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.57</v>
+        <v>3.43</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="CC13" t="n">
         <v>5.34</v>
@@ -6054,16 +6054,16 @@
         <v>1.32</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.7</v>
@@ -6078,34 +6078,34 @@
         <v>2.5</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO13" t="n">
         <v>1.22</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="CR13" t="n">
         <v>1.39</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV13" t="n">
         <v>2.22</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CX13" t="n">
         <v>1.53</v>
@@ -6123,52 +6123,52 @@
         <v>1.24</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DH13" t="n">
-        <v>78.81999999999999</v>
+        <v>79.66</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DM13" t="n">
-        <v>40.37</v>
+        <v>40.17</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.46</v>
+        <v>12.43</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.41</v>
+        <v>13.22</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.050000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6180,28 +6180,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>46.73</v>
+        <v>47</v>
       </c>
       <c r="DW13" t="n">
         <v>0.09</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.41</v>
+        <v>11.56</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.68</v>
+        <v>7.78</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.73</v>
+        <v>3.78</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.09</v>
+        <v>19</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="14">
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6304,49 +6304,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AH14" t="n">
         <v>2</v>
       </c>
       <c r="AI14" t="n">
-        <v>85.8</v>
+        <v>85.55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN14" t="n">
-        <v>37.4</v>
+        <v>38.55</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14.2</v>
+        <v>14.27</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.6</v>
+        <v>14.55</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6358,82 +6358,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>48.6</v>
+        <v>49</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA14" t="n">
-        <v>9</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.2</v>
+        <v>6.73</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.8</v>
+        <v>17.27</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.449999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.55</v>
+        <v>4.57</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="BR14" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BT14" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BU14" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BV14" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BY14" t="n">
         <v>2.82</v>
@@ -6442,16 +6442,16 @@
         <v>2.86</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CC14" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="CD14" t="n">
         <v>4.75</v>
-      </c>
-      <c r="CD14" t="n">
-        <v>4.88</v>
       </c>
       <c r="CE14" t="n">
         <v>1.4</v>
@@ -6460,7 +6460,7 @@
         <v>2.82</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CH14" t="n">
         <v>1.4</v>
@@ -6475,7 +6475,7 @@
         <v>1.64</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CM14" t="n">
         <v>2.16</v>
@@ -6490,88 +6490,88 @@
         <v>2</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CR14" t="n">
         <v>1.43</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CU14" t="n">
         <v>1.41</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB14" t="n">
         <v>1.34</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DH14" t="n">
-        <v>91.5</v>
+        <v>91.13</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.36</v>
+        <v>4.43</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM14" t="n">
-        <v>38.59</v>
+        <v>39.09</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="DP14" t="n">
         <v>14.95</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.73</v>
+        <v>14.7</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.5</v>
+        <v>8.44</v>
       </c>
       <c r="DS14" t="n">
         <v>0.09</v>
@@ -6583,28 +6583,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.41</v>
+        <v>49.56</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.68</v>
+        <v>10.78</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.18</v>
+        <v>7.39</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.5</v>
+        <v>3.39</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.91</v>
+        <v>20.52</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="15">
@@ -6614,10 +6614,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
@@ -6626,82 +6626,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="G15" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="H15" t="n">
-        <v>108.45</v>
+        <v>106.75</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="K15" t="n">
-        <v>5.91</v>
+        <v>5.67</v>
       </c>
       <c r="L15" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="M15" t="n">
-        <v>51.45</v>
+        <v>49.67</v>
       </c>
       <c r="N15" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="O15" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="P15" t="n">
-        <v>11.55</v>
+        <v>11.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.27</v>
+        <v>11.92</v>
       </c>
       <c r="R15" t="n">
-        <v>7.82</v>
+        <v>8.08</v>
       </c>
       <c r="S15" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="T15" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="U15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>57.36</v>
+        <v>55.83</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>15.09</v>
+        <v>14.58</v>
       </c>
       <c r="AA15" t="n">
-        <v>11</v>
+        <v>10.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.09</v>
+        <v>3.92</v>
       </c>
       <c r="AC15" t="n">
-        <v>22.36</v>
+        <v>22.58</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AF15" t="n">
         <v>0.09</v>
@@ -6785,70 +6785,70 @@
         <v>2.55</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.859999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.73</v>
+        <v>4.61</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
       <c r="BR15" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS15" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BT15" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU15" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV15" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.26</v>
+        <v>2.49</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="CC15" t="n">
         <v>4.99</v>
@@ -6860,10 +6860,10 @@
         <v>1.35</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CH15" t="n">
         <v>1.47</v>
@@ -6875,10 +6875,10 @@
         <v>1.72</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CM15" t="n">
         <v>2.39</v>
@@ -6890,16 +6890,16 @@
         <v>1.25</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CT15" t="n">
         <v>3.1</v>
@@ -6929,52 +6929,52 @@
         <v>1.27</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="DE15" t="n">
         <v>0.04</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="DH15" t="n">
-        <v>100.04</v>
+        <v>99.52</v>
       </c>
       <c r="DI15" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.23</v>
+        <v>5.13</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="DM15" t="n">
-        <v>46.27</v>
+        <v>45.57</v>
       </c>
       <c r="DN15" t="n">
         <v>0.78</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.64</v>
+        <v>11.74</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.31</v>
+        <v>13.09</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.140000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="DS15" t="n">
         <v>0.13</v>
@@ -6986,28 +6986,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>54</v>
+        <v>53.35</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.72</v>
+        <v>13.52</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.59</v>
+        <v>9.48</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.14</v>
+        <v>4.04</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="16">
@@ -7017,94 +7017,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F16" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="G16" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="H16" t="n">
-        <v>78.36</v>
+        <v>79.42</v>
       </c>
       <c r="I16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J16" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="L16" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="M16" t="n">
-        <v>38.27</v>
+        <v>37.75</v>
       </c>
       <c r="N16" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="O16" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="P16" t="n">
-        <v>14.27</v>
+        <v>14.42</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.18</v>
+        <v>12.75</v>
       </c>
       <c r="R16" t="n">
-        <v>9.640000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="S16" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="T16" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>50.27</v>
+        <v>50</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.36</v>
+        <v>13.17</v>
       </c>
       <c r="AA16" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.27</v>
+        <v>17.08</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AF16" t="n">
         <v>0.18</v>
@@ -7188,70 +7188,70 @@
         <v>2.55</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.82</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM16" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BO16" t="n">
         <v>1.09</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.18</v>
+        <v>4.22</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.59</v>
+        <v>4.52</v>
       </c>
       <c r="BR16" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS16" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT16" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU16" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV16" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW16" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX16" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="CC16" t="n">
         <v>4.12</v>
@@ -7260,13 +7260,13 @@
         <v>4.34</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="CH16" t="n">
         <v>1.41</v>
@@ -7275,13 +7275,13 @@
         <v>2.02</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CM16" t="n">
         <v>2.16</v>
@@ -7293,124 +7293,124 @@
         <v>1.19</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CU16" t="n">
         <v>1.49</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CW16" t="n">
         <v>1.72</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DB16" t="n">
         <v>1.27</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="DE16" t="n">
         <v>0.13</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="DH16" t="n">
-        <v>79.73</v>
+        <v>80.22</v>
       </c>
       <c r="DI16" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DM16" t="n">
-        <v>36.22</v>
+        <v>36.04</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.68</v>
+        <v>13.78</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.59</v>
+        <v>12.87</v>
       </c>
       <c r="DR16" t="n">
-        <v>9.039999999999999</v>
+        <v>9</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>49.27</v>
+        <v>49.17</v>
       </c>
       <c r="DW16" t="n">
         <v>0.09</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.54</v>
+        <v>12.48</v>
       </c>
       <c r="DY16" t="n">
-        <v>9</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.55</v>
+        <v>3.61</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.64</v>
+        <v>16.56</v>
       </c>
       <c r="EB16" t="n">
         <v>1.3</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="17">
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
         <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
         <v>0.09</v>
@@ -7510,139 +7510,139 @@
         <v>1.64</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AI17" t="n">
-        <v>82.36</v>
+        <v>84.92</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.45</v>
+        <v>5.08</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN17" t="n">
-        <v>36.91</v>
+        <v>37.33</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>13.08</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.36</v>
+        <v>11.58</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.27</v>
+        <v>8.92</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>48</v>
+        <v>49.42</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.91</v>
+        <v>11.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.27</v>
+        <v>8.17</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.64</v>
+        <v>3.33</v>
       </c>
       <c r="BD17" t="n">
-        <v>17.55</v>
+        <v>17.75</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.82</v>
+        <v>9.65</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.18</v>
+        <v>5</v>
       </c>
       <c r="BR17" t="n">
-        <v>86.36</v>
+        <v>82.61</v>
       </c>
       <c r="BS17" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BU17" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV17" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY17" t="n">
         <v>2.17</v>
@@ -7651,19 +7651,19 @@
         <v>2.19</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.46</v>
+        <v>3.38</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF17" t="n">
         <v>2.82</v>
@@ -7684,10 +7684,10 @@
         <v>1.58</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CN17" t="n">
         <v>1.78</v>
@@ -7702,13 +7702,13 @@
         <v>3.36</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CU17" t="n">
         <v>1.43</v>
@@ -7717,7 +7717,7 @@
         <v>2.06</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX17" t="n">
         <v>1.61</v>
@@ -7735,85 +7735,85 @@
         <v>1.33</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="DE17" t="n">
         <v>0.13</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.28</v>
+        <v>3.13</v>
       </c>
       <c r="DH17" t="n">
-        <v>93.45999999999999</v>
+        <v>94.31</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="DK17" t="n">
-        <v>6.05</v>
+        <v>5.83</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="DM17" t="n">
-        <v>41.09</v>
+        <v>41.13</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="DP17" t="n">
-        <v>14.54</v>
+        <v>14.04</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.77</v>
+        <v>11.87</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.64</v>
+        <v>7.52</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>52.18</v>
+        <v>52.74</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.96</v>
+        <v>12.7</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.41</v>
+        <v>9.31</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.55</v>
+        <v>3.39</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.05</v>
+        <v>19.09</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
         <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
         <v>0.09</v>
@@ -7913,139 +7913,139 @@
         <v>1.73</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AI18" t="n">
-        <v>85</v>
+        <v>84.67</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>31</v>
+        <v>32.83</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12</v>
+        <v>12.42</v>
       </c>
       <c r="AR18" t="n">
-        <v>15.18</v>
+        <v>14.83</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.640000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AU18" t="n">
         <v>2</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>53.36</v>
+        <v>52.75</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA18" t="n">
-        <v>13.27</v>
+        <v>13.25</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.73</v>
+        <v>7.83</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.55</v>
+        <v>5.42</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.18</v>
+        <v>17.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.449999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.95</v>
+        <v>5.22</v>
       </c>
       <c r="BR18" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS18" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT18" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU18" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV18" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW18" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BX18" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BY18" t="n">
         <v>1.88</v>
@@ -8057,19 +8057,19 @@
         <v>3.79</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.5</v>
+        <v>3.37</v>
       </c>
       <c r="CE18" t="n">
         <v>1.34</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CG18" t="n">
         <v>3.11</v>
@@ -8078,16 +8078,16 @@
         <v>1.47</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CK18" t="n">
         <v>1.54</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CM18" t="n">
         <v>2.35</v>
@@ -8096,13 +8096,13 @@
         <v>1.83</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP18" t="n">
         <v>1.79</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CR18" t="n">
         <v>1.37</v>
@@ -8117,10 +8117,10 @@
         <v>1.49</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CX18" t="n">
         <v>1.57</v>
@@ -8132,91 +8132,91 @@
         <v>2.35</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB18" t="n">
         <v>1.25</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DD18" t="n">
         <v>2.98</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DH18" t="n">
-        <v>94.91</v>
+        <v>94.31</v>
       </c>
       <c r="DI18" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM18" t="n">
-        <v>40.86</v>
+        <v>41.39</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="DO18" t="n">
         <v>2</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.41</v>
+        <v>12.61</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14</v>
+        <v>13.87</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.1</v>
+        <v>8.18</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>54.9</v>
+        <v>54.52</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX18" t="n">
-        <v>15.91</v>
+        <v>15.78</v>
       </c>
       <c r="DY18" t="n">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.91</v>
+        <v>5.83</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.31</v>
+        <v>19.39</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="19">
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" t="n">
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8319,136 +8319,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AI19" t="n">
-        <v>102</v>
+        <v>100.42</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK19" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.73</v>
+        <v>5.42</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN19" t="n">
-        <v>46.64</v>
+        <v>45.67</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.91</v>
+        <v>2.67</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12.18</v>
+        <v>12.67</v>
       </c>
       <c r="AR19" t="n">
-        <v>14.09</v>
+        <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.18</v>
+        <v>6.83</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>58</v>
+        <v>57.08</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA19" t="n">
-        <v>14.36</v>
+        <v>14.25</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.09</v>
+        <v>9.17</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.27</v>
+        <v>5.08</v>
       </c>
       <c r="BD19" t="n">
-        <v>19.09</v>
+        <v>18.92</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.5</v>
+        <v>10.39</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.09</v>
+        <v>4.04</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="BR19" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS19" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT19" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU19" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV19" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW19" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX19" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BY19" t="n">
         <v>2.44</v>
@@ -8457,16 +8457,16 @@
         <v>2.46</v>
       </c>
       <c r="CA19" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="CB19" t="n">
         <v>3.67</v>
       </c>
-      <c r="CB19" t="n">
-        <v>3.68</v>
-      </c>
       <c r="CC19" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="CE19" t="n">
         <v>1.34</v>
@@ -8475,13 +8475,13 @@
         <v>2.59</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CH19" t="n">
         <v>1.46</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.69</v>
@@ -8490,13 +8490,13 @@
         <v>1.55</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CO19" t="n">
         <v>1.22</v>
@@ -8511,10 +8511,10 @@
         <v>1.38</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CU19" t="n">
         <v>1.47</v>
@@ -8523,7 +8523,7 @@
         <v>2.23</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CX19" t="n">
         <v>1.55</v>
@@ -8550,76 +8550,76 @@
         <v>0</v>
       </c>
       <c r="DF19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>93.61</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>43.65</v>
+      </c>
+      <c r="DN19" t="n">
         <v>1.09</v>
       </c>
-      <c r="DG19" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="DH19" t="n">
-        <v>94.09</v>
-      </c>
-      <c r="DI19" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DJ19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="DK19" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="DL19" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="DM19" t="n">
-        <v>44.04</v>
-      </c>
-      <c r="DN19" t="n">
-        <v>1.05</v>
-      </c>
       <c r="DO19" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.68</v>
+        <v>13.87</v>
       </c>
       <c r="DQ19" t="n">
         <v>13.09</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.36</v>
+        <v>7.17</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.68</v>
+        <v>55.3</v>
       </c>
       <c r="DW19" t="n">
         <v>0.13</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.4</v>
+        <v>13.39</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.539999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.86</v>
+        <v>4.78</v>
       </c>
       <c r="EA19" t="n">
-        <v>18.37</v>
+        <v>18.31</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="EC19" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>0.17</v>
@@ -1469,139 +1469,139 @@
         <v>2.17</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH2" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AI2" t="n">
-        <v>77.73</v>
+        <v>76.67</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AL2" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>37.55</v>
+        <v>37.25</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AP2" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.27</v>
+        <v>11.58</v>
       </c>
       <c r="AR2" t="n">
-        <v>15.82</v>
+        <v>16</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.36</v>
+        <v>7.17</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>46.27</v>
+        <v>45.75</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.36</v>
+        <v>12.17</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.82</v>
+        <v>8.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="BD2" t="n">
-        <v>19.27</v>
+        <v>18.75</v>
       </c>
       <c r="BE2" t="n">
         <v>1.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.35</v>
+        <v>8.17</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.39</v>
+        <v>4.25</v>
       </c>
       <c r="BR2" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BS2" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT2" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BU2" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BV2" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY2" t="n">
         <v>2.93</v>
@@ -1610,31 +1610,31 @@
         <v>3.05</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.73</v>
+        <v>3.79</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.78</v>
+        <v>3.88</v>
       </c>
       <c r="CC2" t="n">
-        <v>4.15</v>
+        <v>4.47</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.94</v>
+        <v>5.35</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.97</v>
+        <v>3.01</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.76</v>
@@ -1646,31 +1646,31 @@
         <v>2.16</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CN2" t="n">
         <v>1.66</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="CR2" t="n">
         <v>1.4</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="CT2" t="n">
         <v>3.09</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CV2" t="n">
         <v>2.08</v>
@@ -1679,100 +1679,100 @@
         <v>1.81</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="DH2" t="n">
-        <v>84.73999999999999</v>
+        <v>83.92</v>
       </c>
       <c r="DI2" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.74</v>
+        <v>4.54</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM2" t="n">
-        <v>42.44</v>
+        <v>42.08</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.22</v>
+        <v>11.88</v>
       </c>
       <c r="DQ2" t="n">
-        <v>15.13</v>
+        <v>15.25</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.04</v>
+        <v>6.96</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47.69</v>
+        <v>47.38</v>
       </c>
       <c r="DW2" t="n">
         <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.78</v>
+        <v>12.67</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.869999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.44</v>
+        <v>18.21</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="3">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0.33</v>
@@ -2275,52 +2275,52 @@
         <v>2.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>83.36</v>
+        <v>84.75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN4" t="n">
-        <v>38.45</v>
+        <v>36.92</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.45</v>
+        <v>13.33</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.91</v>
+        <v>11.25</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.27</v>
+        <v>9.25</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>51.55</v>
+        <v>51.33</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA4" t="n">
-        <v>14.55</v>
+        <v>14.25</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.640000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.91</v>
+        <v>5.58</v>
       </c>
       <c r="BD4" t="n">
-        <v>20.18</v>
+        <v>20.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.04</v>
+        <v>9.83</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.83</v>
+        <v>4.67</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.17</v>
+        <v>5.12</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>91.3</v>
+        <v>87.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BV4" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX4" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BY4" t="n">
         <v>1.66</v>
@@ -2416,13 +2416,13 @@
         <v>1.7</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.23</v>
+        <v>4.19</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CD4" t="n">
         <v>2.25</v>
@@ -2431,154 +2431,154 @@
         <v>1.28</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CK4" t="n">
         <v>1.5</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CW4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DC4" t="n">
         <v>1.66</v>
       </c>
-      <c r="CX4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CY4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="CZ4" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="DA4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="DB4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="DC4" t="n">
-        <v>1.63</v>
-      </c>
       <c r="DD4" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="DH4" t="n">
-        <v>91.09</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="DI4" t="n">
         <v>0.17</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.39</v>
+        <v>5.33</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.87</v>
+        <v>43.84</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="DP4" t="n">
-        <v>14</v>
+        <v>13.92</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.74</v>
+        <v>12.84</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.96</v>
+        <v>8</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>54.22</v>
+        <v>54</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.35</v>
+        <v>16.12</v>
       </c>
       <c r="DY4" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6.35</v>
+        <v>6.16</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.96</v>
+        <v>18.21</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -2678,139 +2678,139 @@
         <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>71.55</v>
+        <v>72.42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>31.27</v>
+        <v>30.83</v>
       </c>
       <c r="AO5" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13</v>
+        <v>12.83</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.55</v>
+        <v>15.58</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.359999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>47.09</v>
+        <v>47.42</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.91</v>
+        <v>10.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.64</v>
+        <v>7.42</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="BD5" t="n">
-        <v>16.82</v>
+        <v>18.17</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.74</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.13</v>
+        <v>5.08</v>
       </c>
       <c r="BR5" t="n">
-        <v>91.3</v>
+        <v>87.5</v>
       </c>
       <c r="BS5" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BU5" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV5" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX5" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BY5" t="n">
         <v>3.97</v>
@@ -2822,37 +2822,37 @@
         <v>4.09</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.23</v>
+        <v>4.24</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.67</v>
+        <v>5.71</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.03</v>
+        <v>6.19</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CG5" t="n">
         <v>3.09</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK5" t="n">
         <v>1.54</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CM5" t="n">
         <v>2.33</v>
@@ -2864,28 +2864,28 @@
         <v>1.24</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CR5" t="n">
         <v>1.39</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CT5" t="n">
         <v>3.09</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CX5" t="n">
         <v>1.57</v>
@@ -2894,7 +2894,7 @@
         <v>1.94</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DA5" t="n">
         <v>1.88</v>
@@ -2906,49 +2906,49 @@
         <v>1.81</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="DE5" t="n">
         <v>0.08</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DH5" t="n">
-        <v>74.61</v>
+        <v>74.92</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.74</v>
+        <v>3.67</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM5" t="n">
-        <v>35.13</v>
+        <v>34.75</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.7</v>
+        <v>11.66</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.87</v>
+        <v>14.92</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.95</v>
+        <v>7.96</v>
       </c>
       <c r="DS5" t="n">
         <v>0.08</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.26</v>
+        <v>49.34</v>
       </c>
       <c r="DW5" t="n">
         <v>0.04</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.13</v>
+        <v>10.92</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.31</v>
+        <v>7.21</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="EA5" t="n">
-        <v>17.83</v>
+        <v>18.46</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>0.08</v>
@@ -3084,49 +3084,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AI6" t="n">
-        <v>86.73</v>
+        <v>86</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>38.18</v>
+        <v>38.83</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13</v>
+        <v>12.83</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.64</v>
+        <v>15</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.359999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>47.36</v>
+        <v>46.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.91</v>
+        <v>10.92</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.64</v>
+        <v>7.58</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="BD6" t="n">
-        <v>21.55</v>
+        <v>20.92</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.09</v>
+        <v>9.08</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS6" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT6" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BV6" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX6" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
         <v>3.96</v>
@@ -3222,43 +3222,43 @@
         <v>3.95</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.16</v>
+        <v>4.17</v>
       </c>
       <c r="CC6" t="n">
-        <v>6.3</v>
+        <v>6.32</v>
       </c>
       <c r="CD6" t="n">
-        <v>6.76</v>
+        <v>6.78</v>
       </c>
       <c r="CE6" t="n">
         <v>1.35</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CK6" t="n">
         <v>1.57</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CN6" t="n">
         <v>1.78</v>
@@ -3267,22 +3267,22 @@
         <v>1.25</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CT6" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CV6" t="n">
         <v>2.04</v>
@@ -3306,52 +3306,52 @@
         <v>1.29</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="DE6" t="n">
         <v>0.04</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DG6" t="n">
         <v>1.96</v>
       </c>
       <c r="DH6" t="n">
-        <v>87.65000000000001</v>
+        <v>87.25</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM6" t="n">
-        <v>35.83</v>
+        <v>36.25</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.57</v>
+        <v>12.5</v>
       </c>
       <c r="DQ6" t="n">
-        <v>15.05</v>
+        <v>14.75</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.949999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="DS6" t="n">
         <v>0.04</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.52</v>
+        <v>46.12</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.87</v>
+        <v>10.88</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.79</v>
+        <v>7.75</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.7</v>
+        <v>20.42</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="7">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="F8" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="G8" t="n">
-        <v>3.42</v>
+        <v>3.23</v>
       </c>
       <c r="H8" t="n">
-        <v>100.33</v>
+        <v>100.38</v>
       </c>
       <c r="I8" t="n">
         <v>0.08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K8" t="n">
-        <v>6.83</v>
+        <v>6.62</v>
       </c>
       <c r="L8" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="M8" t="n">
-        <v>57.33</v>
+        <v>56.54</v>
       </c>
       <c r="N8" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="O8" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="P8" t="n">
-        <v>11.67</v>
+        <v>12.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.67</v>
+        <v>10.15</v>
       </c>
       <c r="R8" t="n">
-        <v>5.83</v>
+        <v>6.08</v>
       </c>
       <c r="S8" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="T8" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="U8" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V8" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>65</v>
+        <v>64.62</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.83</v>
+        <v>20.31</v>
       </c>
       <c r="AA8" t="n">
-        <v>13.75</v>
+        <v>13.31</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.08</v>
+        <v>7</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.75</v>
+        <v>20.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AF8" t="n">
         <v>0.18</v>
@@ -3968,67 +3968,67 @@
         <v>2.36</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.039999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BM8" t="n">
         <v>0.83</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.22</v>
+        <v>4.17</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.83</v>
+        <v>4.67</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS8" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BV8" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX8" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BZ8" t="n">
         <v>1.29</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.7</v>
+        <v>5.68</v>
       </c>
       <c r="CB8" t="n">
         <v>6.07</v>
@@ -4052,7 +4052,7 @@
         <v>1.71</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.71</v>
@@ -4061,10 +4061,10 @@
         <v>1.49</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CN8" t="n">
         <v>1.91</v>
@@ -4102,7 +4102,7 @@
         <v>2.44</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB8" t="n">
         <v>1.15</v>
@@ -4114,79 +4114,79 @@
         <v>2.19</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="DH8" t="n">
-        <v>97</v>
+        <v>97.16</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.43</v>
+        <v>5.38</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM8" t="n">
-        <v>50.83</v>
+        <v>50.67</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.04</v>
+        <v>12.25</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.83</v>
+        <v>10.54</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.7</v>
+        <v>6.79</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>62.52</v>
+        <v>62.42</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>17.17</v>
+        <v>17.04</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.22</v>
+        <v>11.08</v>
       </c>
       <c r="DZ8" t="n">
         <v>5.96</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.04</v>
+        <v>18.79</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="9">
@@ -5002,61 +5002,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F11" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="H11" t="n">
-        <v>96.91</v>
+        <v>100.08</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J11" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="K11" t="n">
-        <v>5.09</v>
+        <v>5.08</v>
       </c>
       <c r="L11" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="M11" t="n">
-        <v>43.36</v>
+        <v>44.92</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="O11" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="P11" t="n">
-        <v>17.73</v>
+        <v>17.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.18</v>
+        <v>9.17</v>
       </c>
       <c r="R11" t="n">
-        <v>7.27</v>
+        <v>6.92</v>
       </c>
       <c r="S11" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="T11" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5068,28 +5068,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>39.09</v>
+        <v>39.92</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.09</v>
+        <v>13.92</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.73</v>
+        <v>9.67</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.36</v>
+        <v>4.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>20.36</v>
+        <v>21.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AF11" t="n">
         <v>0.08</v>
@@ -5173,49 +5173,49 @@
         <v>2.25</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.83</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BK11" t="n">
         <v>0.17</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.74</v>
+        <v>4.67</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.09</v>
+        <v>5.04</v>
       </c>
       <c r="BR11" t="n">
-        <v>78.26000000000001</v>
+        <v>75</v>
       </c>
       <c r="BS11" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BT11" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BU11" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5224,19 +5224,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="CC11" t="n">
         <v>3.27</v>
@@ -5248,10 +5248,10 @@
         <v>1.4</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CH11" t="n">
         <v>1.39</v>
@@ -5266,7 +5266,7 @@
         <v>1.56</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CM11" t="n">
         <v>2.28</v>
@@ -5275,7 +5275,7 @@
         <v>1.81</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP11" t="n">
         <v>1.98</v>
@@ -5290,16 +5290,16 @@
         <v>3.03</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CU11" t="n">
         <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CX11" t="n">
         <v>1.55</v>
@@ -5317,52 +5317,52 @@
         <v>1.34</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="DE11" t="n">
         <v>0.08</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DH11" t="n">
-        <v>94</v>
+        <v>95.7</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.61</v>
+        <v>4.62</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="DM11" t="n">
-        <v>41.17</v>
+        <v>42.04</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DP11" t="n">
-        <v>17.13</v>
+        <v>16.92</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.35</v>
+        <v>9.33</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.74</v>
+        <v>7.54</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>38.13</v>
+        <v>38.58</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.35</v>
+        <v>13.3</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.050000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.65</v>
+        <v>20.12</v>
       </c>
       <c r="EB11" t="n">
         <v>1.44</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="12">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
         <v>12</v>
@@ -5417,82 +5417,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="G12" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="H12" t="n">
-        <v>89.18000000000001</v>
+        <v>90.17</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J12" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="K12" t="n">
-        <v>5.73</v>
+        <v>5.42</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="M12" t="n">
-        <v>43.27</v>
+        <v>43.58</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="O12" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>15.45</v>
+        <v>15.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.91</v>
+        <v>15</v>
       </c>
       <c r="R12" t="n">
-        <v>6.55</v>
+        <v>6.67</v>
       </c>
       <c r="S12" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="U12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>49.55</v>
+        <v>49.75</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.64</v>
+        <v>12.67</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.359999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>19</v>
+        <v>18.92</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5576,70 +5576,70 @@
         <v>2.33</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.17</v>
+        <v>9.08</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="BO12" t="n">
         <v>1</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.35</v>
+        <v>5.29</v>
       </c>
       <c r="BR12" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BS12" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT12" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BU12" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV12" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="CC12" t="n">
         <v>4.56</v>
@@ -5648,13 +5648,13 @@
         <v>4.96</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF12" t="n">
         <v>2.63</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CH12" t="n">
         <v>1.45</v>
@@ -5663,13 +5663,13 @@
         <v>2.03</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK12" t="n">
         <v>1.53</v>
       </c>
       <c r="CL12" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CM12" t="n">
         <v>2.37</v>
@@ -5693,13 +5693,13 @@
         <v>2.89</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CU12" t="n">
         <v>1.46</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CW12" t="n">
         <v>1.78</v>
@@ -5729,43 +5729,43 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="DH12" t="n">
-        <v>85.39</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.79</v>
+        <v>4.67</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.78</v>
+        <v>39.12</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.65</v>
+        <v>15.62</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.91</v>
+        <v>13.04</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.61</v>
+        <v>7.62</v>
       </c>
       <c r="DS12" t="n">
         <v>0.04</v>
@@ -5777,28 +5777,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.13</v>
+        <v>45.42</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.22</v>
+        <v>10.34</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.52</v>
+        <v>7.58</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.39</v>
+        <v>19.34</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="13">
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
         <v>11</v>
@@ -6223,82 +6223,82 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="G14" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="H14" t="n">
-        <v>96.25</v>
+        <v>97.08</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="J14" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="K14" t="n">
-        <v>4.58</v>
+        <v>4.31</v>
       </c>
       <c r="L14" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="M14" t="n">
-        <v>39.58</v>
+        <v>39.77</v>
       </c>
       <c r="N14" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="P14" t="n">
-        <v>15.58</v>
+        <v>15.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>14.83</v>
+        <v>14.69</v>
       </c>
       <c r="R14" t="n">
-        <v>7.92</v>
+        <v>8</v>
       </c>
       <c r="S14" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V14" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>50.08</v>
+        <v>50.15</v>
       </c>
       <c r="Y14" t="n">
         <v>0.08</v>
       </c>
       <c r="Z14" t="n">
-        <v>12.08</v>
+        <v>11.92</v>
       </c>
       <c r="AA14" t="n">
-        <v>8</v>
+        <v>8.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.08</v>
+        <v>3.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>23.5</v>
+        <v>23.31</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6382,70 +6382,70 @@
         <v>2.64</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.43</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.57</v>
+        <v>4.42</v>
       </c>
       <c r="BQ14" t="n">
         <v>3.83</v>
       </c>
       <c r="BR14" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS14" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BT14" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BU14" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BV14" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="CC14" t="n">
         <v>4.57</v>
@@ -6460,7 +6460,7 @@
         <v>2.82</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CH14" t="n">
         <v>1.4</v>
@@ -6469,19 +6469,19 @@
         <v>1.91</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK14" t="n">
         <v>1.64</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CM14" t="n">
         <v>2.16</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CO14" t="n">
         <v>1.3</v>
@@ -6496,31 +6496,31 @@
         <v>1.43</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CU14" t="n">
         <v>1.41</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CY14" t="n">
         <v>2.07</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB14" t="n">
         <v>1.34</v>
@@ -6529,82 +6529,82 @@
         <v>2.09</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="DH14" t="n">
-        <v>91.13</v>
+        <v>91.8</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.43</v>
+        <v>4.29</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DM14" t="n">
-        <v>39.09</v>
+        <v>39.21</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.95</v>
+        <v>15</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.7</v>
+        <v>14.63</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.44</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.56</v>
+        <v>49.62</v>
       </c>
       <c r="DW14" t="n">
         <v>0.08</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.78</v>
+        <v>10.75</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.39</v>
+        <v>7.5</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.52</v>
+        <v>20.54</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="15">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
         <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6704,139 +6704,139 @@
         <v>2.25</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AI15" t="n">
-        <v>91.64</v>
+        <v>90.25</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN15" t="n">
-        <v>41.09</v>
+        <v>40.33</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AP15" t="n">
         <v>2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.73</v>
+        <v>12.17</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.36</v>
+        <v>14.33</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.449999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>50.64</v>
+        <v>50.25</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>12.36</v>
+        <v>12.25</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.18</v>
+        <v>8.25</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="BD15" t="n">
-        <v>18.45</v>
+        <v>19</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.74</v>
+        <v>9.83</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.61</v>
+        <v>4.58</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.13</v>
+        <v>5.25</v>
       </c>
       <c r="BR15" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS15" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY15" t="n">
         <v>2.44</v>
@@ -6848,22 +6848,22 @@
         <v>3.83</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.99</v>
+        <v>4.96</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="CE15" t="n">
         <v>1.35</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CH15" t="n">
         <v>1.47</v>
@@ -6881,13 +6881,13 @@
         <v>2.04</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CN15" t="n">
         <v>1.84</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CP15" t="n">
         <v>1.82</v>
@@ -6902,7 +6902,7 @@
         <v>2.8</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CU15" t="n">
         <v>1.48</v>
@@ -6917,19 +6917,19 @@
         <v>1.56</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.36</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB15" t="n">
         <v>1.27</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DD15" t="n">
         <v>3.12</v>
@@ -6938,76 +6938,76 @@
         <v>0.04</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="DH15" t="n">
-        <v>99.52</v>
+        <v>98.5</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.13</v>
+        <v>5.21</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DM15" t="n">
-        <v>45.57</v>
+        <v>45</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.74</v>
+        <v>11.96</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.09</v>
+        <v>13.12</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.26</v>
+        <v>8.33</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>53.35</v>
+        <v>53.04</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.52</v>
+        <v>13.42</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.48</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.6</v>
+        <v>20.79</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="16">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
         <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
         <v>0.08</v>
@@ -7107,139 +7107,139 @@
         <v>2.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AI16" t="n">
-        <v>81.09</v>
+        <v>81.5</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.18</v>
+        <v>4.25</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>34.18</v>
+        <v>34.83</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.09</v>
+        <v>13.25</v>
       </c>
       <c r="AR16" t="n">
-        <v>13</v>
+        <v>13.42</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.449999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>48.27</v>
+        <v>48.25</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.73</v>
+        <v>11.92</v>
       </c>
       <c r="BB16" t="n">
         <v>8</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.73</v>
+        <v>3.92</v>
       </c>
       <c r="BD16" t="n">
-        <v>16</v>
+        <v>15.75</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.779999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.22</v>
+        <v>4.17</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="BR16" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS16" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT16" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BU16" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX16" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY16" t="n">
         <v>2.43</v>
@@ -7248,16 +7248,16 @@
         <v>2.71</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.12</v>
+        <v>3.99</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.34</v>
+        <v>4.19</v>
       </c>
       <c r="CE16" t="n">
         <v>1.29</v>
@@ -7266,7 +7266,7 @@
         <v>2.48</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CH16" t="n">
         <v>1.41</v>
@@ -7281,22 +7281,22 @@
         <v>1.51</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CN16" t="n">
         <v>1.71</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CR16" t="n">
         <v>1.39</v>
@@ -7332,52 +7332,52 @@
         <v>1.27</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DD16" t="n">
         <v>3.13</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="DH16" t="n">
-        <v>80.22</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="DK16" t="n">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM16" t="n">
-        <v>36.04</v>
+        <v>36.29</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.78</v>
+        <v>13.84</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.87</v>
+        <v>13.08</v>
       </c>
       <c r="DR16" t="n">
-        <v>9</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DS16" t="n">
         <v>0.08</v>
@@ -7389,28 +7389,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>49.17</v>
+        <v>49.12</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.48</v>
+        <v>12.54</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.869999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.61</v>
+        <v>3.71</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.56</v>
+        <v>16.42</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="17">
@@ -7823,94 +7823,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F18" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="G18" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="H18" t="n">
-        <v>104.82</v>
+        <v>104.58</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="K18" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="M18" t="n">
-        <v>50.73</v>
+        <v>49.83</v>
       </c>
       <c r="N18" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="O18" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="P18" t="n">
-        <v>12.82</v>
+        <v>12.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.82</v>
+        <v>12.75</v>
       </c>
       <c r="R18" t="n">
-        <v>6.55</v>
+        <v>6.58</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>56.45</v>
+        <v>57</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>18.55</v>
+        <v>18.08</v>
       </c>
       <c r="AA18" t="n">
-        <v>12.27</v>
+        <v>11.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.27</v>
+        <v>6.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>21.45</v>
+        <v>21.08</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
         <v>0.08</v>
@@ -7994,70 +7994,70 @@
         <v>1.67</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.699999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="BJ18" t="n">
         <v>0.83</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.48</v>
+        <v>4.46</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
       <c r="BR18" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS18" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT18" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BU18" t="n">
-        <v>30.43</v>
+        <v>33.33</v>
       </c>
       <c r="BV18" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW18" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BX18" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.79</v>
+        <v>3.82</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.84</v>
+        <v>3.87</v>
       </c>
       <c r="CC18" t="n">
         <v>3.13</v>
@@ -8072,22 +8072,22 @@
         <v>2.57</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK18" t="n">
         <v>1.54</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CM18" t="n">
         <v>2.35</v>
@@ -8099,31 +8099,31 @@
         <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CR18" t="n">
         <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CU18" t="n">
         <v>1.49</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY18" t="n">
         <v>1.95</v>
@@ -8141,82 +8141,82 @@
         <v>1.81</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="DE18" t="n">
         <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DH18" t="n">
-        <v>94.31</v>
+        <v>94.62</v>
       </c>
       <c r="DI18" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.39</v>
+        <v>41.33</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="DO18" t="n">
         <v>2</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.61</v>
+        <v>12.42</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.87</v>
+        <v>13.79</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.18</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>54.52</v>
+        <v>54.88</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX18" t="n">
-        <v>15.78</v>
+        <v>15.66</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.949999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.83</v>
+        <v>5.84</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.39</v>
+        <v>19.29</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="19">
@@ -8226,10 +8226,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
         <v>12</v>
@@ -8238,82 +8238,82 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G19" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="H19" t="n">
-        <v>86.18000000000001</v>
+        <v>86.67</v>
       </c>
       <c r="I19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J19" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="K19" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="L19" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="M19" t="n">
-        <v>41.45</v>
+        <v>41</v>
       </c>
       <c r="N19" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="O19" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="P19" t="n">
-        <v>15.18</v>
+        <v>15.08</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.09</v>
+        <v>12.42</v>
       </c>
       <c r="R19" t="n">
-        <v>7.55</v>
+        <v>7.42</v>
       </c>
       <c r="S19" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>53.36</v>
+        <v>53.42</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.45</v>
+        <v>12.42</v>
       </c>
       <c r="AA19" t="n">
         <v>8</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.64</v>
+        <v>17.58</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8397,67 +8397,67 @@
         <v>2.08</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.39</v>
+        <v>10.46</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BP19" t="n">
         <v>4.04</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.3</v>
+        <v>6.38</v>
       </c>
       <c r="BR19" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS19" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT19" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BU19" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV19" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX19" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="CB19" t="n">
         <v>3.67</v>
@@ -8472,13 +8472,13 @@
         <v>1.34</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CI19" t="n">
         <v>2.1</v>
@@ -8505,13 +8505,13 @@
         <v>1.79</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CR19" t="n">
         <v>1.38</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CT19" t="n">
         <v>3.17</v>
@@ -8523,7 +8523,7 @@
         <v>2.23</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CX19" t="n">
         <v>1.55</v>
@@ -8550,43 +8550,43 @@
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="DG19" t="n">
         <v>3</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.61</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="DI19" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.13</v>
+        <v>5.12</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="DM19" t="n">
-        <v>43.65</v>
+        <v>43.34</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.87</v>
+        <v>13.88</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.09</v>
+        <v>13.21</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.17</v>
+        <v>7.12</v>
       </c>
       <c r="DS19" t="n">
         <v>0.17</v>
@@ -8598,28 +8598,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.3</v>
+        <v>55.25</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.39</v>
+        <v>13.34</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.609999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.78</v>
+        <v>4.75</v>
       </c>
       <c r="EA19" t="n">
-        <v>18.31</v>
+        <v>18.25</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1526,16 +1526,16 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>45.75</v>
+        <v>45.83</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.08</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.17</v>
+        <v>12.25</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.5</v>
+        <v>8.58</v>
       </c>
       <c r="BC2" t="n">
         <v>3.67</v>
@@ -1751,16 +1751,16 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47.38</v>
+        <v>47.42</v>
       </c>
       <c r="DW2" t="n">
         <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.67</v>
+        <v>12.71</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.710000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="DZ2" t="n">
         <v>3.96</v>
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="G3" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="H3" t="n">
-        <v>77.18000000000001</v>
+        <v>75.75</v>
       </c>
       <c r="I3" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="K3" t="n">
-        <v>4.82</v>
+        <v>4.67</v>
       </c>
       <c r="L3" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>34</v>
+        <v>34.08</v>
       </c>
       <c r="N3" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="O3" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="P3" t="n">
-        <v>12.91</v>
+        <v>12.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>16.18</v>
+        <v>15.67</v>
       </c>
       <c r="R3" t="n">
-        <v>8.18</v>
+        <v>8.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="T3" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>42.82</v>
+        <v>42.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.36</v>
+        <v>10.33</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.27</v>
+        <v>6.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.36</v>
+        <v>18.25</v>
       </c>
       <c r="AD3" t="n">
         <v>1.19</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>2.67</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.91</v>
+        <v>10.21</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.22</v>
+        <v>4.96</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.7</v>
+        <v>4.46</v>
       </c>
       <c r="BR3" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BU3" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BV3" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX3" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.53</v>
+        <v>3.74</v>
       </c>
       <c r="BZ3" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="CB3" t="n">
         <v>3.79</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>3.77</v>
       </c>
       <c r="CC3" t="n">
         <v>4.91</v>
@@ -2025,28 +2025,28 @@
         <v>5.42</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI3" t="n">
         <v>1.91</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK3" t="n">
         <v>1.59</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM3" t="n">
         <v>2.24</v>
@@ -2058,19 +2058,19 @@
         <v>1.29</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="CR3" t="n">
         <v>1.42</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CU3" t="n">
         <v>1.42</v>
@@ -2097,85 +2097,85 @@
         <v>1.33</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="DE3" t="n">
         <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="DH3" t="n">
-        <v>75.43000000000001</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.09</v>
+        <v>4.04</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="DM3" t="n">
-        <v>30.96</v>
+        <v>31.12</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="DO3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="DQ3" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="DR3" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="DS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV3" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="DW3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DX3" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="DY3" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="DZ3" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="EA3" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="EB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="EC3" t="n">
         <v>2.21</v>
-      </c>
-      <c r="DP3" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="DQ3" t="n">
-        <v>15.26</v>
-      </c>
-      <c r="DR3" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="DS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV3" t="n">
-        <v>43.57</v>
-      </c>
-      <c r="DW3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DX3" t="n">
-        <v>8.48</v>
-      </c>
-      <c r="DY3" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="DZ3" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="EA3" t="n">
-        <v>19.52</v>
-      </c>
-      <c r="EB3" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="EC3" t="n">
-        <v>2.31</v>
       </c>
     </row>
     <row r="4">
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>51.33</v>
+        <v>51.42</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.08</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>54</v>
+        <v>54.04</v>
       </c>
       <c r="DW4" t="n">
         <v>0.16</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>47.42</v>
+        <v>47.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.08</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.34</v>
+        <v>49.38</v>
       </c>
       <c r="DW5" t="n">
         <v>0.04</v>
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
         <v>0.09</v>
@@ -3484,52 +3484,52 @@
         <v>2.36</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="AI7" t="n">
         <v>93.92</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.67</v>
+        <v>2.46</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.83</v>
+        <v>6.46</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.67</v>
+        <v>0.54</v>
       </c>
       <c r="AN7" t="n">
-        <v>40.17</v>
+        <v>41.46</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.42</v>
+        <v>13.23</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.92</v>
+        <v>12.77</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.92</v>
+        <v>6.77</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>54.33</v>
+        <v>55.23</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.08</v>
       </c>
       <c r="BA7" t="n">
-        <v>14.5</v>
+        <v>14.46</v>
       </c>
       <c r="BB7" t="n">
         <v>9</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.5</v>
+        <v>5.46</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.92</v>
+        <v>19</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.52</v>
+        <v>10.79</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.13</v>
+        <v>4.88</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.39</v>
+        <v>5.12</v>
       </c>
       <c r="BR7" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS7" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BU7" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BV7" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX7" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BY7" t="n">
         <v>1.37</v>
@@ -3625,31 +3625,31 @@
         <v>1.37</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.88</v>
+        <v>4.86</v>
       </c>
       <c r="CB7" t="n">
-        <v>5.06</v>
+        <v>5.03</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CH7" t="n">
         <v>1.55</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.82</v>
@@ -3673,28 +3673,28 @@
         <v>1.65</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CW7" t="n">
         <v>1.88</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY7" t="n">
         <v>1.95</v>
@@ -3712,82 +3712,82 @@
         <v>1.71</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="DE7" t="n">
         <v>0.17</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="DH7" t="n">
-        <v>105.83</v>
+        <v>105.33</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.35</v>
+        <v>6.67</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.66</v>
+        <v>0.59</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.61</v>
+        <v>52.79</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.57</v>
+        <v>12.5</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.7</v>
+        <v>13.59</v>
       </c>
       <c r="DR7" t="n">
-        <v>5.65</v>
+        <v>5.62</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>58.87</v>
+        <v>59.17</v>
       </c>
       <c r="DW7" t="n">
         <v>0.04</v>
       </c>
       <c r="DX7" t="n">
-        <v>17.65</v>
+        <v>17.5</v>
       </c>
       <c r="DY7" t="n">
-        <v>11.35</v>
+        <v>11.25</v>
       </c>
       <c r="DZ7" t="n">
-        <v>6.3</v>
+        <v>6.25</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.74</v>
+        <v>20.25</v>
       </c>
       <c r="EB7" t="n">
         <v>1.93</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="8">
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>64.62</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="Y8" t="n">
         <v>0.15</v>
@@ -4165,7 +4165,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>62.42</v>
+        <v>62.38</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>0.17</v>
@@ -4286,139 +4286,139 @@
         <v>3</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AI9" t="n">
-        <v>63.73</v>
+        <v>63.25</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AN9" t="n">
-        <v>28.09</v>
+        <v>27.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14</v>
+        <v>13.92</v>
       </c>
       <c r="AR9" t="n">
-        <v>17.09</v>
+        <v>17</v>
       </c>
       <c r="AS9" t="n">
         <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>45.82</v>
+        <v>45.33</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA9" t="n">
-        <v>10.91</v>
+        <v>10.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.18</v>
+        <v>7.08</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.73</v>
+        <v>3.42</v>
       </c>
       <c r="BD9" t="n">
-        <v>16.91</v>
+        <v>17.17</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BF9" t="n">
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.779999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.57</v>
+        <v>5.5</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.65000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="BS9" t="n">
-        <v>91.3</v>
+        <v>87.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU9" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV9" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX9" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BY9" t="n">
         <v>2.96</v>
@@ -4427,31 +4427,31 @@
         <v>3.15</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.73</v>
+        <v>4.7</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.1</v>
+        <v>5.04</v>
       </c>
       <c r="CE9" t="n">
         <v>1.33</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CH9" t="n">
         <v>1.48</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.7</v>
@@ -4460,10 +4460,10 @@
         <v>1.54</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CN9" t="n">
         <v>1.81</v>
@@ -4472,25 +4472,25 @@
         <v>1.23</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CW9" t="n">
         <v>1.71</v>
@@ -4505,88 +4505,88 @@
         <v>2.32</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB9" t="n">
         <v>1.25</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="DH9" t="n">
-        <v>77.83</v>
+        <v>77</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.04</v>
+        <v>4.92</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="DM9" t="n">
-        <v>36.43</v>
+        <v>35.79</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.31</v>
+        <v>13.3</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.91</v>
+        <v>16.88</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.91</v>
+        <v>7.96</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.35</v>
+        <v>50.88</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.26</v>
+        <v>12.96</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.91</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.57</v>
+        <v>17.67</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="EC9" t="n">
         <v>3</v>
@@ -4599,94 +4599,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>72.58</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M10" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P10" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="R10" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.36</v>
       </c>
-      <c r="G10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="H10" t="n">
-        <v>70</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="M10" t="n">
-        <v>29.09</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="P10" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="R10" t="n">
-        <v>10.64</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>41.45</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>13.09</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>19.09</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AF10" t="n">
         <v>0.08</v>
@@ -4770,70 +4770,70 @@
         <v>2.17</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.609999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.96</v>
+        <v>4.88</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.61</v>
+        <v>4.67</v>
       </c>
       <c r="BR10" t="n">
-        <v>95.65000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="BS10" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX10" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="CC10" t="n">
         <v>5.54</v>
@@ -4848,28 +4848,28 @@
         <v>2.63</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CH10" t="n">
         <v>1.37</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.73</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CO10" t="n">
         <v>1.22</v>
@@ -4878,7 +4878,7 @@
         <v>1.82</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CR10" t="n">
         <v>1.41</v>
@@ -4887,7 +4887,7 @@
         <v>2.94</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CU10" t="n">
         <v>1.43</v>
@@ -4899,100 +4899,100 @@
         <v>1.85</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC10" t="n">
         <v>1.95</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="DG10" t="n">
         <v>2.04</v>
       </c>
       <c r="DH10" t="n">
-        <v>68.65000000000001</v>
+        <v>70</v>
       </c>
       <c r="DI10" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.13</v>
+        <v>4.08</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM10" t="n">
-        <v>30.13</v>
+        <v>30.5</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.44</v>
+        <v>13.5</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.83</v>
+        <v>13.88</v>
       </c>
       <c r="DR10" t="n">
-        <v>10.18</v>
+        <v>10.04</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>41.08</v>
+        <v>41.62</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.04</v>
+        <v>11</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.43</v>
+        <v>7.42</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.13</v>
+        <v>19.05</v>
       </c>
       <c r="EB10" t="n">
         <v>1.17</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="11">
@@ -5068,7 +5068,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>39.92</v>
+        <v>39.83</v>
       </c>
       <c r="Y11" t="n">
         <v>0.25</v>
@@ -5374,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>38.58</v>
+        <v>38.54</v>
       </c>
       <c r="DW11" t="n">
         <v>0.16</v>
@@ -5808,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5901,49 +5901,49 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AI13" t="n">
-        <v>76.92</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AN13" t="n">
-        <v>34.67</v>
+        <v>35.08</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.42</v>
+        <v>13.69</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.25</v>
+        <v>13.31</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.67</v>
+        <v>9.69</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5955,82 +5955,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>43.33</v>
+        <v>43.54</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.75</v>
+        <v>10.69</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.58</v>
+        <v>6.69</v>
       </c>
       <c r="BC13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>75</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>45.83</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BW13" t="n">
         <v>4.17</v>
       </c>
-      <c r="BD13" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>91.3</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>78.26000000000001</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>47.83</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>34.78</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>4.35</v>
-      </c>
       <c r="BX13" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>3.19</v>
@@ -6039,25 +6039,25 @@
         <v>3.43</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.15</v>
+        <v>4.12</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.34</v>
+        <v>5.18</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.03</v>
+        <v>5.8</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CH13" t="n">
         <v>1.5</v>
@@ -6072,28 +6072,28 @@
         <v>1.49</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO13" t="n">
         <v>1.22</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CR13" t="n">
         <v>1.39</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CT13" t="n">
         <v>3.13</v>
@@ -6126,49 +6126,49 @@
         <v>1.78</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="DH13" t="n">
-        <v>79.66</v>
+        <v>80.05</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DM13" t="n">
         <v>40.17</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.43</v>
+        <v>12.62</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.22</v>
+        <v>13.25</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.130000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6180,28 +6180,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47</v>
+        <v>46.96</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.56</v>
+        <v>11.5</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.78</v>
+        <v>7.79</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.78</v>
+        <v>3.71</v>
       </c>
       <c r="EA13" t="n">
-        <v>19</v>
+        <v>19.09</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="14">
@@ -6277,7 +6277,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>50.15</v>
+        <v>50.08</v>
       </c>
       <c r="Y14" t="n">
         <v>0.08</v>
@@ -6583,7 +6583,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.62</v>
+        <v>49.58</v>
       </c>
       <c r="DW14" t="n">
         <v>0.08</v>
@@ -7420,94 +7420,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F17" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="G17" t="n">
         <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>104.55</v>
+        <v>106.33</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J17" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="K17" t="n">
-        <v>6.64</v>
+        <v>6.58</v>
       </c>
       <c r="L17" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="M17" t="n">
-        <v>45.27</v>
+        <v>45.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O17" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="P17" t="n">
-        <v>15.09</v>
+        <v>15.17</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.18</v>
+        <v>12.25</v>
       </c>
       <c r="R17" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="S17" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="U17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>56.36</v>
+        <v>56.67</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>14</v>
+        <v>13.83</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.55</v>
+        <v>10.42</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="AC17" t="n">
-        <v>20.55</v>
+        <v>20.83</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AF17" t="n">
         <v>0.17</v>
@@ -7591,67 +7591,67 @@
         <v>2.33</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.65</v>
+        <v>9.58</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="BR17" t="n">
-        <v>82.61</v>
+        <v>79.17</v>
       </c>
       <c r="BS17" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT17" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV17" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BZ17" t="n">
         <v>2.17</v>
       </c>
-      <c r="BZ17" t="n">
-        <v>2.19</v>
-      </c>
       <c r="CA17" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="CB17" t="n">
         <v>3.51</v>
@@ -7663,7 +7663,7 @@
         <v>3.38</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF17" t="n">
         <v>2.82</v>
@@ -7699,7 +7699,7 @@
         <v>1.97</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CR17" t="n">
         <v>1.42</v>
@@ -7714,7 +7714,7 @@
         <v>1.43</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CW17" t="n">
         <v>1.84</v>
@@ -7726,7 +7726,7 @@
         <v>2</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA17" t="n">
         <v>1.81</v>
@@ -7741,46 +7741,46 @@
         <v>3.6</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="DH17" t="n">
-        <v>94.31</v>
+        <v>95.62</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="DK17" t="n">
         <v>5.83</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="DM17" t="n">
-        <v>41.13</v>
+        <v>41.29</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DP17" t="n">
-        <v>14.04</v>
+        <v>14.12</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.87</v>
+        <v>11.92</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.52</v>
+        <v>7.38</v>
       </c>
       <c r="DS17" t="n">
         <v>0.08</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>52.74</v>
+        <v>53.04</v>
       </c>
       <c r="DW17" t="n">
         <v>0.08</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.7</v>
+        <v>12.66</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.31</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.09</v>
+        <v>19.29</v>
       </c>
       <c r="EB17" t="n">
         <v>1.34</v>
       </c>
       <c r="EC17" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1854,19 +1854,19 @@
         <v>0.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.33</v>
+        <v>10.25</v>
       </c>
       <c r="AA3" t="n">
         <v>6.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="AC3" t="n">
         <v>18.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE3" t="n">
         <v>1.75</v>
@@ -1956,7 +1956,7 @@
         <v>2.58</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.21</v>
+        <v>10.17</v>
       </c>
       <c r="BI3" t="n">
         <v>2.58</v>
@@ -2160,13 +2160,13 @@
         <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.539999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="DY3" t="n">
         <v>5.25</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="EA3" t="n">
         <v>19.42</v>
@@ -3502,7 +3502,7 @@
         <v>2.46</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.46</v>
+        <v>6.38</v>
       </c>
       <c r="AM7" t="n">
         <v>0.54</v>
@@ -3547,19 +3547,19 @@
         <v>0.08</v>
       </c>
       <c r="BA7" t="n">
-        <v>14.46</v>
+        <v>14.54</v>
       </c>
       <c r="BB7" t="n">
         <v>9</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.46</v>
+        <v>5.54</v>
       </c>
       <c r="BD7" t="n">
         <v>19</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="BF7" t="n">
         <v>2.38</v>
@@ -3568,7 +3568,7 @@
         <v>3.21</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.79</v>
+        <v>10.75</v>
       </c>
       <c r="BI7" t="n">
         <v>3.21</v>
@@ -3733,7 +3733,7 @@
         <v>2.41</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.67</v>
+        <v>6.62</v>
       </c>
       <c r="DL7" t="n">
         <v>0.59</v>
@@ -3772,13 +3772,13 @@
         <v>0.04</v>
       </c>
       <c r="DX7" t="n">
-        <v>17.5</v>
+        <v>17.54</v>
       </c>
       <c r="DY7" t="n">
         <v>11.25</v>
       </c>
       <c r="DZ7" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="EA7" t="n">
         <v>20.25</v>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="F4" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="G4" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H4" t="n">
+        <v>98.62</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M4" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O4" t="n">
         <v>3</v>
       </c>
-      <c r="H4" t="n">
-        <v>98.17</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="K4" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="M4" t="n">
-        <v>50.75</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.25</v>
-      </c>
       <c r="P4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.42</v>
+        <v>14.46</v>
       </c>
       <c r="R4" t="n">
-        <v>6.75</v>
+        <v>6.69</v>
       </c>
       <c r="S4" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T4" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="U4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>56.67</v>
+        <v>56.92</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>18</v>
+        <v>18.46</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.25</v>
+        <v>11.69</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.75</v>
+        <v>6.77</v>
       </c>
       <c r="AC4" t="n">
-        <v>15.92</v>
+        <v>16.54</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AF4" t="n">
         <v>0.25</v>
@@ -2356,70 +2356,70 @@
         <v>2.33</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.83</v>
+        <v>9.92</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK4" t="n">
         <v>0.88</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.67</v>
+        <v>4.56</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.12</v>
+        <v>5.32</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>87.5</v>
+        <v>84</v>
       </c>
       <c r="BT4" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BU4" t="n">
-        <v>41.67</v>
+        <v>40</v>
       </c>
       <c r="BV4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CA4" t="n">
         <v>4.17</v>
       </c>
-      <c r="BX4" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>4.19</v>
-      </c>
       <c r="CB4" t="n">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
       <c r="CC4" t="n">
         <v>2.3</v>
@@ -2440,22 +2440,22 @@
         <v>1.54</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CO4" t="n">
         <v>1.18</v>
@@ -2467,7 +2467,7 @@
         <v>2.53</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS4" t="n">
         <v>2.55</v>
@@ -2479,7 +2479,7 @@
         <v>1.56</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CW4" t="n">
         <v>1.67</v>
@@ -2494,10 +2494,10 @@
         <v>2.39</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DC4" t="n">
         <v>1.66</v>
@@ -2506,46 +2506,46 @@
         <v>2.63</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="DH4" t="n">
-        <v>91.45999999999999</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.33</v>
+        <v>5.44</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.84</v>
+        <v>43.88</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.92</v>
+        <v>13.68</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.84</v>
+        <v>12.92</v>
       </c>
       <c r="DR4" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="DS4" t="n">
         <v>0.12</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>54.04</v>
+        <v>54.28</v>
       </c>
       <c r="DW4" t="n">
         <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.12</v>
+        <v>16.44</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.960000000000001</v>
+        <v>10.24</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6.16</v>
+        <v>6.2</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.21</v>
+        <v>18.44</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="5">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
         <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>0.38</v>
@@ -3887,139 +3887,139 @@
         <v>1.31</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AI8" t="n">
-        <v>93.36</v>
+        <v>92.17</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.36</v>
+        <v>2.83</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN8" t="n">
-        <v>43.73</v>
+        <v>42.17</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.45</v>
+        <v>12.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>11</v>
+        <v>10.92</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.64</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>59.82</v>
+        <v>58.17</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.18</v>
+        <v>13.08</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.449999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.73</v>
+        <v>4.67</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.18</v>
+        <v>17.08</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.83</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.67</v>
+        <v>4.88</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS8" t="n">
-        <v>87.5</v>
+        <v>84</v>
       </c>
       <c r="BT8" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BU8" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BV8" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX8" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BY8" t="n">
         <v>1.28</v>
@@ -4028,55 +4028,55 @@
         <v>1.29</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.68</v>
+        <v>5.59</v>
       </c>
       <c r="CB8" t="n">
-        <v>6.07</v>
+        <v>5.98</v>
       </c>
       <c r="CC8" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="CD8" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO8" t="n">
         <v>1.12</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
@@ -4087,16 +4087,16 @@
         <v>1.75</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX8" t="n">
         <v>1.52</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.44</v>
@@ -4108,52 +4108,52 @@
         <v>1.15</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="DH8" t="n">
-        <v>97.16</v>
+        <v>96.44</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.38</v>
+        <v>5.32</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DM8" t="n">
-        <v>50.67</v>
+        <v>49.64</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.25</v>
+        <v>12.28</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.54</v>
+        <v>10.52</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.79</v>
+        <v>7</v>
       </c>
       <c r="DS8" t="n">
         <v>0.16</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>62.38</v>
+        <v>61.48</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DX8" t="n">
-        <v>17.04</v>
+        <v>16.84</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.08</v>
+        <v>10.96</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.96</v>
+        <v>5.88</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.79</v>
+        <v>18.68</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
         <v>0.08</v>
@@ -5095,46 +5095,46 @@
         <v>0.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AI11" t="n">
-        <v>91.33</v>
+        <v>92.08</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.17</v>
+        <v>4.23</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AN11" t="n">
-        <v>39.17</v>
+        <v>39.69</v>
       </c>
       <c r="AO11" t="n">
         <v>1.08</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="AQ11" t="n">
-        <v>16.58</v>
+        <v>16.23</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.5</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.17</v>
+        <v>7.92</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="n">
         <v>1.08</v>
@@ -5149,73 +5149,73 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>37.25</v>
+        <v>37.85</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.08</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.67</v>
+        <v>13.46</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.42</v>
+        <v>8.85</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.25</v>
+        <v>4.62</v>
       </c>
       <c r="BD11" t="n">
-        <v>19</v>
+        <v>19.23</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.710000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN11" t="n">
         <v>1.08</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="BQ11" t="n">
         <v>5.04</v>
       </c>
       <c r="BR11" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BS11" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BT11" t="n">
-        <v>33.33</v>
+        <v>36</v>
       </c>
       <c r="BU11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>33.33</v>
+        <v>36</v>
       </c>
       <c r="BY11" t="n">
         <v>2.02</v>
@@ -5236,28 +5236,28 @@
         <v>3.56</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.64</v>
+        <v>3.71</v>
       </c>
       <c r="CE11" t="n">
         <v>1.4</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CH11" t="n">
         <v>1.39</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.83</v>
@@ -5266,7 +5266,7 @@
         <v>1.56</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CM11" t="n">
         <v>2.28</v>
@@ -5296,16 +5296,16 @@
         <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX11" t="n">
         <v>1.55</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.36</v>
@@ -5320,49 +5320,49 @@
         <v>2.08</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="DE11" t="n">
         <v>0.08</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="DH11" t="n">
-        <v>95.7</v>
+        <v>95.92</v>
       </c>
       <c r="DI11" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.62</v>
+        <v>4.64</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM11" t="n">
-        <v>42.04</v>
+        <v>42.2</v>
       </c>
       <c r="DN11" t="n">
         <v>1.08</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DP11" t="n">
-        <v>16.92</v>
+        <v>16.72</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.33</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.54</v>
+        <v>7.44</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>38.54</v>
+        <v>38.8</v>
       </c>
       <c r="DW11" t="n">
         <v>0.16</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.3</v>
+        <v>13.68</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.039999999999999</v>
+        <v>9.24</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.25</v>
+        <v>4.44</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.12</v>
+        <v>20.2</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="12">
@@ -8226,10 +8226,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
         <v>12</v>
@@ -8241,79 +8241,79 @@
         <v>0.92</v>
       </c>
       <c r="G19" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H19" t="n">
-        <v>86.67</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="I19" t="n">
         <v>0.08</v>
       </c>
       <c r="J19" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="K19" t="n">
-        <v>4.83</v>
+        <v>4.69</v>
       </c>
       <c r="L19" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="M19" t="n">
-        <v>41</v>
+        <v>41.23</v>
       </c>
       <c r="N19" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="O19" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="P19" t="n">
-        <v>15.08</v>
+        <v>14.46</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.42</v>
+        <v>12.54</v>
       </c>
       <c r="R19" t="n">
-        <v>7.42</v>
+        <v>7.92</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T19" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U19" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V19" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>53.42</v>
+        <v>53.54</v>
       </c>
       <c r="Y19" t="n">
         <v>0.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.42</v>
+        <v>12</v>
       </c>
       <c r="AA19" t="n">
-        <v>8</v>
+        <v>7.62</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.58</v>
+        <v>17.77</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8397,70 +8397,70 @@
         <v>2.08</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.46</v>
+        <v>10.36</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM19" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.38</v>
+        <v>6.32</v>
       </c>
       <c r="BR19" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS19" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT19" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BU19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX19" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CC19" t="n">
         <v>2.75</v>
@@ -8472,16 +8472,16 @@
         <v>1.34</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.69</v>
@@ -8490,7 +8490,7 @@
         <v>1.55</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CM19" t="n">
         <v>2.31</v>
@@ -8502,25 +8502,25 @@
         <v>1.22</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CR19" t="n">
         <v>1.38</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CU19" t="n">
         <v>1.47</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CW19" t="n">
         <v>1.71</v>
@@ -8532,7 +8532,7 @@
         <v>1.94</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA19" t="n">
         <v>1.87</v>
@@ -8541,10 +8541,10 @@
         <v>1.26</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
@@ -8553,73 +8553,73 @@
         <v>1.12</v>
       </c>
       <c r="DG19" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.54000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="DI19" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.12</v>
+        <v>5.04</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM19" t="n">
-        <v>43.34</v>
+        <v>43.36</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.88</v>
+        <v>13.6</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.21</v>
+        <v>13.24</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.12</v>
+        <v>7.4</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.25</v>
+        <v>55.24</v>
       </c>
       <c r="DW19" t="n">
         <v>0.12</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.34</v>
+        <v>13.08</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.58</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.75</v>
+        <v>4.72</v>
       </c>
       <c r="EA19" t="n">
-        <v>18.25</v>
+        <v>18.32</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,40 +1379,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F2" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="H2" t="n">
-        <v>91.17</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="K2" t="n">
-        <v>5.42</v>
+        <v>5.69</v>
       </c>
       <c r="L2" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="M2" t="n">
-        <v>46.92</v>
+        <v>49.92</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
@@ -1421,52 +1421,52 @@
         <v>3.08</v>
       </c>
       <c r="P2" t="n">
-        <v>12.17</v>
+        <v>12.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.5</v>
+        <v>13.77</v>
       </c>
       <c r="R2" t="n">
-        <v>6.75</v>
+        <v>6.54</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="U2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>49</v>
+        <v>49.77</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.17</v>
+        <v>13.54</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.92</v>
+        <v>9.08</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.25</v>
+        <v>4.46</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.67</v>
+        <v>18.23</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AF2" t="n">
         <v>0.08</v>
@@ -1550,70 +1550,70 @@
         <v>2.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.17</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.25</v>
+        <v>4.32</v>
       </c>
       <c r="BR2" t="n">
-        <v>83.33</v>
+        <v>80</v>
       </c>
       <c r="BS2" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="BT2" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BU2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV2" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CC2" t="n">
         <v>4.47</v>
@@ -1628,13 +1628,13 @@
         <v>2.67</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CH2" t="n">
         <v>1.45</v>
       </c>
       <c r="CI2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.76</v>
@@ -1655,19 +1655,19 @@
         <v>1.25</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CR2" t="n">
         <v>1.4</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CU2" t="n">
         <v>1.46</v>
@@ -1691,55 +1691,55 @@
         <v>1.68</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="DE2" t="n">
         <v>0.12</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="DH2" t="n">
-        <v>83.92</v>
+        <v>86.28</v>
       </c>
       <c r="DI2" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.54</v>
+        <v>4.72</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="DM2" t="n">
-        <v>42.08</v>
+        <v>43.84</v>
       </c>
       <c r="DN2" t="n">
         <v>0.92</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="DP2" t="n">
         <v>11.88</v>
       </c>
       <c r="DQ2" t="n">
-        <v>15.25</v>
+        <v>14.84</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.96</v>
+        <v>6.84</v>
       </c>
       <c r="DS2" t="n">
         <v>0.12</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47.42</v>
+        <v>47.88</v>
       </c>
       <c r="DW2" t="n">
         <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.71</v>
+        <v>12.92</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.75</v>
+        <v>8.84</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.96</v>
+        <v>4.08</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.21</v>
+        <v>18.48</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
         <v>0.08</v>
@@ -1875,49 +1875,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AI3" t="n">
-        <v>73.83</v>
+        <v>77.23</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.42</v>
+        <v>3.23</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AN3" t="n">
-        <v>28.17</v>
+        <v>29.31</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.5</v>
+        <v>11.85</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.42</v>
+        <v>14.23</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.75</v>
+        <v>10.38</v>
       </c>
       <c r="AT3" t="n">
         <v>0.92</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>44.25</v>
+        <v>45.15</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="BD3" t="n">
-        <v>20.58</v>
+        <v>20.85</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.17</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.96</v>
+        <v>4.88</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.46</v>
+        <v>4.28</v>
       </c>
       <c r="BR3" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BS3" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BT3" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BU3" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BV3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX3" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BY3" t="n">
         <v>3.74</v>
@@ -2013,16 +2013,16 @@
         <v>4.01</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.79</v>
+        <v>3.81</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.91</v>
+        <v>4.96</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.42</v>
+        <v>5.47</v>
       </c>
       <c r="CE3" t="n">
         <v>1.38</v>
@@ -2046,31 +2046,31 @@
         <v>1.59</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CO3" t="n">
         <v>1.29</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CR3" t="n">
         <v>1.42</v>
       </c>
       <c r="CS3" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CU3" t="n">
         <v>1.42</v>
@@ -2085,64 +2085,64 @@
         <v>1.61</v>
       </c>
       <c r="CY3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DC3" t="n">
         <v>2.03</v>
       </c>
-      <c r="CZ3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="DA3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="DB3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DC3" t="n">
-        <v>2.04</v>
-      </c>
       <c r="DD3" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="DE3" t="n">
         <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="DH3" t="n">
-        <v>74.79000000000001</v>
+        <v>76.52</v>
       </c>
       <c r="DI3" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.04</v>
+        <v>3.92</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM3" t="n">
-        <v>31.12</v>
+        <v>31.6</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="DP3" t="n">
-        <v>12.04</v>
+        <v>12.2</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.04</v>
+        <v>14.92</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.619999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.16</v>
+        <v>43.68</v>
       </c>
       <c r="DW3" t="n">
         <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.5</v>
+        <v>8.56</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.25</v>
+        <v>5.28</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.42</v>
+        <v>19.6</v>
       </c>
       <c r="EB3" t="n">
         <v>1</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="4">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
@@ -2600,49 +2600,49 @@
         <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="H5" t="n">
-        <v>77.42</v>
+        <v>81.23</v>
       </c>
       <c r="I5" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="K5" t="n">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="L5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>38.67</v>
+        <v>40.15</v>
       </c>
       <c r="N5" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="P5" t="n">
-        <v>10.5</v>
+        <v>10.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.25</v>
+        <v>14.77</v>
       </c>
       <c r="R5" t="n">
-        <v>7.58</v>
+        <v>7.31</v>
       </c>
       <c r="S5" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T5" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="U5" t="n">
         <v>0.08</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>51.25</v>
+        <v>52.54</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.33</v>
+        <v>11.31</v>
       </c>
       <c r="AA5" t="n">
-        <v>7</v>
+        <v>7.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.75</v>
+        <v>19.08</v>
       </c>
       <c r="AD5" t="n">
         <v>1.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AF5" t="n">
         <v>0.08</v>
@@ -2759,70 +2759,70 @@
         <v>2.33</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.619999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.08</v>
+        <v>5.04</v>
       </c>
       <c r="BR5" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BS5" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BT5" t="n">
-        <v>41.67</v>
+        <v>40</v>
       </c>
       <c r="BU5" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BV5" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX5" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.97</v>
+        <v>3.93</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.24</v>
+        <v>4.19</v>
       </c>
       <c r="CC5" t="n">
         <v>5.71</v>
@@ -2834,121 +2834,121 @@
         <v>1.34</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CN5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CP5" t="n">
         <v>1.82</v>
       </c>
-      <c r="CO5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>1.8</v>
-      </c>
       <c r="CQ5" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="DE5" t="n">
         <v>0.08</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="DH5" t="n">
-        <v>74.92</v>
+        <v>77</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM5" t="n">
-        <v>34.75</v>
+        <v>35.68</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.66</v>
+        <v>11.8</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.92</v>
+        <v>15.16</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.96</v>
+        <v>7.8</v>
       </c>
       <c r="DS5" t="n">
         <v>0.08</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.38</v>
+        <v>50.12</v>
       </c>
       <c r="DW5" t="n">
         <v>0.04</v>
@@ -2969,19 +2969,19 @@
         <v>10.92</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.21</v>
+        <v>7.24</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.46</v>
+        <v>18.64</v>
       </c>
       <c r="EB5" t="n">
         <v>1.2</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
         <v>0.08</v>
@@ -3084,46 +3084,46 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AI6" t="n">
-        <v>86</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.83</v>
+        <v>4.46</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>38.83</v>
+        <v>39.15</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AP6" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="AT6" t="n">
         <v>2.08</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>12.83</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.17</v>
       </c>
       <c r="AU6" t="n">
         <v>0.92</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>46.5</v>
+        <v>46.92</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.92</v>
+        <v>11.15</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.58</v>
+        <v>7.54</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.33</v>
+        <v>3.62</v>
       </c>
       <c r="BD6" t="n">
-        <v>20.92</v>
+        <v>21</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.08</v>
+        <v>9.44</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.42</v>
+        <v>4.56</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.67</v>
+        <v>4.88</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS6" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BU6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BY6" t="n">
         <v>3.96</v>
@@ -3222,22 +3222,22 @@
         <v>3.95</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="CC6" t="n">
-        <v>6.32</v>
+        <v>6.12</v>
       </c>
       <c r="CD6" t="n">
-        <v>6.78</v>
+        <v>6.53</v>
       </c>
       <c r="CE6" t="n">
         <v>1.35</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CG6" t="n">
         <v>3.09</v>
@@ -3249,7 +3249,7 @@
         <v>1.98</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK6" t="n">
         <v>1.57</v>
@@ -3264,13 +3264,13 @@
         <v>1.78</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CP6" t="n">
         <v>1.84</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CR6" t="n">
         <v>1.41</v>
@@ -3291,16 +3291,16 @@
         <v>1.85</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB6" t="n">
         <v>1.29</v>
@@ -3315,43 +3315,43 @@
         <v>0.04</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="DH6" t="n">
-        <v>87.25</v>
+        <v>87.48</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>36.52</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="DO6" t="n">
         <v>2.04</v>
       </c>
-      <c r="DK6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="DL6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DM6" t="n">
-        <v>36.25</v>
-      </c>
-      <c r="DN6" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>1.79</v>
-      </c>
       <c r="DP6" t="n">
-        <v>12.5</v>
+        <v>12.56</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.75</v>
+        <v>14.72</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.83</v>
+        <v>9</v>
       </c>
       <c r="DS6" t="n">
         <v>0.04</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.12</v>
+        <v>46.36</v>
       </c>
       <c r="DW6" t="n">
         <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.88</v>
+        <v>11</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.75</v>
+        <v>7.72</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.42</v>
+        <v>20.48</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="G7" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="H7" t="n">
-        <v>118.82</v>
+        <v>115.83</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="K7" t="n">
-        <v>6.91</v>
+        <v>6.92</v>
       </c>
       <c r="L7" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="M7" t="n">
-        <v>66.18000000000001</v>
+        <v>63.58</v>
       </c>
       <c r="N7" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="O7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>11.64</v>
+        <v>11.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.55</v>
+        <v>15.42</v>
       </c>
       <c r="R7" t="n">
-        <v>4.27</v>
+        <v>4.5</v>
       </c>
       <c r="S7" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="U7" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>63.82</v>
+        <v>63.17</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.09</v>
+        <v>20.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>13.91</v>
+        <v>13.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.18</v>
+        <v>7</v>
       </c>
       <c r="AC7" t="n">
-        <v>21.73</v>
+        <v>22.42</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AF7" t="n">
         <v>0.23</v>
@@ -3565,70 +3565,70 @@
         <v>2.38</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.75</v>
+        <v>10.84</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="BJ7" t="n">
         <v>0.92</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="BP7" t="n">
         <v>4.88</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.12</v>
+        <v>5.24</v>
       </c>
       <c r="BR7" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS7" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BT7" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BU7" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BV7" t="n">
-        <v>20.83</v>
+        <v>24</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX7" t="n">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="BY7" t="n">
         <v>1.37</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CA7" t="n">
         <v>4.86</v>
       </c>
       <c r="CB7" t="n">
-        <v>5.03</v>
+        <v>5.02</v>
       </c>
       <c r="CC7" t="n">
         <v>1.66</v>
@@ -3643,16 +3643,16 @@
         <v>2.42</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI7" t="n">
         <v>1.94</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CK7" t="n">
         <v>1.55</v>
@@ -3664,22 +3664,22 @@
         <v>2.3</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CO7" t="n">
         <v>1.18</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CT7" t="n">
         <v>3.24</v>
@@ -3691,10 +3691,10 @@
         <v>2</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY7" t="n">
         <v>1.95</v>
@@ -3709,52 +3709,52 @@
         <v>1.23</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="DG7" t="n">
         <v>3</v>
       </c>
       <c r="DH7" t="n">
-        <v>105.33</v>
+        <v>104.44</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.62</v>
+        <v>6.64</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.79</v>
+        <v>52.08</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="DO7" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.5</v>
+        <v>12.44</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.59</v>
+        <v>14.04</v>
       </c>
       <c r="DR7" t="n">
-        <v>5.62</v>
+        <v>5.68</v>
       </c>
       <c r="DS7" t="n">
         <v>0.16</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.17</v>
+        <v>59.04</v>
       </c>
       <c r="DW7" t="n">
         <v>0.04</v>
       </c>
       <c r="DX7" t="n">
-        <v>17.54</v>
+        <v>17.4</v>
       </c>
       <c r="DY7" t="n">
-        <v>11.25</v>
+        <v>11.16</v>
       </c>
       <c r="DZ7" t="n">
-        <v>6.29</v>
+        <v>6.24</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.25</v>
+        <v>20.64</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="8">
@@ -4196,61 +4196,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F9" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="G9" t="n">
-        <v>4.83</v>
+        <v>4.92</v>
       </c>
       <c r="H9" t="n">
-        <v>90.75</v>
+        <v>90.62</v>
       </c>
       <c r="I9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="K9" t="n">
-        <v>7.08</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="M9" t="n">
-        <v>44.08</v>
+        <v>42.69</v>
       </c>
       <c r="N9" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="O9" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="P9" t="n">
-        <v>12.67</v>
+        <v>12.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.75</v>
+        <v>16.62</v>
       </c>
       <c r="R9" t="n">
-        <v>6.92</v>
+        <v>6.85</v>
       </c>
       <c r="S9" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="T9" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="U9" t="n">
         <v>0.08</v>
@@ -4262,25 +4262,25 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>56.42</v>
+        <v>55.77</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="Z9" t="n">
-        <v>15.42</v>
+        <v>15.31</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.5</v>
+        <v>10.23</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.92</v>
+        <v>5.08</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.17</v>
+        <v>18.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
@@ -4367,70 +4367,70 @@
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.710000000000001</v>
+        <v>10.04</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.21</v>
+        <v>4.36</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.5</v>
+        <v>5.68</v>
       </c>
       <c r="BR9" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS9" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BT9" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BU9" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BV9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX9" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="CA9" t="n">
         <v>3.81</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CC9" t="n">
         <v>4.7</v>
@@ -4445,10 +4445,10 @@
         <v>2.59</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI9" t="n">
         <v>2.09</v>
@@ -4463,7 +4463,7 @@
         <v>2.05</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CN9" t="n">
         <v>1.81</v>
@@ -4475,7 +4475,7 @@
         <v>1.79</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CR9" t="n">
         <v>1.38</v>
@@ -4493,70 +4493,70 @@
         <v>2.21</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY9" t="n">
         <v>1.93</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB9" t="n">
         <v>1.25</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="DE9" t="n">
         <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="DH9" t="n">
-        <v>77</v>
+        <v>77.48</v>
       </c>
       <c r="DI9" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.92</v>
+        <v>4.96</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.79</v>
+        <v>35.4</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.3</v>
+        <v>13.16</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.88</v>
+        <v>16.8</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.96</v>
+        <v>7.88</v>
       </c>
       <c r="DS9" t="n">
         <v>0.12</v>
@@ -4568,25 +4568,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>50.88</v>
+        <v>50.76</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.96</v>
+        <v>13</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.789999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.17</v>
+        <v>4.28</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.67</v>
+        <v>17.92</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC9" t="n">
         <v>3</v>
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
         <v>0.17</v>
@@ -4692,49 +4692,49 @@
         <v>0.08</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AI10" t="n">
-        <v>67.42</v>
+        <v>67.08</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AN10" t="n">
-        <v>31.08</v>
+        <v>30.54</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.17</v>
+        <v>13.46</v>
       </c>
       <c r="AR10" t="n">
-        <v>14.42</v>
+        <v>14.15</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.75</v>
+        <v>9.69</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4746,82 +4746,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>40.75</v>
+        <v>40.77</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.17</v>
+        <v>8.69</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.75</v>
+        <v>6.46</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.17</v>
+        <v>19.15</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.58</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BP10" t="n">
         <v>4.88</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.67</v>
+        <v>4.72</v>
       </c>
       <c r="BR10" t="n">
-        <v>91.67</v>
+        <v>88</v>
       </c>
       <c r="BS10" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BT10" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BU10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV10" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX10" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
         <v>3.02</v>
@@ -4830,25 +4830,25 @@
         <v>3.08</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.54</v>
+        <v>5.4</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.43</v>
+        <v>6.25</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CH10" t="n">
         <v>1.37</v>
@@ -4869,25 +4869,25 @@
         <v>2.12</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO10" t="n">
         <v>1.22</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CR10" t="n">
         <v>1.41</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CU10" t="n">
         <v>1.43</v>
@@ -4902,64 +4902,64 @@
         <v>1.61</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="DE10" t="n">
         <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="DH10" t="n">
-        <v>70</v>
+        <v>69.72</v>
       </c>
       <c r="DI10" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DM10" t="n">
-        <v>30.5</v>
+        <v>30.24</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="DO10" t="n">
         <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.5</v>
+        <v>13.16</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.88</v>
+        <v>13.76</v>
       </c>
       <c r="DR10" t="n">
-        <v>10.04</v>
+        <v>10</v>
       </c>
       <c r="DS10" t="n">
         <v>0.08</v>
@@ -4971,25 +4971,25 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>41.62</v>
+        <v>41.6</v>
       </c>
       <c r="DW10" t="n">
         <v>0.2</v>
       </c>
       <c r="DX10" t="n">
-        <v>11</v>
+        <v>10.68</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.42</v>
+        <v>7.24</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.58</v>
+        <v>3.44</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.05</v>
+        <v>19.04</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="EC10" t="n">
         <v>2.04</v>
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
         <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5501,133 +5501,133 @@
         <v>2</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.67</v>
+        <v>2.46</v>
       </c>
       <c r="AI12" t="n">
-        <v>81.92</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AN12" t="n">
-        <v>34.67</v>
+        <v>33.85</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.83</v>
+        <v>16.08</v>
       </c>
       <c r="AR12" t="n">
         <v>11.08</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.58</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AU12" t="n">
         <v>0.92</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>41.08</v>
+        <v>40.69</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BA12" t="n">
-        <v>8</v>
+        <v>7.85</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.83</v>
+        <v>5.69</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="BD12" t="n">
-        <v>19.75</v>
+        <v>19.77</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.08</v>
+        <v>9</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="BO12" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.29</v>
+        <v>5.2</v>
       </c>
       <c r="BR12" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BS12" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BT12" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BU12" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BV12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BY12" t="n">
         <v>3.11</v>
@@ -5636,13 +5636,13 @@
         <v>3.55</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.56</v>
+        <v>4.54</v>
       </c>
       <c r="CD12" t="n">
         <v>4.96</v>
@@ -5651,31 +5651,31 @@
         <v>1.36</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI12" t="n">
         <v>2.03</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO12" t="n">
         <v>1.25</v>
@@ -5684,121 +5684,121 @@
         <v>1.85</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CR12" t="n">
         <v>1.41</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB12" t="n">
         <v>1.29</v>
       </c>
       <c r="DC12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="DO12" t="n">
         <v>1.92</v>
       </c>
-      <c r="DD12" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="DE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DG12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="DH12" t="n">
-        <v>86.04000000000001</v>
-      </c>
-      <c r="DI12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DJ12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DK12" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="DL12" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="DM12" t="n">
-        <v>39.12</v>
-      </c>
-      <c r="DN12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DO12" t="n">
-        <v>1.88</v>
-      </c>
       <c r="DP12" t="n">
-        <v>15.62</v>
+        <v>15.76</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.04</v>
+        <v>12.96</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.62</v>
+        <v>7.68</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.42</v>
+        <v>45.04</v>
       </c>
       <c r="DW12" t="n">
         <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.34</v>
+        <v>10.16</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.58</v>
+        <v>7.44</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.34</v>
+        <v>19.36</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="13">
@@ -5808,10 +5808,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>13</v>
@@ -5820,49 +5820,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="G13" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="H13" t="n">
-        <v>82.64</v>
+        <v>82.08</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J13" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="K13" t="n">
-        <v>5.64</v>
+        <v>5.67</v>
       </c>
       <c r="L13" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="M13" t="n">
-        <v>46.18</v>
+        <v>45.17</v>
       </c>
       <c r="N13" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="O13" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="P13" t="n">
-        <v>11.36</v>
+        <v>10.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.18</v>
+        <v>12.83</v>
       </c>
       <c r="R13" t="n">
-        <v>8.550000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="T13" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5874,28 +5874,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>51</v>
+        <v>49.42</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.45</v>
+        <v>12.58</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.09</v>
+        <v>9</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="AC13" t="n">
-        <v>22</v>
+        <v>21.17</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5979,70 +5979,70 @@
         <v>2.54</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.5</v>
+        <v>9.68</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM13" t="n">
         <v>0.96</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.38</v>
+        <v>4.56</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="BR13" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BS13" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BT13" t="n">
-        <v>45.83</v>
+        <v>48</v>
       </c>
       <c r="BU13" t="n">
-        <v>33.33</v>
+        <v>36</v>
       </c>
       <c r="BV13" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="BZ13" t="n">
         <v>3.43</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="CC13" t="n">
         <v>5.18</v>
@@ -6069,19 +6069,19 @@
         <v>1.7</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CN13" t="n">
         <v>1.91</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP13" t="n">
         <v>1.76</v>
@@ -6093,19 +6093,19 @@
         <v>1.39</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CU13" t="n">
         <v>1.52</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CX13" t="n">
         <v>1.53</v>
@@ -6117,7 +6117,7 @@
         <v>2.41</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DB13" t="n">
         <v>1.24</v>
@@ -6126,49 +6126,49 @@
         <v>1.78</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DH13" t="n">
-        <v>80.05</v>
+        <v>79.88</v>
       </c>
       <c r="DI13" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DM13" t="n">
-        <v>40.17</v>
+        <v>39.92</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.75</v>
+        <v>0.84</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.62</v>
+        <v>12.36</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.25</v>
+        <v>13.08</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.17</v>
+        <v>9.08</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6180,28 +6180,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>46.96</v>
+        <v>46.36</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.79</v>
+        <v>7.8</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.71</v>
+        <v>3.8</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.09</v>
+        <v>18.8</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="14">
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" t="n">
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6301,139 +6301,139 @@
         <v>1.92</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AI14" t="n">
-        <v>85.55</v>
+        <v>85.25</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.27</v>
+        <v>4.17</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>38.55</v>
+        <v>38.08</v>
       </c>
       <c r="AO14" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14.27</v>
+        <v>14.42</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.55</v>
+        <v>14.33</v>
       </c>
       <c r="AS14" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>47.58</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BA14" t="n">
         <v>9</v>
       </c>
-      <c r="AT14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>49</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>9.359999999999999</v>
-      </c>
       <c r="BB14" t="n">
-        <v>6.73</v>
+        <v>6.33</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.27</v>
+        <v>17.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.289999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.42</v>
+        <v>4.32</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="BR14" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BS14" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BT14" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BU14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BV14" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BY14" t="n">
         <v>2.87</v>
@@ -6442,67 +6442,67 @@
         <v>2.93</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CC14" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.75</v>
+        <v>4.54</v>
       </c>
       <c r="CE14" t="n">
         <v>1.4</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="CR14" t="n">
         <v>1.43</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV14" t="n">
         <v>1.97</v>
@@ -6511,100 +6511,100 @@
         <v>1.9</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="DE14" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="DH14" t="n">
-        <v>91.8</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.29</v>
+        <v>4.24</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM14" t="n">
-        <v>39.21</v>
+        <v>38.96</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="DP14" t="n">
-        <v>15</v>
+        <v>15.04</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.63</v>
+        <v>14.52</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.460000000000001</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.58</v>
+        <v>48.88</v>
       </c>
       <c r="DW14" t="n">
         <v>0.08</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.75</v>
+        <v>10.52</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.5</v>
+        <v>7.28</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.54</v>
+        <v>20.52</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="15">
@@ -6614,10 +6614,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
         <v>12</v>
@@ -6626,82 +6626,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G15" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H15" t="n">
-        <v>106.75</v>
+        <v>105.92</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.33</v>
+        <v>2.54</v>
       </c>
       <c r="K15" t="n">
-        <v>5.67</v>
+        <v>5.54</v>
       </c>
       <c r="L15" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="M15" t="n">
-        <v>49.67</v>
+        <v>49.08</v>
       </c>
       <c r="N15" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="O15" t="n">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="P15" t="n">
-        <v>11.75</v>
+        <v>11.54</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.92</v>
+        <v>12.46</v>
       </c>
       <c r="R15" t="n">
-        <v>8.08</v>
+        <v>7.85</v>
       </c>
       <c r="S15" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T15" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="U15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>55.83</v>
+        <v>56.46</v>
       </c>
       <c r="Y15" t="n">
         <v>0.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>14.58</v>
+        <v>14.31</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.67</v>
+        <v>10.38</v>
       </c>
       <c r="AB15" t="n">
         <v>3.92</v>
       </c>
       <c r="AC15" t="n">
-        <v>22.58</v>
+        <v>23</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="AF15" t="n">
         <v>0.08</v>
@@ -6785,70 +6785,70 @@
         <v>2.42</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.83</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.58</v>
+        <v>4.52</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.25</v>
+        <v>5.16</v>
       </c>
       <c r="BR15" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS15" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BU15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV15" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="CC15" t="n">
         <v>4.96</v>
@@ -6860,16 +6860,16 @@
         <v>1.35</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CH15" t="n">
         <v>1.47</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.72</v>
@@ -6878,37 +6878,37 @@
         <v>1.53</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CW15" t="n">
         <v>1.77</v>
@@ -6920,61 +6920,61 @@
         <v>1.94</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DB15" t="n">
         <v>1.27</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="DE15" t="n">
         <v>0.04</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="DH15" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="DI15" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.21</v>
+        <v>5.16</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="DM15" t="n">
-        <v>45</v>
+        <v>44.88</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.96</v>
+        <v>11.84</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.12</v>
+        <v>13.36</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.33</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS15" t="n">
         <v>0.12</v>
@@ -6986,28 +6986,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>53.04</v>
+        <v>53.48</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.42</v>
+        <v>13.32</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.460000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DZ15" t="n">
         <v>3.96</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.79</v>
+        <v>21.08</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="16">
@@ -7017,94 +7017,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
         <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="F16" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="G16" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>79.42</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="K16" t="n">
-        <v>3.83</v>
+        <v>3.69</v>
       </c>
       <c r="L16" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="M16" t="n">
-        <v>37.75</v>
+        <v>37.08</v>
       </c>
       <c r="N16" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="O16" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="P16" t="n">
-        <v>14.42</v>
+        <v>14.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.75</v>
+        <v>13</v>
       </c>
       <c r="R16" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="S16" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="V16" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>50</v>
+        <v>49.54</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.17</v>
+        <v>13.15</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.67</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.5</v>
+        <v>3.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.08</v>
+        <v>17.46</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AF16" t="n">
         <v>0.17</v>
@@ -7188,70 +7188,70 @@
         <v>2.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.710000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BM16" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BO16" t="n">
         <v>1.08</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.17</v>
+        <v>4.12</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.5</v>
+        <v>4.32</v>
       </c>
       <c r="BR16" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS16" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="BT16" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BU16" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BV16" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX16" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.79</v>
+        <v>3.81</v>
       </c>
       <c r="CC16" t="n">
         <v>3.99</v>
@@ -7260,10 +7260,10 @@
         <v>4.19</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CG16" t="n">
         <v>2.96</v>
@@ -7272,22 +7272,22 @@
         <v>1.41</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK16" t="n">
         <v>1.51</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO16" t="n">
         <v>1.2</v>
@@ -7296,10 +7296,10 @@
         <v>1.76</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS16" t="n">
         <v>2.77</v>
@@ -7311,10 +7311,10 @@
         <v>1.49</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX16" t="n">
         <v>1.59</v>
@@ -7323,7 +7323,7 @@
         <v>1.98</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DA16" t="n">
         <v>1.83</v>
@@ -7332,85 +7332,85 @@
         <v>1.27</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DD16" t="n">
         <v>3.13</v>
       </c>
       <c r="DE16" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>81.31999999999999</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>36</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="DS16" t="n">
         <v>0.12</v>
       </c>
-      <c r="DF16" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="DG16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DH16" t="n">
-        <v>80.45999999999999</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DJ16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DK16" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="DL16" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="DM16" t="n">
-        <v>36.29</v>
-      </c>
-      <c r="DN16" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DO16" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="DP16" t="n">
-        <v>13.84</v>
-      </c>
-      <c r="DQ16" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="DR16" t="n">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="DS16" t="n">
-        <v>0.08</v>
-      </c>
       <c r="DT16" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>49.12</v>
+        <v>48.92</v>
       </c>
       <c r="DW16" t="n">
         <v>0.08</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.54</v>
+        <v>12.56</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.83</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.71</v>
+        <v>3.84</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.42</v>
+        <v>16.64</v>
       </c>
       <c r="EB16" t="n">
         <v>1.32</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" t="n">
         <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
         <v>0.08</v>
@@ -7510,139 +7510,139 @@
         <v>1.58</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.33</v>
+        <v>2.54</v>
       </c>
       <c r="AI17" t="n">
-        <v>84.92</v>
+        <v>85.92</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.42</v>
+        <v>2.77</v>
       </c>
       <c r="AL17" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>37.77</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>49</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BQ17" t="n">
         <v>5.08</v>
       </c>
-      <c r="AM17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>37.33</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>11.58</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>49.42</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>17.75</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>9.58</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>4.96</v>
-      </c>
       <c r="BR17" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BS17" t="n">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="BT17" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="BU17" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BV17" t="n">
-        <v>8.33</v>
+        <v>12</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BY17" t="n">
         <v>2.13</v>
@@ -7651,43 +7651,43 @@
         <v>2.17</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.53</v>
+        <v>3.58</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.51</v>
+        <v>3.56</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.38</v>
+        <v>3.71</v>
       </c>
       <c r="CE17" t="n">
         <v>1.38</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CH17" t="n">
         <v>1.4</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CK17" t="n">
         <v>1.58</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CN17" t="n">
         <v>1.78</v>
@@ -7699,7 +7699,7 @@
         <v>1.97</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="CR17" t="n">
         <v>1.42</v>
@@ -7714,22 +7714,22 @@
         <v>1.43</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY17" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.28</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DB17" t="n">
         <v>1.33</v>
@@ -7738,49 +7738,49 @@
         <v>2.05</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="DE17" t="n">
         <v>0.12</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.17</v>
+        <v>3.24</v>
       </c>
       <c r="DH17" t="n">
-        <v>95.62</v>
+        <v>95.72</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.83</v>
+        <v>5.84</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="DM17" t="n">
-        <v>41.29</v>
+        <v>41.36</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="DP17" t="n">
-        <v>14.12</v>
+        <v>14.44</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.92</v>
+        <v>11.88</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.38</v>
+        <v>7.48</v>
       </c>
       <c r="DS17" t="n">
         <v>0.08</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>53.04</v>
+        <v>52.68</v>
       </c>
       <c r="DW17" t="n">
         <v>0.08</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.66</v>
+        <v>12.64</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.29</v>
+        <v>19.4</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="18">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" t="n">
         <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E18" t="n">
         <v>0.08</v>
@@ -7916,136 +7916,136 @@
         <v>0.08</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AI18" t="n">
-        <v>84.67</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="AJ18" t="n">
         <v>0.08</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.33</v>
+        <v>4.62</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AN18" t="n">
-        <v>32.83</v>
+        <v>34.23</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.17</v>
+        <v>2.46</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.42</v>
+        <v>12.08</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.83</v>
+        <v>14.23</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.67</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AU18" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>52.75</v>
+        <v>53.92</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BA18" t="n">
-        <v>13.25</v>
+        <v>13.62</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.83</v>
+        <v>8.23</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.42</v>
+        <v>5.38</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.67</v>
+        <v>9.84</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.46</v>
+        <v>4.64</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="BR18" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS18" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT18" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BU18" t="n">
-        <v>33.33</v>
+        <v>36</v>
       </c>
       <c r="BV18" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BW18" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BX18" t="n">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="BY18" t="n">
         <v>1.84</v>
@@ -8054,16 +8054,16 @@
         <v>1.86</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CB18" t="n">
         <v>3.87</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.37</v>
+        <v>3.27</v>
       </c>
       <c r="CE18" t="n">
         <v>1.34</v>
@@ -8072,7 +8072,7 @@
         <v>2.57</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CH18" t="n">
         <v>1.48</v>
@@ -8081,13 +8081,13 @@
         <v>2.06</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CK18" t="n">
         <v>1.54</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CM18" t="n">
         <v>2.35</v>
@@ -8099,7 +8099,7 @@
         <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CQ18" t="n">
         <v>2.86</v>
@@ -8108,19 +8108,19 @@
         <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CT18" t="n">
         <v>3.2</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CX18" t="n">
         <v>1.56</v>
@@ -8141,82 +8141,82 @@
         <v>1.81</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="DE18" t="n">
         <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DH18" t="n">
-        <v>94.62</v>
+        <v>95.2</v>
       </c>
       <c r="DI18" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.42</v>
+        <v>4.56</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.33</v>
+        <v>41.72</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="DO18" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.42</v>
+        <v>12.24</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.79</v>
+        <v>13.52</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.119999999999999</v>
+        <v>8.16</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>54.88</v>
+        <v>55.4</v>
       </c>
       <c r="DW18" t="n">
         <v>0.12</v>
       </c>
       <c r="DX18" t="n">
-        <v>15.66</v>
+        <v>15.76</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.83</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.84</v>
+        <v>5.8</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.29</v>
+        <v>18.96</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>45.15</v>
+        <v>45.08</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.68</v>
+        <v>43.64</v>
       </c>
       <c r="DW3" t="n">
         <v>0.08</v>
@@ -3926,7 +3926,7 @@
         <v>10.92</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="AT8" t="n">
         <v>0.58</v>
@@ -4153,7 +4153,7 @@
         <v>10.52</v>
       </c>
       <c r="DR8" t="n">
-        <v>7</v>
+        <v>6.96</v>
       </c>
       <c r="DS8" t="n">
         <v>0.16</v>
@@ -5552,7 +5552,7 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>40.69</v>
+        <v>40.62</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.23</v>
@@ -5777,7 +5777,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.04</v>
+        <v>45</v>
       </c>
       <c r="DW12" t="n">
         <v>0.16</v>
@@ -5820,7 +5820,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="G13" t="n">
         <v>2.33</v>
@@ -5832,7 +5832,7 @@
         <v>0.08</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="K13" t="n">
         <v>5.67</v>
@@ -5895,7 +5895,7 @@
         <v>1.37</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -6132,7 +6132,7 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="DG13" t="n">
         <v>2</v>
@@ -6144,7 +6144,7 @@
         <v>0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="DK13" t="n">
         <v>4.8</v>
@@ -6201,7 +6201,7 @@
         <v>1.29</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="14">
@@ -6680,7 +6680,7 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>56.46</v>
+        <v>56.54</v>
       </c>
       <c r="Y15" t="n">
         <v>0.08</v>
@@ -6986,7 +6986,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>53.48</v>
+        <v>53.52</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
@@ -7083,7 +7083,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>49.54</v>
+        <v>49.62</v>
       </c>
       <c r="Y16" t="n">
         <v>0.15</v>
@@ -7389,7 +7389,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>48.92</v>
+        <v>48.96</v>
       </c>
       <c r="DW16" t="n">
         <v>0.08</v>

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
         <v>13</v>
@@ -1794,49 +1794,49 @@
         <v>0.08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="G3" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="H3" t="n">
-        <v>75.75</v>
+        <v>78</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="J3" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.67</v>
+        <v>4.69</v>
       </c>
       <c r="L3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="M3" t="n">
-        <v>34.08</v>
+        <v>34.54</v>
       </c>
       <c r="N3" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O3" t="n">
         <v>2.08</v>
       </c>
       <c r="P3" t="n">
-        <v>12.58</v>
+        <v>12.77</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.67</v>
+        <v>15.85</v>
       </c>
       <c r="R3" t="n">
-        <v>8.5</v>
+        <v>8.31</v>
       </c>
       <c r="S3" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="T3" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>42.08</v>
+        <v>43.46</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.25</v>
+        <v>10.38</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.25</v>
+        <v>6.38</v>
       </c>
       <c r="AB3" t="n">
         <v>4</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.25</v>
+        <v>18.15</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>2.54</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.880000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="BP3" t="n">
         <v>4.88</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.28</v>
+        <v>4.35</v>
       </c>
       <c r="BR3" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BT3" t="n">
-        <v>52</v>
+        <v>53.85</v>
       </c>
       <c r="BU3" t="n">
-        <v>28</v>
+        <v>30.77</v>
       </c>
       <c r="BV3" t="n">
-        <v>12</v>
+        <v>15.38</v>
       </c>
       <c r="BW3" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX3" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.01</v>
+        <v>3.88</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="CC3" t="n">
         <v>4.96</v>
@@ -2025,16 +2025,16 @@
         <v>5.47</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI3" t="n">
         <v>1.91</v>
@@ -2052,13 +2052,13 @@
         <v>2.25</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO3" t="n">
         <v>1.29</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ3" t="n">
         <v>3.3</v>
@@ -2106,28 +2106,28 @@
         <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="DH3" t="n">
-        <v>76.52</v>
+        <v>77.61</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM3" t="n">
-        <v>31.6</v>
+        <v>31.92</v>
       </c>
       <c r="DN3" t="n">
         <v>0.84</v>
@@ -2136,13 +2136,13 @@
         <v>2.04</v>
       </c>
       <c r="DP3" t="n">
-        <v>12.2</v>
+        <v>12.31</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.92</v>
+        <v>15.04</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.48</v>
+        <v>9.35</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.64</v>
+        <v>44.27</v>
       </c>
       <c r="DW3" t="n">
         <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.56</v>
+        <v>8.69</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.28</v>
+        <v>5.38</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="EB3" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="4">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
         <v>13</v>
@@ -3006,46 +3006,46 @@
         <v>1.08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>88.5</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="K6" t="n">
-        <v>3.67</v>
+        <v>3.54</v>
       </c>
       <c r="L6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="M6" t="n">
-        <v>33.67</v>
+        <v>32.38</v>
       </c>
       <c r="N6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="O6" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="P6" t="n">
-        <v>12.17</v>
+        <v>12.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.5</v>
+        <v>13.92</v>
       </c>
       <c r="R6" t="n">
-        <v>8.58</v>
+        <v>8.77</v>
       </c>
       <c r="S6" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="T6" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="U6" t="n">
         <v>0.08</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>45.75</v>
+        <v>44.69</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.83</v>
+        <v>10.69</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.92</v>
+        <v>7.62</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.92</v>
+        <v>20.08</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>2</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.44</v>
+        <v>9.69</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.56</v>
+        <v>4.54</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.88</v>
+        <v>5.15</v>
       </c>
       <c r="BR6" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BT6" t="n">
-        <v>48</v>
+        <v>46.15</v>
       </c>
       <c r="BU6" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BV6" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BW6" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX6" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.96</v>
+        <v>4.23</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.95</v>
+        <v>4.23</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="CC6" t="n">
         <v>6.12</v>
@@ -3237,7 +3237,7 @@
         <v>1.35</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CG6" t="n">
         <v>3.09</v>
@@ -3255,7 +3255,7 @@
         <v>1.57</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CM6" t="n">
         <v>2.29</v>
@@ -3267,19 +3267,19 @@
         <v>1.24</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="CR6" t="n">
         <v>1.41</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CU6" t="n">
         <v>1.47</v>
@@ -3309,49 +3309,49 @@
         <v>1.92</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="DE6" t="n">
         <v>0.04</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="DH6" t="n">
-        <v>87.48</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM6" t="n">
-        <v>36.52</v>
+        <v>35.76</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="DO6" t="n">
         <v>2.04</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.56</v>
+        <v>12.58</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.72</v>
+        <v>14.42</v>
       </c>
       <c r="DR6" t="n">
-        <v>9</v>
+        <v>9.07</v>
       </c>
       <c r="DS6" t="n">
         <v>0.04</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.36</v>
+        <v>45.8</v>
       </c>
       <c r="DW6" t="n">
         <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>11</v>
+        <v>10.92</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.72</v>
+        <v>7.58</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.48</v>
+        <v>20.54</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="n">
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
         <v>0.08</v>
@@ -3484,139 +3484,139 @@
         <v>2.33</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.62</v>
+        <v>3.29</v>
       </c>
       <c r="AI7" t="n">
-        <v>93.92</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.38</v>
+        <v>6.93</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AN7" t="n">
-        <v>41.46</v>
+        <v>45.5</v>
       </c>
       <c r="AO7" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BK7" t="n">
         <v>0.77</v>
       </c>
-      <c r="AP7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>13.23</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>12.77</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>55.23</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>14.54</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>10.84</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.8</v>
-      </c>
       <c r="BL7" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.88</v>
+        <v>4.85</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.24</v>
+        <v>5.5</v>
       </c>
       <c r="BR7" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS7" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BU7" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BV7" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BW7" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX7" t="n">
-        <v>68</v>
+        <v>65.38</v>
       </c>
       <c r="BY7" t="n">
         <v>1.37</v>
@@ -3625,16 +3625,16 @@
         <v>1.38</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.86</v>
+        <v>4.85</v>
       </c>
       <c r="CB7" t="n">
-        <v>5.02</v>
+        <v>4.99</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CE7" t="n">
         <v>1.29</v>
@@ -3649,16 +3649,16 @@
         <v>1.54</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CM7" t="n">
         <v>2.3</v>
@@ -3673,19 +3673,19 @@
         <v>1.66</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS7" t="n">
         <v>2.58</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV7" t="n">
         <v>2</v>
@@ -3712,82 +3712,82 @@
         <v>1.72</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="DG7" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="DH7" t="n">
-        <v>104.44</v>
+        <v>106.12</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.64</v>
+        <v>6.93</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.08</v>
+        <v>53.84</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.44</v>
+        <v>12.15</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.04</v>
+        <v>14.12</v>
       </c>
       <c r="DR7" t="n">
-        <v>5.68</v>
+        <v>5.61</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.04</v>
+        <v>59.38</v>
       </c>
       <c r="DW7" t="n">
         <v>0.04</v>
       </c>
       <c r="DX7" t="n">
-        <v>17.4</v>
+        <v>17.34</v>
       </c>
       <c r="DY7" t="n">
-        <v>11.16</v>
+        <v>11.23</v>
       </c>
       <c r="DZ7" t="n">
-        <v>6.24</v>
+        <v>6.12</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.64</v>
+        <v>20.77</v>
       </c>
       <c r="EB7" t="n">
         <v>1.91</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="8">
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
         <v>0.15</v>
@@ -4289,136 +4289,136 @@
         <v>0.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AI9" t="n">
-        <v>63.25</v>
+        <v>63.08</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AN9" t="n">
-        <v>27.5</v>
+        <v>28</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.92</v>
+        <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>17</v>
+        <v>16.85</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>9.23</v>
       </c>
       <c r="AT9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>44.92</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BN9" t="n">
         <v>1.58</v>
       </c>
-      <c r="AU9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>45.33</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>7.08</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>17.17</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BO9" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.36</v>
+        <v>4.38</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.68</v>
+        <v>5.69</v>
       </c>
       <c r="BR9" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS9" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BU9" t="n">
-        <v>28</v>
+        <v>30.77</v>
       </c>
       <c r="BV9" t="n">
-        <v>12</v>
+        <v>15.38</v>
       </c>
       <c r="BW9" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX9" t="n">
-        <v>60</v>
+        <v>61.54</v>
       </c>
       <c r="BY9" t="n">
         <v>2.88</v>
@@ -4427,43 +4427,43 @@
         <v>3.07</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.7</v>
+        <v>4.54</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.04</v>
+        <v>4.9</v>
       </c>
       <c r="CE9" t="n">
         <v>1.33</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CH9" t="n">
         <v>1.47</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.7</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL9" t="n">
         <v>2.05</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CN9" t="n">
         <v>1.81</v>
@@ -4472,19 +4472,19 @@
         <v>1.23</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CR9" t="n">
         <v>1.38</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CU9" t="n">
         <v>1.5</v>
@@ -4508,55 +4508,55 @@
         <v>1.88</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC9" t="n">
         <v>1.83</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="DE9" t="n">
         <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="DH9" t="n">
-        <v>77.48</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.96</v>
+        <v>5</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.4</v>
+        <v>35.34</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.16</v>
+        <v>13.23</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.8</v>
+        <v>16.74</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.88</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DS9" t="n">
         <v>0.12</v>
@@ -4568,28 +4568,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>50.76</v>
+        <v>50.34</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX9" t="n">
-        <v>13</v>
+        <v>12.97</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.720000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.28</v>
+        <v>4.43</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.92</v>
+        <v>17.62</v>
       </c>
       <c r="EB9" t="n">
         <v>1.38</v>
       </c>
       <c r="EC9" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="10">

--- a/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Turkey_Süper_Lig_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
         <v>0.15</v>
@@ -1472,49 +1472,49 @@
         <v>0.08</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>76.67</v>
+        <v>79.08</v>
       </c>
       <c r="AJ2" t="n">
         <v>-0.08</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AN2" t="n">
-        <v>37.25</v>
+        <v>38.92</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.58</v>
+        <v>11.23</v>
       </c>
       <c r="AR2" t="n">
-        <v>16</v>
+        <v>16.23</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.17</v>
+        <v>7.15</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AV2" t="n">
         <v>0.08</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>45.83</v>
+        <v>47.54</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.08</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.25</v>
+        <v>12.62</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.58</v>
+        <v>9</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="BD2" t="n">
-        <v>18.75</v>
+        <v>19.23</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.279999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="BP2" t="n">
         <v>3.96</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.32</v>
+        <v>4.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BS2" t="n">
-        <v>72</v>
+        <v>73.08</v>
       </c>
       <c r="BT2" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BU2" t="n">
-        <v>24</v>
+        <v>26.92</v>
       </c>
       <c r="BV2" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>60</v>
+        <v>61.54</v>
       </c>
       <c r="BY2" t="n">
         <v>2.86</v>
@@ -1610,31 +1610,31 @@
         <v>2.97</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="CC2" t="n">
-        <v>4.47</v>
+        <v>4.41</v>
       </c>
       <c r="CD2" t="n">
-        <v>5.35</v>
+        <v>5.23</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CH2" t="n">
         <v>1.45</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.76</v>
@@ -1646,43 +1646,43 @@
         <v>2.16</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CN2" t="n">
         <v>1.66</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.11</v>
@@ -1694,49 +1694,49 @@
         <v>1.29</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.23</v>
+        <v>3.27</v>
       </c>
       <c r="DE2" t="n">
         <v>0.12</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="DH2" t="n">
-        <v>86.28</v>
+        <v>87.12</v>
       </c>
       <c r="DI2" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.72</v>
+        <v>4.84</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DM2" t="n">
-        <v>43.84</v>
+        <v>44.42</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.88</v>
+        <v>11.69</v>
       </c>
       <c r="DQ2" t="n">
-        <v>14.84</v>
+        <v>15</v>
       </c>
       <c r="DR2" t="n">
         <v>6.84</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47.88</v>
+        <v>48.66</v>
       </c>
       <c r="DW2" t="n">
         <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.92</v>
+        <v>13.08</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.84</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.48</v>
+        <v>18.73</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="3">
@@ -1794,7 +1794,7 @@
         <v>0.08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="G3" t="n">
         <v>2.23</v>
@@ -1806,7 +1806,7 @@
         <v>0.15</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="K3" t="n">
         <v>4.69</v>
@@ -1869,7 +1869,7 @@
         <v>1.19</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -2106,7 +2106,7 @@
         <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="DG3" t="n">
         <v>1.73</v>
@@ -2118,7 +2118,7 @@
         <v>0.08</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DK3" t="n">
         <v>3.96</v>
@@ -2175,7 +2175,7 @@
         <v>1.02</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
         <v>0.31</v>
@@ -2275,52 +2275,52 @@
         <v>2.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="AI4" t="n">
-        <v>84.75</v>
+        <v>86.08</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.33</v>
+        <v>4.77</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AN4" t="n">
-        <v>36.92</v>
+        <v>39.08</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.33</v>
+        <v>13</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.25</v>
+        <v>10.85</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.25</v>
+        <v>9.08</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>51.42</v>
+        <v>52.77</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.08</v>
       </c>
       <c r="BA4" t="n">
-        <v>14.25</v>
+        <v>15</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.67</v>
+        <v>9.31</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.58</v>
+        <v>5.69</v>
       </c>
       <c r="BD4" t="n">
-        <v>20.5</v>
+        <v>19.77</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="BG4" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.92</v>
+        <v>10.15</v>
       </c>
       <c r="BI4" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.56</v>
+        <v>4.65</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.32</v>
+        <v>5.46</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BT4" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BU4" t="n">
-        <v>40</v>
+        <v>38.46</v>
       </c>
       <c r="BV4" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BW4" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX4" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BY4" t="n">
         <v>1.73</v>
@@ -2416,31 +2416,31 @@
         <v>1.77</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="CE4" t="n">
         <v>1.28</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CG4" t="n">
         <v>3.35</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.64</v>
@@ -2464,7 +2464,7 @@
         <v>1.63</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CR4" t="n">
         <v>1.36</v>
@@ -2476,10 +2476,10 @@
         <v>3.25</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CW4" t="n">
         <v>1.67</v>
@@ -2497,55 +2497,55 @@
         <v>1.9</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="DC4" t="n">
         <v>1.66</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.96</v>
+        <v>3.03</v>
       </c>
       <c r="DH4" t="n">
-        <v>91.95999999999999</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.44</v>
+        <v>5.62</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.88</v>
+        <v>44.7</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.68</v>
+        <v>13.5</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.92</v>
+        <v>12.66</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.92</v>
+        <v>7.88</v>
       </c>
       <c r="DS4" t="n">
         <v>0.12</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>54.28</v>
+        <v>54.84</v>
       </c>
       <c r="DW4" t="n">
         <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.44</v>
+        <v>16.73</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.24</v>
+        <v>10.5</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6.2</v>
+        <v>6.23</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.44</v>
+        <v>18.15</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n">
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -2681,49 +2681,49 @@
         <v>0.08</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AI5" t="n">
-        <v>72.42</v>
+        <v>72</v>
       </c>
       <c r="AJ5" t="n">
         <v>0.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AN5" t="n">
-        <v>30.83</v>
+        <v>30.15</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.83</v>
+        <v>12.85</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.58</v>
+        <v>15.85</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.33</v>
+        <v>8.31</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AV5" t="n">
         <v>0.08</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>47.5</v>
+        <v>48.08</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.08</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.5</v>
+        <v>10.31</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.42</v>
+        <v>7.38</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="BD5" t="n">
-        <v>18.17</v>
+        <v>18.15</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.48</v>
+        <v>9.27</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.4</v>
+        <v>4.31</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.04</v>
+        <v>4.92</v>
       </c>
       <c r="BR5" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>64</v>
+        <v>61.54</v>
       </c>
       <c r="BT5" t="n">
-        <v>40</v>
+        <v>38.46</v>
       </c>
       <c r="BU5" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BV5" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BW5" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX5" t="n">
-        <v>44</v>
+        <v>42.31</v>
       </c>
       <c r="BY5" t="n">
         <v>3.93</v>
@@ -2819,25 +2819,25 @@
         <v>4.36</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.71</v>
+        <v>5.55</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.19</v>
+        <v>6.04</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CH5" t="n">
         <v>1.47</v>
@@ -2855,7 +2855,7 @@
         <v>2.06</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CN5" t="n">
         <v>1.81</v>
@@ -2864,25 +2864,25 @@
         <v>1.25</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CR5" t="n">
         <v>1.4</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CW5" t="n">
         <v>1.79</v>
@@ -2912,43 +2912,43 @@
         <v>0.08</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="DH5" t="n">
-        <v>77</v>
+        <v>76.61</v>
       </c>
       <c r="DI5" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM5" t="n">
-        <v>35.68</v>
+        <v>35.15</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.8</v>
+        <v>11.85</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.16</v>
+        <v>15.31</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.8</v>
+        <v>7.81</v>
       </c>
       <c r="DS5" t="n">
         <v>0.08</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.12</v>
+        <v>50.31</v>
       </c>
       <c r="DW5" t="n">
         <v>0.04</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.92</v>
+        <v>10.81</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.24</v>
+        <v>7.23</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.64</v>
+        <v>18.61</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="6">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
         <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="F8" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="G8" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="H8" t="n">
-        <v>100.38</v>
+        <v>98.64</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="K8" t="n">
-        <v>6.62</v>
+        <v>6.79</v>
       </c>
       <c r="L8" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="M8" t="n">
-        <v>56.54</v>
+        <v>56.14</v>
       </c>
       <c r="N8" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>12.08</v>
+        <v>12.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.15</v>
+        <v>10.29</v>
       </c>
       <c r="R8" t="n">
-        <v>6.08</v>
+        <v>6.07</v>
       </c>
       <c r="S8" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="T8" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="U8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="V8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>64.54000000000001</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.31</v>
+        <v>20.21</v>
       </c>
       <c r="AA8" t="n">
-        <v>13.31</v>
+        <v>13.29</v>
       </c>
       <c r="AB8" t="n">
-        <v>7</v>
+        <v>6.93</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.15</v>
+        <v>19.93</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AF8" t="n">
         <v>0.17</v>
@@ -3971,67 +3971,67 @@
         <v>3.08</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.960000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="BI8" t="n">
         <v>3.08</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.08</v>
+        <v>4.23</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.88</v>
+        <v>4.85</v>
       </c>
       <c r="BR8" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS8" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BT8" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BU8" t="n">
-        <v>44</v>
+        <v>42.31</v>
       </c>
       <c r="BV8" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BW8" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX8" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.59</v>
+        <v>5.54</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.98</v>
+        <v>5.95</v>
       </c>
       <c r="CC8" t="n">
         <v>1.63</v>
@@ -4043,16 +4043,16 @@
         <v>1.22</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="CH8" t="n">
         <v>1.7</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.7</v>
@@ -4064,7 +4064,7 @@
         <v>1.93</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CN8" t="n">
         <v>1.9</v>
@@ -4087,7 +4087,7 @@
         <v>1.75</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CW8" t="n">
         <v>1.76</v>
@@ -4114,79 +4114,79 @@
         <v>2.21</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="DH8" t="n">
-        <v>96.44</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.32</v>
+        <v>5.47</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="DM8" t="n">
-        <v>49.64</v>
+        <v>49.69</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.52</v>
+        <v>2.61</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.28</v>
+        <v>12.31</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.52</v>
+        <v>10.58</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.96</v>
+        <v>6.92</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>61.48</v>
+        <v>61.69</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.84</v>
+        <v>16.92</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.96</v>
+        <v>11.04</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.88</v>
+        <v>5.89</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.68</v>
+        <v>18.61</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="EC8" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="9">
@@ -4599,91 +4599,91 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
         <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F10" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="H10" t="n">
-        <v>72.58</v>
+        <v>71.92</v>
       </c>
       <c r="I10" t="n">
         <v>0.08</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="K10" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="L10" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="M10" t="n">
-        <v>29.92</v>
+        <v>30.23</v>
       </c>
       <c r="N10" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="O10" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="P10" t="n">
-        <v>12.83</v>
+        <v>12.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.33</v>
+        <v>13.08</v>
       </c>
       <c r="R10" t="n">
-        <v>10.33</v>
+        <v>10.77</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T10" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="U10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>42.5</v>
+        <v>41.62</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.83</v>
+        <v>12.69</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.08</v>
+        <v>8</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.75</v>
+        <v>4.69</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.92</v>
+        <v>19</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE10" t="n">
         <v>1.92</v>
@@ -4770,70 +4770,70 @@
         <v>2.15</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.640000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BP10" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>4.88</v>
       </c>
-      <c r="BQ10" t="n">
-        <v>4.72</v>
-      </c>
       <c r="BR10" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BT10" t="n">
-        <v>56</v>
+        <v>53.85</v>
       </c>
       <c r="BU10" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BV10" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BW10" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="CC10" t="n">
         <v>5.4</v>
@@ -4845,10 +4845,10 @@
         <v>1.31</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CH10" t="n">
         <v>1.37</v>
@@ -4866,7 +4866,7 @@
         <v>1.98</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN10" t="n">
         <v>1.68</v>
@@ -4878,16 +4878,16 @@
         <v>1.83</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CR10" t="n">
         <v>1.41</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CU10" t="n">
         <v>1.43</v>
@@ -4902,64 +4902,64 @@
         <v>1.61</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DB10" t="n">
         <v>1.3</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="DE10" t="n">
         <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="DH10" t="n">
-        <v>69.72</v>
+        <v>69.5</v>
       </c>
       <c r="DI10" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="DK10" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DM10" t="n">
-        <v>30.24</v>
+        <v>30.38</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="DO10" t="n">
         <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.16</v>
+        <v>12.81</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.76</v>
+        <v>13.62</v>
       </c>
       <c r="DR10" t="n">
-        <v>10</v>
+        <v>10.23</v>
       </c>
       <c r="DS10" t="n">
         <v>0.08</v>
@@ -4971,28 +4971,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>41.6</v>
+        <v>41.2</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.68</v>
+        <v>10.69</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.24</v>
+        <v>7.23</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.04</v>
+        <v>19.08</v>
       </c>
       <c r="EB10" t="n">
         <v>1.14</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="11">
@@ -5002,61 +5002,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="G11" t="n">
         <v>2.92</v>
       </c>
       <c r="H11" t="n">
-        <v>100.08</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>0.08</v>
       </c>
       <c r="J11" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="K11" t="n">
         <v>5.08</v>
       </c>
       <c r="L11" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="M11" t="n">
-        <v>44.92</v>
+        <v>44.23</v>
       </c>
       <c r="N11" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="O11" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="P11" t="n">
-        <v>17.25</v>
+        <v>17.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.17</v>
+        <v>8.92</v>
       </c>
       <c r="R11" t="n">
-        <v>6.92</v>
+        <v>7</v>
       </c>
       <c r="S11" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="T11" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5068,28 +5068,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>39.83</v>
+        <v>39.23</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.92</v>
+        <v>13.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.67</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.25</v>
+        <v>4.31</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.25</v>
+        <v>19.92</v>
       </c>
       <c r="AD11" t="n">
         <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AF11" t="n">
         <v>0.08</v>
@@ -5173,49 +5173,49 @@
         <v>2.23</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.640000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.76</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.6</v>
+        <v>4.58</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.04</v>
+        <v>5.19</v>
       </c>
       <c r="BR11" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BS11" t="n">
-        <v>60</v>
+        <v>61.54</v>
       </c>
       <c r="BT11" t="n">
-        <v>36</v>
+        <v>38.46</v>
       </c>
       <c r="BU11" t="n">
-        <v>12</v>
+        <v>15.38</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5224,19 +5224,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>36</v>
+        <v>38.46</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="CC11" t="n">
         <v>3.31</v>
@@ -5248,121 +5248,121 @@
         <v>1.4</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI11" t="n">
         <v>1.89</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL11" t="n">
         <v>2.03</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CO11" t="n">
         <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="CR11" t="n">
         <v>1.43</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CU11" t="n">
         <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW11" t="n">
         <v>1.9</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB11" t="n">
         <v>1.34</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="DH11" t="n">
-        <v>95.92</v>
+        <v>95.31</v>
       </c>
       <c r="DI11" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.64</v>
+        <v>4.66</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="DM11" t="n">
-        <v>42.2</v>
+        <v>41.96</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DP11" t="n">
-        <v>16.72</v>
+        <v>16.8</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.279999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.44</v>
+        <v>7.46</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>38.8</v>
+        <v>38.54</v>
       </c>
       <c r="DW11" t="n">
         <v>0.16</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.68</v>
+        <v>13.66</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.24</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.44</v>
+        <v>4.46</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.2</v>
+        <v>19.58</v>
       </c>
       <c r="EB11" t="n">
         <v>1.48</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="12">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
         <v>13</v>
@@ -5417,49 +5417,49 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="G12" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="H12" t="n">
-        <v>90.17</v>
+        <v>91.62</v>
       </c>
       <c r="I12" t="n">
         <v>0.08</v>
       </c>
       <c r="J12" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="K12" t="n">
-        <v>5.42</v>
+        <v>5.15</v>
       </c>
       <c r="L12" t="n">
         <v>0.92</v>
       </c>
       <c r="M12" t="n">
-        <v>43.58</v>
+        <v>42.85</v>
       </c>
       <c r="N12" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="P12" t="n">
-        <v>15.42</v>
+        <v>15.31</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>14.85</v>
       </c>
       <c r="R12" t="n">
-        <v>6.67</v>
+        <v>6.54</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="T12" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="U12" t="n">
         <v>0.08</v>
@@ -5471,28 +5471,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>49.75</v>
+        <v>49.38</v>
       </c>
       <c r="Y12" t="n">
         <v>0.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.67</v>
+        <v>12.38</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.33</v>
+        <v>9.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="AC12" t="n">
-        <v>18.92</v>
+        <v>19.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5576,70 +5576,70 @@
         <v>2.38</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="BH12" t="n">
-        <v>9</v>
+        <v>8.81</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="BO12" t="n">
         <v>1.04</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.76</v>
+        <v>3.69</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.2</v>
+        <v>5.08</v>
       </c>
       <c r="BR12" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BS12" t="n">
-        <v>72</v>
+        <v>69.23</v>
       </c>
       <c r="BT12" t="n">
-        <v>44</v>
+        <v>42.31</v>
       </c>
       <c r="BU12" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BV12" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>56</v>
+        <v>53.85</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.11</v>
+        <v>3.03</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CC12" t="n">
         <v>4.54</v>
@@ -5651,16 +5651,16 @@
         <v>1.36</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CG12" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CH12" t="n">
         <v>1.44</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.74</v>
@@ -5672,34 +5672,34 @@
         <v>2.02</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CP12" t="n">
         <v>1.86</v>
       </c>
-      <c r="CO12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="CP12" t="n">
-        <v>1.85</v>
-      </c>
       <c r="CQ12" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CR12" t="n">
         <v>1.41</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CU12" t="n">
         <v>1.45</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CW12" t="n">
         <v>1.79</v>
@@ -5729,43 +5729,43 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="DH12" t="n">
-        <v>86.2</v>
+        <v>87.08</v>
       </c>
       <c r="DI12" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.52</v>
+        <v>38.35</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.76</v>
+        <v>15.69</v>
       </c>
       <c r="DQ12" t="n">
         <v>12.96</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.68</v>
+        <v>7.58</v>
       </c>
       <c r="DS12" t="n">
         <v>0.08</v>
@@ -5783,22 +5783,22 @@
         <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.16</v>
+        <v>10.12</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.44</v>
+        <v>7.42</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.36</v>
+        <v>19.81</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="13">
@@ -5808,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5901,49 +5901,49 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AI13" t="n">
-        <v>77.84999999999999</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="AL13" t="n">
-        <v>4</v>
+        <v>4.29</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AN13" t="n">
-        <v>35.08</v>
+        <v>34.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.69</v>
+        <v>13.57</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.31</v>
+        <v>13.29</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.69</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5955,82 +5955,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>43.54</v>
+        <v>42.79</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.69</v>
+        <v>10.71</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.69</v>
+        <v>6.86</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="BD13" t="n">
-        <v>16.62</v>
+        <v>16.29</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.68</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM13" t="n">
         <v>0.96</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.56</v>
+        <v>4.73</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="BR13" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BT13" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>36</v>
+        <v>34.62</v>
       </c>
       <c r="BV13" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BW13" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX13" t="n">
-        <v>52</v>
+        <v>53.85</v>
       </c>
       <c r="BY13" t="n">
         <v>3.22</v>
@@ -6039,31 +6039,31 @@
         <v>3.43</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.11</v>
+        <v>4.08</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.18</v>
+        <v>5.08</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.8</v>
+        <v>5.69</v>
       </c>
       <c r="CE13" t="n">
         <v>1.33</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.7</v>
@@ -6072,40 +6072,40 @@
         <v>1.5</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM13" t="n">
         <v>2.47</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO13" t="n">
         <v>1.23</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="CR13" t="n">
         <v>1.39</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CX13" t="n">
         <v>1.53</v>
@@ -6114,7 +6114,7 @@
         <v>1.87</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DA13" t="n">
         <v>1.93</v>
@@ -6123,52 +6123,52 @@
         <v>1.24</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="DG13" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DH13" t="n">
-        <v>79.88</v>
+        <v>80</v>
       </c>
       <c r="DI13" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.8</v>
+        <v>4.93</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM13" t="n">
-        <v>39.92</v>
+        <v>39.42</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.36</v>
+        <v>12.35</v>
       </c>
       <c r="DQ13" t="n">
         <v>13.08</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.08</v>
+        <v>9.16</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6180,28 +6180,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>46.36</v>
+        <v>45.85</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.6</v>
+        <v>11.57</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.8</v>
+        <v>7.85</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.8</v>
+        <v>18.54</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="14">
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
@@ -6223,82 +6223,82 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="G14" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="H14" t="n">
-        <v>97.08</v>
+        <v>95.64</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>4.31</v>
+        <v>4.57</v>
       </c>
       <c r="L14" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="M14" t="n">
-        <v>39.77</v>
+        <v>38.43</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="O14" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="P14" t="n">
-        <v>15.62</v>
+        <v>15.93</v>
       </c>
       <c r="Q14" t="n">
-        <v>14.69</v>
+        <v>13.93</v>
       </c>
       <c r="R14" t="n">
-        <v>8</v>
+        <v>8.07</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="V14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>50.08</v>
+        <v>49.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.92</v>
+        <v>11.79</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.15</v>
+        <v>8.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.77</v>
+        <v>3.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>23.31</v>
+        <v>22.57</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AF14" t="n">
         <v>0.08</v>
@@ -6382,70 +6382,70 @@
         <v>2.58</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="BR14" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BT14" t="n">
-        <v>28</v>
+        <v>30.77</v>
       </c>
       <c r="BU14" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BV14" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>36</v>
+        <v>38.46</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="CC14" t="n">
         <v>4.38</v>
@@ -6454,31 +6454,31 @@
         <v>4.54</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CH14" t="n">
         <v>1.39</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CK14" t="n">
         <v>1.65</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CN14" t="n">
         <v>1.71</v>
@@ -6487,124 +6487,124 @@
         <v>1.31</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.43</v>
+        <v>3.46</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CU14" t="n">
         <v>1.4</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB14" t="n">
         <v>1.35</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="DE14" t="n">
         <v>0.04</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="DH14" t="n">
-        <v>91.40000000000001</v>
+        <v>90.84</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.24</v>
+        <v>4.39</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="DM14" t="n">
-        <v>38.96</v>
+        <v>38.27</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.04</v>
+        <v>15.23</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.52</v>
+        <v>14.11</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.279999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.88</v>
+        <v>48.61</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.52</v>
+        <v>10.5</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.28</v>
+        <v>7.27</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.52</v>
+        <v>20.23</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="15">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6707,136 +6707,136 @@
         <v>0.08</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AI15" t="n">
-        <v>90.25</v>
+        <v>91.31</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.75</v>
+        <v>4.92</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AN15" t="n">
-        <v>40.33</v>
+        <v>39.62</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AP15" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12.17</v>
+        <v>11.54</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.33</v>
+        <v>14.77</v>
       </c>
       <c r